--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1046"/>
+  <dimension ref="A1:L1147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46031,8 +46031,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E991" t="inlineStr"/>
-      <c r="F991" t="inlineStr"/>
       <c r="G991" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -46079,8 +46077,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E992" t="inlineStr"/>
-      <c r="F992" t="inlineStr"/>
       <c r="G992" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -46127,8 +46123,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E993" t="inlineStr"/>
-      <c r="F993" t="inlineStr"/>
       <c r="G993" t="inlineStr">
         <is>
           <t>3-3</t>
@@ -46175,8 +46169,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E994" t="inlineStr"/>
-      <c r="F994" t="inlineStr"/>
       <c r="G994" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -46223,8 +46215,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E995" t="inlineStr"/>
-      <c r="F995" t="inlineStr"/>
       <c r="G995" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -46271,8 +46261,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E996" t="inlineStr"/>
-      <c r="F996" t="inlineStr"/>
       <c r="G996" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -46319,8 +46307,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E997" t="inlineStr"/>
-      <c r="F997" t="inlineStr"/>
       <c r="G997" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -46367,8 +46353,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E998" t="inlineStr"/>
-      <c r="F998" t="inlineStr"/>
       <c r="G998" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -46415,8 +46399,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E999" t="inlineStr"/>
-      <c r="F999" t="inlineStr"/>
       <c r="G999" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -46463,8 +46445,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1000" t="inlineStr"/>
-      <c r="F1000" t="inlineStr"/>
       <c r="G1000" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -46511,8 +46491,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1001" t="inlineStr"/>
-      <c r="F1001" t="inlineStr"/>
       <c r="G1001" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -46559,8 +46537,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1002" t="inlineStr"/>
-      <c r="F1002" t="inlineStr"/>
       <c r="G1002" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -46607,8 +46583,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1003" t="inlineStr"/>
-      <c r="F1003" t="inlineStr"/>
       <c r="G1003" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -46655,8 +46629,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1004" t="inlineStr"/>
-      <c r="F1004" t="inlineStr"/>
       <c r="G1004" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -46703,8 +46675,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1005" t="inlineStr"/>
-      <c r="F1005" t="inlineStr"/>
       <c r="G1005" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -46751,8 +46721,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1006" t="inlineStr"/>
-      <c r="F1006" t="inlineStr"/>
       <c r="G1006" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -46799,8 +46767,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1007" t="inlineStr"/>
-      <c r="F1007" t="inlineStr"/>
       <c r="G1007" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -46847,8 +46813,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1008" t="inlineStr"/>
-      <c r="F1008" t="inlineStr"/>
       <c r="G1008" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -46895,8 +46859,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1009" t="inlineStr"/>
-      <c r="F1009" t="inlineStr"/>
       <c r="G1009" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -46943,8 +46905,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1010" t="inlineStr"/>
-      <c r="F1010" t="inlineStr"/>
       <c r="G1010" t="inlineStr">
         <is>
           <t>0-4</t>
@@ -46991,8 +46951,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1011" t="inlineStr"/>
-      <c r="F1011" t="inlineStr"/>
       <c r="G1011" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -47039,8 +46997,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1012" t="inlineStr"/>
-      <c r="F1012" t="inlineStr"/>
       <c r="G1012" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -47087,8 +47043,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1013" t="inlineStr"/>
-      <c r="F1013" t="inlineStr"/>
       <c r="G1013" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -47135,8 +47089,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1014" t="inlineStr"/>
-      <c r="F1014" t="inlineStr"/>
       <c r="G1014" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -47183,8 +47135,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1015" t="inlineStr"/>
-      <c r="F1015" t="inlineStr"/>
       <c r="G1015" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -47231,8 +47181,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1016" t="inlineStr"/>
-      <c r="F1016" t="inlineStr"/>
       <c r="G1016" t="inlineStr">
         <is>
           <t>1-4</t>
@@ -47279,8 +47227,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1017" t="inlineStr"/>
-      <c r="F1017" t="inlineStr"/>
       <c r="G1017" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -47327,8 +47273,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1018" t="inlineStr"/>
-      <c r="F1018" t="inlineStr"/>
       <c r="G1018" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -47375,8 +47319,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1019" t="inlineStr"/>
-      <c r="F1019" t="inlineStr"/>
       <c r="G1019" t="inlineStr">
         <is>
           <t>2-4</t>
@@ -47423,8 +47365,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1020" t="inlineStr"/>
-      <c r="F1020" t="inlineStr"/>
       <c r="G1020" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -47471,8 +47411,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1021" t="inlineStr"/>
-      <c r="F1021" t="inlineStr"/>
       <c r="G1021" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -47519,8 +47457,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1022" t="inlineStr"/>
-      <c r="F1022" t="inlineStr"/>
       <c r="G1022" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -47567,8 +47503,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1023" t="inlineStr"/>
-      <c r="F1023" t="inlineStr"/>
       <c r="G1023" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -47615,8 +47549,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1024" t="inlineStr"/>
-      <c r="F1024" t="inlineStr"/>
       <c r="G1024" t="inlineStr">
         <is>
           <t>6-0</t>
@@ -47663,8 +47595,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1025" t="inlineStr"/>
-      <c r="F1025" t="inlineStr"/>
       <c r="G1025" t="inlineStr">
         <is>
           <t>1-4</t>
@@ -47711,8 +47641,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1026" t="inlineStr"/>
-      <c r="F1026" t="inlineStr"/>
       <c r="G1026" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -47759,8 +47687,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1027" t="inlineStr"/>
-      <c r="F1027" t="inlineStr"/>
       <c r="G1027" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -47807,8 +47733,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1028" t="inlineStr"/>
-      <c r="F1028" t="inlineStr"/>
       <c r="G1028" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -47855,8 +47779,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1029" t="inlineStr"/>
-      <c r="F1029" t="inlineStr"/>
       <c r="G1029" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -47903,8 +47825,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1030" t="inlineStr"/>
-      <c r="F1030" t="inlineStr"/>
       <c r="G1030" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -47951,8 +47871,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1031" t="inlineStr"/>
-      <c r="F1031" t="inlineStr"/>
       <c r="G1031" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -47999,8 +47917,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1032" t="inlineStr"/>
-      <c r="F1032" t="inlineStr"/>
       <c r="G1032" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -48047,8 +47963,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1033" t="inlineStr"/>
-      <c r="F1033" t="inlineStr"/>
       <c r="G1033" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -48095,8 +48009,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1034" t="inlineStr"/>
-      <c r="F1034" t="inlineStr"/>
       <c r="G1034" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -48143,8 +48055,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1035" t="inlineStr"/>
-      <c r="F1035" t="inlineStr"/>
       <c r="G1035" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -48191,8 +48101,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1036" t="inlineStr"/>
-      <c r="F1036" t="inlineStr"/>
       <c r="G1036" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -48239,8 +48147,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1037" t="inlineStr"/>
-      <c r="F1037" t="inlineStr"/>
       <c r="G1037" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -48287,8 +48193,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1038" t="inlineStr"/>
-      <c r="F1038" t="inlineStr"/>
       <c r="G1038" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -48335,8 +48239,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1039" t="inlineStr"/>
-      <c r="F1039" t="inlineStr"/>
       <c r="G1039" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -48383,8 +48285,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1040" t="inlineStr"/>
-      <c r="F1040" t="inlineStr"/>
       <c r="G1040" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -48431,8 +48331,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1041" t="inlineStr"/>
-      <c r="F1041" t="inlineStr"/>
       <c r="G1041" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -48479,8 +48377,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1042" t="inlineStr"/>
-      <c r="F1042" t="inlineStr"/>
       <c r="G1042" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -48527,8 +48423,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1043" t="inlineStr"/>
-      <c r="F1043" t="inlineStr"/>
       <c r="G1043" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -48575,8 +48469,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1044" t="inlineStr"/>
-      <c r="F1044" t="inlineStr"/>
       <c r="G1044" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -48623,8 +48515,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1045" t="inlineStr"/>
-      <c r="F1045" t="inlineStr"/>
       <c r="G1045" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -48671,8 +48561,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1046" t="inlineStr"/>
-      <c r="F1046" t="inlineStr"/>
       <c r="G1046" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -48693,6 +48581,4854 @@
         <v>0</v>
       </c>
       <c r="L1046" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>Fakel Voronezh vs FC Baltika Kaliningrad</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>FC Baltika Kaliningrad</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr"/>
+      <c r="F1047" t="inlineStr"/>
+      <c r="G1047" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1047" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1047" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1047" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1047" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>Derby County vs Birmingham City</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>Birmingham City</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr"/>
+      <c r="F1048" t="inlineStr"/>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1048" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1048" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>West Bromwich Albion vs Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>West Bromwich Albion</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr"/>
+      <c r="F1049" t="inlineStr"/>
+      <c r="G1049" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1049" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1049" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>FC Andorra vs Real Sociedad II</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>FC Andorra</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr"/>
+      <c r="F1050" t="inlineStr"/>
+      <c r="G1050" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H1050" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1050" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1050" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1050" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1050" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>Genoa vs Frosinone</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr"/>
+      <c r="F1051" t="inlineStr"/>
+      <c r="G1051" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1051" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1051" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>Zenit St Petersburg vs Lokomotiv Moscow</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>Zenit St Petersburg</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr"/>
+      <c r="F1052" t="inlineStr"/>
+      <c r="G1052" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1052" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1052" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1052" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1052" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1052" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>Borussia Dortmund vs SC Paderborn 07</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr"/>
+      <c r="F1053" t="inlineStr"/>
+      <c r="G1053" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1053" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1053" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>TSG Hoffenheim vs VfB Stuttgart</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>TSG Hoffenheim</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr"/>
+      <c r="F1054" t="inlineStr"/>
+      <c r="G1054" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1054" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1054" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>SC Freiburg vs Borussia Mönchengladbach</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>SC Freiburg</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr"/>
+      <c r="F1055" t="inlineStr"/>
+      <c r="G1055" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="H1055" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1055" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>FC Augsburg vs Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr"/>
+      <c r="F1056" t="inlineStr"/>
+      <c r="G1056" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1056" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1056" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1056" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1056" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1056" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>Mainz vs Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr"/>
+      <c r="F1057" t="inlineStr"/>
+      <c r="G1057" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H1057" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1057" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>Aston Villa vs Nottingham Forest</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr"/>
+      <c r="F1058" t="inlineStr"/>
+      <c r="G1058" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1058" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1058" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>Chelsea vs Hull City</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr"/>
+      <c r="F1059" t="inlineStr"/>
+      <c r="G1059" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1059" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1059" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>Crystal Palace vs Ipswich Town</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr"/>
+      <c r="F1060" t="inlineStr"/>
+      <c r="G1060" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H1060" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1060" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>Liverpool vs Fulham</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr"/>
+      <c r="F1061" t="inlineStr"/>
+      <c r="G1061" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1061" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1061" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>Waasland-Beveren vs Sint-Truidense</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>Sint-Truidense</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr"/>
+      <c r="F1062" t="inlineStr"/>
+      <c r="G1062" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1062" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1062" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>Middlesbrough vs Norwich City</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr"/>
+      <c r="F1063" t="inlineStr"/>
+      <c r="G1063" t="inlineStr">
+        <is>
+          <t>4-3</t>
+        </is>
+      </c>
+      <c r="H1063" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1063" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>Preston North End vs Lincoln City</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>Preston North End</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr"/>
+      <c r="F1064" t="inlineStr"/>
+      <c r="G1064" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1064" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1064" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>Southampton vs Bristol City</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr"/>
+      <c r="F1065" t="inlineStr"/>
+      <c r="G1065" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H1065" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1065" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>Swansea City vs Burnley</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>Swansea City</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr"/>
+      <c r="F1066" t="inlineStr"/>
+      <c r="G1066" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1066" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1066" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>Watford vs Stoke City</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>Watford</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr"/>
+      <c r="F1067" t="inlineStr"/>
+      <c r="G1067" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1067" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1067" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>Eyupspor vs Caykur Rizespor</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>Caykur Rizespor</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr"/>
+      <c r="F1068" t="inlineStr"/>
+      <c r="G1068" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1068" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1068" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>Samsunspor vs Çorum FK</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>Samsunspor</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr"/>
+      <c r="F1069" t="inlineStr"/>
+      <c r="G1069" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="H1069" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1069" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1069" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>Ross County vs Hibernian</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr"/>
+      <c r="F1070" t="inlineStr"/>
+      <c r="G1070" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H1070" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1070" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1070" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1070" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1070" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>Osasuna vs Espanyol</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr"/>
+      <c r="F1071" t="inlineStr"/>
+      <c r="G1071" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1071" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1071" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>FC Twente vs ADO Den Haag</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>FC Twente</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr"/>
+      <c r="F1072" t="inlineStr"/>
+      <c r="G1072" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1072" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1072" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>Strasbourg vs AS Monaco</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>AS Monaco</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr"/>
+      <c r="F1073" t="inlineStr"/>
+      <c r="G1073" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1073" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1073" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>Los Chankas vs FC Cajamarca</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>Los Chankas</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr"/>
+      <c r="F1074" t="inlineStr"/>
+      <c r="G1074" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1074" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1074" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1074" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1074" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1074" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>Al Taawoun vs Al Hilal</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>Al Hilal</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr"/>
+      <c r="F1075" t="inlineStr"/>
+      <c r="G1075" t="inlineStr">
+        <is>
+          <t>0-6</t>
+        </is>
+      </c>
+      <c r="H1075" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1075" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>Lazio vs AC Milan</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1076" t="inlineStr"/>
+      <c r="F1076" t="inlineStr"/>
+      <c r="G1076" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1076" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1076" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>Olympiacos vs OFI Crete</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>Olympiacos</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr"/>
+      <c r="F1077" t="inlineStr"/>
+      <c r="G1077" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1077" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1077" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>Racing (Montevideo) vs Boston River</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>Racing (Montevideo)</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr"/>
+      <c r="F1078" t="inlineStr"/>
+      <c r="G1078" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1078" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1078" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur vs Everton</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr"/>
+      <c r="F1079" t="inlineStr"/>
+      <c r="G1079" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1079" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1079" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1079" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1079" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1079" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>FC Cologne vs Werder Bremen</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>FC Cologne</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr"/>
+      <c r="F1080" t="inlineStr"/>
+      <c r="G1080" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1080" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1080" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1080" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1080" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1080" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>Athletic Club vs Elche</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr"/>
+      <c r="F1081" t="inlineStr"/>
+      <c r="G1081" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1081" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1081" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1081" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1081" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>Girona vs Castellón</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr"/>
+      <c r="F1082" t="inlineStr"/>
+      <c r="G1082" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1082" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1082" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1082" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1082" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1082" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>Granada vs Albacete</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr"/>
+      <c r="F1083" t="inlineStr"/>
+      <c r="G1083" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1083" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1083" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1083" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1083" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1083" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles vs FC Groningen</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr"/>
+      <c r="F1084" t="inlineStr"/>
+      <c r="G1084" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1084" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1084" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1084" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1084" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1084" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>Kilmarnock vs Aberdeen</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>Aberdeen</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr"/>
+      <c r="F1085" t="inlineStr"/>
+      <c r="G1085" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1085" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1085" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1085" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>Casa Pia vs FC Porto</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>FC Porto</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr"/>
+      <c r="F1086" t="inlineStr"/>
+      <c r="G1086" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="H1086" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1086" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1086" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1086" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1086" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>Alanyaspor vs Goztepe</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>Alanyaspor</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr"/>
+      <c r="F1087" t="inlineStr"/>
+      <c r="G1087" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1087" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1087" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1087" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1087" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1087" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>Konyaspor vs Trabzonspor</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>Trabzonspor</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr"/>
+      <c r="F1088" t="inlineStr"/>
+      <c r="G1088" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1088" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1088" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1088" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1088" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1088" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>Estudiantes de La Plata vs Platense</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>Estudiantes de La Plata</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr"/>
+      <c r="F1089" t="inlineStr"/>
+      <c r="G1089" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1089" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1089" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1089" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1089" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia vs Aldosivi</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr"/>
+      <c r="F1090" t="inlineStr"/>
+      <c r="G1090" t="inlineStr">
+        <is>
+          <t>4-3</t>
+        </is>
+      </c>
+      <c r="H1090" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1090" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1090" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1090" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1090" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>CSKA Moscow vs Rubin Kazan</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr"/>
+      <c r="F1091" t="inlineStr"/>
+      <c r="G1091" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1091" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1091" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1091" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1091" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1091" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>Fortuna Sittard vs Ajax Amsterdam</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>Ajax Amsterdam</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr"/>
+      <c r="F1092" t="inlineStr"/>
+      <c r="G1092" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="H1092" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1092" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1092" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1092" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1092" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>Cobresal vs Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr"/>
+      <c r="F1093" t="inlineStr"/>
+      <c r="G1093" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1093" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1093" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>Comerciantes Unidos vs Sport Huancayo</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>Comerciantes Unidos</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr"/>
+      <c r="F1094" t="inlineStr"/>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1094" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1094" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1094" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1094" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1094" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>Al Khaleej vs Al Nassr</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr"/>
+      <c r="F1095" t="inlineStr"/>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1095" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1095" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1095" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1095" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>Al Shabab vs Al Fayha</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>Al Shabab</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr"/>
+      <c r="F1096" t="inlineStr"/>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1096" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1096" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1096" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1096" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1096" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>Atalanta vs Cagliari</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>Atalanta</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr"/>
+      <c r="F1097" t="inlineStr"/>
+      <c r="G1097" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1097" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1097" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1097" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>Sunderland vs Arsenal</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr"/>
+      <c r="F1098" t="inlineStr"/>
+      <c r="G1098" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1098" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1098" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1098" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1098" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1098" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>Real Madrid vs Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr"/>
+      <c r="F1099" t="inlineStr"/>
+      <c r="G1099" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H1099" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1099" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1099" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1099" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1099" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>Atlético-MG vs Fluminense</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>Atlético-MG</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr"/>
+      <c r="F1100" t="inlineStr"/>
+      <c r="G1100" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1100" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1100" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1100" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1100" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1100" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>SC Cambuur vs NEC Nijmegen</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>NEC Nijmegen</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr"/>
+      <c r="F1101" t="inlineStr"/>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1101" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1101" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1101" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1101" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1101" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>Manta F.C. vs Aucas</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>Aucas</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr"/>
+      <c r="F1102" t="inlineStr"/>
+      <c r="G1102" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1102" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1102" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1102" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1102" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1102" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>Guaraní vs Cerro Porteño</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>Cerro Porteño</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr"/>
+      <c r="F1103" t="inlineStr"/>
+      <c r="G1103" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1103" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1103" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1103" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>Académico de Viseu vs Vitória de Guimaraes</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>Vitória de Guimaraes</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr"/>
+      <c r="F1104" t="inlineStr"/>
+      <c r="G1104" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1104" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1104" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1104" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>Montevideo Wanderers vs Nacional</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr"/>
+      <c r="F1105" t="inlineStr"/>
+      <c r="G1105" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1105" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1105" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>Chapecoense vs Internacional</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>Internacional</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr"/>
+      <c r="F1106" t="inlineStr"/>
+      <c r="G1106" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1106" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1106" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1106" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1106" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1106" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>Atlético Tucumán vs River Plate</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr"/>
+      <c r="F1107" t="inlineStr"/>
+      <c r="G1107" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1107" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1107" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1107" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>Internacional de Bogotá vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>Internacional de Bogotá</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr"/>
+      <c r="F1108" t="inlineStr"/>
+      <c r="G1108" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1108" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1108" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1108" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>Palmeiras vs São Paulo</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr"/>
+      <c r="F1109" t="inlineStr"/>
+      <c r="G1109" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1109" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1109" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1109" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>Deportivo Recoleta vs Sportivo Trinidense</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>Sportivo Trinidense</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr"/>
+      <c r="F1110" t="inlineStr"/>
+      <c r="G1110" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H1110" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1110" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1110" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>Forward Madison FC vs Sarasota Paradise</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>Forward Madison FC</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr"/>
+      <c r="F1111" t="inlineStr"/>
+      <c r="G1111" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1111" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1111" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1111" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>Talleres (Córdoba) vs Unión (Santa Fe)</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>Talleres (Córdoba)</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr"/>
+      <c r="F1112" t="inlineStr"/>
+      <c r="G1112" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1112" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1112" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1112" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1112" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1112" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>Cerro Largo vs Central Español Fútbol Club</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>Cerro Largo</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr"/>
+      <c r="F1113" t="inlineStr"/>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1113" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1113" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1113" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1113" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1113" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>Venados FC vs Tepatitlán FC</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>Venados FC</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr"/>
+      <c r="F1114" t="inlineStr"/>
+      <c r="G1114" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="H1114" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1114" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1114" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>Brooklyn FC vs Miami FC</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>Brooklyn FC</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr"/>
+      <c r="F1115" t="inlineStr"/>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1115" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1115" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1115" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1115" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1115" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>Hartford Athletic vs Tampa Bay Rowdies</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rowdies</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr"/>
+      <c r="F1116" t="inlineStr"/>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1116" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1116" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1116" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1116" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1116" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>Louisville City FC vs El Paso Locomotive FC</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>Louisville City FC</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr"/>
+      <c r="F1117" t="inlineStr"/>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1117" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1117" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1117" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1117" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1117" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>Pittsburgh Riverhounds vs Loudoun United FC</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>Pittsburgh Riverhounds</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr"/>
+      <c r="F1118" t="inlineStr"/>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1118" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1118" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1118" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1118" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1118" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>Sporting JAX vs Rhode Island FC</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>Rhode Island FC</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr"/>
+      <c r="F1119" t="inlineStr"/>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H1119" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1119" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>Birmingham Legion FC vs Charleston Battery</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>Charleston Battery</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr"/>
+      <c r="F1120" t="inlineStr"/>
+      <c r="G1120" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1120" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1120" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1120" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1120" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1120" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>Greenville Triumph vs Fort Wayne</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>Greenville Triumph</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr"/>
+      <c r="F1121" t="inlineStr"/>
+      <c r="G1121" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H1121" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1121" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1121" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1121" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1121" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>Toluca vs Atlas</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>Toluca</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr"/>
+      <c r="F1122" t="inlineStr"/>
+      <c r="G1122" t="inlineStr">
+        <is>
+          <t>5-2</t>
+        </is>
+      </c>
+      <c r="H1122" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1122" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1122" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1122" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1122" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>Boyacá Chicó FC vs Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr"/>
+      <c r="F1123" t="inlineStr"/>
+      <c r="G1123" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1123" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1123" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>Richmond Kickers vs Chattanooga Red Wolves</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>Chattanooga Red Wolves</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr"/>
+      <c r="F1124" t="inlineStr"/>
+      <c r="G1124" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1124" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1124" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1124" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>Botafogo vs Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr"/>
+      <c r="F1125" t="inlineStr"/>
+      <c r="G1125" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1125" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1125" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1125" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>Inter Miami CF vs Nashville SC</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>Inter Miami CF</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr"/>
+      <c r="F1126" t="inlineStr"/>
+      <c r="G1126" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1126" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1126" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1126" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>FC Cincinnati vs Charlotte FC</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr"/>
+      <c r="F1127" t="inlineStr"/>
+      <c r="G1127" t="inlineStr">
+        <is>
+          <t>3-3</t>
+        </is>
+      </c>
+      <c r="H1127" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1127" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>Orlando City SC vs Toronto FC</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>Orlando City SC</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr"/>
+      <c r="F1128" t="inlineStr"/>
+      <c r="G1128" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1128" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1128" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>D.C. United vs Atlanta United FC</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>D.C. United</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr"/>
+      <c r="F1129" t="inlineStr"/>
+      <c r="G1129" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1129" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1129" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>Charlotte Independence vs Westchester SC</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>Charlotte Independence</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr"/>
+      <c r="F1130" t="inlineStr"/>
+      <c r="G1130" t="inlineStr">
+        <is>
+          <t>5-4</t>
+        </is>
+      </c>
+      <c r="H1130" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1130" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>Santos vs Cruzeiro</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr"/>
+      <c r="F1131" t="inlineStr"/>
+      <c r="G1131" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1131" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1131" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>Sporting Kansas City vs LAFC</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>LAFC</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr"/>
+      <c r="F1132" t="inlineStr"/>
+      <c r="G1132" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1132" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1132" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>FC Dallas vs Portland Timbers</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr"/>
+      <c r="F1133" t="inlineStr"/>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1133" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1133" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>St. Louis CITY SC vs Minnesota United FC</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>St. Louis CITY SC</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr"/>
+      <c r="F1134" t="inlineStr"/>
+      <c r="G1134" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="H1134" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1134" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>Corpus Christi FC vs Union Omaha</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>Union Omaha</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr"/>
+      <c r="F1135" t="inlineStr"/>
+      <c r="G1135" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1135" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1135" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>Dorados de Sinaloa vs Tapatío</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>Dorados de Sinaloa</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr"/>
+      <c r="F1136" t="inlineStr"/>
+      <c r="G1136" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1136" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1136" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>Alianza Lima vs Universitario</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>Alianza Lima</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr"/>
+      <c r="F1137" t="inlineStr"/>
+      <c r="G1137" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1137" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1137" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>Monterrey vs Tigres UANL</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr"/>
+      <c r="F1138" t="inlineStr"/>
+      <c r="G1138" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1138" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1138" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1138" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1138" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1138" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>Alianza FC vs Atlético Junior</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>Atlético Junior</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr"/>
+      <c r="F1139" t="inlineStr"/>
+      <c r="G1139" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1139" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1139" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1139" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1139" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1139" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>Real Salt Lake vs New York City FC</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr"/>
+      <c r="F1140" t="inlineStr"/>
+      <c r="G1140" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1140" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1140" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1140" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1140" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1140" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>Colorado Rapids vs CF Montréal</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr"/>
+      <c r="F1141" t="inlineStr"/>
+      <c r="G1141" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1141" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1141" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>Oakland Roots vs Lexington</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>Oakland Roots</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr"/>
+      <c r="F1142" t="inlineStr"/>
+      <c r="G1142" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="H1142" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1142" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1142" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1142" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1142" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>Orange County SC vs Las Vegas Lights FC</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>Orange County SC</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr"/>
+      <c r="F1143" t="inlineStr"/>
+      <c r="G1143" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1143" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1143" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>Phoenix Rising FC vs FC Tulsa</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>Phoenix Rising FC</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr"/>
+      <c r="F1144" t="inlineStr"/>
+      <c r="G1144" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1144" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1144" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1144" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1144" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1144" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>Sacramento Republic FC vs Detroit City FC</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>Sacramento Republic FC</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr"/>
+      <c r="F1145" t="inlineStr"/>
+      <c r="G1145" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1145" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1145" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1145" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1145" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1145" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs Seattle Sounders FC</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr"/>
+      <c r="F1146" t="inlineStr"/>
+      <c r="G1146" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1146" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1146" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1146" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1146" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1146" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>Cruz Azul vs América</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>Cruz Azul</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr"/>
+      <c r="F1147" t="inlineStr"/>
+      <c r="G1147" t="inlineStr">
+        <is>
+          <t>4-3</t>
+        </is>
+      </c>
+      <c r="H1147" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1147" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1147" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1147" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1147" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -48709,7 +53445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49305,6 +54041,25 @@
       </c>
       <c r="E32" t="n">
         <v>56</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>101</v>
+      </c>
+      <c r="C33" t="n">
+        <v>65</v>
+      </c>
+      <c r="D33" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="E33" t="n">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -49318,7 +54073,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E140"/>
+  <dimension ref="A1:E150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52267,6 +57022,216 @@
         <v>0</v>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>8</v>
+      </c>
+      <c r="D141" t="n">
+        <v>4</v>
+      </c>
+      <c r="E141" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>siguen_empatados_70</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>3</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>9</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>11</v>
+      </c>
+      <c r="D144" t="n">
+        <v>3</v>
+      </c>
+      <c r="E144" t="n">
+        <v>27.3</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>9</v>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>5</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>gol_de_cierre</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>3</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0</v>
+      </c>
+      <c r="E147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>7</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0</v>
+      </c>
+      <c r="E148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>16</v>
+      </c>
+      <c r="D149" t="n">
+        <v>1</v>
+      </c>
+      <c r="E149" t="n">
+        <v>6.2</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>siguen_empatados_55</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>1</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0</v>
+      </c>
+      <c r="E150" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1147"/>
+  <dimension ref="A1:L1236"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48607,8 +48607,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1047" t="inlineStr"/>
-      <c r="F1047" t="inlineStr"/>
       <c r="G1047" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -48655,8 +48653,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1048" t="inlineStr"/>
-      <c r="F1048" t="inlineStr"/>
       <c r="G1048" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -48703,8 +48699,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1049" t="inlineStr"/>
-      <c r="F1049" t="inlineStr"/>
       <c r="G1049" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -48751,8 +48745,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1050" t="inlineStr"/>
-      <c r="F1050" t="inlineStr"/>
       <c r="G1050" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -48799,8 +48791,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1051" t="inlineStr"/>
-      <c r="F1051" t="inlineStr"/>
       <c r="G1051" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -48847,8 +48837,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1052" t="inlineStr"/>
-      <c r="F1052" t="inlineStr"/>
       <c r="G1052" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -48895,8 +48883,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1053" t="inlineStr"/>
-      <c r="F1053" t="inlineStr"/>
       <c r="G1053" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -48943,8 +48929,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1054" t="inlineStr"/>
-      <c r="F1054" t="inlineStr"/>
       <c r="G1054" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -48991,8 +48975,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1055" t="inlineStr"/>
-      <c r="F1055" t="inlineStr"/>
       <c r="G1055" t="inlineStr">
         <is>
           <t>5-0</t>
@@ -49039,8 +49021,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1056" t="inlineStr"/>
-      <c r="F1056" t="inlineStr"/>
       <c r="G1056" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -49087,8 +49067,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1057" t="inlineStr"/>
-      <c r="F1057" t="inlineStr"/>
       <c r="G1057" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -49135,8 +49113,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1058" t="inlineStr"/>
-      <c r="F1058" t="inlineStr"/>
       <c r="G1058" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -49183,8 +49159,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1059" t="inlineStr"/>
-      <c r="F1059" t="inlineStr"/>
       <c r="G1059" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -49231,8 +49205,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1060" t="inlineStr"/>
-      <c r="F1060" t="inlineStr"/>
       <c r="G1060" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -49279,8 +49251,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1061" t="inlineStr"/>
-      <c r="F1061" t="inlineStr"/>
       <c r="G1061" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -49327,8 +49297,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1062" t="inlineStr"/>
-      <c r="F1062" t="inlineStr"/>
       <c r="G1062" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -49375,8 +49343,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1063" t="inlineStr"/>
-      <c r="F1063" t="inlineStr"/>
       <c r="G1063" t="inlineStr">
         <is>
           <t>4-3</t>
@@ -49423,8 +49389,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1064" t="inlineStr"/>
-      <c r="F1064" t="inlineStr"/>
       <c r="G1064" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -49471,8 +49435,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1065" t="inlineStr"/>
-      <c r="F1065" t="inlineStr"/>
       <c r="G1065" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -49519,8 +49481,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1066" t="inlineStr"/>
-      <c r="F1066" t="inlineStr"/>
       <c r="G1066" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -49567,8 +49527,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1067" t="inlineStr"/>
-      <c r="F1067" t="inlineStr"/>
       <c r="G1067" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -49615,8 +49573,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1068" t="inlineStr"/>
-      <c r="F1068" t="inlineStr"/>
       <c r="G1068" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -49663,8 +49619,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1069" t="inlineStr"/>
-      <c r="F1069" t="inlineStr"/>
       <c r="G1069" t="inlineStr">
         <is>
           <t>1-5</t>
@@ -49711,8 +49665,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1070" t="inlineStr"/>
-      <c r="F1070" t="inlineStr"/>
       <c r="G1070" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -49759,8 +49711,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1071" t="inlineStr"/>
-      <c r="F1071" t="inlineStr"/>
       <c r="G1071" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -49807,8 +49757,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1072" t="inlineStr"/>
-      <c r="F1072" t="inlineStr"/>
       <c r="G1072" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -49855,8 +49803,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1073" t="inlineStr"/>
-      <c r="F1073" t="inlineStr"/>
       <c r="G1073" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -49903,8 +49849,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1074" t="inlineStr"/>
-      <c r="F1074" t="inlineStr"/>
       <c r="G1074" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -49951,8 +49895,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1075" t="inlineStr"/>
-      <c r="F1075" t="inlineStr"/>
       <c r="G1075" t="inlineStr">
         <is>
           <t>0-6</t>
@@ -49999,8 +49941,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1076" t="inlineStr"/>
-      <c r="F1076" t="inlineStr"/>
       <c r="G1076" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -50047,8 +49987,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1077" t="inlineStr"/>
-      <c r="F1077" t="inlineStr"/>
       <c r="G1077" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -50095,8 +50033,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1078" t="inlineStr"/>
-      <c r="F1078" t="inlineStr"/>
       <c r="G1078" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -50143,8 +50079,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1079" t="inlineStr"/>
-      <c r="F1079" t="inlineStr"/>
       <c r="G1079" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -50191,8 +50125,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1080" t="inlineStr"/>
-      <c r="F1080" t="inlineStr"/>
       <c r="G1080" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -50239,8 +50171,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1081" t="inlineStr"/>
-      <c r="F1081" t="inlineStr"/>
       <c r="G1081" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -50287,8 +50217,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1082" t="inlineStr"/>
-      <c r="F1082" t="inlineStr"/>
       <c r="G1082" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -50335,8 +50263,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1083" t="inlineStr"/>
-      <c r="F1083" t="inlineStr"/>
       <c r="G1083" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -50383,8 +50309,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1084" t="inlineStr"/>
-      <c r="F1084" t="inlineStr"/>
       <c r="G1084" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -50431,8 +50355,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1085" t="inlineStr"/>
-      <c r="F1085" t="inlineStr"/>
       <c r="G1085" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -50479,8 +50401,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1086" t="inlineStr"/>
-      <c r="F1086" t="inlineStr"/>
       <c r="G1086" t="inlineStr">
         <is>
           <t>1-4</t>
@@ -50527,8 +50447,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1087" t="inlineStr"/>
-      <c r="F1087" t="inlineStr"/>
       <c r="G1087" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -50575,8 +50493,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1088" t="inlineStr"/>
-      <c r="F1088" t="inlineStr"/>
       <c r="G1088" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -50623,8 +50539,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1089" t="inlineStr"/>
-      <c r="F1089" t="inlineStr"/>
       <c r="G1089" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -50671,8 +50585,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1090" t="inlineStr"/>
-      <c r="F1090" t="inlineStr"/>
       <c r="G1090" t="inlineStr">
         <is>
           <t>4-3</t>
@@ -50719,8 +50631,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1091" t="inlineStr"/>
-      <c r="F1091" t="inlineStr"/>
       <c r="G1091" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -50767,8 +50677,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1092" t="inlineStr"/>
-      <c r="F1092" t="inlineStr"/>
       <c r="G1092" t="inlineStr">
         <is>
           <t>1-5</t>
@@ -50815,8 +50723,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1093" t="inlineStr"/>
-      <c r="F1093" t="inlineStr"/>
       <c r="G1093" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -50863,8 +50769,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1094" t="inlineStr"/>
-      <c r="F1094" t="inlineStr"/>
       <c r="G1094" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -50911,8 +50815,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1095" t="inlineStr"/>
-      <c r="F1095" t="inlineStr"/>
       <c r="G1095" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -50959,8 +50861,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1096" t="inlineStr"/>
-      <c r="F1096" t="inlineStr"/>
       <c r="G1096" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -51007,8 +50907,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1097" t="inlineStr"/>
-      <c r="F1097" t="inlineStr"/>
       <c r="G1097" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -51055,8 +50953,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1098" t="inlineStr"/>
-      <c r="F1098" t="inlineStr"/>
       <c r="G1098" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -51103,8 +50999,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1099" t="inlineStr"/>
-      <c r="F1099" t="inlineStr"/>
       <c r="G1099" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -51151,8 +51045,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1100" t="inlineStr"/>
-      <c r="F1100" t="inlineStr"/>
       <c r="G1100" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -51199,8 +51091,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1101" t="inlineStr"/>
-      <c r="F1101" t="inlineStr"/>
       <c r="G1101" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -51247,8 +51137,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1102" t="inlineStr"/>
-      <c r="F1102" t="inlineStr"/>
       <c r="G1102" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -51295,8 +51183,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1103" t="inlineStr"/>
-      <c r="F1103" t="inlineStr"/>
       <c r="G1103" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -51343,8 +51229,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1104" t="inlineStr"/>
-      <c r="F1104" t="inlineStr"/>
       <c r="G1104" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -51391,8 +51275,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1105" t="inlineStr"/>
-      <c r="F1105" t="inlineStr"/>
       <c r="G1105" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -51439,8 +51321,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1106" t="inlineStr"/>
-      <c r="F1106" t="inlineStr"/>
       <c r="G1106" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -51487,8 +51367,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1107" t="inlineStr"/>
-      <c r="F1107" t="inlineStr"/>
       <c r="G1107" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -51535,8 +51413,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1108" t="inlineStr"/>
-      <c r="F1108" t="inlineStr"/>
       <c r="G1108" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -51583,8 +51459,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1109" t="inlineStr"/>
-      <c r="F1109" t="inlineStr"/>
       <c r="G1109" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -51631,8 +51505,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1110" t="inlineStr"/>
-      <c r="F1110" t="inlineStr"/>
       <c r="G1110" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -51679,8 +51551,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1111" t="inlineStr"/>
-      <c r="F1111" t="inlineStr"/>
       <c r="G1111" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -51727,8 +51597,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1112" t="inlineStr"/>
-      <c r="F1112" t="inlineStr"/>
       <c r="G1112" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -51775,8 +51643,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1113" t="inlineStr"/>
-      <c r="F1113" t="inlineStr"/>
       <c r="G1113" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -51823,8 +51689,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1114" t="inlineStr"/>
-      <c r="F1114" t="inlineStr"/>
       <c r="G1114" t="inlineStr">
         <is>
           <t>5-0</t>
@@ -51871,8 +51735,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1115" t="inlineStr"/>
-      <c r="F1115" t="inlineStr"/>
       <c r="G1115" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -51919,8 +51781,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1116" t="inlineStr"/>
-      <c r="F1116" t="inlineStr"/>
       <c r="G1116" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -51967,8 +51827,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1117" t="inlineStr"/>
-      <c r="F1117" t="inlineStr"/>
       <c r="G1117" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -52015,8 +51873,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1118" t="inlineStr"/>
-      <c r="F1118" t="inlineStr"/>
       <c r="G1118" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -52063,8 +51919,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1119" t="inlineStr"/>
-      <c r="F1119" t="inlineStr"/>
       <c r="G1119" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -52111,8 +51965,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1120" t="inlineStr"/>
-      <c r="F1120" t="inlineStr"/>
       <c r="G1120" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -52159,8 +52011,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1121" t="inlineStr"/>
-      <c r="F1121" t="inlineStr"/>
       <c r="G1121" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -52207,8 +52057,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1122" t="inlineStr"/>
-      <c r="F1122" t="inlineStr"/>
       <c r="G1122" t="inlineStr">
         <is>
           <t>5-2</t>
@@ -52255,8 +52103,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1123" t="inlineStr"/>
-      <c r="F1123" t="inlineStr"/>
       <c r="G1123" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -52303,8 +52149,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1124" t="inlineStr"/>
-      <c r="F1124" t="inlineStr"/>
       <c r="G1124" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -52351,8 +52195,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1125" t="inlineStr"/>
-      <c r="F1125" t="inlineStr"/>
       <c r="G1125" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -52399,8 +52241,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1126" t="inlineStr"/>
-      <c r="F1126" t="inlineStr"/>
       <c r="G1126" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -52447,8 +52287,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1127" t="inlineStr"/>
-      <c r="F1127" t="inlineStr"/>
       <c r="G1127" t="inlineStr">
         <is>
           <t>3-3</t>
@@ -52495,8 +52333,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1128" t="inlineStr"/>
-      <c r="F1128" t="inlineStr"/>
       <c r="G1128" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -52543,8 +52379,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1129" t="inlineStr"/>
-      <c r="F1129" t="inlineStr"/>
       <c r="G1129" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -52591,8 +52425,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1130" t="inlineStr"/>
-      <c r="F1130" t="inlineStr"/>
       <c r="G1130" t="inlineStr">
         <is>
           <t>5-4</t>
@@ -52639,8 +52471,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1131" t="inlineStr"/>
-      <c r="F1131" t="inlineStr"/>
       <c r="G1131" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -52687,8 +52517,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1132" t="inlineStr"/>
-      <c r="F1132" t="inlineStr"/>
       <c r="G1132" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -52735,8 +52563,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1133" t="inlineStr"/>
-      <c r="F1133" t="inlineStr"/>
       <c r="G1133" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -52783,8 +52609,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1134" t="inlineStr"/>
-      <c r="F1134" t="inlineStr"/>
       <c r="G1134" t="inlineStr">
         <is>
           <t>4-2</t>
@@ -52831,8 +52655,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1135" t="inlineStr"/>
-      <c r="F1135" t="inlineStr"/>
       <c r="G1135" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -52879,8 +52701,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1136" t="inlineStr"/>
-      <c r="F1136" t="inlineStr"/>
       <c r="G1136" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -52927,8 +52747,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1137" t="inlineStr"/>
-      <c r="F1137" t="inlineStr"/>
       <c r="G1137" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -52975,8 +52793,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1138" t="inlineStr"/>
-      <c r="F1138" t="inlineStr"/>
       <c r="G1138" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -53023,8 +52839,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1139" t="inlineStr"/>
-      <c r="F1139" t="inlineStr"/>
       <c r="G1139" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -53071,8 +52885,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1140" t="inlineStr"/>
-      <c r="F1140" t="inlineStr"/>
       <c r="G1140" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -53119,8 +52931,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1141" t="inlineStr"/>
-      <c r="F1141" t="inlineStr"/>
       <c r="G1141" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -53167,8 +52977,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1142" t="inlineStr"/>
-      <c r="F1142" t="inlineStr"/>
       <c r="G1142" t="inlineStr">
         <is>
           <t>1-4</t>
@@ -53215,8 +53023,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1143" t="inlineStr"/>
-      <c r="F1143" t="inlineStr"/>
       <c r="G1143" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -53263,8 +53069,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1144" t="inlineStr"/>
-      <c r="F1144" t="inlineStr"/>
       <c r="G1144" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -53311,8 +53115,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1145" t="inlineStr"/>
-      <c r="F1145" t="inlineStr"/>
       <c r="G1145" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -53359,8 +53161,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1146" t="inlineStr"/>
-      <c r="F1146" t="inlineStr"/>
       <c r="G1146" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -53407,8 +53207,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1147" t="inlineStr"/>
-      <c r="F1147" t="inlineStr"/>
       <c r="G1147" t="inlineStr">
         <is>
           <t>4-3</t>
@@ -53429,6 +53227,4278 @@
         <v>0</v>
       </c>
       <c r="L1147" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>Excelsior vs FC Utrecht</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>Excelsior</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr"/>
+      <c r="F1148" t="inlineStr"/>
+      <c r="G1148" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1148" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1148" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1148" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1148" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1148" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>Sheffield United vs Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr"/>
+      <c r="F1149" t="inlineStr"/>
+      <c r="G1149" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1149" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1149" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1149" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1149" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1149" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>Club Brugge vs Antwerp</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr"/>
+      <c r="F1150" t="inlineStr"/>
+      <c r="G1150" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1150" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1150" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1150" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1150" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1150" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>Akhmat Grozny vs Dynamo Makhachkala</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>Akhmat Grozny</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr"/>
+      <c r="F1151" t="inlineStr"/>
+      <c r="G1151" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1151" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1151" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>1. FC Heidenheim 1846 vs Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>1. FC Heidenheim 1846</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr"/>
+      <c r="F1152" t="inlineStr"/>
+      <c r="G1152" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1152" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1152" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>Karlsruher SC vs Energie Cottbus</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>Karlsruher SC</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr"/>
+      <c r="F1153" t="inlineStr"/>
+      <c r="G1153" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H1153" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1153" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>Celta Vigo vs Málaga</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr"/>
+      <c r="F1154" t="inlineStr"/>
+      <c r="G1154" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1154" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1154" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>Lyngby Boldklub vs Sønderjyske Fodbold</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>Lyngby Boldklub</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr"/>
+      <c r="F1155" t="inlineStr"/>
+      <c r="G1155" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1155" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1155" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1155" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1155" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1155" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>Silkeborg IF vs Viborg FF</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>Viborg FF</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr"/>
+      <c r="F1156" t="inlineStr"/>
+      <c r="G1156" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1156" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1156" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>IF Elfsborg vs Kalmar FF</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>IF Elfsborg</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr"/>
+      <c r="F1157" t="inlineStr"/>
+      <c r="G1157" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1157" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1157" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1157" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1157" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1157" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>Hammarby IF vs IF Brommapojkarna</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>Hammarby IF</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr"/>
+      <c r="F1158" t="inlineStr"/>
+      <c r="G1158" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1158" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1158" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1158" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1158" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1158" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>Sporting Gijón vs Eldense</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>Sporting Gijón</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr"/>
+      <c r="F1159" t="inlineStr"/>
+      <c r="G1159" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1159" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1159" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>Austria Vienna vs Austria Lustenau</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>Austria Vienna</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr"/>
+      <c r="F1160" t="inlineStr"/>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1160" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1160" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1160" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1160" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1160" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>WSG Swarovski Tirol vs TSV Hartberg</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>WSG Swarovski Tirol</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr"/>
+      <c r="F1161" t="inlineStr"/>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1161" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1161" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1161" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1161" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1161" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>Heerenveen vs Telstar</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>Heerenveen</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr"/>
+      <c r="F1162" t="inlineStr"/>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1162" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1162" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1162" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1162" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1162" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>Viking FK vs Kristiansund BK</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>Viking FK</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr"/>
+      <c r="F1163" t="inlineStr"/>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>8-1</t>
+        </is>
+      </c>
+      <c r="H1163" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1163" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>Coventry City vs Brighton &amp; Hove Albion</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>Brighton &amp; Hove Albion</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr"/>
+      <c r="F1164" t="inlineStr"/>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="H1164" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1164" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1164" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1164" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1164" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>Lille vs Troyes</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr"/>
+      <c r="F1165" t="inlineStr"/>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1165" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1165" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1165" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1165" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1165" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>Progreso vs Cerro</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>Progreso</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr"/>
+      <c r="F1166" t="inlineStr"/>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H1166" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1166" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1166" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1166" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1166" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>RB Leipzig vs Hamburg SV</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr"/>
+      <c r="F1167" t="inlineStr"/>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="H1167" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1167" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1167" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1167" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1167" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>Racing Genk vs KAA Gent</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>Racing Genk</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr"/>
+      <c r="F1168" t="inlineStr"/>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1168" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1168" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1168" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1168" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1168" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>Randers FC vs Odense Boldklub</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>Randers FC</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr"/>
+      <c r="F1169" t="inlineStr"/>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1169" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1169" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1169" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1169" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1169" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>Spartak Moscow vs Rostov</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>Spartak Moscow</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr"/>
+      <c r="F1170" t="inlineStr"/>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1170" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1170" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1170" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1170" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1170" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>Genclerbirligi vs Kasimpasa</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>Genclerbirligi</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr"/>
+      <c r="F1171" t="inlineStr"/>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1171" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1171" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1171" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1171" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1171" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>Levante vs Barcelona</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr"/>
+      <c r="F1172" t="inlineStr"/>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="H1172" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1172" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1172" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1172" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1172" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>Malmö FF vs Örgryte IS</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>Malmö FF</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr"/>
+      <c r="F1173" t="inlineStr"/>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H1173" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1173" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1173" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1173" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1173" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>PEC Zwolle vs Feyenoord Rotterdam</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>Feyenoord Rotterdam</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr"/>
+      <c r="F1174" t="inlineStr"/>
+      <c r="G1174" t="inlineStr">
+        <is>
+          <t>0-7</t>
+        </is>
+      </c>
+      <c r="H1174" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1174" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1174" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1174" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1174" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>FC Volendam vs FC Den Bosch</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>FC Volendam</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr"/>
+      <c r="F1175" t="inlineStr"/>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1175" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1175" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1175" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1175" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1175" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>SK Sturm Graz vs LASK Linz</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>LASK Linz</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr"/>
+      <c r="F1176" t="inlineStr"/>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1176" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1176" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1176" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1176" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1176" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>KFUM Oslo vs Aalesund</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>KFUM Oslo</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr"/>
+      <c r="F1177" t="inlineStr"/>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1177" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1177" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1177" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1177" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1177" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>IK Start vs SK Brann</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>SK Brann</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr"/>
+      <c r="F1178" t="inlineStr"/>
+      <c r="G1178" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1178" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1178" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1178" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1178" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1178" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>Le Mans vs Lens</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr"/>
+      <c r="F1179" t="inlineStr"/>
+      <c r="G1179" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1179" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1179" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1179" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1179" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1179" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>US Avellino vs Palermo</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>Palermo</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr"/>
+      <c r="F1180" t="inlineStr"/>
+      <c r="G1180" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1180" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1180" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1180" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1180" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1180" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>Mantova vs Sampdoria</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>Mantova</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr"/>
+      <c r="F1181" t="inlineStr"/>
+      <c r="G1181" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1181" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1181" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1181" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1181" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1181" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>Manchester United vs Manchester City</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr"/>
+      <c r="F1182" t="inlineStr"/>
+      <c r="G1182" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1182" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1182" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1182" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1182" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1182" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>SV Elversberg vs Bayern Munich</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr"/>
+      <c r="F1183" t="inlineStr"/>
+      <c r="G1183" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1183" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1183" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1183" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1183" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1183" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>Napoli vs Bologna</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr"/>
+      <c r="F1184" t="inlineStr"/>
+      <c r="G1184" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1184" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1184" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1184" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1184" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1184" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>FC Nordsjælland vs AGF</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>FC Nordsjælland</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr"/>
+      <c r="F1185" t="inlineStr"/>
+      <c r="G1185" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1185" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1185" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1185" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1185" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1185" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>Asteras Tripoli vs AEK Athens</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>AEK Athens</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr"/>
+      <c r="F1186" t="inlineStr"/>
+      <c r="G1186" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1186" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1186" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1186" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1186" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1186" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>Juventud vs Danubio</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>Juventud</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr"/>
+      <c r="F1187" t="inlineStr"/>
+      <c r="G1187" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1187" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1187" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1187" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1187" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1187" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>Neom SC vs Al Fateh</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>Neom SC</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr"/>
+      <c r="F1188" t="inlineStr"/>
+      <c r="G1188" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="H1188" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1188" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1188" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1188" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>Getafe vs Deportivo</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr"/>
+      <c r="F1189" t="inlineStr"/>
+      <c r="G1189" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1189" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1189" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1189" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1189" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1189" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>Krasnodar vs Akron Tolyatti</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>Krasnodar</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr"/>
+      <c r="F1190" t="inlineStr"/>
+      <c r="G1190" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1190" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1190" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1190" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1190" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1190" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>Mallorca vs CD Sabadell</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr"/>
+      <c r="F1191" t="inlineStr"/>
+      <c r="G1191" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1191" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1191" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1191" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1191" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1191" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>Benfica vs Gil Vicente</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>Benfica</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr"/>
+      <c r="F1192" t="inlineStr"/>
+      <c r="G1192" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1192" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1192" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1192" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1192" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1192" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>Galatasaray vs Kocaelispor</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>Galatasaray</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr"/>
+      <c r="F1193" t="inlineStr"/>
+      <c r="G1193" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1193" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1193" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1193" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1193" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1193" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>Amed SFK vs Istanbul Basaksehir</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>Amed SFK</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr"/>
+      <c r="F1194" t="inlineStr"/>
+      <c r="G1194" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="H1194" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1194" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1194" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1194" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1194" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>RAAL La Louvière vs KV Kortrijk</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>RAAL La Louvière</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr"/>
+      <c r="F1195" t="inlineStr"/>
+      <c r="G1195" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1195" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1195" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1195" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1195" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1195" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>Fredrikstad vs Sarpsborg FK</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>Fredrikstad</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr"/>
+      <c r="F1196" t="inlineStr"/>
+      <c r="G1196" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1196" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1196" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1196" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1196" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1196" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>Sarmiento (Junín) vs Belgrano (Córdoba)</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>Belgrano (Córdoba)</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr"/>
+      <c r="F1197" t="inlineStr"/>
+      <c r="G1197" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1197" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1197" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1197" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1197" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1197" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>Kifisia vs Levadiakos</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>Kifisia</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr"/>
+      <c r="F1198" t="inlineStr"/>
+      <c r="G1198" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1198" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1198" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1198" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1198" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1198" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>PAOK vs Aris</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>PAOK</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr"/>
+      <c r="F1199" t="inlineStr"/>
+      <c r="G1199" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1199" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1199" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1199" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1199" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1199" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven vs Sparta Rotterdam</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr"/>
+      <c r="F1200" t="inlineStr"/>
+      <c r="G1200" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H1200" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1200" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1200" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1200" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1200" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>La Serena vs Universidad de Chile</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>Universidad de Chile</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr"/>
+      <c r="F1201" t="inlineStr"/>
+      <c r="G1201" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H1201" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1201" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1201" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1201" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1201" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>Leones vs Técnico Universitario</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>Leones</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr"/>
+      <c r="F1202" t="inlineStr"/>
+      <c r="G1202" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1202" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1202" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1202" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1202" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1202" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>Sport Boys vs Deportivo Garcilaso</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>Sport Boys</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr"/>
+      <c r="F1203" t="inlineStr"/>
+      <c r="G1203" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1203" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1203" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1203" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1203" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1203" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>Al Diriyah vs Abha</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>Al Diriyah</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr"/>
+      <c r="F1204" t="inlineStr"/>
+      <c r="G1204" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1204" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1204" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1204" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1204" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1204" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>Al Riyadh vs Al Kholood</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>Al Kholood</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr"/>
+      <c r="F1205" t="inlineStr"/>
+      <c r="G1205" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1205" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1205" t="n">
+        <v>6</v>
+      </c>
+      <c r="J1205" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1205" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1205" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>Panathinaikos vs Panetolikos</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr"/>
+      <c r="F1206" t="inlineStr"/>
+      <c r="G1206" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1206" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1206" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1206" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1206" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1206" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>Brest vs Paris Saint-Germain</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>Paris Saint-Germain</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr"/>
+      <c r="F1207" t="inlineStr"/>
+      <c r="G1207" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1207" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1207" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1207" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1207" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1207" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>Sassuolo vs Juventus</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr"/>
+      <c r="F1208" t="inlineStr"/>
+      <c r="G1208" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1208" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1208" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1208" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1208" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1208" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>Real Sociedad vs Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr"/>
+      <c r="F1209" t="inlineStr"/>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H1209" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1209" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1209" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1209" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>Mirassol vs Vitória</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr"/>
+      <c r="F1210" t="inlineStr"/>
+      <c r="G1210" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1210" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1210" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1210" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1210" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1210" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>Atlético Goianiense vs Criciúma</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>Atlético Goianiense</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr"/>
+      <c r="F1211" t="inlineStr"/>
+      <c r="G1211" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H1211" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1211" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1211" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1211" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1211" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira vs Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr"/>
+      <c r="F1212" t="inlineStr"/>
+      <c r="G1212" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H1212" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1212" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1212" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1212" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1212" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>Club Olimpia vs Sportivo Luqueño</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>Club Olimpia</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr"/>
+      <c r="F1213" t="inlineStr"/>
+      <c r="G1213" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1213" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1213" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1213" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1213" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1213" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>Tenerife vs Leganés</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>Tenerife</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr"/>
+      <c r="F1214" t="inlineStr"/>
+      <c r="G1214" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1214" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1214" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1214" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1214" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>FC Famalicao vs Sporting CP</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>Sporting CP</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr"/>
+      <c r="F1215" t="inlineStr"/>
+      <c r="G1215" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1215" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1215" t="n">
+        <v>6</v>
+      </c>
+      <c r="J1215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1215" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1215" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors vs Gimnasia La Plata</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>Argentinos Juniors</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr"/>
+      <c r="F1216" t="inlineStr"/>
+      <c r="G1216" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1216" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1216" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1216" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1216" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1216" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>Atlético Grau vs Alianza Atlético</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>Atlético Grau</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr"/>
+      <c r="F1217" t="inlineStr"/>
+      <c r="G1217" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1217" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1217" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1217" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1217" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>Flamengo vs Corinthians</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr"/>
+      <c r="F1218" t="inlineStr"/>
+      <c r="G1218" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1218" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1218" t="n">
+        <v>7</v>
+      </c>
+      <c r="J1218" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1218" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1218" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>Colo Colo vs Deportes Concepcion</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>Colo Colo</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr"/>
+      <c r="F1219" t="inlineStr"/>
+      <c r="G1219" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1219" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1219" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1219" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1219" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1219" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>Macará vs Emelec</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>Macará</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr"/>
+      <c r="F1220" t="inlineStr"/>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1220" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1220" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1220" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1220" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1220" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>Juventude vs Athletic</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr"/>
+      <c r="F1221" t="inlineStr"/>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1221" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1221" t="n">
+        <v>6</v>
+      </c>
+      <c r="J1221" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1221" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1221" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>Atlético Nacional vs Águilas Doradas</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr"/>
+      <c r="F1222" t="inlineStr"/>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1222" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1222" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1222" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1222" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1222" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>Chicago Fire FC vs New England Revolution</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>Chicago Fire FC</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr"/>
+      <c r="F1223" t="inlineStr"/>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1223" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1223" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1223" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1223" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1223" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>Fortaleza vs Ceará</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr"/>
+      <c r="F1224" t="inlineStr"/>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1224" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1224" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1224" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1224" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1224" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>Novorizontino vs Cuiabá</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr"/>
+      <c r="F1225" t="inlineStr"/>
+      <c r="G1225" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1225" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1225" t="n">
+        <v>7</v>
+      </c>
+      <c r="J1225" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1225" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1225" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>Rubio Ñú vs Nacional Asunción</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>Nacional Asunción</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr"/>
+      <c r="F1226" t="inlineStr"/>
+      <c r="G1226" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1226" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1226" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1226" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1226" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1226" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>Portland Hearts of Pine vs AV Alta FC</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>Portland Hearts of Pine</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr"/>
+      <c r="F1227" t="inlineStr"/>
+      <c r="G1227" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1227" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1227" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1227" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1227" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1227" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>Independiente vs San Lorenzo</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>Independiente</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1228" t="inlineStr"/>
+      <c r="F1228" t="inlineStr"/>
+      <c r="G1228" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1228" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1228" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1228" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1228" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1228" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>Peñarol vs Albion FC</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>Peñarol</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr"/>
+      <c r="F1229" t="inlineStr"/>
+      <c r="G1229" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1229" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1229" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1229" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1229" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1229" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs Austin FC</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr"/>
+      <c r="F1230" t="inlineStr"/>
+      <c r="G1230" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1230" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1230" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1230" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1230" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1230" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>Barcelona SC vs Delfín</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>Barcelona SC</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1231" t="inlineStr"/>
+      <c r="F1231" t="inlineStr"/>
+      <c r="G1231" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1231" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1231" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1231" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1231" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1231" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>Libertad (Ecuador) vs Independiente del Valle</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>Independiente del Valle</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1232" t="inlineStr"/>
+      <c r="F1232" t="inlineStr"/>
+      <c r="G1232" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H1232" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1232" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1232" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1232" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1232" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>Once Caldas vs Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1233" t="inlineStr"/>
+      <c r="F1233" t="inlineStr"/>
+      <c r="G1233" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1233" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1233" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1233" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1233" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1233" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>Santos vs FC Juarez</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>FC Juarez</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1234" t="inlineStr"/>
+      <c r="F1234" t="inlineStr"/>
+      <c r="G1234" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1234" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1234" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1234" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1234" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1234" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>San Diego FC vs Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr"/>
+      <c r="F1235" t="inlineStr"/>
+      <c r="G1235" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="H1235" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1235" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1235" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1235" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1235" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>Cúcuta Deportivo vs Millonarios</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1236" t="inlineStr"/>
+      <c r="F1236" t="inlineStr"/>
+      <c r="G1236" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1236" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1236" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1236" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1236" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1236" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -53445,7 +57515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54060,6 +58130,25 @@
       </c>
       <c r="E33" t="n">
         <v>101</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>89</v>
+      </c>
+      <c r="C34" t="n">
+        <v>63</v>
+      </c>
+      <c r="D34" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="E34" t="n">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -54073,7 +58162,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E150"/>
+  <dimension ref="A1:E160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57232,6 +61321,216 @@
         <v>0</v>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>6</v>
+      </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
+      <c r="E151" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>7</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0</v>
+      </c>
+      <c r="E152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>siguen_empatados_55</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>3</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0</v>
+      </c>
+      <c r="E153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>22</v>
+      </c>
+      <c r="D154" t="n">
+        <v>3</v>
+      </c>
+      <c r="E154" t="n">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>gol_de_cierre</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>10</v>
+      </c>
+      <c r="D155" t="n">
+        <v>2</v>
+      </c>
+      <c r="E155" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>8</v>
+      </c>
+      <c r="D156" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>9</v>
+      </c>
+      <c r="D157" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>4</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>11</v>
+      </c>
+      <c r="D159" t="n">
+        <v>2</v>
+      </c>
+      <c r="E159" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>siguen_empatados_70</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>3</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0</v>
+      </c>
+      <c r="E160" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1236"/>
+  <dimension ref="A1:L1267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53253,8 +53253,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1148" t="inlineStr"/>
-      <c r="F1148" t="inlineStr"/>
       <c r="G1148" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -53301,8 +53299,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1149" t="inlineStr"/>
-      <c r="F1149" t="inlineStr"/>
       <c r="G1149" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -53349,8 +53345,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1150" t="inlineStr"/>
-      <c r="F1150" t="inlineStr"/>
       <c r="G1150" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -53397,8 +53391,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1151" t="inlineStr"/>
-      <c r="F1151" t="inlineStr"/>
       <c r="G1151" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -53445,8 +53437,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1152" t="inlineStr"/>
-      <c r="F1152" t="inlineStr"/>
       <c r="G1152" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -53493,8 +53483,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1153" t="inlineStr"/>
-      <c r="F1153" t="inlineStr"/>
       <c r="G1153" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -53541,8 +53529,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1154" t="inlineStr"/>
-      <c r="F1154" t="inlineStr"/>
       <c r="G1154" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -53589,8 +53575,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1155" t="inlineStr"/>
-      <c r="F1155" t="inlineStr"/>
       <c r="G1155" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -53637,8 +53621,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1156" t="inlineStr"/>
-      <c r="F1156" t="inlineStr"/>
       <c r="G1156" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -53685,8 +53667,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1157" t="inlineStr"/>
-      <c r="F1157" t="inlineStr"/>
       <c r="G1157" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -53733,8 +53713,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1158" t="inlineStr"/>
-      <c r="F1158" t="inlineStr"/>
       <c r="G1158" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -53781,8 +53759,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1159" t="inlineStr"/>
-      <c r="F1159" t="inlineStr"/>
       <c r="G1159" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -53829,8 +53805,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1160" t="inlineStr"/>
-      <c r="F1160" t="inlineStr"/>
       <c r="G1160" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -53877,8 +53851,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1161" t="inlineStr"/>
-      <c r="F1161" t="inlineStr"/>
       <c r="G1161" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -53925,8 +53897,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1162" t="inlineStr"/>
-      <c r="F1162" t="inlineStr"/>
       <c r="G1162" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -53973,8 +53943,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1163" t="inlineStr"/>
-      <c r="F1163" t="inlineStr"/>
       <c r="G1163" t="inlineStr">
         <is>
           <t>8-1</t>
@@ -54021,8 +53989,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1164" t="inlineStr"/>
-      <c r="F1164" t="inlineStr"/>
       <c r="G1164" t="inlineStr">
         <is>
           <t>0-5</t>
@@ -54069,8 +54035,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1165" t="inlineStr"/>
-      <c r="F1165" t="inlineStr"/>
       <c r="G1165" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -54117,8 +54081,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1166" t="inlineStr"/>
-      <c r="F1166" t="inlineStr"/>
       <c r="G1166" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -54165,8 +54127,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1167" t="inlineStr"/>
-      <c r="F1167" t="inlineStr"/>
       <c r="G1167" t="inlineStr">
         <is>
           <t>5-0</t>
@@ -54213,8 +54173,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1168" t="inlineStr"/>
-      <c r="F1168" t="inlineStr"/>
       <c r="G1168" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -54261,8 +54219,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1169" t="inlineStr"/>
-      <c r="F1169" t="inlineStr"/>
       <c r="G1169" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -54309,8 +54265,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1170" t="inlineStr"/>
-      <c r="F1170" t="inlineStr"/>
       <c r="G1170" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -54357,8 +54311,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1171" t="inlineStr"/>
-      <c r="F1171" t="inlineStr"/>
       <c r="G1171" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -54405,8 +54357,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1172" t="inlineStr"/>
-      <c r="F1172" t="inlineStr"/>
       <c r="G1172" t="inlineStr">
         <is>
           <t>2-4</t>
@@ -54453,8 +54403,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1173" t="inlineStr"/>
-      <c r="F1173" t="inlineStr"/>
       <c r="G1173" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -54501,8 +54449,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1174" t="inlineStr"/>
-      <c r="F1174" t="inlineStr"/>
       <c r="G1174" t="inlineStr">
         <is>
           <t>0-7</t>
@@ -54549,8 +54495,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1175" t="inlineStr"/>
-      <c r="F1175" t="inlineStr"/>
       <c r="G1175" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -54597,8 +54541,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1176" t="inlineStr"/>
-      <c r="F1176" t="inlineStr"/>
       <c r="G1176" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -54645,8 +54587,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1177" t="inlineStr"/>
-      <c r="F1177" t="inlineStr"/>
       <c r="G1177" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -54693,8 +54633,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1178" t="inlineStr"/>
-      <c r="F1178" t="inlineStr"/>
       <c r="G1178" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -54741,8 +54679,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1179" t="inlineStr"/>
-      <c r="F1179" t="inlineStr"/>
       <c r="G1179" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -54789,8 +54725,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1180" t="inlineStr"/>
-      <c r="F1180" t="inlineStr"/>
       <c r="G1180" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -54837,8 +54771,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1181" t="inlineStr"/>
-      <c r="F1181" t="inlineStr"/>
       <c r="G1181" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -54885,8 +54817,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1182" t="inlineStr"/>
-      <c r="F1182" t="inlineStr"/>
       <c r="G1182" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -54933,8 +54863,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1183" t="inlineStr"/>
-      <c r="F1183" t="inlineStr"/>
       <c r="G1183" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -54981,8 +54909,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1184" t="inlineStr"/>
-      <c r="F1184" t="inlineStr"/>
       <c r="G1184" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -55029,8 +54955,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1185" t="inlineStr"/>
-      <c r="F1185" t="inlineStr"/>
       <c r="G1185" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -55077,8 +55001,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1186" t="inlineStr"/>
-      <c r="F1186" t="inlineStr"/>
       <c r="G1186" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -55125,8 +55047,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1187" t="inlineStr"/>
-      <c r="F1187" t="inlineStr"/>
       <c r="G1187" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -55173,8 +55093,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1188" t="inlineStr"/>
-      <c r="F1188" t="inlineStr"/>
       <c r="G1188" t="inlineStr">
         <is>
           <t>4-2</t>
@@ -55221,8 +55139,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1189" t="inlineStr"/>
-      <c r="F1189" t="inlineStr"/>
       <c r="G1189" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -55269,8 +55185,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1190" t="inlineStr"/>
-      <c r="F1190" t="inlineStr"/>
       <c r="G1190" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -55317,8 +55231,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1191" t="inlineStr"/>
-      <c r="F1191" t="inlineStr"/>
       <c r="G1191" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -55365,8 +55277,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1192" t="inlineStr"/>
-      <c r="F1192" t="inlineStr"/>
       <c r="G1192" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -55413,8 +55323,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1193" t="inlineStr"/>
-      <c r="F1193" t="inlineStr"/>
       <c r="G1193" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -55461,8 +55369,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1194" t="inlineStr"/>
-      <c r="F1194" t="inlineStr"/>
       <c r="G1194" t="inlineStr">
         <is>
           <t>5-0</t>
@@ -55509,8 +55415,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1195" t="inlineStr"/>
-      <c r="F1195" t="inlineStr"/>
       <c r="G1195" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -55557,8 +55461,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1196" t="inlineStr"/>
-      <c r="F1196" t="inlineStr"/>
       <c r="G1196" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -55605,8 +55507,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1197" t="inlineStr"/>
-      <c r="F1197" t="inlineStr"/>
       <c r="G1197" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -55653,8 +55553,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1198" t="inlineStr"/>
-      <c r="F1198" t="inlineStr"/>
       <c r="G1198" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -55701,8 +55599,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1199" t="inlineStr"/>
-      <c r="F1199" t="inlineStr"/>
       <c r="G1199" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -55749,8 +55645,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1200" t="inlineStr"/>
-      <c r="F1200" t="inlineStr"/>
       <c r="G1200" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -55797,8 +55691,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1201" t="inlineStr"/>
-      <c r="F1201" t="inlineStr"/>
       <c r="G1201" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -55845,8 +55737,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1202" t="inlineStr"/>
-      <c r="F1202" t="inlineStr"/>
       <c r="G1202" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -55893,8 +55783,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1203" t="inlineStr"/>
-      <c r="F1203" t="inlineStr"/>
       <c r="G1203" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -55941,8 +55829,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1204" t="inlineStr"/>
-      <c r="F1204" t="inlineStr"/>
       <c r="G1204" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -55989,8 +55875,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1205" t="inlineStr"/>
-      <c r="F1205" t="inlineStr"/>
       <c r="G1205" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -56037,8 +55921,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1206" t="inlineStr"/>
-      <c r="F1206" t="inlineStr"/>
       <c r="G1206" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -56085,8 +55967,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1207" t="inlineStr"/>
-      <c r="F1207" t="inlineStr"/>
       <c r="G1207" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -56133,8 +56013,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1208" t="inlineStr"/>
-      <c r="F1208" t="inlineStr"/>
       <c r="G1208" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -56181,8 +56059,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1209" t="inlineStr"/>
-      <c r="F1209" t="inlineStr"/>
       <c r="G1209" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -56229,8 +56105,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1210" t="inlineStr"/>
-      <c r="F1210" t="inlineStr"/>
       <c r="G1210" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -56277,8 +56151,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1211" t="inlineStr"/>
-      <c r="F1211" t="inlineStr"/>
       <c r="G1211" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -56325,8 +56197,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1212" t="inlineStr"/>
-      <c r="F1212" t="inlineStr"/>
       <c r="G1212" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -56373,8 +56243,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1213" t="inlineStr"/>
-      <c r="F1213" t="inlineStr"/>
       <c r="G1213" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -56421,8 +56289,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1214" t="inlineStr"/>
-      <c r="F1214" t="inlineStr"/>
       <c r="G1214" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -56469,8 +56335,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1215" t="inlineStr"/>
-      <c r="F1215" t="inlineStr"/>
       <c r="G1215" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -56517,8 +56381,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1216" t="inlineStr"/>
-      <c r="F1216" t="inlineStr"/>
       <c r="G1216" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -56565,8 +56427,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1217" t="inlineStr"/>
-      <c r="F1217" t="inlineStr"/>
       <c r="G1217" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -56613,8 +56473,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1218" t="inlineStr"/>
-      <c r="F1218" t="inlineStr"/>
       <c r="G1218" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -56661,8 +56519,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1219" t="inlineStr"/>
-      <c r="F1219" t="inlineStr"/>
       <c r="G1219" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -56709,8 +56565,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1220" t="inlineStr"/>
-      <c r="F1220" t="inlineStr"/>
       <c r="G1220" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -56757,8 +56611,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1221" t="inlineStr"/>
-      <c r="F1221" t="inlineStr"/>
       <c r="G1221" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -56805,8 +56657,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1222" t="inlineStr"/>
-      <c r="F1222" t="inlineStr"/>
       <c r="G1222" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -56853,8 +56703,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1223" t="inlineStr"/>
-      <c r="F1223" t="inlineStr"/>
       <c r="G1223" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -56901,8 +56749,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1224" t="inlineStr"/>
-      <c r="F1224" t="inlineStr"/>
       <c r="G1224" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -56949,8 +56795,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1225" t="inlineStr"/>
-      <c r="F1225" t="inlineStr"/>
       <c r="G1225" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -56997,8 +56841,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1226" t="inlineStr"/>
-      <c r="F1226" t="inlineStr"/>
       <c r="G1226" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -57045,8 +56887,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1227" t="inlineStr"/>
-      <c r="F1227" t="inlineStr"/>
       <c r="G1227" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -57093,8 +56933,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1228" t="inlineStr"/>
-      <c r="F1228" t="inlineStr"/>
       <c r="G1228" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -57141,8 +56979,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1229" t="inlineStr"/>
-      <c r="F1229" t="inlineStr"/>
       <c r="G1229" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -57189,8 +57025,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1230" t="inlineStr"/>
-      <c r="F1230" t="inlineStr"/>
       <c r="G1230" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -57237,8 +57071,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1231" t="inlineStr"/>
-      <c r="F1231" t="inlineStr"/>
       <c r="G1231" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -57285,8 +57117,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1232" t="inlineStr"/>
-      <c r="F1232" t="inlineStr"/>
       <c r="G1232" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -57333,8 +57163,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1233" t="inlineStr"/>
-      <c r="F1233" t="inlineStr"/>
       <c r="G1233" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -57381,8 +57209,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1234" t="inlineStr"/>
-      <c r="F1234" t="inlineStr"/>
       <c r="G1234" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -57429,8 +57255,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1235" t="inlineStr"/>
-      <c r="F1235" t="inlineStr"/>
       <c r="G1235" t="inlineStr">
         <is>
           <t>0-5</t>
@@ -57477,8 +57301,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1236" t="inlineStr"/>
-      <c r="F1236" t="inlineStr"/>
       <c r="G1236" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -57499,6 +57321,1494 @@
         <v>0</v>
       </c>
       <c r="L1236" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>Neftchi Fergana vs Air Force Club</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>Neftchi Fergana</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1237" t="inlineStr"/>
+      <c r="F1237" t="inlineStr"/>
+      <c r="G1237" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1237" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1237" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1237" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1237" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1237" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>Shabab Al-Ahli vs Traktor Sazi FC</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>Shabab Al-Ahli</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1238" t="inlineStr"/>
+      <c r="F1238" t="inlineStr"/>
+      <c r="G1238" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1238" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1238" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1238" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1238" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1238" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>Como vs Parma</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1239" t="inlineStr"/>
+      <c r="F1239" t="inlineStr"/>
+      <c r="G1239" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1239" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1239" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1239" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1239" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1239" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>Torino vs AS Roma</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>AS Roma</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1240" t="inlineStr"/>
+      <c r="F1240" t="inlineStr"/>
+      <c r="G1240" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1240" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1240" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1240" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1240" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1240" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>FC Midtjylland vs Brøndby IF</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>FC Midtjylland</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1241" t="inlineStr"/>
+      <c r="F1241" t="inlineStr"/>
+      <c r="G1241" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H1241" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1241" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1241" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1241" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1241" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>Bodo/Glimt vs Sandefjord</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>Bodo/Glimt</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1242" t="inlineStr"/>
+      <c r="F1242" t="inlineStr"/>
+      <c r="G1242" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1242" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1242" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1242" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1242" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1242" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>Djurgården vs GAIS</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>Djurgården</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1243" t="inlineStr"/>
+      <c r="F1243" t="inlineStr"/>
+      <c r="G1243" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1243" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1243" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1243" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1243" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1243" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>Gaziantep FK vs Fenerbahce</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>Fenerbahce</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1244" t="inlineStr"/>
+      <c r="F1244" t="inlineStr"/>
+      <c r="G1244" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1244" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1244" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1244" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1244" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1244" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>IK Sirius vs Degerfors IF</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>IK Sirius</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1245" t="inlineStr"/>
+      <c r="F1245" t="inlineStr"/>
+      <c r="G1245" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1245" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1245" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1245" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1245" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1245" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>Jong PSV vs Jong AZ</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>Jong AZ</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr"/>
+      <c r="F1246" t="inlineStr"/>
+      <c r="G1246" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1246" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1246" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1246" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1246" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1246" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>Jong FC Utrecht vs Jong Ajax</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>Jong FC Utrecht</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr"/>
+      <c r="F1247" t="inlineStr"/>
+      <c r="G1247" t="inlineStr">
+        <is>
+          <t>6-1</t>
+        </is>
+      </c>
+      <c r="H1247" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1247" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1247" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1247" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1247" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>Esteghlal vs Al Sadd</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>Al Sadd</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr"/>
+      <c r="F1248" t="inlineStr"/>
+      <c r="G1248" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1248" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1248" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1248" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1248" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1248" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>Al Ahli vs Pakhtakor Tashkent</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>Al Ahli</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr"/>
+      <c r="F1249" t="inlineStr"/>
+      <c r="G1249" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1249" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1249" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1249" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1249" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1249" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>Al Qadsiah vs Al Wasl</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>Al Qadsiah</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr"/>
+      <c r="F1250" t="inlineStr"/>
+      <c r="G1250" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1250" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1250" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1250" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1250" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1250" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>Defensores de Belgrano vs Deportivo Madryn</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>Defensores de Belgrano</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr"/>
+      <c r="F1251" t="inlineStr"/>
+      <c r="G1251" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1251" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1251" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1251" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1251" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1251" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>Internazionale vs Udinese</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>Internazionale</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr"/>
+      <c r="F1252" t="inlineStr"/>
+      <c r="G1252" t="inlineStr">
+        <is>
+          <t>5-3</t>
+        </is>
+      </c>
+      <c r="H1252" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1252" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1252" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1252" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1252" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>Red Star FC 93 vs Metz</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>Red Star FC 93</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr"/>
+      <c r="F1253" t="inlineStr"/>
+      <c r="G1253" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1253" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1253" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1253" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1253" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1253" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>Leeds United vs Newcastle United</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>Leeds United</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr"/>
+      <c r="F1254" t="inlineStr"/>
+      <c r="G1254" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H1254" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1254" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1254" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1254" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1254" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>Villarreal vs Real Betis</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr"/>
+      <c r="F1255" t="inlineStr"/>
+      <c r="G1255" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1255" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1255" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1255" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1255" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1255" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>Moreirense vs Maritimo</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>Moreirense</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr"/>
+      <c r="F1256" t="inlineStr"/>
+      <c r="G1256" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1256" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1256" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1256" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1256" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1256" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>Braga vs Estoril</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr"/>
+      <c r="F1257" t="inlineStr"/>
+      <c r="G1257" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1257" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1257" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1257" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1257" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1257" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>Banfield vs Barracas Central</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>Banfield</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr"/>
+      <c r="F1258" t="inlineStr"/>
+      <c r="G1258" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1258" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1258" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1258" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1258" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1258" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>América Mineiro vs São Bernardo</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>América Mineiro</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1259" t="inlineStr"/>
+      <c r="F1259" t="inlineStr"/>
+      <c r="G1259" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1259" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1259" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1259" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1259" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1259" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>Botafogo-SP vs Goiás</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>Botafogo-SP</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1260" t="inlineStr"/>
+      <c r="F1260" t="inlineStr"/>
+      <c r="G1260" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H1260" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1260" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1260" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1260" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1260" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>Bahia vs Remo</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>Bahia</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr"/>
+      <c r="F1261" t="inlineStr"/>
+      <c r="G1261" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1261" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1261" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1261" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1261" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1261" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>Unión La Calera vs Deportes Limache</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>Unión La Calera</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1262" t="inlineStr"/>
+      <c r="F1262" t="inlineStr"/>
+      <c r="G1262" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1262" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1262" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1262" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1262" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1262" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>Universidad Católica (Quito) vs Orense</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>Universidad Católica (Quito)</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1263" t="inlineStr"/>
+      <c r="F1263" t="inlineStr"/>
+      <c r="G1263" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1263" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1263" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1263" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1263" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1263" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>Instituto (Córdoba) vs Estudiantes de Río Cuarto</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>Instituto (Córdoba)</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr"/>
+      <c r="F1264" t="inlineStr"/>
+      <c r="G1264" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1264" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1264" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1264" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1264" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1264" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>León vs Atlético de San Luis</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>León</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1265" t="inlineStr"/>
+      <c r="F1265" t="inlineStr"/>
+      <c r="G1265" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1265" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1265" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1265" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1265" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1265" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>América de Cali vs Deportivo Pasto</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>América de Cali</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr"/>
+      <c r="F1266" t="inlineStr"/>
+      <c r="G1266" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1266" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1266" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1266" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1266" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1266" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>Antigua GFC vs Suchitepequez</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>Antigua GFC</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1267" t="inlineStr"/>
+      <c r="F1267" t="inlineStr"/>
+      <c r="G1267" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1267" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1267" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1267" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1267" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1267" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -57515,7 +58825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58149,6 +59459,25 @@
       </c>
       <c r="E34" t="n">
         <v>89</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>31</v>
+      </c>
+      <c r="C35" t="n">
+        <v>24</v>
+      </c>
+      <c r="D35" t="n">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="E35" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -58162,7 +59491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E160"/>
+  <dimension ref="A1:E167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61531,6 +62860,153 @@
         <v>0</v>
       </c>
     </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>siguen_empatados_70</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>2</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>2</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0</v>
+      </c>
+      <c r="E162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>11</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1</v>
+      </c>
+      <c r="E163" t="n">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>4</v>
+      </c>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>7</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0</v>
+      </c>
+      <c r="E165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>6</v>
+      </c>
+      <c r="D166" t="n">
+        <v>2</v>
+      </c>
+      <c r="E166" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>1</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0</v>
+      </c>
+      <c r="E167" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1267"/>
+  <dimension ref="A1:L1314"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57347,8 +57347,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1237" t="inlineStr"/>
-      <c r="F1237" t="inlineStr"/>
       <c r="G1237" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -57395,8 +57393,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1238" t="inlineStr"/>
-      <c r="F1238" t="inlineStr"/>
       <c r="G1238" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -57443,8 +57439,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1239" t="inlineStr"/>
-      <c r="F1239" t="inlineStr"/>
       <c r="G1239" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -57491,8 +57485,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1240" t="inlineStr"/>
-      <c r="F1240" t="inlineStr"/>
       <c r="G1240" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -57539,8 +57531,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1241" t="inlineStr"/>
-      <c r="F1241" t="inlineStr"/>
       <c r="G1241" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -57587,8 +57577,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1242" t="inlineStr"/>
-      <c r="F1242" t="inlineStr"/>
       <c r="G1242" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -57635,8 +57623,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1243" t="inlineStr"/>
-      <c r="F1243" t="inlineStr"/>
       <c r="G1243" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -57683,8 +57669,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1244" t="inlineStr"/>
-      <c r="F1244" t="inlineStr"/>
       <c r="G1244" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -57731,8 +57715,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1245" t="inlineStr"/>
-      <c r="F1245" t="inlineStr"/>
       <c r="G1245" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -57779,8 +57761,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1246" t="inlineStr"/>
-      <c r="F1246" t="inlineStr"/>
       <c r="G1246" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -57827,8 +57807,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1247" t="inlineStr"/>
-      <c r="F1247" t="inlineStr"/>
       <c r="G1247" t="inlineStr">
         <is>
           <t>6-1</t>
@@ -57875,8 +57853,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1248" t="inlineStr"/>
-      <c r="F1248" t="inlineStr"/>
       <c r="G1248" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -57923,8 +57899,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1249" t="inlineStr"/>
-      <c r="F1249" t="inlineStr"/>
       <c r="G1249" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -57971,8 +57945,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1250" t="inlineStr"/>
-      <c r="F1250" t="inlineStr"/>
       <c r="G1250" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -58019,8 +57991,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1251" t="inlineStr"/>
-      <c r="F1251" t="inlineStr"/>
       <c r="G1251" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -58067,8 +58037,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1252" t="inlineStr"/>
-      <c r="F1252" t="inlineStr"/>
       <c r="G1252" t="inlineStr">
         <is>
           <t>5-3</t>
@@ -58115,8 +58083,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1253" t="inlineStr"/>
-      <c r="F1253" t="inlineStr"/>
       <c r="G1253" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -58163,8 +58129,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1254" t="inlineStr"/>
-      <c r="F1254" t="inlineStr"/>
       <c r="G1254" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -58211,8 +58175,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1255" t="inlineStr"/>
-      <c r="F1255" t="inlineStr"/>
       <c r="G1255" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -58259,8 +58221,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1256" t="inlineStr"/>
-      <c r="F1256" t="inlineStr"/>
       <c r="G1256" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -58307,8 +58267,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1257" t="inlineStr"/>
-      <c r="F1257" t="inlineStr"/>
       <c r="G1257" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -58355,8 +58313,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1258" t="inlineStr"/>
-      <c r="F1258" t="inlineStr"/>
       <c r="G1258" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -58403,8 +58359,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1259" t="inlineStr"/>
-      <c r="F1259" t="inlineStr"/>
       <c r="G1259" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -58451,8 +58405,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1260" t="inlineStr"/>
-      <c r="F1260" t="inlineStr"/>
       <c r="G1260" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -58499,8 +58451,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1261" t="inlineStr"/>
-      <c r="F1261" t="inlineStr"/>
       <c r="G1261" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -58547,8 +58497,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1262" t="inlineStr"/>
-      <c r="F1262" t="inlineStr"/>
       <c r="G1262" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -58595,8 +58543,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1263" t="inlineStr"/>
-      <c r="F1263" t="inlineStr"/>
       <c r="G1263" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -58643,8 +58589,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1264" t="inlineStr"/>
-      <c r="F1264" t="inlineStr"/>
       <c r="G1264" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -58691,8 +58635,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1265" t="inlineStr"/>
-      <c r="F1265" t="inlineStr"/>
       <c r="G1265" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -58739,8 +58681,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1266" t="inlineStr"/>
-      <c r="F1266" t="inlineStr"/>
       <c r="G1266" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -58787,8 +58727,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1267" t="inlineStr"/>
-      <c r="F1267" t="inlineStr"/>
       <c r="G1267" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -58809,6 +58747,2262 @@
         <v>0</v>
       </c>
       <c r="L1267" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>Daejeon Hana Citizen vs Kyoto Sanga</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>Daejeon Hana Citizen</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1268" t="inlineStr"/>
+      <c r="F1268" t="inlineStr"/>
+      <c r="G1268" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1268" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1268" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1268" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1268" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1268" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>Kashima Antlers vs Newcastle Jets</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>Kashima Antlers</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1269" t="inlineStr"/>
+      <c r="F1269" t="inlineStr"/>
+      <c r="G1269" t="inlineStr">
+        <is>
+          <t>7-1</t>
+        </is>
+      </c>
+      <c r="H1269" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1269" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1269" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1269" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1269" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>Beijing Guoan vs Pohang Steelers</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>Beijing Guoan</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1270" t="inlineStr"/>
+      <c r="F1270" t="inlineStr"/>
+      <c r="G1270" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1270" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1270" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1270" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1270" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1270" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>Johor Darul Ta'zim vs Buriram United</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>Johor Darul Ta'zim</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1271" t="inlineStr"/>
+      <c r="F1271" t="inlineStr"/>
+      <c r="G1271" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1271" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1271" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1271" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1271" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1271" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>Al Ain vs Al Nassr</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>Al Nassr</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1272" t="inlineStr"/>
+      <c r="F1272" t="inlineStr"/>
+      <c r="G1272" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H1272" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1272" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1272" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1272" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1272" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>Genoa vs Sudtirol</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>Genoa</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1273" t="inlineStr"/>
+      <c r="F1273" t="inlineStr"/>
+      <c r="G1273" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1273" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1273" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1273" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1273" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1273" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano vs Espanyol</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1274" t="inlineStr"/>
+      <c r="F1274" t="inlineStr"/>
+      <c r="G1274" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1274" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1274" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1274" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1274" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1274" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>Alavés vs Valencia</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>Alavés</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1275" t="inlineStr"/>
+      <c r="F1275" t="inlineStr"/>
+      <c r="G1275" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1275" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1275" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1275" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1275" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1275" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>Ajax Amsterdam vs Willem II</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>Ajax Amsterdam</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1276" t="inlineStr"/>
+      <c r="F1276" t="inlineStr"/>
+      <c r="G1276" t="inlineStr">
+        <is>
+          <t>5-1</t>
+        </is>
+      </c>
+      <c r="H1276" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1276" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1276" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1276" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1276" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>York City vs Newcastle United U21</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>York City</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1277" t="inlineStr"/>
+      <c r="F1277" t="inlineStr"/>
+      <c r="G1277" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H1277" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1277" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1277" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1277" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1277" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>Chesterfield vs Manchester City U21</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1278" t="inlineStr"/>
+      <c r="F1278" t="inlineStr"/>
+      <c r="G1278" t="inlineStr">
+        <is>
+          <t>5-3</t>
+        </is>
+      </c>
+      <c r="H1278" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1278" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1278" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1278" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1278" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>Wycombe Wanderers vs Chelsea U21</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>Wycombe Wanderers</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1279" t="inlineStr"/>
+      <c r="F1279" t="inlineStr"/>
+      <c r="G1279" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1279" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1279" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1279" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1279" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1279" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>Swindon Town vs Crystal Palace U21</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>Swindon Town</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1280" t="inlineStr"/>
+      <c r="F1280" t="inlineStr"/>
+      <c r="G1280" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1280" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1280" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1280" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1280" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1280" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>Leyton Orient vs Arsenal U21</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>Leyton Orient</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1281" t="inlineStr"/>
+      <c r="F1281" t="inlineStr"/>
+      <c r="G1281" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1281" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1281" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1281" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1281" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1281" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>Peterborough United vs Barnsley</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>Peterborough United</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1282" t="inlineStr"/>
+      <c r="F1282" t="inlineStr"/>
+      <c r="G1282" t="inlineStr">
+        <is>
+          <t>3-3</t>
+        </is>
+      </c>
+      <c r="H1282" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1282" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1282" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1282" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1282" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>Bristol City vs Lincoln City</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>Bristol City</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1283" t="inlineStr"/>
+      <c r="F1283" t="inlineStr"/>
+      <c r="G1283" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1283" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1283" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1283" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1283" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1283" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>Middlesbrough vs Millwall</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1284" t="inlineStr"/>
+      <c r="F1284" t="inlineStr"/>
+      <c r="G1284" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1284" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1284" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1284" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1284" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1284" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>Stenhousemuir vs Partick Thistle</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>Partick Thistle</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1285" t="inlineStr"/>
+      <c r="F1285" t="inlineStr"/>
+      <c r="G1285" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1285" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1285" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1285" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1285" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1285" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>Falkirk vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1286" t="inlineStr"/>
+      <c r="F1286" t="inlineStr"/>
+      <c r="G1286" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1286" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1286" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1286" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1286" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1286" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>Hibernian vs Kilmarnock</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1287" t="inlineStr"/>
+      <c r="F1287" t="inlineStr"/>
+      <c r="G1287" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1287" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1287" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1287" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1287" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1287" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>Motherwell vs Aberdeen</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>Motherwell</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1288" t="inlineStr"/>
+      <c r="F1288" t="inlineStr"/>
+      <c r="G1288" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="H1288" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1288" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1288" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1288" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1288" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>West Ham United vs Fulham</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>Fulham</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1289" t="inlineStr"/>
+      <c r="F1289" t="inlineStr"/>
+      <c r="G1289" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H1289" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1289" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1289" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1289" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1289" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>Aldershot Town vs Yeovil Town</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>Aldershot Town</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1290" t="inlineStr"/>
+      <c r="F1290" t="inlineStr"/>
+      <c r="G1290" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1290" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1290" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1290" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1290" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1290" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>Boston United vs Woking</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>Boston United</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1291" t="inlineStr"/>
+      <c r="F1291" t="inlineStr"/>
+      <c r="G1291" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1291" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1291" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1291" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1291" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1291" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>Carlisle United vs Forest Green Rovers</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>Carlisle United</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1292" t="inlineStr"/>
+      <c r="F1292" t="inlineStr"/>
+      <c r="G1292" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1292" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1292" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1292" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1292" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1292" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>Harrogate Town vs AFC Fylde</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>Harrogate Town</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1293" t="inlineStr"/>
+      <c r="F1293" t="inlineStr"/>
+      <c r="G1293" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1293" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1293" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1293" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1293" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1293" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>Solihull Moors vs Barrow</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>Barrow</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1294" t="inlineStr"/>
+      <c r="F1294" t="inlineStr"/>
+      <c r="G1294" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1294" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1294" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1294" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1294" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1294" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>Southend United vs Tamworth</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>Southend United</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1295" t="inlineStr"/>
+      <c r="F1295" t="inlineStr"/>
+      <c r="G1295" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1295" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1295" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1295" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1295" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1295" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>Sutton United vs Eastleigh</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>Sutton United</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1296" t="inlineStr"/>
+      <c r="F1296" t="inlineStr"/>
+      <c r="G1296" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1296" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1296" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1296" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1296" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1296" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>Wealdstone vs FC Halifax Town</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>Wealdstone</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1297" t="inlineStr"/>
+      <c r="F1297" t="inlineStr"/>
+      <c r="G1297" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1297" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1297" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1297" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1297" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1297" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>Worthing vs AFC Hornchurch</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>Worthing</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1298" t="inlineStr"/>
+      <c r="F1298" t="inlineStr"/>
+      <c r="G1298" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1298" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1298" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1298" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1298" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1298" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>Ipswich Town vs Arsenal</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1299" t="inlineStr"/>
+      <c r="F1299" t="inlineStr"/>
+      <c r="G1299" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="H1299" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1299" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1299" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1299" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1299" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>Liverpool vs Tottenham Hotspur</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1300" t="inlineStr"/>
+      <c r="F1300" t="inlineStr"/>
+      <c r="G1300" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1300" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1300" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1300" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1300" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1300" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>Reading vs Brentford</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>Brentford</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1301" t="inlineStr"/>
+      <c r="F1301" t="inlineStr"/>
+      <c r="G1301" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1301" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1301" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1301" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1301" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1301" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>Fiorentina vs Pisa</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>Fiorentina</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1302" t="inlineStr"/>
+      <c r="F1302" t="inlineStr"/>
+      <c r="G1302" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1302" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1302" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1302" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1302" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1302" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>Real Oruro vs Real Potosí</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>Real Potosí</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1303" t="inlineStr"/>
+      <c r="F1303" t="inlineStr"/>
+      <c r="G1303" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1303" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1303" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1303" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1303" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1303" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>Elche vs Real Madrid</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1304" t="inlineStr"/>
+      <c r="F1304" t="inlineStr"/>
+      <c r="G1304" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H1304" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1304" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1304" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1304" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1304" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>ABB vs The Strongest</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>The Strongest</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1305" t="inlineStr"/>
+      <c r="F1305" t="inlineStr"/>
+      <c r="G1305" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1305" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1305" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1305" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1305" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1305" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>Vasco da Gama vs Independiente Santa Fe</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1306" t="inlineStr"/>
+      <c r="F1306" t="inlineStr"/>
+      <c r="G1306" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1306" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1306" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1306" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1306" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1306" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>Londrina vs Ponte Preta</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>Londrina</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1307" t="inlineStr"/>
+      <c r="F1307" t="inlineStr"/>
+      <c r="G1307" t="inlineStr">
+        <is>
+          <t>6-0</t>
+        </is>
+      </c>
+      <c r="H1307" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1307" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1307" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1307" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1307" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>Náutico vs Operário PR</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1308" t="inlineStr"/>
+      <c r="F1308" t="inlineStr"/>
+      <c r="G1308" t="inlineStr">
+        <is>
+          <t>3-3</t>
+        </is>
+      </c>
+      <c r="H1308" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1308" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1308" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1308" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1308" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>Indy Eleven vs Brooklyn FC</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>Indy Eleven</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1309" t="inlineStr"/>
+      <c r="F1309" t="inlineStr"/>
+      <c r="G1309" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H1309" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1309" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1309" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1309" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1309" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>CRB vs Sport</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1310" t="inlineStr"/>
+      <c r="F1310" t="inlineStr"/>
+      <c r="G1310" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1310" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1310" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1310" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1310" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1310" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>São Paulo vs Boca Juniors</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1311" t="inlineStr"/>
+      <c r="F1311" t="inlineStr"/>
+      <c r="G1311" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1311" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1311" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1311" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1311" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1311" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>Boyacá Chicó FC vs Alianza FC</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>Boyacá Chicó FC</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1312" t="inlineStr"/>
+      <c r="F1312" t="inlineStr"/>
+      <c r="G1312" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1312" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1312" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1312" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1312" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1312" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>Puebla vs Toluca</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>Toluca</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1313" t="inlineStr"/>
+      <c r="F1313" t="inlineStr"/>
+      <c r="G1313" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1313" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1313" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1313" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1313" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1313" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>Dorados de Sinaloa vs Cancún FC</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>Dorados de Sinaloa</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1314" t="inlineStr"/>
+      <c r="F1314" t="inlineStr"/>
+      <c r="G1314" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1314" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1314" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1314" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1314" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1314" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -58825,7 +61019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59478,6 +61672,25 @@
       </c>
       <c r="E35" t="n">
         <v>31</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>47</v>
+      </c>
+      <c r="C36" t="n">
+        <v>32</v>
+      </c>
+      <c r="D36" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="E36" t="n">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -59491,7 +61704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E167"/>
+  <dimension ref="A1:E175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63007,6 +65220,174 @@
         <v>0</v>
       </c>
     </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>4</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0</v>
+      </c>
+      <c r="E168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>8</v>
+      </c>
+      <c r="D169" t="n">
+        <v>2</v>
+      </c>
+      <c r="E169" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>6</v>
+      </c>
+      <c r="D170" t="n">
+        <v>1</v>
+      </c>
+      <c r="E170" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>5</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>7</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0</v>
+      </c>
+      <c r="E172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>gol_de_cierre</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>2</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0</v>
+      </c>
+      <c r="E173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>4</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>1</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1314"/>
+  <dimension ref="A1:L1371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58773,8 +58773,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1268" t="inlineStr"/>
-      <c r="F1268" t="inlineStr"/>
       <c r="G1268" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -58821,8 +58819,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1269" t="inlineStr"/>
-      <c r="F1269" t="inlineStr"/>
       <c r="G1269" t="inlineStr">
         <is>
           <t>7-1</t>
@@ -58869,8 +58865,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1270" t="inlineStr"/>
-      <c r="F1270" t="inlineStr"/>
       <c r="G1270" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -58917,8 +58911,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1271" t="inlineStr"/>
-      <c r="F1271" t="inlineStr"/>
       <c r="G1271" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -58965,8 +58957,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1272" t="inlineStr"/>
-      <c r="F1272" t="inlineStr"/>
       <c r="G1272" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -59013,8 +59003,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1273" t="inlineStr"/>
-      <c r="F1273" t="inlineStr"/>
       <c r="G1273" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -59061,8 +59049,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1274" t="inlineStr"/>
-      <c r="F1274" t="inlineStr"/>
       <c r="G1274" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -59109,8 +59095,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1275" t="inlineStr"/>
-      <c r="F1275" t="inlineStr"/>
       <c r="G1275" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -59157,8 +59141,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1276" t="inlineStr"/>
-      <c r="F1276" t="inlineStr"/>
       <c r="G1276" t="inlineStr">
         <is>
           <t>5-1</t>
@@ -59205,8 +59187,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1277" t="inlineStr"/>
-      <c r="F1277" t="inlineStr"/>
       <c r="G1277" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -59253,8 +59233,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1278" t="inlineStr"/>
-      <c r="F1278" t="inlineStr"/>
       <c r="G1278" t="inlineStr">
         <is>
           <t>5-3</t>
@@ -59301,8 +59279,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1279" t="inlineStr"/>
-      <c r="F1279" t="inlineStr"/>
       <c r="G1279" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -59349,8 +59325,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1280" t="inlineStr"/>
-      <c r="F1280" t="inlineStr"/>
       <c r="G1280" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -59397,8 +59371,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1281" t="inlineStr"/>
-      <c r="F1281" t="inlineStr"/>
       <c r="G1281" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -59445,8 +59417,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1282" t="inlineStr"/>
-      <c r="F1282" t="inlineStr"/>
       <c r="G1282" t="inlineStr">
         <is>
           <t>3-3</t>
@@ -59493,8 +59463,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1283" t="inlineStr"/>
-      <c r="F1283" t="inlineStr"/>
       <c r="G1283" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -59541,8 +59509,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1284" t="inlineStr"/>
-      <c r="F1284" t="inlineStr"/>
       <c r="G1284" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -59589,8 +59555,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1285" t="inlineStr"/>
-      <c r="F1285" t="inlineStr"/>
       <c r="G1285" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -59637,8 +59601,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1286" t="inlineStr"/>
-      <c r="F1286" t="inlineStr"/>
       <c r="G1286" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -59685,8 +59647,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1287" t="inlineStr"/>
-      <c r="F1287" t="inlineStr"/>
       <c r="G1287" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -59733,8 +59693,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1288" t="inlineStr"/>
-      <c r="F1288" t="inlineStr"/>
       <c r="G1288" t="inlineStr">
         <is>
           <t>0-4</t>
@@ -59781,8 +59739,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1289" t="inlineStr"/>
-      <c r="F1289" t="inlineStr"/>
       <c r="G1289" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -59829,8 +59785,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1290" t="inlineStr"/>
-      <c r="F1290" t="inlineStr"/>
       <c r="G1290" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -59877,8 +59831,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1291" t="inlineStr"/>
-      <c r="F1291" t="inlineStr"/>
       <c r="G1291" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -59925,8 +59877,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1292" t="inlineStr"/>
-      <c r="F1292" t="inlineStr"/>
       <c r="G1292" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -59973,8 +59923,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1293" t="inlineStr"/>
-      <c r="F1293" t="inlineStr"/>
       <c r="G1293" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -60021,8 +59969,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1294" t="inlineStr"/>
-      <c r="F1294" t="inlineStr"/>
       <c r="G1294" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -60069,8 +60015,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1295" t="inlineStr"/>
-      <c r="F1295" t="inlineStr"/>
       <c r="G1295" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -60117,8 +60061,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1296" t="inlineStr"/>
-      <c r="F1296" t="inlineStr"/>
       <c r="G1296" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -60165,8 +60107,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1297" t="inlineStr"/>
-      <c r="F1297" t="inlineStr"/>
       <c r="G1297" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -60213,8 +60153,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1298" t="inlineStr"/>
-      <c r="F1298" t="inlineStr"/>
       <c r="G1298" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -60261,8 +60199,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1299" t="inlineStr"/>
-      <c r="F1299" t="inlineStr"/>
       <c r="G1299" t="inlineStr">
         <is>
           <t>2-4</t>
@@ -60309,8 +60245,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1300" t="inlineStr"/>
-      <c r="F1300" t="inlineStr"/>
       <c r="G1300" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -60357,8 +60291,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1301" t="inlineStr"/>
-      <c r="F1301" t="inlineStr"/>
       <c r="G1301" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -60405,8 +60337,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1302" t="inlineStr"/>
-      <c r="F1302" t="inlineStr"/>
       <c r="G1302" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -60453,8 +60383,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1303" t="inlineStr"/>
-      <c r="F1303" t="inlineStr"/>
       <c r="G1303" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -60501,8 +60429,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1304" t="inlineStr"/>
-      <c r="F1304" t="inlineStr"/>
       <c r="G1304" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -60549,8 +60475,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1305" t="inlineStr"/>
-      <c r="F1305" t="inlineStr"/>
       <c r="G1305" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -60597,8 +60521,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1306" t="inlineStr"/>
-      <c r="F1306" t="inlineStr"/>
       <c r="G1306" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -60645,8 +60567,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1307" t="inlineStr"/>
-      <c r="F1307" t="inlineStr"/>
       <c r="G1307" t="inlineStr">
         <is>
           <t>6-0</t>
@@ -60693,8 +60613,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1308" t="inlineStr"/>
-      <c r="F1308" t="inlineStr"/>
       <c r="G1308" t="inlineStr">
         <is>
           <t>3-3</t>
@@ -60741,8 +60659,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1309" t="inlineStr"/>
-      <c r="F1309" t="inlineStr"/>
       <c r="G1309" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -60789,8 +60705,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1310" t="inlineStr"/>
-      <c r="F1310" t="inlineStr"/>
       <c r="G1310" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -60837,8 +60751,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1311" t="inlineStr"/>
-      <c r="F1311" t="inlineStr"/>
       <c r="G1311" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -60885,8 +60797,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1312" t="inlineStr"/>
-      <c r="F1312" t="inlineStr"/>
       <c r="G1312" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -60933,8 +60843,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1313" t="inlineStr"/>
-      <c r="F1313" t="inlineStr"/>
       <c r="G1313" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -60981,8 +60889,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1314" t="inlineStr"/>
-      <c r="F1314" t="inlineStr"/>
       <c r="G1314" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -61003,6 +60909,2742 @@
         <v>0</v>
       </c>
       <c r="L1314" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>Jeonbuk Motors vs Kashiwa Reysol</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>Kashiwa Reysol</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1315" t="inlineStr"/>
+      <c r="F1315" t="inlineStr"/>
+      <c r="G1315" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1315" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1315" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1315" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1315" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1315" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>FC Seoul vs Persib</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>FC Seoul</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr"/>
+      <c r="F1316" t="inlineStr"/>
+      <c r="G1316" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1316" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1316" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1316" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1316" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1316" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>Port FC vs Vissel Kobe</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>Vissel Kobe</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr"/>
+      <c r="F1317" t="inlineStr"/>
+      <c r="G1317" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1317" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1317" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1317" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1317" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1317" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>Viettel vs Melbourne Victory</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>Melbourne Victory</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1318" t="inlineStr"/>
+      <c r="F1318" t="inlineStr"/>
+      <c r="G1318" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1318" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1318" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1318" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1318" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1318" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>Greenville Triumph vs Corpus Christi FC</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>Greenville Triumph</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1319" t="inlineStr"/>
+      <c r="F1319" t="inlineStr"/>
+      <c r="G1319" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1319" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1319" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1319" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1319" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1319" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>Spartak Moscow vs Fakel Voronezh</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>Spartak Moscow</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr"/>
+      <c r="F1320" t="inlineStr"/>
+      <c r="G1320" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1320" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1320" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1320" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1320" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1320" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>Al Hussein vs SC East Bengal</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>Al Hussein</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr"/>
+      <c r="F1321" t="inlineStr"/>
+      <c r="G1321" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1321" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1321" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1321" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1321" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1321" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>Khaldiya vs Nasaf Qarshi</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>Khaldiya</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1322" t="inlineStr"/>
+      <c r="F1322" t="inlineStr"/>
+      <c r="G1322" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1322" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1322" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1322" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1322" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1322" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>Al-Nahda Muscat Club vs Al Taawoun</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>Al Taawoun</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1323" t="inlineStr"/>
+      <c r="F1323" t="inlineStr"/>
+      <c r="G1323" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1323" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1323" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1323" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1323" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1323" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>Omonia Nicosia vs Celta Vigo</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1324" t="inlineStr"/>
+      <c r="F1324" t="inlineStr"/>
+      <c r="G1324" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1324" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1324" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1324" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1324" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1324" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>Atlético Madrid vs Osasuna</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>Atlético Madrid</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1325" t="inlineStr"/>
+      <c r="F1325" t="inlineStr"/>
+      <c r="G1325" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H1325" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1325" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1325" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1325" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1325" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>Deportivo vs Sevilla</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>Deportivo</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1326" t="inlineStr"/>
+      <c r="F1326" t="inlineStr"/>
+      <c r="G1326" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1326" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1326" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1326" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1326" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1326" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>AIK vs Mjällby AIF</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>AIK</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1327" t="inlineStr"/>
+      <c r="F1327" t="inlineStr"/>
+      <c r="G1327" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1327" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1327" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1327" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1327" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1327" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>Union Omaha vs Spokane Velocity FC</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>Union Omaha</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1328" t="inlineStr"/>
+      <c r="F1328" t="inlineStr"/>
+      <c r="G1328" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1328" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1328" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1328" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1328" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1328" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>FC Baltika Kaliningrad vs Zenit St Petersburg</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>Zenit St Petersburg</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1329" t="inlineStr"/>
+      <c r="F1329" t="inlineStr"/>
+      <c r="G1329" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H1329" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1329" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1329" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1329" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1329" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>Lokomotiv Moscow vs Krylia Sovetov</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>Lokomotiv Moscow</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1330" t="inlineStr"/>
+      <c r="F1330" t="inlineStr"/>
+      <c r="G1330" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1330" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1330" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1330" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1330" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1330" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>San Martín (San Juan) vs Tristán Suárez</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>San Martín (San Juan)</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1331" t="inlineStr"/>
+      <c r="F1331" t="inlineStr"/>
+      <c r="G1331" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1331" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1331" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1331" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1331" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1331" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>Al Rayyan vs Al-Faisaly</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>Al Rayyan</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1332" t="inlineStr"/>
+      <c r="F1332" t="inlineStr"/>
+      <c r="G1332" t="inlineStr">
+        <is>
+          <t>4-3</t>
+        </is>
+      </c>
+      <c r="H1332" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1332" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1332" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1332" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1332" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>Everton vs Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1333" t="inlineStr"/>
+      <c r="F1333" t="inlineStr"/>
+      <c r="G1333" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1333" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1333" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1333" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1333" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1333" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>Fleetwood Town vs Sheffield United</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>Sheffield United</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1334" t="inlineStr"/>
+      <c r="F1334" t="inlineStr"/>
+      <c r="G1334" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1334" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1334" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1334" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1334" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1334" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>Altrincham vs Hartlepool United</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>Altrincham</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1335" t="inlineStr"/>
+      <c r="F1335" t="inlineStr"/>
+      <c r="G1335" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1335" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1335" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1335" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1335" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1335" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>Kidderminster Harriers vs Gateshead</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>Kidderminster Harriers</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1336" t="inlineStr"/>
+      <c r="F1336" t="inlineStr"/>
+      <c r="G1336" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1336" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1336" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1336" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1336" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1336" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>Scunthorpe United vs Boreham Wood</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>Boreham Wood</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1337" t="inlineStr"/>
+      <c r="F1337" t="inlineStr"/>
+      <c r="G1337" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1337" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1337" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1337" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1337" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1337" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>AC Milan vs Benfica</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1338" t="inlineStr"/>
+      <c r="F1338" t="inlineStr"/>
+      <c r="G1338" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1338" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1338" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1338" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1338" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1338" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>Anderlecht vs Lyon</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1339" t="inlineStr"/>
+      <c r="F1339" t="inlineStr"/>
+      <c r="G1339" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1339" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1339" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1339" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1339" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1339" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen vs NK Celje</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1340" t="inlineStr"/>
+      <c r="F1340" t="inlineStr"/>
+      <c r="G1340" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1340" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1340" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1340" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1340" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1340" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>Hapoel Be'er vs Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>Dinamo Zagreb</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1341" t="inlineStr"/>
+      <c r="F1341" t="inlineStr"/>
+      <c r="G1341" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1341" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1341" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1341" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1341" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1341" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>Olympiacos vs Jagiellonia Bialystok</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>Olympiacos</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1342" t="inlineStr"/>
+      <c r="F1342" t="inlineStr"/>
+      <c r="G1342" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1342" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1342" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1342" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1342" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1342" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>SK Sturm Graz vs Stade Rennais</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>Stade Rennais</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1343" t="inlineStr"/>
+      <c r="F1343" t="inlineStr"/>
+      <c r="G1343" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1343" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1343" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1343" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1343" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1343" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>Sunderland vs AZ Alkmaar</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>Sunderland</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1344" t="inlineStr"/>
+      <c r="F1344" t="inlineStr"/>
+      <c r="G1344" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1344" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1344" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1344" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1344" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1344" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>Guabirá vs Aurora</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>Guabirá</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1345" t="inlineStr"/>
+      <c r="F1345" t="inlineStr"/>
+      <c r="G1345" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1345" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1345" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1345" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1345" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1345" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>Coventry City vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>Aston Villa</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1346" t="inlineStr"/>
+      <c r="F1346" t="inlineStr"/>
+      <c r="G1346" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H1346" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1346" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1346" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1346" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1346" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>Manchester United vs Brighton &amp; Hove Albion</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1347" t="inlineStr"/>
+      <c r="F1347" t="inlineStr"/>
+      <c r="G1347" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H1347" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1347" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1347" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1347" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1347" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>Barcelona vs Racing Santander</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1348" t="inlineStr"/>
+      <c r="F1348" t="inlineStr"/>
+      <c r="G1348" t="inlineStr">
+        <is>
+          <t>7-2</t>
+        </is>
+      </c>
+      <c r="H1348" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1348" t="n">
+        <v>8</v>
+      </c>
+      <c r="J1348" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1348" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1348" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>Levante vs Athletic Club</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1349" t="inlineStr"/>
+      <c r="F1349" t="inlineStr"/>
+      <c r="G1349" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1349" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1349" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1349" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1349" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1349" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>Portuguesa vs Estudiantes de Mérida</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>Portuguesa</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1350" t="inlineStr"/>
+      <c r="F1350" t="inlineStr"/>
+      <c r="G1350" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1350" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1350" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1350" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1350" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1350" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>Atlético-MG vs Santos</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>Atlético-MG</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1351" t="inlineStr"/>
+      <c r="F1351" t="inlineStr"/>
+      <c r="G1351" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="H1351" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1351" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1351" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1351" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1351" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia vs Atlético Tucumán</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1352" t="inlineStr"/>
+      <c r="F1352" t="inlineStr"/>
+      <c r="G1352" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1352" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1352" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1352" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1352" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1352" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>Nacional Potosí vs Always Ready</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>Always Ready</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1353" t="inlineStr"/>
+      <c r="F1353" t="inlineStr"/>
+      <c r="G1353" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="H1353" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1353" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1353" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1353" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1353" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>Hartford Athletic vs Sporting JAX</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>Hartford Athletic</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1354" t="inlineStr"/>
+      <c r="F1354" t="inlineStr"/>
+      <c r="G1354" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1354" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1354" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1354" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1354" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1354" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>Monagas SC vs Zamora FC</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>Monagas SC</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1355" t="inlineStr"/>
+      <c r="F1355" t="inlineStr"/>
+      <c r="G1355" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1355" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1355" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1355" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1355" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1355" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>Botafogo vs Grêmio</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>Botafogo</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1356" t="inlineStr"/>
+      <c r="F1356" t="inlineStr"/>
+      <c r="G1356" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1356" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1356" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1356" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1356" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1356" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>Columbus Crew vs Orlando City SC</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>Columbus Crew</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1357" t="inlineStr"/>
+      <c r="F1357" t="inlineStr"/>
+      <c r="G1357" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1357" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1357" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1357" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1357" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1357" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>Trujillanos vs Rayo Zuliano</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>Trujillanos</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1358" t="inlineStr"/>
+      <c r="F1358" t="inlineStr"/>
+      <c r="G1358" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="H1358" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1358" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1358" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1358" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1358" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>Westchester SC vs Richmond Kickers</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>Westchester SC</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1359" t="inlineStr"/>
+      <c r="F1359" t="inlineStr"/>
+      <c r="G1359" t="inlineStr">
+        <is>
+          <t>5-2</t>
+        </is>
+      </c>
+      <c r="H1359" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1359" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1359" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1359" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1359" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>Once Caldas vs Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1360" t="inlineStr"/>
+      <c r="F1360" t="inlineStr"/>
+      <c r="G1360" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1360" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1360" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1360" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1360" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1360" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>Metropolitanos vs Caracas FC</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>Metropolitanos</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1361" t="inlineStr"/>
+      <c r="F1361" t="inlineStr"/>
+      <c r="G1361" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1361" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1361" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1361" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1361" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1361" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>Fort Wayne vs One Knoxville</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>Fort Wayne</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1362" t="inlineStr"/>
+      <c r="F1362" t="inlineStr"/>
+      <c r="G1362" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H1362" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1362" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1362" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1362" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1362" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>Corinthians vs Estudiantes de La Plata</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1363" t="inlineStr"/>
+      <c r="F1363" t="inlineStr"/>
+      <c r="G1363" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1363" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1363" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1363" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1363" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1363" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>Blooming vs Universitario de Vinto</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>Blooming</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1364" t="inlineStr"/>
+      <c r="F1364" t="inlineStr"/>
+      <c r="G1364" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1364" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1364" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1364" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1364" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1364" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>Birmingham Legion FC vs New Mexico United</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>Birmingham Legion FC</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1365" t="inlineStr"/>
+      <c r="F1365" t="inlineStr"/>
+      <c r="G1365" t="inlineStr">
+        <is>
+          <t>4-4</t>
+        </is>
+      </c>
+      <c r="H1365" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1365" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1365" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1365" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1365" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>Cartaginés vs Saprissa</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>Cartaginés</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1366" t="inlineStr"/>
+      <c r="F1366" t="inlineStr"/>
+      <c r="G1366" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1366" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1366" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1366" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1366" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1366" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>Internacional Santa Tecla vs CD FAS</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>CD FAS</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1367" t="inlineStr"/>
+      <c r="F1367" t="inlineStr"/>
+      <c r="G1367" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1367" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1367" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1367" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1367" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1367" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>Athletic Club Boise vs Charlotte Independence</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>Athletic Club Boise</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1368" t="inlineStr"/>
+      <c r="F1368" t="inlineStr"/>
+      <c r="G1368" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1368" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1368" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1368" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1368" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1368" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>Internacional de Bogotá vs Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1369" t="inlineStr"/>
+      <c r="F1369" t="inlineStr"/>
+      <c r="G1369" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H1369" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1369" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1369" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1369" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1369" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>Colorado Rapids vs St. Louis CITY SC</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1370" t="inlineStr"/>
+      <c r="F1370" t="inlineStr"/>
+      <c r="G1370" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H1370" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1370" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1370" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1370" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1370" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>Alianza FC vs FC Motagua</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>FC Motagua</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1371" t="inlineStr"/>
+      <c r="F1371" t="inlineStr"/>
+      <c r="G1371" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1371" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1371" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1371" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1371" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1371" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -61019,7 +63661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61691,6 +64333,25 @@
       </c>
       <c r="E36" t="n">
         <v>47</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>57</v>
+      </c>
+      <c r="C37" t="n">
+        <v>43</v>
+      </c>
+      <c r="D37" t="n">
+        <v>75.40000000000001</v>
+      </c>
+      <c r="E37" t="n">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -61704,7 +64365,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E175"/>
+  <dimension ref="A1:E185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65388,6 +68049,216 @@
         <v>0</v>
       </c>
     </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>2</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>10</v>
+      </c>
+      <c r="D177" t="n">
+        <v>3</v>
+      </c>
+      <c r="E177" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>1</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>siguen_empatados_55</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>1</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0</v>
+      </c>
+      <c r="E179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>siguen_empatados_70</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>1</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>10</v>
+      </c>
+      <c r="D181" t="n">
+        <v>3</v>
+      </c>
+      <c r="E181" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>3</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>5</v>
+      </c>
+      <c r="D183" t="n">
+        <v>2</v>
+      </c>
+      <c r="E183" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>gol_de_cierre</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>1</v>
+      </c>
+      <c r="D184" t="n">
+        <v>1</v>
+      </c>
+      <c r="E184" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>3</v>
+      </c>
+      <c r="D185" t="n">
+        <v>2</v>
+      </c>
+      <c r="E185" t="n">
+        <v>66.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1371"/>
+  <dimension ref="A1:L1393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60935,8 +60935,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1315" t="inlineStr"/>
-      <c r="F1315" t="inlineStr"/>
       <c r="G1315" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -60983,8 +60981,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1316" t="inlineStr"/>
-      <c r="F1316" t="inlineStr"/>
       <c r="G1316" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -61031,8 +61027,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1317" t="inlineStr"/>
-      <c r="F1317" t="inlineStr"/>
       <c r="G1317" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -61079,8 +61073,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1318" t="inlineStr"/>
-      <c r="F1318" t="inlineStr"/>
       <c r="G1318" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -61127,8 +61119,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1319" t="inlineStr"/>
-      <c r="F1319" t="inlineStr"/>
       <c r="G1319" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -61175,8 +61165,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1320" t="inlineStr"/>
-      <c r="F1320" t="inlineStr"/>
       <c r="G1320" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -61223,8 +61211,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1321" t="inlineStr"/>
-      <c r="F1321" t="inlineStr"/>
       <c r="G1321" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -61271,8 +61257,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1322" t="inlineStr"/>
-      <c r="F1322" t="inlineStr"/>
       <c r="G1322" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -61319,8 +61303,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1323" t="inlineStr"/>
-      <c r="F1323" t="inlineStr"/>
       <c r="G1323" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -61367,8 +61349,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1324" t="inlineStr"/>
-      <c r="F1324" t="inlineStr"/>
       <c r="G1324" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -61415,8 +61395,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1325" t="inlineStr"/>
-      <c r="F1325" t="inlineStr"/>
       <c r="G1325" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -61463,8 +61441,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1326" t="inlineStr"/>
-      <c r="F1326" t="inlineStr"/>
       <c r="G1326" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -61511,8 +61487,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1327" t="inlineStr"/>
-      <c r="F1327" t="inlineStr"/>
       <c r="G1327" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -61559,8 +61533,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1328" t="inlineStr"/>
-      <c r="F1328" t="inlineStr"/>
       <c r="G1328" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -61607,8 +61579,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1329" t="inlineStr"/>
-      <c r="F1329" t="inlineStr"/>
       <c r="G1329" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -61655,8 +61625,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1330" t="inlineStr"/>
-      <c r="F1330" t="inlineStr"/>
       <c r="G1330" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -61703,8 +61671,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1331" t="inlineStr"/>
-      <c r="F1331" t="inlineStr"/>
       <c r="G1331" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -61751,8 +61717,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1332" t="inlineStr"/>
-      <c r="F1332" t="inlineStr"/>
       <c r="G1332" t="inlineStr">
         <is>
           <t>4-3</t>
@@ -61799,8 +61763,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1333" t="inlineStr"/>
-      <c r="F1333" t="inlineStr"/>
       <c r="G1333" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -61847,8 +61809,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1334" t="inlineStr"/>
-      <c r="F1334" t="inlineStr"/>
       <c r="G1334" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -61895,8 +61855,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1335" t="inlineStr"/>
-      <c r="F1335" t="inlineStr"/>
       <c r="G1335" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -61943,8 +61901,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1336" t="inlineStr"/>
-      <c r="F1336" t="inlineStr"/>
       <c r="G1336" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -61991,8 +61947,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1337" t="inlineStr"/>
-      <c r="F1337" t="inlineStr"/>
       <c r="G1337" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -62039,8 +61993,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1338" t="inlineStr"/>
-      <c r="F1338" t="inlineStr"/>
       <c r="G1338" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -62087,8 +62039,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1339" t="inlineStr"/>
-      <c r="F1339" t="inlineStr"/>
       <c r="G1339" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -62135,8 +62085,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1340" t="inlineStr"/>
-      <c r="F1340" t="inlineStr"/>
       <c r="G1340" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -62183,8 +62131,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1341" t="inlineStr"/>
-      <c r="F1341" t="inlineStr"/>
       <c r="G1341" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -62231,8 +62177,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1342" t="inlineStr"/>
-      <c r="F1342" t="inlineStr"/>
       <c r="G1342" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -62279,8 +62223,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1343" t="inlineStr"/>
-      <c r="F1343" t="inlineStr"/>
       <c r="G1343" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -62327,8 +62269,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1344" t="inlineStr"/>
-      <c r="F1344" t="inlineStr"/>
       <c r="G1344" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -62375,8 +62315,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1345" t="inlineStr"/>
-      <c r="F1345" t="inlineStr"/>
       <c r="G1345" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -62423,8 +62361,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1346" t="inlineStr"/>
-      <c r="F1346" t="inlineStr"/>
       <c r="G1346" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -62471,8 +62407,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1347" t="inlineStr"/>
-      <c r="F1347" t="inlineStr"/>
       <c r="G1347" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -62519,8 +62453,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1348" t="inlineStr"/>
-      <c r="F1348" t="inlineStr"/>
       <c r="G1348" t="inlineStr">
         <is>
           <t>7-2</t>
@@ -62567,8 +62499,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1349" t="inlineStr"/>
-      <c r="F1349" t="inlineStr"/>
       <c r="G1349" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -62615,8 +62545,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1350" t="inlineStr"/>
-      <c r="F1350" t="inlineStr"/>
       <c r="G1350" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -62663,8 +62591,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1351" t="inlineStr"/>
-      <c r="F1351" t="inlineStr"/>
       <c r="G1351" t="inlineStr">
         <is>
           <t>4-2</t>
@@ -62711,8 +62637,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1352" t="inlineStr"/>
-      <c r="F1352" t="inlineStr"/>
       <c r="G1352" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -62759,8 +62683,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1353" t="inlineStr"/>
-      <c r="F1353" t="inlineStr"/>
       <c r="G1353" t="inlineStr">
         <is>
           <t>0-4</t>
@@ -62807,8 +62729,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1354" t="inlineStr"/>
-      <c r="F1354" t="inlineStr"/>
       <c r="G1354" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -62855,8 +62775,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1355" t="inlineStr"/>
-      <c r="F1355" t="inlineStr"/>
       <c r="G1355" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -62903,8 +62821,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1356" t="inlineStr"/>
-      <c r="F1356" t="inlineStr"/>
       <c r="G1356" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -62951,8 +62867,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1357" t="inlineStr"/>
-      <c r="F1357" t="inlineStr"/>
       <c r="G1357" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -62999,8 +62913,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1358" t="inlineStr"/>
-      <c r="F1358" t="inlineStr"/>
       <c r="G1358" t="inlineStr">
         <is>
           <t>2-4</t>
@@ -63047,8 +62959,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1359" t="inlineStr"/>
-      <c r="F1359" t="inlineStr"/>
       <c r="G1359" t="inlineStr">
         <is>
           <t>5-2</t>
@@ -63095,8 +63005,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1360" t="inlineStr"/>
-      <c r="F1360" t="inlineStr"/>
       <c r="G1360" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -63143,8 +63051,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1361" t="inlineStr"/>
-      <c r="F1361" t="inlineStr"/>
       <c r="G1361" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -63191,8 +63097,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1362" t="inlineStr"/>
-      <c r="F1362" t="inlineStr"/>
       <c r="G1362" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -63239,8 +63143,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1363" t="inlineStr"/>
-      <c r="F1363" t="inlineStr"/>
       <c r="G1363" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -63287,8 +63189,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1364" t="inlineStr"/>
-      <c r="F1364" t="inlineStr"/>
       <c r="G1364" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -63335,8 +63235,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1365" t="inlineStr"/>
-      <c r="F1365" t="inlineStr"/>
       <c r="G1365" t="inlineStr">
         <is>
           <t>4-4</t>
@@ -63383,8 +63281,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1366" t="inlineStr"/>
-      <c r="F1366" t="inlineStr"/>
       <c r="G1366" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -63431,8 +63327,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1367" t="inlineStr"/>
-      <c r="F1367" t="inlineStr"/>
       <c r="G1367" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -63479,8 +63373,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1368" t="inlineStr"/>
-      <c r="F1368" t="inlineStr"/>
       <c r="G1368" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -63527,8 +63419,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1369" t="inlineStr"/>
-      <c r="F1369" t="inlineStr"/>
       <c r="G1369" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -63575,8 +63465,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1370" t="inlineStr"/>
-      <c r="F1370" t="inlineStr"/>
       <c r="G1370" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -63623,8 +63511,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1371" t="inlineStr"/>
-      <c r="F1371" t="inlineStr"/>
       <c r="G1371" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -63645,6 +63531,1062 @@
         <v>0</v>
       </c>
       <c r="L1371" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>Machida Zelvia vs Preah Khan Reach Svay Rieng FC</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>Machida Zelvia</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1372" t="inlineStr"/>
+      <c r="F1372" t="inlineStr"/>
+      <c r="G1372" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1372" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1372" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1372" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1372" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1372" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>Adelaide United vs Tai Po FC</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>Adelaide United</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1373" t="inlineStr"/>
+      <c r="F1373" t="inlineStr"/>
+      <c r="G1373" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1373" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1373" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1373" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1373" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1373" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>Kitchee vs Gangwon FC</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>Kitchee</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1374" t="inlineStr"/>
+      <c r="F1374" t="inlineStr"/>
+      <c r="G1374" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1374" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1374" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1374" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1374" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1374" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>Shanghai Shenhua vs BG Tampines Rovers FC</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>Shanghai Shenhua</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1375" t="inlineStr"/>
+      <c r="F1375" t="inlineStr"/>
+      <c r="G1375" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1375" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1375" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1375" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1375" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1375" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>Gazovik Orenburg vs Krasnodar</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>Krasnodar</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1376" t="inlineStr"/>
+      <c r="F1376" t="inlineStr"/>
+      <c r="G1376" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1376" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1376" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1376" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1376" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1376" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>Akron Tolyatti vs Akhmat Grozny</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>Akhmat Grozny</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1377" t="inlineStr"/>
+      <c r="F1377" t="inlineStr"/>
+      <c r="G1377" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1377" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1377" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1377" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1377" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1377" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>OFI Crete vs TSG Hoffenheim</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>TSG Hoffenheim</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1378" t="inlineStr"/>
+      <c r="F1378" t="inlineStr"/>
+      <c r="G1378" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1378" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1378" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1378" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1378" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1378" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>Real Betis vs Getafe</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1379" t="inlineStr"/>
+      <c r="F1379" t="inlineStr"/>
+      <c r="G1379" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1379" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1379" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1379" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1379" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1379" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>Orlando Pirates vs Durban City</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>Orlando Pirates</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1380" t="inlineStr"/>
+      <c r="F1380" t="inlineStr"/>
+      <c r="G1380" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1380" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1380" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1380" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1380" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1380" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>Dynamo Makhachkala vs CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>CSKA Moscow</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1381" t="inlineStr"/>
+      <c r="F1381" t="inlineStr"/>
+      <c r="G1381" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H1381" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1381" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1381" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1381" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1381" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>Manchester City vs Norwich City</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1382" t="inlineStr"/>
+      <c r="F1382" t="inlineStr"/>
+      <c r="G1382" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="H1382" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1382" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1382" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1382" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1382" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>Besiktas vs Marseille</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1383" t="inlineStr"/>
+      <c r="F1383" t="inlineStr"/>
+      <c r="G1383" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H1383" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1383" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1383" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1383" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1383" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>Celtic vs Ferencvaros</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1384" t="inlineStr"/>
+      <c r="F1384" t="inlineStr"/>
+      <c r="G1384" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H1384" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1384" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1384" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1384" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1384" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>Crystal Palace vs Lech Poznan</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>Crystal Palace</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1385" t="inlineStr"/>
+      <c r="F1385" t="inlineStr"/>
+      <c r="G1385" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H1385" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1385" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1385" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1385" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1385" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>Juventus vs NEC Nijmegen</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1386" t="inlineStr"/>
+      <c r="F1386" t="inlineStr"/>
+      <c r="G1386" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="H1386" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1386" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1386" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1386" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1386" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>Lillestrom vs Torreense</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>Lillestrom</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1387" t="inlineStr"/>
+      <c r="F1387" t="inlineStr"/>
+      <c r="G1387" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1387" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1387" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1387" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1387" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1387" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>Real Sociedad vs AFC Bournemouth</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>AFC Bournemouth</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1388" t="inlineStr"/>
+      <c r="F1388" t="inlineStr"/>
+      <c r="G1388" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1388" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1388" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1388" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1388" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1388" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>AFC Wimbledon vs Milton Keynes Dons</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>Milton Keynes Dons</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1389" t="inlineStr"/>
+      <c r="F1389" t="inlineStr"/>
+      <c r="G1389" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1389" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1389" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1389" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1389" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1389" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>Málaga vs Villarreal</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1390" t="inlineStr"/>
+      <c r="F1390" t="inlineStr"/>
+      <c r="G1390" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H1390" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1390" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1390" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1390" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1390" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1391" t="inlineStr"/>
+      <c r="F1391" t="inlineStr"/>
+      <c r="G1391" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1391" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1391" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1391" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1391" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1391" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1392" t="inlineStr"/>
+      <c r="F1392" t="inlineStr"/>
+      <c r="G1392" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1392" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1392" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1392" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1392" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1392" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>Flamengo vs Independiente del Valle</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1393" t="inlineStr"/>
+      <c r="F1393" t="inlineStr"/>
+      <c r="G1393" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1393" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1393" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1393" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1393" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1393" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -63661,7 +64603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64352,6 +65294,25 @@
       </c>
       <c r="E37" t="n">
         <v>57</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>22</v>
+      </c>
+      <c r="C38" t="n">
+        <v>16</v>
+      </c>
+      <c r="D38" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="E38" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -64365,7 +65326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E185"/>
+  <dimension ref="A1:E193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68259,6 +69220,174 @@
         <v>66.7</v>
       </c>
     </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>4</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>3</v>
+      </c>
+      <c r="D187" t="n">
+        <v>1</v>
+      </c>
+      <c r="E187" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>3</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>3</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0</v>
+      </c>
+      <c r="E189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>1</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>4</v>
+      </c>
+      <c r="D191" t="n">
+        <v>2</v>
+      </c>
+      <c r="E191" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>gol_de_cierre</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>1</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0</v>
+      </c>
+      <c r="E192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>1</v>
+      </c>
+      <c r="D193" t="n">
+        <v>1</v>
+      </c>
+      <c r="E193" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1393"/>
+  <dimension ref="A1:L1443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63557,8 +63557,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1372" t="inlineStr"/>
-      <c r="F1372" t="inlineStr"/>
       <c r="G1372" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -63605,8 +63603,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1373" t="inlineStr"/>
-      <c r="F1373" t="inlineStr"/>
       <c r="G1373" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -63653,8 +63649,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1374" t="inlineStr"/>
-      <c r="F1374" t="inlineStr"/>
       <c r="G1374" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -63701,8 +63695,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1375" t="inlineStr"/>
-      <c r="F1375" t="inlineStr"/>
       <c r="G1375" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -63749,8 +63741,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1376" t="inlineStr"/>
-      <c r="F1376" t="inlineStr"/>
       <c r="G1376" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -63797,8 +63787,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1377" t="inlineStr"/>
-      <c r="F1377" t="inlineStr"/>
       <c r="G1377" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -63845,8 +63833,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1378" t="inlineStr"/>
-      <c r="F1378" t="inlineStr"/>
       <c r="G1378" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -63893,8 +63879,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1379" t="inlineStr"/>
-      <c r="F1379" t="inlineStr"/>
       <c r="G1379" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -63941,8 +63925,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1380" t="inlineStr"/>
-      <c r="F1380" t="inlineStr"/>
       <c r="G1380" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -63989,8 +63971,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1381" t="inlineStr"/>
-      <c r="F1381" t="inlineStr"/>
       <c r="G1381" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -64037,8 +64017,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1382" t="inlineStr"/>
-      <c r="F1382" t="inlineStr"/>
       <c r="G1382" t="inlineStr">
         <is>
           <t>5-0</t>
@@ -64085,8 +64063,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1383" t="inlineStr"/>
-      <c r="F1383" t="inlineStr"/>
       <c r="G1383" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -64133,8 +64109,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1384" t="inlineStr"/>
-      <c r="F1384" t="inlineStr"/>
       <c r="G1384" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -64181,8 +64155,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1385" t="inlineStr"/>
-      <c r="F1385" t="inlineStr"/>
       <c r="G1385" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -64229,8 +64201,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1386" t="inlineStr"/>
-      <c r="F1386" t="inlineStr"/>
       <c r="G1386" t="inlineStr">
         <is>
           <t>5-0</t>
@@ -64277,8 +64247,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1387" t="inlineStr"/>
-      <c r="F1387" t="inlineStr"/>
       <c r="G1387" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -64325,8 +64293,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1388" t="inlineStr"/>
-      <c r="F1388" t="inlineStr"/>
       <c r="G1388" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -64373,8 +64339,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1389" t="inlineStr"/>
-      <c r="F1389" t="inlineStr"/>
       <c r="G1389" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -64421,8 +64385,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1390" t="inlineStr"/>
-      <c r="F1390" t="inlineStr"/>
       <c r="G1390" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -64469,8 +64431,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1391" t="inlineStr"/>
-      <c r="F1391" t="inlineStr"/>
       <c r="G1391" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -64517,8 +64477,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1392" t="inlineStr"/>
-      <c r="F1392" t="inlineStr"/>
       <c r="G1392" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -64565,8 +64523,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1393" t="inlineStr"/>
-      <c r="F1393" t="inlineStr"/>
       <c r="G1393" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -64587,6 +64543,2406 @@
         <v>0</v>
       </c>
       <c r="L1393" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>SpVgg Greuther Fürth vs 1. FC Magdeburg</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>1. FC Magdeburg</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1394" t="inlineStr"/>
+      <c r="F1394" t="inlineStr"/>
+      <c r="G1394" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1394" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1394" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1394" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1394" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1394" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>VfL Wolfsburg vs SV Darmstadt 98</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>VfL Wolfsburg</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1395" t="inlineStr"/>
+      <c r="F1395" t="inlineStr"/>
+      <c r="G1395" t="inlineStr">
+        <is>
+          <t>5-1</t>
+        </is>
+      </c>
+      <c r="H1395" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1395" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1395" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1395" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1395" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>Lyngby Boldklub vs Silkeborg IF</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>Lyngby Boldklub</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1396" t="inlineStr"/>
+      <c r="F1396" t="inlineStr"/>
+      <c r="G1396" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="H1396" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1396" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1396" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1396" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1396" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>Sarpsborg FK vs KFUM Oslo</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>Sarpsborg FK</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1397" t="inlineStr"/>
+      <c r="F1397" t="inlineStr"/>
+      <c r="G1397" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H1397" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1397" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1397" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1397" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1397" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>Kasimpasa vs Konyaspor</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>Kasimpasa</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1398" t="inlineStr"/>
+      <c r="F1398" t="inlineStr"/>
+      <c r="G1398" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1398" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1398" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1398" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1398" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1398" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>Rapid Vienna vs WSG Swarovski Tirol</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>Rapid Vienna</t>
+        </is>
+      </c>
+      <c r="D1399" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1399" t="inlineStr"/>
+      <c r="F1399" t="inlineStr"/>
+      <c r="G1399" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1399" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1399" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1399" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1399" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1399" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>FC Groningen vs PEC Zwolle</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>FC Groningen</t>
+        </is>
+      </c>
+      <c r="D1400" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1400" t="inlineStr"/>
+      <c r="F1400" t="inlineStr"/>
+      <c r="G1400" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1400" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1400" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1400" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1400" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1400" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>Comunicaciones vs Defensores Unidos</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>Comunicaciones</t>
+        </is>
+      </c>
+      <c r="D1401" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1401" t="inlineStr"/>
+      <c r="F1401" t="inlineStr"/>
+      <c r="G1401" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1401" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1401" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1401" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1401" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1401" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1402">
+      <c r="A1402" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1402" t="inlineStr">
+        <is>
+          <t>Annecy vs Dijon FCO</t>
+        </is>
+      </c>
+      <c r="C1402" t="inlineStr">
+        <is>
+          <t>Annecy</t>
+        </is>
+      </c>
+      <c r="D1402" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1402" t="inlineStr"/>
+      <c r="F1402" t="inlineStr"/>
+      <c r="G1402" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1402" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1402" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1402" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1402" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1402" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1403">
+      <c r="A1403" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1403" t="inlineStr">
+        <is>
+          <t>Grenoble vs Clermont Foot</t>
+        </is>
+      </c>
+      <c r="C1403" t="inlineStr">
+        <is>
+          <t>Grenoble</t>
+        </is>
+      </c>
+      <c r="D1403" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1403" t="inlineStr"/>
+      <c r="F1403" t="inlineStr"/>
+      <c r="G1403" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1403" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1403" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1403" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1403" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1403" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1404">
+      <c r="A1404" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1404" t="inlineStr">
+        <is>
+          <t>Stade Laval vs Sochaux</t>
+        </is>
+      </c>
+      <c r="C1404" t="inlineStr">
+        <is>
+          <t>Stade Laval</t>
+        </is>
+      </c>
+      <c r="D1404" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1404" t="inlineStr"/>
+      <c r="F1404" t="inlineStr"/>
+      <c r="G1404" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1404" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1404" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1404" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1404" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1404" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1405">
+      <c r="A1405" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1405" t="inlineStr">
+        <is>
+          <t>Pau vs Dunkerque</t>
+        </is>
+      </c>
+      <c r="C1405" t="inlineStr">
+        <is>
+          <t>Pau</t>
+        </is>
+      </c>
+      <c r="D1405" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1405" t="inlineStr"/>
+      <c r="F1405" t="inlineStr"/>
+      <c r="G1405" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1405" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1405" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1405" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1405" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1405" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1406">
+      <c r="A1406" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1406" t="inlineStr">
+        <is>
+          <t>Stade de Reims vs Montpellier</t>
+        </is>
+      </c>
+      <c r="C1406" t="inlineStr">
+        <is>
+          <t>Stade de Reims</t>
+        </is>
+      </c>
+      <c r="D1406" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1406" t="inlineStr"/>
+      <c r="F1406" t="inlineStr"/>
+      <c r="G1406" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1406" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1406" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1406" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1406" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1406" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1407">
+      <c r="A1407" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1407" t="inlineStr">
+        <is>
+          <t>Rodez Aveyron vs AS Nancy Lorraine</t>
+        </is>
+      </c>
+      <c r="C1407" t="inlineStr">
+        <is>
+          <t>Rodez Aveyron</t>
+        </is>
+      </c>
+      <c r="D1407" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1407" t="inlineStr"/>
+      <c r="F1407" t="inlineStr"/>
+      <c r="G1407" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="H1407" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1407" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1407" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1407" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1407" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1408">
+      <c r="A1408" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1408" t="inlineStr">
+        <is>
+          <t>Almere City vs Heracles Almelo</t>
+        </is>
+      </c>
+      <c r="C1408" t="inlineStr">
+        <is>
+          <t>Heracles Almelo</t>
+        </is>
+      </c>
+      <c r="D1408" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1408" t="inlineStr"/>
+      <c r="F1408" t="inlineStr"/>
+      <c r="G1408" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1408" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1408" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1408" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1408" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1408" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1409">
+      <c r="A1409" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1409" t="inlineStr">
+        <is>
+          <t>FC Den Bosch vs Helmond Sport</t>
+        </is>
+      </c>
+      <c r="C1409" t="inlineStr">
+        <is>
+          <t>FC Den Bosch</t>
+        </is>
+      </c>
+      <c r="D1409" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1409" t="inlineStr"/>
+      <c r="F1409" t="inlineStr"/>
+      <c r="G1409" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1409" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1409" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1409" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1409" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1409" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1410">
+      <c r="A1410" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1410" t="inlineStr">
+        <is>
+          <t>FC Eindhoven vs FC Emmen</t>
+        </is>
+      </c>
+      <c r="C1410" t="inlineStr">
+        <is>
+          <t>FC Emmen</t>
+        </is>
+      </c>
+      <c r="D1410" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1410" t="inlineStr"/>
+      <c r="F1410" t="inlineStr"/>
+      <c r="G1410" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1410" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1410" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1410" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1410" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1410" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1411">
+      <c r="A1411" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1411" t="inlineStr">
+        <is>
+          <t>Jong Ajax vs Roda JC Kerkrade</t>
+        </is>
+      </c>
+      <c r="C1411" t="inlineStr">
+        <is>
+          <t>Roda JC Kerkrade</t>
+        </is>
+      </c>
+      <c r="D1411" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1411" t="inlineStr"/>
+      <c r="F1411" t="inlineStr"/>
+      <c r="G1411" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1411" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1411" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1411" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1411" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1411" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1412">
+      <c r="A1412" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1412" t="inlineStr">
+        <is>
+          <t>Jong AZ vs FC Volendam</t>
+        </is>
+      </c>
+      <c r="C1412" t="inlineStr">
+        <is>
+          <t>FC Volendam</t>
+        </is>
+      </c>
+      <c r="D1412" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1412" t="inlineStr"/>
+      <c r="F1412" t="inlineStr"/>
+      <c r="G1412" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H1412" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1412" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1412" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1412" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1412" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1413">
+      <c r="A1413" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1413" t="inlineStr">
+        <is>
+          <t>Jong FC Utrecht vs VVV-Venlo</t>
+        </is>
+      </c>
+      <c r="C1413" t="inlineStr">
+        <is>
+          <t>Jong FC Utrecht</t>
+        </is>
+      </c>
+      <c r="D1413" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1413" t="inlineStr"/>
+      <c r="F1413" t="inlineStr"/>
+      <c r="G1413" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H1413" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1413" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1413" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1413" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1413" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1414">
+      <c r="A1414" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1414" t="inlineStr">
+        <is>
+          <t>RKC Waalwijk vs MVV Maastricht</t>
+        </is>
+      </c>
+      <c r="C1414" t="inlineStr">
+        <is>
+          <t>RKC Waalwijk</t>
+        </is>
+      </c>
+      <c r="D1414" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1414" t="inlineStr"/>
+      <c r="F1414" t="inlineStr"/>
+      <c r="G1414" t="inlineStr">
+        <is>
+          <t>6-1</t>
+        </is>
+      </c>
+      <c r="H1414" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1414" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1414" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1414" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1414" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1415">
+      <c r="A1415" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1415" t="inlineStr">
+        <is>
+          <t>Bayern Munich vs 1. FC Union Berlin</t>
+        </is>
+      </c>
+      <c r="C1415" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="D1415" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1415" t="inlineStr"/>
+      <c r="F1415" t="inlineStr"/>
+      <c r="G1415" t="inlineStr">
+        <is>
+          <t>7-0</t>
+        </is>
+      </c>
+      <c r="H1415" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1415" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1415" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1415" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1415" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1416">
+      <c r="A1416" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1416" t="inlineStr">
+        <is>
+          <t>Queen's Park vs Ayr United</t>
+        </is>
+      </c>
+      <c r="C1416" t="inlineStr">
+        <is>
+          <t>Ayr United</t>
+        </is>
+      </c>
+      <c r="D1416" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1416" t="inlineStr"/>
+      <c r="F1416" t="inlineStr"/>
+      <c r="G1416" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1416" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1416" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1416" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1416" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1416" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1417">
+      <c r="A1417" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1417" t="inlineStr">
+        <is>
+          <t>Juve Stabia vs Cesena</t>
+        </is>
+      </c>
+      <c r="C1417" t="inlineStr">
+        <is>
+          <t>Juve Stabia</t>
+        </is>
+      </c>
+      <c r="D1417" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1417" t="inlineStr"/>
+      <c r="F1417" t="inlineStr"/>
+      <c r="G1417" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1417" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1417" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1417" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1417" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1417" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1418">
+      <c r="A1418" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1418" t="inlineStr">
+        <is>
+          <t>Albacete vs Córdoba</t>
+        </is>
+      </c>
+      <c r="C1418" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="D1418" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1418" t="inlineStr"/>
+      <c r="F1418" t="inlineStr"/>
+      <c r="G1418" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1418" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1418" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1418" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1418" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1418" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1419">
+      <c r="A1419" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1419" t="inlineStr">
+        <is>
+          <t>AS Monaco vs Lens</t>
+        </is>
+      </c>
+      <c r="C1419" t="inlineStr">
+        <is>
+          <t>AS Monaco</t>
+        </is>
+      </c>
+      <c r="D1419" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1419" t="inlineStr"/>
+      <c r="F1419" t="inlineStr"/>
+      <c r="G1419" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1419" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1419" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1419" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1419" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1419" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1420">
+      <c r="A1420" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1420" t="inlineStr">
+        <is>
+          <t>Monza vs Sassuolo</t>
+        </is>
+      </c>
+      <c r="C1420" t="inlineStr">
+        <is>
+          <t>Sassuolo</t>
+        </is>
+      </c>
+      <c r="D1420" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1420" t="inlineStr"/>
+      <c r="F1420" t="inlineStr"/>
+      <c r="G1420" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1420" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1420" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1420" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1420" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1420" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1421">
+      <c r="A1421" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1421" t="inlineStr">
+        <is>
+          <t>KAA Gent vs Standard Liege</t>
+        </is>
+      </c>
+      <c r="C1421" t="inlineStr">
+        <is>
+          <t>KAA Gent</t>
+        </is>
+      </c>
+      <c r="D1421" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1421" t="inlineStr"/>
+      <c r="F1421" t="inlineStr"/>
+      <c r="G1421" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1421" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1421" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1421" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1421" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1421" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1422">
+      <c r="A1422" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1422" t="inlineStr">
+        <is>
+          <t>Yeovil Town vs Solihull Moors</t>
+        </is>
+      </c>
+      <c r="C1422" t="inlineStr">
+        <is>
+          <t>Yeovil Town</t>
+        </is>
+      </c>
+      <c r="D1422" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1422" t="inlineStr"/>
+      <c r="F1422" t="inlineStr"/>
+      <c r="G1422" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H1422" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1422" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1422" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1422" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1422" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1423">
+      <c r="A1423" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1423" t="inlineStr">
+        <is>
+          <t>Worcester City vs Stratford Town</t>
+        </is>
+      </c>
+      <c r="C1423" t="inlineStr">
+        <is>
+          <t>Worcester City</t>
+        </is>
+      </c>
+      <c r="D1423" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1423" t="inlineStr"/>
+      <c r="F1423" t="inlineStr"/>
+      <c r="G1423" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1423" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1423" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1423" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1423" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1423" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1424">
+      <c r="A1424" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1424" t="inlineStr">
+        <is>
+          <t>Yate Town vs Chippenham Town</t>
+        </is>
+      </c>
+      <c r="C1424" t="inlineStr">
+        <is>
+          <t>Yate Town</t>
+        </is>
+      </c>
+      <c r="D1424" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1424" t="inlineStr"/>
+      <c r="F1424" t="inlineStr"/>
+      <c r="G1424" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1424" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1424" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1424" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1424" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1424" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1425">
+      <c r="A1425" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1425" t="inlineStr">
+        <is>
+          <t>Brentford vs Chelsea</t>
+        </is>
+      </c>
+      <c r="C1425" t="inlineStr">
+        <is>
+          <t>Chelsea</t>
+        </is>
+      </c>
+      <c r="D1425" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1425" t="inlineStr"/>
+      <c r="F1425" t="inlineStr"/>
+      <c r="G1425" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1425" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1425" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1425" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1425" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1425" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1426">
+      <c r="A1426" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1426" t="inlineStr">
+        <is>
+          <t>Espanyol vs Elche</t>
+        </is>
+      </c>
+      <c r="C1426" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="D1426" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1426" t="inlineStr"/>
+      <c r="F1426" t="inlineStr"/>
+      <c r="G1426" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H1426" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1426" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1426" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1426" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1426" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1427">
+      <c r="A1427" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1427" t="inlineStr">
+        <is>
+          <t>Bristol City vs Watford</t>
+        </is>
+      </c>
+      <c r="C1427" t="inlineStr">
+        <is>
+          <t>Bristol City</t>
+        </is>
+      </c>
+      <c r="D1427" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1427" t="inlineStr"/>
+      <c r="F1427" t="inlineStr"/>
+      <c r="G1427" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1427" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1427" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1427" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1427" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1427" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1428">
+      <c r="A1428" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1428" t="inlineStr">
+        <is>
+          <t>Sportivo Trinidense vs Guaraní</t>
+        </is>
+      </c>
+      <c r="C1428" t="inlineStr">
+        <is>
+          <t>Sportivo Trinidense</t>
+        </is>
+      </c>
+      <c r="D1428" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1428" t="inlineStr"/>
+      <c r="F1428" t="inlineStr"/>
+      <c r="G1428" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1428" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1428" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1428" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1428" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1428" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1429">
+      <c r="A1429" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1429" t="inlineStr">
+        <is>
+          <t>Alianza Atlético vs Comerciantes Unidos</t>
+        </is>
+      </c>
+      <c r="C1429" t="inlineStr">
+        <is>
+          <t>Alianza Atlético</t>
+        </is>
+      </c>
+      <c r="D1429" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1429" t="inlineStr"/>
+      <c r="F1429" t="inlineStr"/>
+      <c r="G1429" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1429" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1429" t="n">
+        <v>7</v>
+      </c>
+      <c r="J1429" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1429" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1429" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1430">
+      <c r="A1430" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1430" t="inlineStr">
+        <is>
+          <t>Águilas Doradas vs Deportivo Pereira</t>
+        </is>
+      </c>
+      <c r="C1430" t="inlineStr">
+        <is>
+          <t>Águilas Doradas</t>
+        </is>
+      </c>
+      <c r="D1430" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1430" t="inlineStr"/>
+      <c r="F1430" t="inlineStr"/>
+      <c r="G1430" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1430" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1430" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1430" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1430" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1430" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1431">
+      <c r="A1431" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1431" t="inlineStr">
+        <is>
+          <t>Platense vs UPNFM</t>
+        </is>
+      </c>
+      <c r="C1431" t="inlineStr">
+        <is>
+          <t>Platense</t>
+        </is>
+      </c>
+      <c r="D1431" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1431" t="inlineStr"/>
+      <c r="F1431" t="inlineStr"/>
+      <c r="G1431" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1431" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1431" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1431" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1431" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1431" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1432">
+      <c r="A1432" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1432" t="inlineStr">
+        <is>
+          <t>Nacional Asunción vs 2 de Mayo</t>
+        </is>
+      </c>
+      <c r="C1432" t="inlineStr">
+        <is>
+          <t>Nacional Asunción</t>
+        </is>
+      </c>
+      <c r="D1432" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1432" t="inlineStr"/>
+      <c r="F1432" t="inlineStr"/>
+      <c r="G1432" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1432" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1432" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1432" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1432" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1432" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1433">
+      <c r="A1433" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1433" t="inlineStr">
+        <is>
+          <t>Vila Nova vs América Mineiro</t>
+        </is>
+      </c>
+      <c r="C1433" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="D1433" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1433" t="inlineStr"/>
+      <c r="F1433" t="inlineStr"/>
+      <c r="G1433" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1433" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1433" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1433" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1433" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1433" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1434">
+      <c r="A1434" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1434" t="inlineStr">
+        <is>
+          <t>Independiente Petrolero vs San Antonio Bulo Bulo</t>
+        </is>
+      </c>
+      <c r="C1434" t="inlineStr">
+        <is>
+          <t>Independiente Petrolero</t>
+        </is>
+      </c>
+      <c r="D1434" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1434" t="inlineStr"/>
+      <c r="F1434" t="inlineStr"/>
+      <c r="G1434" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H1434" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1434" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1434" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1434" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1434" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1435">
+      <c r="A1435" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1435" t="inlineStr">
+        <is>
+          <t>Ceará vs Novorizontino</t>
+        </is>
+      </c>
+      <c r="C1435" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="D1435" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1435" t="inlineStr"/>
+      <c r="F1435" t="inlineStr"/>
+      <c r="G1435" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1435" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1435" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1435" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1435" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1435" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1436">
+      <c r="A1436" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1436" t="inlineStr">
+        <is>
+          <t>São Bernardo vs Atlético Goianiense</t>
+        </is>
+      </c>
+      <c r="C1436" t="inlineStr">
+        <is>
+          <t>São Bernardo</t>
+        </is>
+      </c>
+      <c r="D1436" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1436" t="inlineStr"/>
+      <c r="F1436" t="inlineStr"/>
+      <c r="G1436" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1436" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1436" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1436" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1436" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1436" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1437">
+      <c r="A1437" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1437" t="inlineStr">
+        <is>
+          <t>Racing Club vs Sarmiento (Junín)</t>
+        </is>
+      </c>
+      <c r="C1437" t="inlineStr">
+        <is>
+          <t>Racing Club</t>
+        </is>
+      </c>
+      <c r="D1437" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1437" t="inlineStr"/>
+      <c r="F1437" t="inlineStr"/>
+      <c r="G1437" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1437" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1437" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1437" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1437" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1437" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1438">
+      <c r="A1438" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1438" t="inlineStr">
+        <is>
+          <t>Puebla vs Atlante</t>
+        </is>
+      </c>
+      <c r="C1438" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
+      <c r="D1438" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1438" t="inlineStr"/>
+      <c r="F1438" t="inlineStr"/>
+      <c r="G1438" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1438" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1438" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1438" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1439">
+      <c r="A1439" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1439" t="inlineStr">
+        <is>
+          <t>Tepatitlán FC vs Mineros de Zacatecas</t>
+        </is>
+      </c>
+      <c r="C1439" t="inlineStr">
+        <is>
+          <t>Mineros de Zacatecas</t>
+        </is>
+      </c>
+      <c r="D1439" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1439" t="inlineStr"/>
+      <c r="F1439" t="inlineStr"/>
+      <c r="G1439" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1439" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1439" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1439" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1439" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1439" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1440">
+      <c r="A1440" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1440" t="inlineStr">
+        <is>
+          <t>Piratas vs Venados FC</t>
+        </is>
+      </c>
+      <c r="C1440" t="inlineStr">
+        <is>
+          <t>Piratas</t>
+        </is>
+      </c>
+      <c r="D1440" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1440" t="inlineStr"/>
+      <c r="F1440" t="inlineStr"/>
+      <c r="G1440" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1440" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1440" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1440" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1440" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1440" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1441">
+      <c r="A1441" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1441" t="inlineStr">
+        <is>
+          <t>Alianza Lima vs ADT</t>
+        </is>
+      </c>
+      <c r="C1441" t="inlineStr">
+        <is>
+          <t>Alianza Lima</t>
+        </is>
+      </c>
+      <c r="D1441" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1441" t="inlineStr"/>
+      <c r="F1441" t="inlineStr"/>
+      <c r="G1441" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1441" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1441" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1441" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1441" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1441" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1442">
+      <c r="A1442" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1442" t="inlineStr">
+        <is>
+          <t>Pérez Zeledón vs Sporting San José</t>
+        </is>
+      </c>
+      <c r="C1442" t="inlineStr">
+        <is>
+          <t>Sporting San José</t>
+        </is>
+      </c>
+      <c r="D1442" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1442" t="inlineStr"/>
+      <c r="F1442" t="inlineStr"/>
+      <c r="G1442" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1442" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1442" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1442" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1442" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1442" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1443">
+      <c r="A1443" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B1443" t="inlineStr">
+        <is>
+          <t>FC Juarez vs Tigres UANL</t>
+        </is>
+      </c>
+      <c r="C1443" t="inlineStr">
+        <is>
+          <t>FC Juarez</t>
+        </is>
+      </c>
+      <c r="D1443" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1443" t="inlineStr"/>
+      <c r="F1443" t="inlineStr"/>
+      <c r="G1443" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1443" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1443" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1443" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1443" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1443" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -64603,7 +66959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65313,6 +67669,25 @@
       </c>
       <c r="E38" t="n">
         <v>22</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>50</v>
+      </c>
+      <c r="C39" t="n">
+        <v>32</v>
+      </c>
+      <c r="D39" t="n">
+        <v>64</v>
+      </c>
+      <c r="E39" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -65326,7 +67701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E193"/>
+  <dimension ref="A1:E202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -69388,6 +71763,195 @@
         <v>100</v>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>7</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0</v>
+      </c>
+      <c r="E194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>14</v>
+      </c>
+      <c r="D195" t="n">
+        <v>1</v>
+      </c>
+      <c r="E195" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>7</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0</v>
+      </c>
+      <c r="E196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>7</v>
+      </c>
+      <c r="D197" t="n">
+        <v>2</v>
+      </c>
+      <c r="E197" t="n">
+        <v>28.6</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>7</v>
+      </c>
+      <c r="D198" t="n">
+        <v>1</v>
+      </c>
+      <c r="E198" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>gol_de_cierre</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>5</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0</v>
+      </c>
+      <c r="E199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>2</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>1</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0</v>
+      </c>
+      <c r="E201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>siguen_empatados_70</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>1</v>
+      </c>
+      <c r="D202" t="n">
+        <v>0</v>
+      </c>
+      <c r="E202" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1443"/>
+  <dimension ref="A1:L1551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64569,8 +64569,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1394" t="inlineStr"/>
-      <c r="F1394" t="inlineStr"/>
       <c r="G1394" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -64617,8 +64615,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1395" t="inlineStr"/>
-      <c r="F1395" t="inlineStr"/>
       <c r="G1395" t="inlineStr">
         <is>
           <t>5-1</t>
@@ -64665,8 +64661,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1396" t="inlineStr"/>
-      <c r="F1396" t="inlineStr"/>
       <c r="G1396" t="inlineStr">
         <is>
           <t>0-4</t>
@@ -64713,8 +64707,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1397" t="inlineStr"/>
-      <c r="F1397" t="inlineStr"/>
       <c r="G1397" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -64761,8 +64753,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1398" t="inlineStr"/>
-      <c r="F1398" t="inlineStr"/>
       <c r="G1398" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -64809,8 +64799,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1399" t="inlineStr"/>
-      <c r="F1399" t="inlineStr"/>
       <c r="G1399" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -64857,8 +64845,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1400" t="inlineStr"/>
-      <c r="F1400" t="inlineStr"/>
       <c r="G1400" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -64905,8 +64891,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1401" t="inlineStr"/>
-      <c r="F1401" t="inlineStr"/>
       <c r="G1401" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -64953,8 +64937,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1402" t="inlineStr"/>
-      <c r="F1402" t="inlineStr"/>
       <c r="G1402" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -65001,8 +64983,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1403" t="inlineStr"/>
-      <c r="F1403" t="inlineStr"/>
       <c r="G1403" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -65049,8 +65029,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1404" t="inlineStr"/>
-      <c r="F1404" t="inlineStr"/>
       <c r="G1404" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -65097,8 +65075,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1405" t="inlineStr"/>
-      <c r="F1405" t="inlineStr"/>
       <c r="G1405" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -65145,8 +65121,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1406" t="inlineStr"/>
-      <c r="F1406" t="inlineStr"/>
       <c r="G1406" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -65193,8 +65167,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1407" t="inlineStr"/>
-      <c r="F1407" t="inlineStr"/>
       <c r="G1407" t="inlineStr">
         <is>
           <t>3-4</t>
@@ -65241,8 +65213,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1408" t="inlineStr"/>
-      <c r="F1408" t="inlineStr"/>
       <c r="G1408" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -65289,8 +65259,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1409" t="inlineStr"/>
-      <c r="F1409" t="inlineStr"/>
       <c r="G1409" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -65337,8 +65305,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1410" t="inlineStr"/>
-      <c r="F1410" t="inlineStr"/>
       <c r="G1410" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -65385,8 +65351,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1411" t="inlineStr"/>
-      <c r="F1411" t="inlineStr"/>
       <c r="G1411" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -65433,8 +65397,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1412" t="inlineStr"/>
-      <c r="F1412" t="inlineStr"/>
       <c r="G1412" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -65481,8 +65443,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1413" t="inlineStr"/>
-      <c r="F1413" t="inlineStr"/>
       <c r="G1413" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -65529,8 +65489,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1414" t="inlineStr"/>
-      <c r="F1414" t="inlineStr"/>
       <c r="G1414" t="inlineStr">
         <is>
           <t>6-1</t>
@@ -65577,8 +65535,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1415" t="inlineStr"/>
-      <c r="F1415" t="inlineStr"/>
       <c r="G1415" t="inlineStr">
         <is>
           <t>7-0</t>
@@ -65625,8 +65581,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1416" t="inlineStr"/>
-      <c r="F1416" t="inlineStr"/>
       <c r="G1416" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -65673,8 +65627,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1417" t="inlineStr"/>
-      <c r="F1417" t="inlineStr"/>
       <c r="G1417" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -65721,8 +65673,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1418" t="inlineStr"/>
-      <c r="F1418" t="inlineStr"/>
       <c r="G1418" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -65769,8 +65719,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1419" t="inlineStr"/>
-      <c r="F1419" t="inlineStr"/>
       <c r="G1419" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -65817,8 +65765,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1420" t="inlineStr"/>
-      <c r="F1420" t="inlineStr"/>
       <c r="G1420" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -65865,8 +65811,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1421" t="inlineStr"/>
-      <c r="F1421" t="inlineStr"/>
       <c r="G1421" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -65913,8 +65857,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1422" t="inlineStr"/>
-      <c r="F1422" t="inlineStr"/>
       <c r="G1422" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -65961,8 +65903,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1423" t="inlineStr"/>
-      <c r="F1423" t="inlineStr"/>
       <c r="G1423" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -66009,8 +65949,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1424" t="inlineStr"/>
-      <c r="F1424" t="inlineStr"/>
       <c r="G1424" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -66057,8 +65995,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1425" t="inlineStr"/>
-      <c r="F1425" t="inlineStr"/>
       <c r="G1425" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -66105,8 +66041,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1426" t="inlineStr"/>
-      <c r="F1426" t="inlineStr"/>
       <c r="G1426" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -66153,8 +66087,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1427" t="inlineStr"/>
-      <c r="F1427" t="inlineStr"/>
       <c r="G1427" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -66201,8 +66133,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1428" t="inlineStr"/>
-      <c r="F1428" t="inlineStr"/>
       <c r="G1428" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -66249,8 +66179,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1429" t="inlineStr"/>
-      <c r="F1429" t="inlineStr"/>
       <c r="G1429" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -66297,8 +66225,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1430" t="inlineStr"/>
-      <c r="F1430" t="inlineStr"/>
       <c r="G1430" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -66345,8 +66271,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1431" t="inlineStr"/>
-      <c r="F1431" t="inlineStr"/>
       <c r="G1431" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -66393,8 +66317,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1432" t="inlineStr"/>
-      <c r="F1432" t="inlineStr"/>
       <c r="G1432" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -66441,8 +66363,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1433" t="inlineStr"/>
-      <c r="F1433" t="inlineStr"/>
       <c r="G1433" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -66489,8 +66409,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1434" t="inlineStr"/>
-      <c r="F1434" t="inlineStr"/>
       <c r="G1434" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -66537,8 +66455,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1435" t="inlineStr"/>
-      <c r="F1435" t="inlineStr"/>
       <c r="G1435" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -66585,8 +66501,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1436" t="inlineStr"/>
-      <c r="F1436" t="inlineStr"/>
       <c r="G1436" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -66633,8 +66547,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1437" t="inlineStr"/>
-      <c r="F1437" t="inlineStr"/>
       <c r="G1437" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -66681,8 +66593,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1438" t="inlineStr"/>
-      <c r="F1438" t="inlineStr"/>
       <c r="G1438" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -66729,8 +66639,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1439" t="inlineStr"/>
-      <c r="F1439" t="inlineStr"/>
       <c r="G1439" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -66777,8 +66685,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1440" t="inlineStr"/>
-      <c r="F1440" t="inlineStr"/>
       <c r="G1440" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -66825,8 +66731,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1441" t="inlineStr"/>
-      <c r="F1441" t="inlineStr"/>
       <c r="G1441" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -66873,8 +66777,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1442" t="inlineStr"/>
-      <c r="F1442" t="inlineStr"/>
       <c r="G1442" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -66921,8 +66823,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1443" t="inlineStr"/>
-      <c r="F1443" t="inlineStr"/>
       <c r="G1443" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -66943,6 +66843,5190 @@
         <v>0</v>
       </c>
       <c r="L1443" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1444">
+      <c r="A1444" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1444" t="inlineStr">
+        <is>
+          <t>Auckland FC vs Western Sydney Wanderers</t>
+        </is>
+      </c>
+      <c r="C1444" t="inlineStr">
+        <is>
+          <t>Auckland FC</t>
+        </is>
+      </c>
+      <c r="D1444" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1444" t="inlineStr"/>
+      <c r="F1444" t="inlineStr"/>
+      <c r="G1444" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H1444" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1444" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1444" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1444" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1444" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1445">
+      <c r="A1445" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1445" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur vs Aston Villa</t>
+        </is>
+      </c>
+      <c r="C1445" t="inlineStr">
+        <is>
+          <t>Tottenham Hotspur</t>
+        </is>
+      </c>
+      <c r="D1445" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1445" t="inlineStr"/>
+      <c r="F1445" t="inlineStr"/>
+      <c r="G1445" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H1445" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1445" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1445" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1445" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1445" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1446">
+      <c r="A1446" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1446" t="inlineStr">
+        <is>
+          <t>Cardiff City vs Charlton Athletic</t>
+        </is>
+      </c>
+      <c r="C1446" t="inlineStr">
+        <is>
+          <t>Cardiff City</t>
+        </is>
+      </c>
+      <c r="D1446" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1446" t="inlineStr"/>
+      <c r="F1446" t="inlineStr"/>
+      <c r="G1446" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1446" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1446" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1446" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1446" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1446" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1447">
+      <c r="A1447" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1447" t="inlineStr">
+        <is>
+          <t>Millwall vs West Ham United</t>
+        </is>
+      </c>
+      <c r="C1447" t="inlineStr">
+        <is>
+          <t>West Ham United</t>
+        </is>
+      </c>
+      <c r="D1447" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1447" t="inlineStr"/>
+      <c r="F1447" t="inlineStr"/>
+      <c r="G1447" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1447" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1447" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1447" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1447" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1447" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1448">
+      <c r="A1448" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1448" t="inlineStr">
+        <is>
+          <t>Stoke City vs Sheffield United</t>
+        </is>
+      </c>
+      <c r="C1448" t="inlineStr">
+        <is>
+          <t>Stoke City</t>
+        </is>
+      </c>
+      <c r="D1448" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1448" t="inlineStr"/>
+      <c r="F1448" t="inlineStr"/>
+      <c r="G1448" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1448" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1448" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1448" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1448" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1448" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1449">
+      <c r="A1449" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1449" t="inlineStr">
+        <is>
+          <t>Osasuna vs Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="C1449" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="D1449" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1449" t="inlineStr"/>
+      <c r="F1449" t="inlineStr"/>
+      <c r="G1449" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1449" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1449" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1449" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1449" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1449" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1450">
+      <c r="A1450" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1450" t="inlineStr">
+        <is>
+          <t>Real Sociedad II vs Mallorca</t>
+        </is>
+      </c>
+      <c r="C1450" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="D1450" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1450" t="inlineStr"/>
+      <c r="F1450" t="inlineStr"/>
+      <c r="G1450" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1450" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1450" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1450" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1450" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1450" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1451">
+      <c r="A1451" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1451" t="inlineStr">
+        <is>
+          <t>Bologna vs Torino</t>
+        </is>
+      </c>
+      <c r="C1451" t="inlineStr">
+        <is>
+          <t>Bologna</t>
+        </is>
+      </c>
+      <c r="D1451" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1451" t="inlineStr"/>
+      <c r="F1451" t="inlineStr"/>
+      <c r="G1451" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1451" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1451" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1451" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1451" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1451" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1452">
+      <c r="A1452" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1452" t="inlineStr">
+        <is>
+          <t>Udinese vs Cagliari</t>
+        </is>
+      </c>
+      <c r="C1452" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="D1452" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1452" t="inlineStr"/>
+      <c r="F1452" t="inlineStr"/>
+      <c r="G1452" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1452" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1452" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1452" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1452" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1452" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1453">
+      <c r="A1453" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1453" t="inlineStr">
+        <is>
+          <t>Castro Daire vs Portimonense</t>
+        </is>
+      </c>
+      <c r="C1453" t="inlineStr">
+        <is>
+          <t>Portimonense</t>
+        </is>
+      </c>
+      <c r="D1453" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1453" t="inlineStr"/>
+      <c r="F1453" t="inlineStr"/>
+      <c r="G1453" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1453" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1453" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1453" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1453" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1453" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1454">
+      <c r="A1454" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1454" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt vs SC Freiburg</t>
+        </is>
+      </c>
+      <c r="C1454" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="D1454" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1454" t="inlineStr"/>
+      <c r="F1454" t="inlineStr"/>
+      <c r="G1454" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1454" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1454" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1454" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1454" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1454" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1455">
+      <c r="A1455" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1455" t="inlineStr">
+        <is>
+          <t>Werder Bremen vs FC Augsburg</t>
+        </is>
+      </c>
+      <c r="C1455" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="D1455" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1455" t="inlineStr"/>
+      <c r="F1455" t="inlineStr"/>
+      <c r="G1455" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1455" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1455" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1455" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1455" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1455" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1456">
+      <c r="A1456" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1456" t="inlineStr">
+        <is>
+          <t>Borussia Mönchengladbach vs Mainz</t>
+        </is>
+      </c>
+      <c r="C1456" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="D1456" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1456" t="inlineStr"/>
+      <c r="F1456" t="inlineStr"/>
+      <c r="G1456" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="H1456" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1456" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1456" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1456" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1456" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1457">
+      <c r="A1457" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1457" t="inlineStr">
+        <is>
+          <t>Brighton &amp; Hove Albion vs Arsenal</t>
+        </is>
+      </c>
+      <c r="C1457" t="inlineStr">
+        <is>
+          <t>Arsenal</t>
+        </is>
+      </c>
+      <c r="D1457" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1457" t="inlineStr"/>
+      <c r="F1457" t="inlineStr"/>
+      <c r="G1457" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1457" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1457" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1457" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1457" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1457" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1458">
+      <c r="A1458" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1458" t="inlineStr">
+        <is>
+          <t>Everton vs Ipswich Town</t>
+        </is>
+      </c>
+      <c r="C1458" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="D1458" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1458" t="inlineStr"/>
+      <c r="F1458" t="inlineStr"/>
+      <c r="G1458" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1458" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1458" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1458" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1458" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1458" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1459">
+      <c r="A1459" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1459" t="inlineStr">
+        <is>
+          <t>Newcastle United vs Hull City</t>
+        </is>
+      </c>
+      <c r="C1459" t="inlineStr">
+        <is>
+          <t>Newcastle United</t>
+        </is>
+      </c>
+      <c r="D1459" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1459" t="inlineStr"/>
+      <c r="F1459" t="inlineStr"/>
+      <c r="G1459" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1459" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1459" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1459" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1459" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1459" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1460">
+      <c r="A1460" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1460" t="inlineStr">
+        <is>
+          <t>OH Leuven vs RAAL La Louvière</t>
+        </is>
+      </c>
+      <c r="C1460" t="inlineStr">
+        <is>
+          <t>OH Leuven</t>
+        </is>
+      </c>
+      <c r="D1460" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1460" t="inlineStr"/>
+      <c r="F1460" t="inlineStr"/>
+      <c r="G1460" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1460" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1460" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1460" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1460" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1460" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1461">
+      <c r="A1461" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1461" t="inlineStr">
+        <is>
+          <t>Birmingham City vs Middlesbrough</t>
+        </is>
+      </c>
+      <c r="C1461" t="inlineStr">
+        <is>
+          <t>Middlesbrough</t>
+        </is>
+      </c>
+      <c r="D1461" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1461" t="inlineStr"/>
+      <c r="F1461" t="inlineStr"/>
+      <c r="G1461" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1461" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1461" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1461" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1461" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1461" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1462">
+      <c r="A1462" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1462" t="inlineStr">
+        <is>
+          <t>Burnley vs Derby County</t>
+        </is>
+      </c>
+      <c r="C1462" t="inlineStr">
+        <is>
+          <t>Burnley</t>
+        </is>
+      </c>
+      <c r="D1462" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1462" t="inlineStr"/>
+      <c r="F1462" t="inlineStr"/>
+      <c r="G1462" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1462" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1462" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1462" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1462" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1462" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1463">
+      <c r="A1463" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1463" t="inlineStr">
+        <is>
+          <t>Portsmouth vs Blackburn Rovers</t>
+        </is>
+      </c>
+      <c r="C1463" t="inlineStr">
+        <is>
+          <t>Portsmouth</t>
+        </is>
+      </c>
+      <c r="D1463" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1463" t="inlineStr"/>
+      <c r="F1463" t="inlineStr"/>
+      <c r="G1463" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1463" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1463" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1463" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1463" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1463" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1464">
+      <c r="A1464" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1464" t="inlineStr">
+        <is>
+          <t>Queens Park Rangers vs Preston North End</t>
+        </is>
+      </c>
+      <c r="C1464" t="inlineStr">
+        <is>
+          <t>Queens Park Rangers</t>
+        </is>
+      </c>
+      <c r="D1464" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1464" t="inlineStr"/>
+      <c r="F1464" t="inlineStr"/>
+      <c r="G1464" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1464" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1464" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1464" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1464" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1464" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1465">
+      <c r="A1465" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1465" t="inlineStr">
+        <is>
+          <t>Wrexham vs Southampton</t>
+        </is>
+      </c>
+      <c r="C1465" t="inlineStr">
+        <is>
+          <t>Southampton</t>
+        </is>
+      </c>
+      <c r="D1465" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1465" t="inlineStr"/>
+      <c r="F1465" t="inlineStr"/>
+      <c r="G1465" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1465" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1465" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1465" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1465" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1465" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1466">
+      <c r="A1466" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1466" t="inlineStr">
+        <is>
+          <t>Dundee vs Motherwell</t>
+        </is>
+      </c>
+      <c r="C1466" t="inlineStr">
+        <is>
+          <t>Motherwell</t>
+        </is>
+      </c>
+      <c r="D1466" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1466" t="inlineStr"/>
+      <c r="F1466" t="inlineStr"/>
+      <c r="G1466" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1466" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1466" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1466" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1466" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1466" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1467">
+      <c r="A1467" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1467" t="inlineStr">
+        <is>
+          <t>Hibernian vs Aberdeen</t>
+        </is>
+      </c>
+      <c r="C1467" t="inlineStr">
+        <is>
+          <t>Hibernian</t>
+        </is>
+      </c>
+      <c r="D1467" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1467" t="inlineStr"/>
+      <c r="F1467" t="inlineStr"/>
+      <c r="G1467" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1467" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1467" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1467" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1467" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1467" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1468">
+      <c r="A1468" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1468" t="inlineStr">
+        <is>
+          <t>St Johnstone vs Falkirk</t>
+        </is>
+      </c>
+      <c r="C1468" t="inlineStr">
+        <is>
+          <t>St Johnstone</t>
+        </is>
+      </c>
+      <c r="D1468" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1468" t="inlineStr"/>
+      <c r="F1468" t="inlineStr"/>
+      <c r="G1468" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1468" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1468" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1468" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1468" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1468" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1469">
+      <c r="A1469" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1469" t="inlineStr">
+        <is>
+          <t>St Mirren vs Dundee United</t>
+        </is>
+      </c>
+      <c r="C1469" t="inlineStr">
+        <is>
+          <t>St Mirren</t>
+        </is>
+      </c>
+      <c r="D1469" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1469" t="inlineStr"/>
+      <c r="F1469" t="inlineStr"/>
+      <c r="G1469" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H1469" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1469" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1469" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1469" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1469" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1470">
+      <c r="A1470" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1470" t="inlineStr">
+        <is>
+          <t>Çorum FK vs Alanyaspor</t>
+        </is>
+      </c>
+      <c r="C1470" t="inlineStr">
+        <is>
+          <t>Çorum FK</t>
+        </is>
+      </c>
+      <c r="D1470" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1470" t="inlineStr"/>
+      <c r="F1470" t="inlineStr"/>
+      <c r="G1470" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1470" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1470" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1470" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1470" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1470" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1471">
+      <c r="A1471" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1471" t="inlineStr">
+        <is>
+          <t>Kocaelispor vs Gaziantep FK</t>
+        </is>
+      </c>
+      <c r="C1471" t="inlineStr">
+        <is>
+          <t>Kocaelispor</t>
+        </is>
+      </c>
+      <c r="D1471" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1471" t="inlineStr"/>
+      <c r="F1471" t="inlineStr"/>
+      <c r="G1471" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1471" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1471" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1471" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1471" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1471" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1472">
+      <c r="A1472" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1472" t="inlineStr">
+        <is>
+          <t>Lincoln City vs Swansea City</t>
+        </is>
+      </c>
+      <c r="C1472" t="inlineStr">
+        <is>
+          <t>Swansea City</t>
+        </is>
+      </c>
+      <c r="D1472" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1472" t="inlineStr"/>
+      <c r="F1472" t="inlineStr"/>
+      <c r="G1472" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1472" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1472" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1472" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1472" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1472" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1473">
+      <c r="A1473" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1473" t="inlineStr">
+        <is>
+          <t>Vitoria Sernache vs Varzim</t>
+        </is>
+      </c>
+      <c r="C1473" t="inlineStr">
+        <is>
+          <t>Varzim</t>
+        </is>
+      </c>
+      <c r="D1473" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1473" t="inlineStr"/>
+      <c r="F1473" t="inlineStr"/>
+      <c r="G1473" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1473" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1473" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1473" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1473" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1473" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1474">
+      <c r="A1474" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1474" t="inlineStr">
+        <is>
+          <t>Athletic Club vs Alavés</t>
+        </is>
+      </c>
+      <c r="C1474" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="D1474" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1474" t="inlineStr"/>
+      <c r="F1474" t="inlineStr"/>
+      <c r="G1474" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1474" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1474" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1474" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1474" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1474" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1475">
+      <c r="A1475" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1475" t="inlineStr">
+        <is>
+          <t>ADO Den Haag vs SC Cambuur</t>
+        </is>
+      </c>
+      <c r="C1475" t="inlineStr">
+        <is>
+          <t>ADO Den Haag</t>
+        </is>
+      </c>
+      <c r="D1475" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1475" t="inlineStr"/>
+      <c r="F1475" t="inlineStr"/>
+      <c r="G1475" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1475" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1475" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1475" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1475" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1475" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1476" t="inlineStr">
+        <is>
+          <t>Gil Vicente vs Maritimo</t>
+        </is>
+      </c>
+      <c r="C1476" t="inlineStr">
+        <is>
+          <t>Gil Vicente</t>
+        </is>
+      </c>
+      <c r="D1476" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1476" t="inlineStr"/>
+      <c r="F1476" t="inlineStr"/>
+      <c r="G1476" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1476" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1476" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1476" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1476" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1476" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1477">
+      <c r="A1477" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1477" t="inlineStr">
+        <is>
+          <t>C.D. Nacional vs FC Famalicao</t>
+        </is>
+      </c>
+      <c r="C1477" t="inlineStr">
+        <is>
+          <t>FC Famalicao</t>
+        </is>
+      </c>
+      <c r="D1477" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1477" t="inlineStr"/>
+      <c r="F1477" t="inlineStr"/>
+      <c r="G1477" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="H1477" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1477" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1477" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1477" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1477" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1478">
+      <c r="A1478" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1478" t="inlineStr">
+        <is>
+          <t>Atlético CP vs Lagoa</t>
+        </is>
+      </c>
+      <c r="C1478" t="inlineStr">
+        <is>
+          <t>Atlético CP</t>
+        </is>
+      </c>
+      <c r="D1478" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1478" t="inlineStr"/>
+      <c r="F1478" t="inlineStr"/>
+      <c r="G1478" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H1478" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1478" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1478" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1478" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1478" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1479" t="inlineStr">
+        <is>
+          <t>Sagueiros vs Feirense</t>
+        </is>
+      </c>
+      <c r="C1479" t="inlineStr">
+        <is>
+          <t>Feirense</t>
+        </is>
+      </c>
+      <c r="D1479" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1479" t="inlineStr"/>
+      <c r="F1479" t="inlineStr"/>
+      <c r="G1479" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1479" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1479" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1479" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1479" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1479" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1480" t="inlineStr">
+        <is>
+          <t>Boston River vs Progreso</t>
+        </is>
+      </c>
+      <c r="C1480" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="D1480" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1480" t="inlineStr"/>
+      <c r="F1480" t="inlineStr"/>
+      <c r="G1480" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1480" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1480" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1480" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1480" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1480" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1481" t="inlineStr">
+        <is>
+          <t>Paris FC vs Strasbourg</t>
+        </is>
+      </c>
+      <c r="C1481" t="inlineStr">
+        <is>
+          <t>Paris FC</t>
+        </is>
+      </c>
+      <c r="D1481" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1481" t="inlineStr"/>
+      <c r="F1481" t="inlineStr"/>
+      <c r="G1481" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1481" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1481" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1481" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1481" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1481" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1482">
+      <c r="A1482" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1482" t="inlineStr">
+        <is>
+          <t>Atromitos vs Kifisia</t>
+        </is>
+      </c>
+      <c r="C1482" t="inlineStr">
+        <is>
+          <t>Atromitos</t>
+        </is>
+      </c>
+      <c r="D1482" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1482" t="inlineStr"/>
+      <c r="F1482" t="inlineStr"/>
+      <c r="G1482" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1482" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1482" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1482" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1482" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1482" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1483">
+      <c r="A1483" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1483" t="inlineStr">
+        <is>
+          <t>Oliveirense vs FC Penafiel</t>
+        </is>
+      </c>
+      <c r="C1483" t="inlineStr">
+        <is>
+          <t>FC Penafiel</t>
+        </is>
+      </c>
+      <c r="D1483" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1483" t="inlineStr"/>
+      <c r="F1483" t="inlineStr"/>
+      <c r="G1483" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1483" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1483" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1483" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1483" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1483" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1484">
+      <c r="A1484" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1484" t="inlineStr">
+        <is>
+          <t>Royal Charleroi SC vs Cercle Brugge KSV</t>
+        </is>
+      </c>
+      <c r="C1484" t="inlineStr">
+        <is>
+          <t>Royal Charleroi SC</t>
+        </is>
+      </c>
+      <c r="D1484" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1484" t="inlineStr"/>
+      <c r="F1484" t="inlineStr"/>
+      <c r="G1484" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1484" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1484" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1484" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1484" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1484" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1485" t="inlineStr">
+        <is>
+          <t>Nottingham Forest vs Coventry City</t>
+        </is>
+      </c>
+      <c r="C1485" t="inlineStr">
+        <is>
+          <t>Nottingham Forest</t>
+        </is>
+      </c>
+      <c r="D1485" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1485" t="inlineStr"/>
+      <c r="F1485" t="inlineStr"/>
+      <c r="G1485" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1485" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1485" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1485" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1485" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1485" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1486">
+      <c r="A1486" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1486" t="inlineStr">
+        <is>
+          <t>VfB Stuttgart vs Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="C1486" t="inlineStr">
+        <is>
+          <t>VfB Stuttgart</t>
+        </is>
+      </c>
+      <c r="D1486" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1486" t="inlineStr"/>
+      <c r="F1486" t="inlineStr"/>
+      <c r="G1486" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1486" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1486" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1486" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1486" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1486" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1487">
+      <c r="A1487" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1487" t="inlineStr">
+        <is>
+          <t>Celta Vigo vs Racing Santander</t>
+        </is>
+      </c>
+      <c r="C1487" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="D1487" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1487" t="inlineStr"/>
+      <c r="F1487" t="inlineStr"/>
+      <c r="G1487" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="H1487" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1487" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1487" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1487" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1487" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1488">
+      <c r="A1488" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1488" t="inlineStr">
+        <is>
+          <t>Aris vs Iraklis</t>
+        </is>
+      </c>
+      <c r="C1488" t="inlineStr">
+        <is>
+          <t>Aris</t>
+        </is>
+      </c>
+      <c r="D1488" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1488" t="inlineStr"/>
+      <c r="F1488" t="inlineStr"/>
+      <c r="G1488" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1488" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1488" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1488" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1488" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1488" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1489" t="inlineStr">
+        <is>
+          <t>Castellón vs Tenerife</t>
+        </is>
+      </c>
+      <c r="C1489" t="inlineStr">
+        <is>
+          <t>Castellón</t>
+        </is>
+      </c>
+      <c r="D1489" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1489" t="inlineStr"/>
+      <c r="F1489" t="inlineStr"/>
+      <c r="G1489" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="H1489" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1489" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1489" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1489" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1489" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1490" t="inlineStr">
+        <is>
+          <t>Eldense vs Eibar</t>
+        </is>
+      </c>
+      <c r="C1490" t="inlineStr">
+        <is>
+          <t>Eibar</t>
+        </is>
+      </c>
+      <c r="D1490" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1490" t="inlineStr"/>
+      <c r="F1490" t="inlineStr"/>
+      <c r="G1490" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1490" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1490" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1490" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1490" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1490" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1491" t="inlineStr">
+        <is>
+          <t>Kilmarnock vs Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="C1491" t="inlineStr">
+        <is>
+          <t>Heart of Midlothian</t>
+        </is>
+      </c>
+      <c r="D1491" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1491" t="inlineStr"/>
+      <c r="F1491" t="inlineStr"/>
+      <c r="G1491" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1491" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1491" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1491" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1491" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1491" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1492" t="inlineStr">
+        <is>
+          <t>Alverca vs Rio Ave</t>
+        </is>
+      </c>
+      <c r="C1492" t="inlineStr">
+        <is>
+          <t>Alverca</t>
+        </is>
+      </c>
+      <c r="D1492" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1492" t="inlineStr"/>
+      <c r="F1492" t="inlineStr"/>
+      <c r="G1492" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1492" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1492" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1492" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1492" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1492" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1493">
+      <c r="A1493" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1493" t="inlineStr">
+        <is>
+          <t>Istanbul Basaksehir vs Genclerbirligi</t>
+        </is>
+      </c>
+      <c r="C1493" t="inlineStr">
+        <is>
+          <t>Istanbul Basaksehir</t>
+        </is>
+      </c>
+      <c r="D1493" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1493" t="inlineStr"/>
+      <c r="F1493" t="inlineStr"/>
+      <c r="G1493" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H1493" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1493" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1493" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1493" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1493" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1494">
+      <c r="A1494" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1494" t="inlineStr">
+        <is>
+          <t>Trabzonspor vs Galatasaray</t>
+        </is>
+      </c>
+      <c r="C1494" t="inlineStr">
+        <is>
+          <t>Galatasaray</t>
+        </is>
+      </c>
+      <c r="D1494" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1494" t="inlineStr"/>
+      <c r="F1494" t="inlineStr"/>
+      <c r="G1494" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H1494" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1494" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1494" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1494" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1494" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1495">
+      <c r="A1495" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1495" t="inlineStr">
+        <is>
+          <t>Mafra vs Tirsense</t>
+        </is>
+      </c>
+      <c r="C1495" t="inlineStr">
+        <is>
+          <t>Mafra</t>
+        </is>
+      </c>
+      <c r="D1495" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1495" t="inlineStr"/>
+      <c r="F1495" t="inlineStr"/>
+      <c r="G1495" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1495" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1495" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1495" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1495" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1495" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1496" t="inlineStr">
+        <is>
+          <t>O Elvas vs Uniao Leiria</t>
+        </is>
+      </c>
+      <c r="C1496" t="inlineStr">
+        <is>
+          <t>Uniao Leiria</t>
+        </is>
+      </c>
+      <c r="D1496" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1496" t="inlineStr"/>
+      <c r="F1496" t="inlineStr"/>
+      <c r="G1496" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1496" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1496" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1496" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1496" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1496" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1497" t="inlineStr">
+        <is>
+          <t>Gimnasia La Plata vs Banfield</t>
+        </is>
+      </c>
+      <c r="C1497" t="inlineStr">
+        <is>
+          <t>Gimnasia La Plata</t>
+        </is>
+      </c>
+      <c r="D1497" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1497" t="inlineStr"/>
+      <c r="F1497" t="inlineStr"/>
+      <c r="G1497" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1497" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1497" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1497" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1497" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1497" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1498">
+      <c r="A1498" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1498" t="inlineStr">
+        <is>
+          <t>Gimnasia (Mendoza) vs Deportivo Riestra</t>
+        </is>
+      </c>
+      <c r="C1498" t="inlineStr">
+        <is>
+          <t>Gimnasia (Mendoza)</t>
+        </is>
+      </c>
+      <c r="D1498" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1498" t="inlineStr"/>
+      <c r="F1498" t="inlineStr"/>
+      <c r="G1498" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1498" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1498" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1498" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1498" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1498" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1499" t="inlineStr">
+        <is>
+          <t>Ajax Amsterdam vs Excelsior</t>
+        </is>
+      </c>
+      <c r="C1499" t="inlineStr">
+        <is>
+          <t>Ajax Amsterdam</t>
+        </is>
+      </c>
+      <c r="D1499" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1499" t="inlineStr"/>
+      <c r="F1499" t="inlineStr"/>
+      <c r="G1499" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1499" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1499" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1499" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1499" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1499" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1500">
+      <c r="A1500" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1500" t="inlineStr">
+        <is>
+          <t>FC Cajamarca vs Cusco FC</t>
+        </is>
+      </c>
+      <c r="C1500" t="inlineStr">
+        <is>
+          <t>Cusco FC</t>
+        </is>
+      </c>
+      <c r="D1500" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1500" t="inlineStr"/>
+      <c r="F1500" t="inlineStr"/>
+      <c r="G1500" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1500" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1500" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1500" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1500" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1500" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1501">
+      <c r="A1501" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1501" t="inlineStr">
+        <is>
+          <t>Cerro vs Peñarol</t>
+        </is>
+      </c>
+      <c r="C1501" t="inlineStr">
+        <is>
+          <t>Peñarol</t>
+        </is>
+      </c>
+      <c r="D1501" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1501" t="inlineStr"/>
+      <c r="F1501" t="inlineStr"/>
+      <c r="G1501" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1501" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1501" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1501" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1501" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1501" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1502">
+      <c r="A1502" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1502" t="inlineStr">
+        <is>
+          <t>Angers vs Troyes</t>
+        </is>
+      </c>
+      <c r="C1502" t="inlineStr">
+        <is>
+          <t>Angers</t>
+        </is>
+      </c>
+      <c r="D1502" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1502" t="inlineStr"/>
+      <c r="F1502" t="inlineStr"/>
+      <c r="G1502" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1502" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1502" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1502" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1502" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1502" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1503" t="inlineStr">
+        <is>
+          <t>Lyon vs Stade Rennais</t>
+        </is>
+      </c>
+      <c r="C1503" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="D1503" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1503" t="inlineStr"/>
+      <c r="F1503" t="inlineStr"/>
+      <c r="G1503" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H1503" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1503" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1503" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1503" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1503" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1504" t="inlineStr">
+        <is>
+          <t>Toulouse vs Le Havre AC</t>
+        </is>
+      </c>
+      <c r="C1504" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="D1504" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1504" t="inlineStr"/>
+      <c r="F1504" t="inlineStr"/>
+      <c r="G1504" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1504" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1504" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1504" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1504" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1504" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1505" t="inlineStr">
+        <is>
+          <t>Venezia vs Lazio</t>
+        </is>
+      </c>
+      <c r="C1505" t="inlineStr">
+        <is>
+          <t>Lazio</t>
+        </is>
+      </c>
+      <c r="D1505" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1505" t="inlineStr"/>
+      <c r="F1505" t="inlineStr"/>
+      <c r="G1505" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1505" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1505" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1505" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1505" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1505" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1506" t="inlineStr">
+        <is>
+          <t>Anderlecht vs Zulte-Waregem</t>
+        </is>
+      </c>
+      <c r="C1506" t="inlineStr">
+        <is>
+          <t>Anderlecht</t>
+        </is>
+      </c>
+      <c r="D1506" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1506" t="inlineStr"/>
+      <c r="F1506" t="inlineStr"/>
+      <c r="G1506" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1506" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1506" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1506" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1506" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1506" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1507" t="inlineStr">
+        <is>
+          <t>Sevilla vs Barcelona</t>
+        </is>
+      </c>
+      <c r="C1507" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="D1507" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1507" t="inlineStr"/>
+      <c r="F1507" t="inlineStr"/>
+      <c r="G1507" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H1507" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1507" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1507" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1507" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1507" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1508">
+      <c r="A1508" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1508" t="inlineStr">
+        <is>
+          <t>Atlético-MG vs Chapecoense</t>
+        </is>
+      </c>
+      <c r="C1508" t="inlineStr">
+        <is>
+          <t>Atlético-MG</t>
+        </is>
+      </c>
+      <c r="D1508" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1508" t="inlineStr"/>
+      <c r="F1508" t="inlineStr"/>
+      <c r="G1508" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1508" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1508" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1508" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1508" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1508" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1509">
+      <c r="A1509" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1509" t="inlineStr">
+        <is>
+          <t>Millonarios vs Boyacá Chicó FC</t>
+        </is>
+      </c>
+      <c r="C1509" t="inlineStr">
+        <is>
+          <t>Millonarios</t>
+        </is>
+      </c>
+      <c r="D1509" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1509" t="inlineStr"/>
+      <c r="F1509" t="inlineStr"/>
+      <c r="G1509" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1509" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1509" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1509" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1509" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1509" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1510">
+      <c r="A1510" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1510" t="inlineStr">
+        <is>
+          <t>Libertad vs Sportivo Ameliano</t>
+        </is>
+      </c>
+      <c r="C1510" t="inlineStr">
+        <is>
+          <t>Libertad</t>
+        </is>
+      </c>
+      <c r="D1510" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1510" t="inlineStr"/>
+      <c r="F1510" t="inlineStr"/>
+      <c r="G1510" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1510" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1510" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1510" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1510" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1510" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1511">
+      <c r="A1511" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1511" t="inlineStr">
+        <is>
+          <t>Cádiz vs Girona</t>
+        </is>
+      </c>
+      <c r="C1511" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="D1511" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1511" t="inlineStr"/>
+      <c r="F1511" t="inlineStr"/>
+      <c r="G1511" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1511" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1511" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1511" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1511" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1511" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1512">
+      <c r="A1512" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1512" t="inlineStr">
+        <is>
+          <t>Beira Mar vs Os Belenenses</t>
+        </is>
+      </c>
+      <c r="C1512" t="inlineStr">
+        <is>
+          <t>Os Belenenses</t>
+        </is>
+      </c>
+      <c r="D1512" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1512" t="inlineStr"/>
+      <c r="F1512" t="inlineStr"/>
+      <c r="G1512" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1512" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1512" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1512" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1512" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1512" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1513">
+      <c r="A1513" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1513" t="inlineStr">
+        <is>
+          <t>Sporting CP vs Arouca</t>
+        </is>
+      </c>
+      <c r="C1513" t="inlineStr">
+        <is>
+          <t>Sporting CP</t>
+        </is>
+      </c>
+      <c r="D1513" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1513" t="inlineStr"/>
+      <c r="F1513" t="inlineStr"/>
+      <c r="G1513" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1513" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1513" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1513" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1513" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1513" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1514">
+      <c r="A1514" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1514" t="inlineStr">
+        <is>
+          <t>Sport vs Juventude</t>
+        </is>
+      </c>
+      <c r="C1514" t="inlineStr">
+        <is>
+          <t>Sport</t>
+        </is>
+      </c>
+      <c r="D1514" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1514" t="inlineStr"/>
+      <c r="F1514" t="inlineStr"/>
+      <c r="G1514" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1514" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1514" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1514" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1514" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1514" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1515">
+      <c r="A1515" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1515" t="inlineStr">
+        <is>
+          <t>Unión (Santa Fe) vs Independiente</t>
+        </is>
+      </c>
+      <c r="C1515" t="inlineStr">
+        <is>
+          <t>Unión (Santa Fe)</t>
+        </is>
+      </c>
+      <c r="D1515" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1515" t="inlineStr"/>
+      <c r="F1515" t="inlineStr"/>
+      <c r="G1515" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1515" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1515" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1515" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1515" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1515" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1516">
+      <c r="A1516" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1516" t="inlineStr">
+        <is>
+          <t>Mirassol vs Botafogo</t>
+        </is>
+      </c>
+      <c r="C1516" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="D1516" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1516" t="inlineStr"/>
+      <c r="F1516" t="inlineStr"/>
+      <c r="G1516" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1516" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1516" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1516" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1516" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1516" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1517">
+      <c r="A1517" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1517" t="inlineStr">
+        <is>
+          <t>Sporting Cristal vs Atlético Grau</t>
+        </is>
+      </c>
+      <c r="C1517" t="inlineStr">
+        <is>
+          <t>Sporting Cristal</t>
+        </is>
+      </c>
+      <c r="D1517" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1517" t="inlineStr"/>
+      <c r="F1517" t="inlineStr"/>
+      <c r="G1517" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1517" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1517" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1517" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1517" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1517" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1518">
+      <c r="A1518" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1518" t="inlineStr">
+        <is>
+          <t>Athletic vs Botafogo-SP</t>
+        </is>
+      </c>
+      <c r="C1518" t="inlineStr">
+        <is>
+          <t>Athletic</t>
+        </is>
+      </c>
+      <c r="D1518" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1518" t="inlineStr"/>
+      <c r="F1518" t="inlineStr"/>
+      <c r="G1518" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1518" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1518" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1518" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1518" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1518" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1519">
+      <c r="A1519" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1519" t="inlineStr">
+        <is>
+          <t>Cerro Porteño vs Rubio Ñú</t>
+        </is>
+      </c>
+      <c r="C1519" t="inlineStr">
+        <is>
+          <t>Cerro Porteño</t>
+        </is>
+      </c>
+      <c r="D1519" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1519" t="inlineStr"/>
+      <c r="F1519" t="inlineStr"/>
+      <c r="G1519" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1519" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1519" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1519" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1519" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1519" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1520">
+      <c r="A1520" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1520" t="inlineStr">
+        <is>
+          <t>Guayaquil City FC vs Leones</t>
+        </is>
+      </c>
+      <c r="C1520" t="inlineStr">
+        <is>
+          <t>Guayaquil City FC</t>
+        </is>
+      </c>
+      <c r="D1520" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1520" t="inlineStr"/>
+      <c r="F1520" t="inlineStr"/>
+      <c r="G1520" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1520" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1520" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1520" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1520" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1520" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1521">
+      <c r="A1521" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1521" t="inlineStr">
+        <is>
+          <t>River Plate vs Huracán</t>
+        </is>
+      </c>
+      <c r="C1521" t="inlineStr">
+        <is>
+          <t>River Plate</t>
+        </is>
+      </c>
+      <c r="D1521" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1521" t="inlineStr"/>
+      <c r="F1521" t="inlineStr"/>
+      <c r="G1521" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1521" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1521" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1521" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1521" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1521" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1522">
+      <c r="A1522" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1522" t="inlineStr">
+        <is>
+          <t>Atlético de San Luis vs Necaxa</t>
+        </is>
+      </c>
+      <c r="C1522" t="inlineStr">
+        <is>
+          <t>Atlético de San Luis</t>
+        </is>
+      </c>
+      <c r="D1522" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1522" t="inlineStr"/>
+      <c r="F1522" t="inlineStr"/>
+      <c r="G1522" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1522" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1522" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1522" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1522" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1522" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1523">
+      <c r="A1523" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1523" t="inlineStr">
+        <is>
+          <t>Deportivo Garcilaso vs Universitario</t>
+        </is>
+      </c>
+      <c r="C1523" t="inlineStr">
+        <is>
+          <t>Universitario</t>
+        </is>
+      </c>
+      <c r="D1523" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1523" t="inlineStr"/>
+      <c r="F1523" t="inlineStr"/>
+      <c r="G1523" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H1523" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1523" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1523" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1523" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1523" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1524">
+      <c r="A1524" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1524" t="inlineStr">
+        <is>
+          <t>Brooklyn FC vs FC Tulsa</t>
+        </is>
+      </c>
+      <c r="C1524" t="inlineStr">
+        <is>
+          <t>Brooklyn FC</t>
+        </is>
+      </c>
+      <c r="D1524" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1524" t="inlineStr"/>
+      <c r="F1524" t="inlineStr"/>
+      <c r="G1524" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1524" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1524" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1524" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1524" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1524" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1525">
+      <c r="A1525" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1525" t="inlineStr">
+        <is>
+          <t>Charleston Battery vs Monterey Bay</t>
+        </is>
+      </c>
+      <c r="C1525" t="inlineStr">
+        <is>
+          <t>Charleston Battery</t>
+        </is>
+      </c>
+      <c r="D1525" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1525" t="inlineStr"/>
+      <c r="F1525" t="inlineStr"/>
+      <c r="G1525" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1525" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1525" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1525" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1525" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1525" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1526">
+      <c r="A1526" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1526" t="inlineStr">
+        <is>
+          <t>Detroit City FC vs Pittsburgh Riverhounds</t>
+        </is>
+      </c>
+      <c r="C1526" t="inlineStr">
+        <is>
+          <t>Detroit City FC</t>
+        </is>
+      </c>
+      <c r="D1526" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1526" t="inlineStr"/>
+      <c r="F1526" t="inlineStr"/>
+      <c r="G1526" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1526" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1526" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1526" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1526" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1526" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1527">
+      <c r="A1527" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1527" t="inlineStr">
+        <is>
+          <t>Lexington vs Orange County SC</t>
+        </is>
+      </c>
+      <c r="C1527" t="inlineStr">
+        <is>
+          <t>Lexington</t>
+        </is>
+      </c>
+      <c r="D1527" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1527" t="inlineStr"/>
+      <c r="F1527" t="inlineStr"/>
+      <c r="G1527" t="inlineStr">
+        <is>
+          <t>6-0</t>
+        </is>
+      </c>
+      <c r="H1527" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1527" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1527" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1527" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1527" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1528">
+      <c r="A1528" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1528" t="inlineStr">
+        <is>
+          <t>Louisville City FC vs Loudoun United FC</t>
+        </is>
+      </c>
+      <c r="C1528" t="inlineStr">
+        <is>
+          <t>Louisville City FC</t>
+        </is>
+      </c>
+      <c r="D1528" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1528" t="inlineStr"/>
+      <c r="F1528" t="inlineStr"/>
+      <c r="G1528" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1528" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1528" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1528" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1528" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1528" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1529">
+      <c r="A1529" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1529" t="inlineStr">
+        <is>
+          <t>Deportivo Cali vs Cúcuta Deportivo</t>
+        </is>
+      </c>
+      <c r="C1529" t="inlineStr">
+        <is>
+          <t>Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="D1529" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1529" t="inlineStr"/>
+      <c r="F1529" t="inlineStr"/>
+      <c r="G1529" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1529" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1529" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1529" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1529" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1529" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1530">
+      <c r="A1530" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1530" t="inlineStr">
+        <is>
+          <t>Vasco da Gama vs Coritiba</t>
+        </is>
+      </c>
+      <c r="C1530" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="D1530" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1530" t="inlineStr"/>
+      <c r="F1530" t="inlineStr"/>
+      <c r="G1530" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="H1530" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1530" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1530" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1530" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1530" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1531">
+      <c r="A1531" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1531" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes vs LAFC</t>
+        </is>
+      </c>
+      <c r="C1531" t="inlineStr">
+        <is>
+          <t>LAFC</t>
+        </is>
+      </c>
+      <c r="D1531" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1531" t="inlineStr"/>
+      <c r="F1531" t="inlineStr"/>
+      <c r="G1531" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1531" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1531" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1531" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1531" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1531" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1532">
+      <c r="A1532" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1532" t="inlineStr">
+        <is>
+          <t>CF Montréal vs Columbus Crew</t>
+        </is>
+      </c>
+      <c r="C1532" t="inlineStr">
+        <is>
+          <t>CF Montréal</t>
+        </is>
+      </c>
+      <c r="D1532" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1532" t="inlineStr"/>
+      <c r="F1532" t="inlineStr"/>
+      <c r="G1532" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1532" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1532" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1532" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1532" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1532" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1533">
+      <c r="A1533" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1533" t="inlineStr">
+        <is>
+          <t>New England Revolution vs Orlando City SC</t>
+        </is>
+      </c>
+      <c r="C1533" t="inlineStr">
+        <is>
+          <t>New England Revolution</t>
+        </is>
+      </c>
+      <c r="D1533" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1533" t="inlineStr"/>
+      <c r="F1533" t="inlineStr"/>
+      <c r="G1533" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="H1533" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1533" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1533" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1533" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1533" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1534">
+      <c r="A1534" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1534" t="inlineStr">
+        <is>
+          <t>Rhode Island FC vs Miami FC</t>
+        </is>
+      </c>
+      <c r="C1534" t="inlineStr">
+        <is>
+          <t>Rhode Island FC</t>
+        </is>
+      </c>
+      <c r="D1534" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1534" t="inlineStr"/>
+      <c r="F1534" t="inlineStr"/>
+      <c r="G1534" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1534" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1534" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1534" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1534" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1534" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1535">
+      <c r="A1535" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1535" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rowdies vs Birmingham Legion FC</t>
+        </is>
+      </c>
+      <c r="C1535" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rowdies</t>
+        </is>
+      </c>
+      <c r="D1535" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1535" t="inlineStr"/>
+      <c r="F1535" t="inlineStr"/>
+      <c r="G1535" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H1535" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1535" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1535" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1535" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1535" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1536">
+      <c r="A1536" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1536" t="inlineStr">
+        <is>
+          <t>D.C. United vs Charlotte FC</t>
+        </is>
+      </c>
+      <c r="C1536" t="inlineStr">
+        <is>
+          <t>Charlotte FC</t>
+        </is>
+      </c>
+      <c r="D1536" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1536" t="inlineStr"/>
+      <c r="F1536" t="inlineStr"/>
+      <c r="G1536" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1536" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1536" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1536" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1536" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1536" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1537">
+      <c r="A1537" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1537" t="inlineStr">
+        <is>
+          <t>São Paulo vs Internacional</t>
+        </is>
+      </c>
+      <c r="C1537" t="inlineStr">
+        <is>
+          <t>São Paulo</t>
+        </is>
+      </c>
+      <c r="D1537" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1537" t="inlineStr"/>
+      <c r="F1537" t="inlineStr"/>
+      <c r="G1537" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1537" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1537" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1537" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1537" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1537" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1538">
+      <c r="A1538" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1538" t="inlineStr">
+        <is>
+          <t>Emelec vs Libertad (Ecuador)</t>
+        </is>
+      </c>
+      <c r="C1538" t="inlineStr">
+        <is>
+          <t>Emelec</t>
+        </is>
+      </c>
+      <c r="D1538" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1538" t="inlineStr"/>
+      <c r="F1538" t="inlineStr"/>
+      <c r="G1538" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1538" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1538" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1538" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1538" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1538" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1539">
+      <c r="A1539" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1539" t="inlineStr">
+        <is>
+          <t>Instituto (Córdoba) vs Talleres (Córdoba)</t>
+        </is>
+      </c>
+      <c r="C1539" t="inlineStr">
+        <is>
+          <t>Instituto (Córdoba)</t>
+        </is>
+      </c>
+      <c r="D1539" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1539" t="inlineStr"/>
+      <c r="F1539" t="inlineStr"/>
+      <c r="G1539" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1539" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1539" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1539" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1539" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1539" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1540">
+      <c r="A1540" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1540" t="inlineStr">
+        <is>
+          <t>Minnesota United FC vs LA Galaxy</t>
+        </is>
+      </c>
+      <c r="C1540" t="inlineStr">
+        <is>
+          <t>Minnesota United FC</t>
+        </is>
+      </c>
+      <c r="D1540" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1540" t="inlineStr"/>
+      <c r="F1540" t="inlineStr"/>
+      <c r="G1540" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H1540" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1540" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1540" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1540" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1540" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1541">
+      <c r="A1541" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1541" t="inlineStr">
+        <is>
+          <t>Houston Dynamo FC vs FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="C1541" t="inlineStr">
+        <is>
+          <t>Houston Dynamo FC</t>
+        </is>
+      </c>
+      <c r="D1541" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1541" t="inlineStr"/>
+      <c r="F1541" t="inlineStr"/>
+      <c r="G1541" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1541" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1541" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1541" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1541" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1541" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1542">
+      <c r="A1542" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1542" t="inlineStr">
+        <is>
+          <t>Sporting Kansas City vs Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="C1542" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="D1542" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1542" t="inlineStr"/>
+      <c r="F1542" t="inlineStr"/>
+      <c r="G1542" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="H1542" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1542" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1542" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1542" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1542" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1543">
+      <c r="A1543" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1543" t="inlineStr">
+        <is>
+          <t>FC Dallas vs Austin FC</t>
+        </is>
+      </c>
+      <c r="C1543" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="D1543" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1543" t="inlineStr"/>
+      <c r="F1543" t="inlineStr"/>
+      <c r="G1543" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1543" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1543" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1543" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1543" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1543" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1544">
+      <c r="A1544" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1544" t="inlineStr">
+        <is>
+          <t>St. Louis CITY SC vs Toronto FC</t>
+        </is>
+      </c>
+      <c r="C1544" t="inlineStr">
+        <is>
+          <t>St. Louis CITY SC</t>
+        </is>
+      </c>
+      <c r="D1544" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1544" t="inlineStr"/>
+      <c r="F1544" t="inlineStr"/>
+      <c r="G1544" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1544" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1544" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1544" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1544" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1544" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1545">
+      <c r="A1545" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1545" t="inlineStr">
+        <is>
+          <t>Deportivo Pasto vs Once Caldas</t>
+        </is>
+      </c>
+      <c r="C1545" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="D1545" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1545" t="inlineStr"/>
+      <c r="F1545" t="inlineStr"/>
+      <c r="G1545" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1545" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1545" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1545" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1545" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1545" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1546">
+      <c r="A1546" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1546" t="inlineStr">
+        <is>
+          <t>Melgar vs Sport Boys</t>
+        </is>
+      </c>
+      <c r="C1546" t="inlineStr">
+        <is>
+          <t>Melgar</t>
+        </is>
+      </c>
+      <c r="D1546" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1546" t="inlineStr"/>
+      <c r="F1546" t="inlineStr"/>
+      <c r="G1546" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1546" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1546" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1546" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1546" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1546" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1547">
+      <c r="A1547" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1547" t="inlineStr">
+        <is>
+          <t>Colorado Rapids vs Seattle Sounders FC</t>
+        </is>
+      </c>
+      <c r="C1547" t="inlineStr">
+        <is>
+          <t>Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="D1547" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1547" t="inlineStr"/>
+      <c r="F1547" t="inlineStr"/>
+      <c r="G1547" t="inlineStr">
+        <is>
+          <t>3-3</t>
+        </is>
+      </c>
+      <c r="H1547" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1547" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1547" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1547" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1547" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1548">
+      <c r="A1548" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1548" t="inlineStr">
+        <is>
+          <t>Real Salt Lake vs Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="C1548" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="D1548" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1548" t="inlineStr"/>
+      <c r="F1548" t="inlineStr"/>
+      <c r="G1548" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H1548" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1548" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1548" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1548" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1548" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1549">
+      <c r="A1549" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1549" t="inlineStr">
+        <is>
+          <t>Nashville SC vs Chicago Fire FC</t>
+        </is>
+      </c>
+      <c r="C1549" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="D1549" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1549" t="inlineStr"/>
+      <c r="F1549" t="inlineStr"/>
+      <c r="G1549" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1549" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1549" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1549" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1549" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1549" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1550">
+      <c r="A1550" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1550" t="inlineStr">
+        <is>
+          <t>Portland Timbers vs Atlanta United FC</t>
+        </is>
+      </c>
+      <c r="C1550" t="inlineStr">
+        <is>
+          <t>Portland Timbers</t>
+        </is>
+      </c>
+      <c r="D1550" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1550" t="inlineStr"/>
+      <c r="F1550" t="inlineStr"/>
+      <c r="G1550" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1550" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1550" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1550" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1550" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1550" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1551">
+      <c r="A1551" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B1551" t="inlineStr">
+        <is>
+          <t>América vs Guadalajara</t>
+        </is>
+      </c>
+      <c r="C1551" t="inlineStr">
+        <is>
+          <t>América</t>
+        </is>
+      </c>
+      <c r="D1551" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1551" t="inlineStr"/>
+      <c r="F1551" t="inlineStr"/>
+      <c r="G1551" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1551" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1551" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1551" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1551" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1551" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -66959,7 +72043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67688,6 +72772,25 @@
       </c>
       <c r="E39" t="n">
         <v>50</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>108</v>
+      </c>
+      <c r="C40" t="n">
+        <v>76</v>
+      </c>
+      <c r="D40" t="n">
+        <v>70.40000000000001</v>
+      </c>
+      <c r="E40" t="n">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -67701,7 +72804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E202"/>
+  <dimension ref="A1:E211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71952,6 +77055,195 @@
         <v>0</v>
       </c>
     </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>siguen_empatados_70</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>2</v>
+      </c>
+      <c r="D203" t="n">
+        <v>0</v>
+      </c>
+      <c r="E203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>7</v>
+      </c>
+      <c r="D204" t="n">
+        <v>4</v>
+      </c>
+      <c r="E204" t="n">
+        <v>57.1</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>18</v>
+      </c>
+      <c r="D205" t="n">
+        <v>1</v>
+      </c>
+      <c r="E205" t="n">
+        <v>5.6</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>10</v>
+      </c>
+      <c r="D206" t="n">
+        <v>1</v>
+      </c>
+      <c r="E206" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>15</v>
+      </c>
+      <c r="D207" t="n">
+        <v>3</v>
+      </c>
+      <c r="E207" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>8</v>
+      </c>
+      <c r="D208" t="n">
+        <v>1</v>
+      </c>
+      <c r="E208" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>6</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0</v>
+      </c>
+      <c r="E209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>3</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0</v>
+      </c>
+      <c r="E210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>gol_de_cierre</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>3</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0</v>
+      </c>
+      <c r="E211" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1551"/>
+  <dimension ref="A1:L1638"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66869,8 +66869,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1444" t="inlineStr"/>
-      <c r="F1444" t="inlineStr"/>
       <c r="G1444" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -66917,8 +66915,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1445" t="inlineStr"/>
-      <c r="F1445" t="inlineStr"/>
       <c r="G1445" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -66965,8 +66961,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1446" t="inlineStr"/>
-      <c r="F1446" t="inlineStr"/>
       <c r="G1446" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -67013,8 +67007,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1447" t="inlineStr"/>
-      <c r="F1447" t="inlineStr"/>
       <c r="G1447" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -67061,8 +67053,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1448" t="inlineStr"/>
-      <c r="F1448" t="inlineStr"/>
       <c r="G1448" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -67109,8 +67099,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1449" t="inlineStr"/>
-      <c r="F1449" t="inlineStr"/>
       <c r="G1449" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -67157,8 +67145,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1450" t="inlineStr"/>
-      <c r="F1450" t="inlineStr"/>
       <c r="G1450" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -67205,8 +67191,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1451" t="inlineStr"/>
-      <c r="F1451" t="inlineStr"/>
       <c r="G1451" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -67253,8 +67237,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1452" t="inlineStr"/>
-      <c r="F1452" t="inlineStr"/>
       <c r="G1452" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -67301,8 +67283,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1453" t="inlineStr"/>
-      <c r="F1453" t="inlineStr"/>
       <c r="G1453" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -67349,8 +67329,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1454" t="inlineStr"/>
-      <c r="F1454" t="inlineStr"/>
       <c r="G1454" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -67397,8 +67375,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1455" t="inlineStr"/>
-      <c r="F1455" t="inlineStr"/>
       <c r="G1455" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -67445,8 +67421,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1456" t="inlineStr"/>
-      <c r="F1456" t="inlineStr"/>
       <c r="G1456" t="inlineStr">
         <is>
           <t>3-4</t>
@@ -67493,8 +67467,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1457" t="inlineStr"/>
-      <c r="F1457" t="inlineStr"/>
       <c r="G1457" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -67541,8 +67513,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1458" t="inlineStr"/>
-      <c r="F1458" t="inlineStr"/>
       <c r="G1458" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -67589,8 +67559,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1459" t="inlineStr"/>
-      <c r="F1459" t="inlineStr"/>
       <c r="G1459" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -67637,8 +67605,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1460" t="inlineStr"/>
-      <c r="F1460" t="inlineStr"/>
       <c r="G1460" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -67685,8 +67651,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1461" t="inlineStr"/>
-      <c r="F1461" t="inlineStr"/>
       <c r="G1461" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -67733,8 +67697,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1462" t="inlineStr"/>
-      <c r="F1462" t="inlineStr"/>
       <c r="G1462" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -67781,8 +67743,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1463" t="inlineStr"/>
-      <c r="F1463" t="inlineStr"/>
       <c r="G1463" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -67829,8 +67789,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1464" t="inlineStr"/>
-      <c r="F1464" t="inlineStr"/>
       <c r="G1464" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -67877,8 +67835,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1465" t="inlineStr"/>
-      <c r="F1465" t="inlineStr"/>
       <c r="G1465" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -67925,8 +67881,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1466" t="inlineStr"/>
-      <c r="F1466" t="inlineStr"/>
       <c r="G1466" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -67973,8 +67927,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1467" t="inlineStr"/>
-      <c r="F1467" t="inlineStr"/>
       <c r="G1467" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -68021,8 +67973,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1468" t="inlineStr"/>
-      <c r="F1468" t="inlineStr"/>
       <c r="G1468" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -68069,8 +68019,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1469" t="inlineStr"/>
-      <c r="F1469" t="inlineStr"/>
       <c r="G1469" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -68117,8 +68065,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1470" t="inlineStr"/>
-      <c r="F1470" t="inlineStr"/>
       <c r="G1470" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -68165,8 +68111,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1471" t="inlineStr"/>
-      <c r="F1471" t="inlineStr"/>
       <c r="G1471" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -68213,8 +68157,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1472" t="inlineStr"/>
-      <c r="F1472" t="inlineStr"/>
       <c r="G1472" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -68261,8 +68203,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1473" t="inlineStr"/>
-      <c r="F1473" t="inlineStr"/>
       <c r="G1473" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -68309,8 +68249,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1474" t="inlineStr"/>
-      <c r="F1474" t="inlineStr"/>
       <c r="G1474" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -68357,8 +68295,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1475" t="inlineStr"/>
-      <c r="F1475" t="inlineStr"/>
       <c r="G1475" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -68405,8 +68341,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1476" t="inlineStr"/>
-      <c r="F1476" t="inlineStr"/>
       <c r="G1476" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -68453,8 +68387,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1477" t="inlineStr"/>
-      <c r="F1477" t="inlineStr"/>
       <c r="G1477" t="inlineStr">
         <is>
           <t>0-4</t>
@@ -68501,8 +68433,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1478" t="inlineStr"/>
-      <c r="F1478" t="inlineStr"/>
       <c r="G1478" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -68549,8 +68479,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1479" t="inlineStr"/>
-      <c r="F1479" t="inlineStr"/>
       <c r="G1479" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -68597,8 +68525,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1480" t="inlineStr"/>
-      <c r="F1480" t="inlineStr"/>
       <c r="G1480" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -68645,8 +68571,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1481" t="inlineStr"/>
-      <c r="F1481" t="inlineStr"/>
       <c r="G1481" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -68693,8 +68617,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1482" t="inlineStr"/>
-      <c r="F1482" t="inlineStr"/>
       <c r="G1482" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -68741,8 +68663,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1483" t="inlineStr"/>
-      <c r="F1483" t="inlineStr"/>
       <c r="G1483" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -68789,8 +68709,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1484" t="inlineStr"/>
-      <c r="F1484" t="inlineStr"/>
       <c r="G1484" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -68837,8 +68755,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1485" t="inlineStr"/>
-      <c r="F1485" t="inlineStr"/>
       <c r="G1485" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -68885,8 +68801,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1486" t="inlineStr"/>
-      <c r="F1486" t="inlineStr"/>
       <c r="G1486" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -68933,8 +68847,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1487" t="inlineStr"/>
-      <c r="F1487" t="inlineStr"/>
       <c r="G1487" t="inlineStr">
         <is>
           <t>5-0</t>
@@ -68981,8 +68893,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1488" t="inlineStr"/>
-      <c r="F1488" t="inlineStr"/>
       <c r="G1488" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -69029,8 +68939,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1489" t="inlineStr"/>
-      <c r="F1489" t="inlineStr"/>
       <c r="G1489" t="inlineStr">
         <is>
           <t>5-0</t>
@@ -69077,8 +68985,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1490" t="inlineStr"/>
-      <c r="F1490" t="inlineStr"/>
       <c r="G1490" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -69125,8 +69031,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1491" t="inlineStr"/>
-      <c r="F1491" t="inlineStr"/>
       <c r="G1491" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -69173,8 +69077,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1492" t="inlineStr"/>
-      <c r="F1492" t="inlineStr"/>
       <c r="G1492" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -69221,8 +69123,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1493" t="inlineStr"/>
-      <c r="F1493" t="inlineStr"/>
       <c r="G1493" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -69269,8 +69169,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1494" t="inlineStr"/>
-      <c r="F1494" t="inlineStr"/>
       <c r="G1494" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -69317,8 +69215,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1495" t="inlineStr"/>
-      <c r="F1495" t="inlineStr"/>
       <c r="G1495" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -69365,8 +69261,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1496" t="inlineStr"/>
-      <c r="F1496" t="inlineStr"/>
       <c r="G1496" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -69413,8 +69307,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1497" t="inlineStr"/>
-      <c r="F1497" t="inlineStr"/>
       <c r="G1497" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -69461,8 +69353,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1498" t="inlineStr"/>
-      <c r="F1498" t="inlineStr"/>
       <c r="G1498" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -69509,8 +69399,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1499" t="inlineStr"/>
-      <c r="F1499" t="inlineStr"/>
       <c r="G1499" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -69557,8 +69445,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1500" t="inlineStr"/>
-      <c r="F1500" t="inlineStr"/>
       <c r="G1500" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -69605,8 +69491,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1501" t="inlineStr"/>
-      <c r="F1501" t="inlineStr"/>
       <c r="G1501" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -69653,8 +69537,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1502" t="inlineStr"/>
-      <c r="F1502" t="inlineStr"/>
       <c r="G1502" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -69701,8 +69583,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1503" t="inlineStr"/>
-      <c r="F1503" t="inlineStr"/>
       <c r="G1503" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -69749,8 +69629,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1504" t="inlineStr"/>
-      <c r="F1504" t="inlineStr"/>
       <c r="G1504" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -69797,8 +69675,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1505" t="inlineStr"/>
-      <c r="F1505" t="inlineStr"/>
       <c r="G1505" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -69845,8 +69721,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1506" t="inlineStr"/>
-      <c r="F1506" t="inlineStr"/>
       <c r="G1506" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -69893,8 +69767,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1507" t="inlineStr"/>
-      <c r="F1507" t="inlineStr"/>
       <c r="G1507" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -69941,8 +69813,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1508" t="inlineStr"/>
-      <c r="F1508" t="inlineStr"/>
       <c r="G1508" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -69989,8 +69859,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1509" t="inlineStr"/>
-      <c r="F1509" t="inlineStr"/>
       <c r="G1509" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -70037,8 +69905,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1510" t="inlineStr"/>
-      <c r="F1510" t="inlineStr"/>
       <c r="G1510" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -70085,8 +69951,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1511" t="inlineStr"/>
-      <c r="F1511" t="inlineStr"/>
       <c r="G1511" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -70133,8 +69997,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1512" t="inlineStr"/>
-      <c r="F1512" t="inlineStr"/>
       <c r="G1512" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -70181,8 +70043,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1513" t="inlineStr"/>
-      <c r="F1513" t="inlineStr"/>
       <c r="G1513" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -70229,8 +70089,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1514" t="inlineStr"/>
-      <c r="F1514" t="inlineStr"/>
       <c r="G1514" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -70277,8 +70135,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1515" t="inlineStr"/>
-      <c r="F1515" t="inlineStr"/>
       <c r="G1515" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -70325,8 +70181,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1516" t="inlineStr"/>
-      <c r="F1516" t="inlineStr"/>
       <c r="G1516" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -70373,8 +70227,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1517" t="inlineStr"/>
-      <c r="F1517" t="inlineStr"/>
       <c r="G1517" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -70421,8 +70273,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1518" t="inlineStr"/>
-      <c r="F1518" t="inlineStr"/>
       <c r="G1518" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -70469,8 +70319,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1519" t="inlineStr"/>
-      <c r="F1519" t="inlineStr"/>
       <c r="G1519" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -70517,8 +70365,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1520" t="inlineStr"/>
-      <c r="F1520" t="inlineStr"/>
       <c r="G1520" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -70565,8 +70411,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1521" t="inlineStr"/>
-      <c r="F1521" t="inlineStr"/>
       <c r="G1521" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -70613,8 +70457,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1522" t="inlineStr"/>
-      <c r="F1522" t="inlineStr"/>
       <c r="G1522" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -70661,8 +70503,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1523" t="inlineStr"/>
-      <c r="F1523" t="inlineStr"/>
       <c r="G1523" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -70709,8 +70549,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1524" t="inlineStr"/>
-      <c r="F1524" t="inlineStr"/>
       <c r="G1524" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -70757,8 +70595,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1525" t="inlineStr"/>
-      <c r="F1525" t="inlineStr"/>
       <c r="G1525" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -70805,8 +70641,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1526" t="inlineStr"/>
-      <c r="F1526" t="inlineStr"/>
       <c r="G1526" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -70853,8 +70687,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1527" t="inlineStr"/>
-      <c r="F1527" t="inlineStr"/>
       <c r="G1527" t="inlineStr">
         <is>
           <t>6-0</t>
@@ -70901,8 +70733,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1528" t="inlineStr"/>
-      <c r="F1528" t="inlineStr"/>
       <c r="G1528" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -70949,8 +70779,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1529" t="inlineStr"/>
-      <c r="F1529" t="inlineStr"/>
       <c r="G1529" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -70997,8 +70825,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1530" t="inlineStr"/>
-      <c r="F1530" t="inlineStr"/>
       <c r="G1530" t="inlineStr">
         <is>
           <t>5-0</t>
@@ -71045,8 +70871,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1531" t="inlineStr"/>
-      <c r="F1531" t="inlineStr"/>
       <c r="G1531" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -71093,8 +70917,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1532" t="inlineStr"/>
-      <c r="F1532" t="inlineStr"/>
       <c r="G1532" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -71141,8 +70963,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1533" t="inlineStr"/>
-      <c r="F1533" t="inlineStr"/>
       <c r="G1533" t="inlineStr">
         <is>
           <t>4-2</t>
@@ -71189,8 +71009,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1534" t="inlineStr"/>
-      <c r="F1534" t="inlineStr"/>
       <c r="G1534" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -71237,8 +71055,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1535" t="inlineStr"/>
-      <c r="F1535" t="inlineStr"/>
       <c r="G1535" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -71285,8 +71101,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1536" t="inlineStr"/>
-      <c r="F1536" t="inlineStr"/>
       <c r="G1536" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -71333,8 +71147,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1537" t="inlineStr"/>
-      <c r="F1537" t="inlineStr"/>
       <c r="G1537" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -71381,8 +71193,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1538" t="inlineStr"/>
-      <c r="F1538" t="inlineStr"/>
       <c r="G1538" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -71429,8 +71239,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1539" t="inlineStr"/>
-      <c r="F1539" t="inlineStr"/>
       <c r="G1539" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -71477,8 +71285,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1540" t="inlineStr"/>
-      <c r="F1540" t="inlineStr"/>
       <c r="G1540" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -71525,8 +71331,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1541" t="inlineStr"/>
-      <c r="F1541" t="inlineStr"/>
       <c r="G1541" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -71573,8 +71377,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1542" t="inlineStr"/>
-      <c r="F1542" t="inlineStr"/>
       <c r="G1542" t="inlineStr">
         <is>
           <t>3-4</t>
@@ -71621,8 +71423,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1543" t="inlineStr"/>
-      <c r="F1543" t="inlineStr"/>
       <c r="G1543" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -71669,8 +71469,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1544" t="inlineStr"/>
-      <c r="F1544" t="inlineStr"/>
       <c r="G1544" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -71717,8 +71515,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1545" t="inlineStr"/>
-      <c r="F1545" t="inlineStr"/>
       <c r="G1545" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -71765,8 +71561,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1546" t="inlineStr"/>
-      <c r="F1546" t="inlineStr"/>
       <c r="G1546" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -71813,8 +71607,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1547" t="inlineStr"/>
-      <c r="F1547" t="inlineStr"/>
       <c r="G1547" t="inlineStr">
         <is>
           <t>3-3</t>
@@ -71861,8 +71653,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1548" t="inlineStr"/>
-      <c r="F1548" t="inlineStr"/>
       <c r="G1548" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -71909,8 +71699,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1549" t="inlineStr"/>
-      <c r="F1549" t="inlineStr"/>
       <c r="G1549" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -71957,8 +71745,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1550" t="inlineStr"/>
-      <c r="F1550" t="inlineStr"/>
       <c r="G1550" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -72005,8 +71791,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1551" t="inlineStr"/>
-      <c r="F1551" t="inlineStr"/>
       <c r="G1551" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -72027,6 +71811,4182 @@
         <v>0</v>
       </c>
       <c r="L1551" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1552">
+      <c r="A1552" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1552" t="inlineStr">
+        <is>
+          <t>Fafe vs Juventude Lajense</t>
+        </is>
+      </c>
+      <c r="C1552" t="inlineStr">
+        <is>
+          <t>Fafe</t>
+        </is>
+      </c>
+      <c r="D1552" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1552" t="inlineStr"/>
+      <c r="F1552" t="inlineStr"/>
+      <c r="G1552" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H1552" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1552" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1552" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1552" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1552" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1553">
+      <c r="A1553" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1553" t="inlineStr">
+        <is>
+          <t>Feyenoord Rotterdam vs FC Utrecht</t>
+        </is>
+      </c>
+      <c r="C1553" t="inlineStr">
+        <is>
+          <t>Feyenoord Rotterdam</t>
+        </is>
+      </c>
+      <c r="D1553" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1553" t="inlineStr"/>
+      <c r="F1553" t="inlineStr"/>
+      <c r="G1553" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="H1553" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1553" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1553" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1553" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1553" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1554">
+      <c r="A1554" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1554" t="inlineStr">
+        <is>
+          <t>Fiorentina vs Napoli</t>
+        </is>
+      </c>
+      <c r="C1554" t="inlineStr">
+        <is>
+          <t>Napoli</t>
+        </is>
+      </c>
+      <c r="D1554" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1554" t="inlineStr"/>
+      <c r="F1554" t="inlineStr"/>
+      <c r="G1554" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1554" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1554" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1554" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1554" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1554" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1555">
+      <c r="A1555" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1555" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers vs West Bromwich Albion</t>
+        </is>
+      </c>
+      <c r="C1555" t="inlineStr">
+        <is>
+          <t>Wolverhampton Wanderers</t>
+        </is>
+      </c>
+      <c r="D1555" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1555" t="inlineStr"/>
+      <c r="F1555" t="inlineStr"/>
+      <c r="G1555" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1555" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1555" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1555" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1555" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1555" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1556">
+      <c r="A1556" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1556" t="inlineStr">
+        <is>
+          <t>Celtic vs Rangers</t>
+        </is>
+      </c>
+      <c r="C1556" t="inlineStr">
+        <is>
+          <t>Celtic</t>
+        </is>
+      </c>
+      <c r="D1556" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1556" t="inlineStr"/>
+      <c r="F1556" t="inlineStr"/>
+      <c r="G1556" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1556" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1556" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1556" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1556" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1556" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1557">
+      <c r="A1557" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1557" t="inlineStr">
+        <is>
+          <t>Antwerp vs Union St.-Gilloise</t>
+        </is>
+      </c>
+      <c r="C1557" t="inlineStr">
+        <is>
+          <t>Union St.-Gilloise</t>
+        </is>
+      </c>
+      <c r="D1557" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1557" t="inlineStr"/>
+      <c r="F1557" t="inlineStr"/>
+      <c r="G1557" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1557" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1557" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1557" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1557" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1557" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1558">
+      <c r="A1558" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1558" t="inlineStr">
+        <is>
+          <t>Arminia Bielefeld vs 1. FC Heidenheim 1846</t>
+        </is>
+      </c>
+      <c r="C1558" t="inlineStr">
+        <is>
+          <t>Arminia Bielefeld</t>
+        </is>
+      </c>
+      <c r="D1558" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1558" t="inlineStr"/>
+      <c r="F1558" t="inlineStr"/>
+      <c r="G1558" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1558" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1558" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1558" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1558" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1558" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1559">
+      <c r="A1559" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1559" t="inlineStr">
+        <is>
+          <t>Energie Cottbus vs St. Pauli</t>
+        </is>
+      </c>
+      <c r="C1559" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="D1559" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1559" t="inlineStr"/>
+      <c r="F1559" t="inlineStr"/>
+      <c r="G1559" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1559" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1559" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1559" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1559" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1559" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1560">
+      <c r="A1560" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1560" t="inlineStr">
+        <is>
+          <t>Hannover 96 vs VfL Bochum</t>
+        </is>
+      </c>
+      <c r="C1560" t="inlineStr">
+        <is>
+          <t>Hannover 96</t>
+        </is>
+      </c>
+      <c r="D1560" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1560" t="inlineStr"/>
+      <c r="F1560" t="inlineStr"/>
+      <c r="G1560" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1560" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1560" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1560" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1560" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1560" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1561">
+      <c r="A1561" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1561" t="inlineStr">
+        <is>
+          <t>Getafe vs Málaga</t>
+        </is>
+      </c>
+      <c r="C1561" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="D1561" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1561" t="inlineStr"/>
+      <c r="F1561" t="inlineStr"/>
+      <c r="G1561" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1561" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1561" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1561" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1561" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1561" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1562">
+      <c r="A1562" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1562" t="inlineStr">
+        <is>
+          <t>CD Sabadell vs Real Oviedo</t>
+        </is>
+      </c>
+      <c r="C1562" t="inlineStr">
+        <is>
+          <t>CD Sabadell</t>
+        </is>
+      </c>
+      <c r="D1562" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1562" t="inlineStr"/>
+      <c r="F1562" t="inlineStr"/>
+      <c r="G1562" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1562" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1562" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1562" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1562" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1562" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1563">
+      <c r="A1563" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1563" t="inlineStr">
+        <is>
+          <t>Norwich City vs Bolton Wanderers</t>
+        </is>
+      </c>
+      <c r="C1563" t="inlineStr">
+        <is>
+          <t>Norwich City</t>
+        </is>
+      </c>
+      <c r="D1563" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1563" t="inlineStr"/>
+      <c r="F1563" t="inlineStr"/>
+      <c r="G1563" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="H1563" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1563" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1563" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1563" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1563" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1564">
+      <c r="A1564" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1564" t="inlineStr">
+        <is>
+          <t>AZ Alkmaar vs Telstar</t>
+        </is>
+      </c>
+      <c r="C1564" t="inlineStr">
+        <is>
+          <t>AZ Alkmaar</t>
+        </is>
+      </c>
+      <c r="D1564" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1564" t="inlineStr"/>
+      <c r="F1564" t="inlineStr"/>
+      <c r="G1564" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1564" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1564" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1564" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1564" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1564" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1565">
+      <c r="A1565" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1565" t="inlineStr">
+        <is>
+          <t>FC Twente vs PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="C1565" t="inlineStr">
+        <is>
+          <t>PSV Eindhoven</t>
+        </is>
+      </c>
+      <c r="D1565" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1565" t="inlineStr"/>
+      <c r="F1565" t="inlineStr"/>
+      <c r="G1565" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1565" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1565" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1565" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1565" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1565" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1566">
+      <c r="A1566" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1566" t="inlineStr">
+        <is>
+          <t>AFC Bournemouth vs Liverpool</t>
+        </is>
+      </c>
+      <c r="C1566" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="D1566" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1566" t="inlineStr"/>
+      <c r="F1566" t="inlineStr"/>
+      <c r="G1566" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1566" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1566" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1566" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1566" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1566" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1567">
+      <c r="A1567" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1567" t="inlineStr">
+        <is>
+          <t>Leeds United vs Crystal Palace</t>
+        </is>
+      </c>
+      <c r="C1567" t="inlineStr">
+        <is>
+          <t>Leeds United</t>
+        </is>
+      </c>
+      <c r="D1567" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1567" t="inlineStr"/>
+      <c r="F1567" t="inlineStr"/>
+      <c r="G1567" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1567" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1567" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1567" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1567" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1567" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1568">
+      <c r="A1568" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1568" t="inlineStr">
+        <is>
+          <t>Manchester City vs Sunderland</t>
+        </is>
+      </c>
+      <c r="C1568" t="inlineStr">
+        <is>
+          <t>Manchester City</t>
+        </is>
+      </c>
+      <c r="D1568" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1568" t="inlineStr"/>
+      <c r="F1568" t="inlineStr"/>
+      <c r="G1568" t="inlineStr">
+        <is>
+          <t>5-3</t>
+        </is>
+      </c>
+      <c r="H1568" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1568" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1568" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1568" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1568" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1569">
+      <c r="A1569" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1569" t="inlineStr">
+        <is>
+          <t>Frosinone vs Como</t>
+        </is>
+      </c>
+      <c r="C1569" t="inlineStr">
+        <is>
+          <t>Como</t>
+        </is>
+      </c>
+      <c r="D1569" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1569" t="inlineStr"/>
+      <c r="F1569" t="inlineStr"/>
+      <c r="G1569" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1569" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1569" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1569" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1569" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1569" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1570">
+      <c r="A1570" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1570" t="inlineStr">
+        <is>
+          <t>Arezzo vs Sudtirol</t>
+        </is>
+      </c>
+      <c r="C1570" t="inlineStr">
+        <is>
+          <t>Arezzo</t>
+        </is>
+      </c>
+      <c r="D1570" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1570" t="inlineStr"/>
+      <c r="F1570" t="inlineStr"/>
+      <c r="G1570" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="H1570" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1570" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1570" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1570" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1570" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1571">
+      <c r="A1571" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1571" t="inlineStr">
+        <is>
+          <t>Hellas Verona vs Vicenza</t>
+        </is>
+      </c>
+      <c r="C1571" t="inlineStr">
+        <is>
+          <t>Hellas Verona</t>
+        </is>
+      </c>
+      <c r="D1571" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1571" t="inlineStr"/>
+      <c r="F1571" t="inlineStr"/>
+      <c r="G1571" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1571" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1571" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1571" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1571" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1571" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1572">
+      <c r="A1572" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1572" t="inlineStr">
+        <is>
+          <t>AJ Auxerre vs Brest</t>
+        </is>
+      </c>
+      <c r="C1572" t="inlineStr">
+        <is>
+          <t>Brest</t>
+        </is>
+      </c>
+      <c r="D1572" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1572" t="inlineStr"/>
+      <c r="F1572" t="inlineStr"/>
+      <c r="G1572" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1572" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1572" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1572" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1572" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1572" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1573">
+      <c r="A1573" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1573" t="inlineStr">
+        <is>
+          <t>CD Cinfães vs Leixoes</t>
+        </is>
+      </c>
+      <c r="C1573" t="inlineStr">
+        <is>
+          <t>Leixoes</t>
+        </is>
+      </c>
+      <c r="D1573" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1573" t="inlineStr"/>
+      <c r="F1573" t="inlineStr"/>
+      <c r="G1573" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="H1573" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1573" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1573" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1573" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1573" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1574" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen vs RB Leipzig</t>
+        </is>
+      </c>
+      <c r="C1574" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="D1574" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1574" t="inlineStr"/>
+      <c r="F1574" t="inlineStr"/>
+      <c r="G1574" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1574" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1574" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1574" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1574" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1574" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1575" t="inlineStr">
+        <is>
+          <t>Sint-Truidense vs KVC Westerlo</t>
+        </is>
+      </c>
+      <c r="C1575" t="inlineStr">
+        <is>
+          <t>Sint-Truidense</t>
+        </is>
+      </c>
+      <c r="D1575" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1575" t="inlineStr"/>
+      <c r="F1575" t="inlineStr"/>
+      <c r="G1575" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1575" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1575" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1575" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1575" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1575" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1576" t="inlineStr">
+        <is>
+          <t>Grêmio vs Palmeiras</t>
+        </is>
+      </c>
+      <c r="C1576" t="inlineStr">
+        <is>
+          <t>Palmeiras</t>
+        </is>
+      </c>
+      <c r="D1576" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1576" t="inlineStr"/>
+      <c r="F1576" t="inlineStr"/>
+      <c r="G1576" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1576" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1576" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1576" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1576" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1576" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1577" t="inlineStr">
+        <is>
+          <t>Levadiakos vs Olympiacos</t>
+        </is>
+      </c>
+      <c r="C1577" t="inlineStr">
+        <is>
+          <t>Olympiacos</t>
+        </is>
+      </c>
+      <c r="D1577" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1577" t="inlineStr"/>
+      <c r="F1577" t="inlineStr"/>
+      <c r="G1577" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1577" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1577" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1577" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1577" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1577" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1578" t="inlineStr">
+        <is>
+          <t>Fenerbahce vs Eyupspor</t>
+        </is>
+      </c>
+      <c r="C1578" t="inlineStr">
+        <is>
+          <t>Fenerbahce</t>
+        </is>
+      </c>
+      <c r="D1578" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1578" t="inlineStr"/>
+      <c r="F1578" t="inlineStr"/>
+      <c r="G1578" t="inlineStr">
+        <is>
+          <t>8-0</t>
+        </is>
+      </c>
+      <c r="H1578" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1578" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1578" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1578" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1578" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1579" t="inlineStr">
+        <is>
+          <t>Ponte Preta vs CRB</t>
+        </is>
+      </c>
+      <c r="C1579" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="D1579" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1579" t="inlineStr"/>
+      <c r="F1579" t="inlineStr"/>
+      <c r="G1579" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1579" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1579" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1579" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1579" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1579" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1580" t="inlineStr">
+        <is>
+          <t>Fatima vs Vinhais</t>
+        </is>
+      </c>
+      <c r="C1580" t="inlineStr">
+        <is>
+          <t>Fatima</t>
+        </is>
+      </c>
+      <c r="D1580" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1580" t="inlineStr"/>
+      <c r="F1580" t="inlineStr"/>
+      <c r="G1580" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H1580" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1580" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1580" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1580" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1580" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1581" t="inlineStr">
+        <is>
+          <t>Bragança vs Celoricense</t>
+        </is>
+      </c>
+      <c r="C1581" t="inlineStr">
+        <is>
+          <t>Bragança</t>
+        </is>
+      </c>
+      <c r="D1581" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1581" t="inlineStr"/>
+      <c r="F1581" t="inlineStr"/>
+      <c r="G1581" t="inlineStr">
+        <is>
+          <t>6-1</t>
+        </is>
+      </c>
+      <c r="H1581" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1581" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1581" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1581" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1581" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1582" t="inlineStr">
+        <is>
+          <t>Mortágua vs Leca</t>
+        </is>
+      </c>
+      <c r="C1582" t="inlineStr">
+        <is>
+          <t>Leca</t>
+        </is>
+      </c>
+      <c r="D1582" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1582" t="inlineStr"/>
+      <c r="F1582" t="inlineStr"/>
+      <c r="G1582" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1582" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1582" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1582" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1582" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1582" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1583" t="inlineStr">
+        <is>
+          <t>Ponte Barca vs Amarante</t>
+        </is>
+      </c>
+      <c r="C1583" t="inlineStr">
+        <is>
+          <t>Amarante</t>
+        </is>
+      </c>
+      <c r="D1583" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1583" t="inlineStr"/>
+      <c r="F1583" t="inlineStr"/>
+      <c r="G1583" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1583" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1583" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1583" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1583" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1583" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1584" t="inlineStr">
+        <is>
+          <t>Serpa vs Louletano</t>
+        </is>
+      </c>
+      <c r="C1584" t="inlineStr">
+        <is>
+          <t>Louletano</t>
+        </is>
+      </c>
+      <c r="D1584" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1584" t="inlineStr"/>
+      <c r="F1584" t="inlineStr"/>
+      <c r="G1584" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1584" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1584" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1584" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1584" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1584" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1585" t="inlineStr">
+        <is>
+          <t>Sintrense vs AVS</t>
+        </is>
+      </c>
+      <c r="C1585" t="inlineStr">
+        <is>
+          <t>AVS</t>
+        </is>
+      </c>
+      <c r="D1585" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1585" t="inlineStr"/>
+      <c r="F1585" t="inlineStr"/>
+      <c r="G1585" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1585" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1585" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1585" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1585" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1585" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1586" t="inlineStr">
+        <is>
+          <t>Atlético Madrid vs Real Madrid</t>
+        </is>
+      </c>
+      <c r="C1586" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="D1586" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1586" t="inlineStr"/>
+      <c r="F1586" t="inlineStr"/>
+      <c r="G1586" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1586" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1586" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1586" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1586" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1586" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1587" t="inlineStr">
+        <is>
+          <t>Estrela vs Académico de Viseu</t>
+        </is>
+      </c>
+      <c r="C1587" t="inlineStr">
+        <is>
+          <t>Estrela</t>
+        </is>
+      </c>
+      <c r="D1587" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1587" t="inlineStr"/>
+      <c r="F1587" t="inlineStr"/>
+      <c r="G1587" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1587" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1587" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1587" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1587" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1587" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1588" t="inlineStr">
+        <is>
+          <t>Vitória de Guimaraes vs Moreirense</t>
+        </is>
+      </c>
+      <c r="C1588" t="inlineStr">
+        <is>
+          <t>Vitória de Guimaraes</t>
+        </is>
+      </c>
+      <c r="D1588" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1588" t="inlineStr"/>
+      <c r="F1588" t="inlineStr"/>
+      <c r="G1588" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1588" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1588" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1588" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1588" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1588" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1589" t="inlineStr">
+        <is>
+          <t>NEC Nijmegen vs Go Ahead Eagles</t>
+        </is>
+      </c>
+      <c r="C1589" t="inlineStr">
+        <is>
+          <t>NEC Nijmegen</t>
+        </is>
+      </c>
+      <c r="D1589" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1589" t="inlineStr"/>
+      <c r="F1589" t="inlineStr"/>
+      <c r="G1589" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1589" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1589" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1589" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1589" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1589" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1590" t="inlineStr">
+        <is>
+          <t>Volos NFC vs AEK Athens</t>
+        </is>
+      </c>
+      <c r="C1590" t="inlineStr">
+        <is>
+          <t>AEK Athens</t>
+        </is>
+      </c>
+      <c r="D1590" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1590" t="inlineStr"/>
+      <c r="F1590" t="inlineStr"/>
+      <c r="G1590" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1590" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1590" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1590" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1590" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1590" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1591" t="inlineStr">
+        <is>
+          <t>Paredes vs SC Maria da Fonte</t>
+        </is>
+      </c>
+      <c r="C1591" t="inlineStr">
+        <is>
+          <t>Paredes</t>
+        </is>
+      </c>
+      <c r="D1591" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1591" t="inlineStr"/>
+      <c r="F1591" t="inlineStr"/>
+      <c r="G1591" t="inlineStr">
+        <is>
+          <t>5-1</t>
+        </is>
+      </c>
+      <c r="H1591" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1591" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1591" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1591" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1591" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1592" t="inlineStr">
+        <is>
+          <t>Nice vs Lille</t>
+        </is>
+      </c>
+      <c r="C1592" t="inlineStr">
+        <is>
+          <t>Lille</t>
+        </is>
+      </c>
+      <c r="D1592" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1592" t="inlineStr"/>
+      <c r="F1592" t="inlineStr"/>
+      <c r="G1592" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1592" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1592" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1592" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1592" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1592" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1593" t="inlineStr">
+        <is>
+          <t>Fulham vs Manchester United</t>
+        </is>
+      </c>
+      <c r="C1593" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="D1593" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1593" t="inlineStr"/>
+      <c r="F1593" t="inlineStr"/>
+      <c r="G1593" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1593" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1593" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1593" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1593" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1593" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1594" t="inlineStr">
+        <is>
+          <t>Schalke 04 vs SV Elversberg</t>
+        </is>
+      </c>
+      <c r="C1594" t="inlineStr">
+        <is>
+          <t>Schalke 04</t>
+        </is>
+      </c>
+      <c r="D1594" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1594" t="inlineStr"/>
+      <c r="F1594" t="inlineStr"/>
+      <c r="G1594" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1594" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1594" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1594" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1594" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1594" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1595" t="inlineStr">
+        <is>
+          <t>Juventus vs Atalanta</t>
+        </is>
+      </c>
+      <c r="C1595" t="inlineStr">
+        <is>
+          <t>Juventus</t>
+        </is>
+      </c>
+      <c r="D1595" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1595" t="inlineStr"/>
+      <c r="F1595" t="inlineStr"/>
+      <c r="G1595" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1595" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1595" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1595" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1595" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1595" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1596" t="inlineStr">
+        <is>
+          <t>Danubio vs Montevideo Wanderers</t>
+        </is>
+      </c>
+      <c r="C1596" t="inlineStr">
+        <is>
+          <t>Danubio</t>
+        </is>
+      </c>
+      <c r="D1596" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1596" t="inlineStr"/>
+      <c r="F1596" t="inlineStr"/>
+      <c r="G1596" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1596" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1596" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1596" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1596" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1596" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1597" t="inlineStr">
+        <is>
+          <t>OFI CRETE vs Asteras Tripoli</t>
+        </is>
+      </c>
+      <c r="C1597" t="inlineStr">
+        <is>
+          <t>OFI CRETE</t>
+        </is>
+      </c>
+      <c r="D1597" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1597" t="inlineStr"/>
+      <c r="F1597" t="inlineStr"/>
+      <c r="G1597" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1597" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1597" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1597" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1597" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1597" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1598" t="inlineStr">
+        <is>
+          <t>AD Marco 09 vs FC Maia Lidador</t>
+        </is>
+      </c>
+      <c r="C1598" t="inlineStr">
+        <is>
+          <t>AD Marco 09</t>
+        </is>
+      </c>
+      <c r="D1598" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1598" t="inlineStr"/>
+      <c r="F1598" t="inlineStr"/>
+      <c r="G1598" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1598" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1598" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1598" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1598" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1598" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1599" t="inlineStr">
+        <is>
+          <t>Deportivo vs Real Betis</t>
+        </is>
+      </c>
+      <c r="C1599" t="inlineStr">
+        <is>
+          <t>Real Betis</t>
+        </is>
+      </c>
+      <c r="D1599" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1599" t="inlineStr"/>
+      <c r="F1599" t="inlineStr"/>
+      <c r="G1599" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1599" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1599" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1599" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1599" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1599" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1600" t="inlineStr">
+        <is>
+          <t>Villarreal vs Levante</t>
+        </is>
+      </c>
+      <c r="C1600" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="D1600" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1600" t="inlineStr"/>
+      <c r="F1600" t="inlineStr"/>
+      <c r="G1600" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1600" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1600" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1600" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1600" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1600" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1601" t="inlineStr">
+        <is>
+          <t>Club Brugge vs Racing Genk</t>
+        </is>
+      </c>
+      <c r="C1601" t="inlineStr">
+        <is>
+          <t>Club Brugge</t>
+        </is>
+      </c>
+      <c r="D1601" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1601" t="inlineStr"/>
+      <c r="F1601" t="inlineStr"/>
+      <c r="G1601" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1601" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1601" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1601" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1601" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1601" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1602" t="inlineStr">
+        <is>
+          <t>Kalamata vs Panathinaikos</t>
+        </is>
+      </c>
+      <c r="C1602" t="inlineStr">
+        <is>
+          <t>Panathinaikos</t>
+        </is>
+      </c>
+      <c r="D1602" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1602" t="inlineStr"/>
+      <c r="F1602" t="inlineStr"/>
+      <c r="G1602" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1602" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1602" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1602" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1602" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1602" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1603" t="inlineStr">
+        <is>
+          <t>Las Palmas vs Burgos</t>
+        </is>
+      </c>
+      <c r="C1603" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="D1603" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1603" t="inlineStr"/>
+      <c r="F1603" t="inlineStr"/>
+      <c r="G1603" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1603" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1603" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1603" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1603" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1603" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1604" t="inlineStr">
+        <is>
+          <t>Estoril vs Casa Pia</t>
+        </is>
+      </c>
+      <c r="C1604" t="inlineStr">
+        <is>
+          <t>Estoril</t>
+        </is>
+      </c>
+      <c r="D1604" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1604" t="inlineStr"/>
+      <c r="F1604" t="inlineStr"/>
+      <c r="G1604" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1604" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1604" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1604" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1604" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1604" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1605" t="inlineStr">
+        <is>
+          <t>Santa Clara vs Braga</t>
+        </is>
+      </c>
+      <c r="C1605" t="inlineStr">
+        <is>
+          <t>Braga</t>
+        </is>
+      </c>
+      <c r="D1605" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1605" t="inlineStr"/>
+      <c r="F1605" t="inlineStr"/>
+      <c r="G1605" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1605" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1605" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1605" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1605" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1605" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1606" t="inlineStr">
+        <is>
+          <t>Amed SFK vs Besiktas</t>
+        </is>
+      </c>
+      <c r="C1606" t="inlineStr">
+        <is>
+          <t>Besiktas</t>
+        </is>
+      </c>
+      <c r="D1606" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1606" t="inlineStr"/>
+      <c r="F1606" t="inlineStr"/>
+      <c r="G1606" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1606" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1606" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1606" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1606" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1606" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1607">
+      <c r="A1607" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1607" t="inlineStr">
+        <is>
+          <t>Goztepe vs Caykur Rizespor</t>
+        </is>
+      </c>
+      <c r="C1607" t="inlineStr">
+        <is>
+          <t>Goztepe</t>
+        </is>
+      </c>
+      <c r="D1607" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1607" t="inlineStr"/>
+      <c r="F1607" t="inlineStr"/>
+      <c r="G1607" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1607" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1607" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1607" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1607" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1607" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1608">
+      <c r="A1608" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1608" t="inlineStr">
+        <is>
+          <t>SC Paderborn 07 vs TSG Hoffenheim</t>
+        </is>
+      </c>
+      <c r="C1608" t="inlineStr">
+        <is>
+          <t>TSG Hoffenheim</t>
+        </is>
+      </c>
+      <c r="D1608" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1608" t="inlineStr"/>
+      <c r="F1608" t="inlineStr"/>
+      <c r="G1608" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1608" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1608" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1608" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1608" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1608" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1609" t="inlineStr">
+        <is>
+          <t>San Lorenzo vs Boca Juniors</t>
+        </is>
+      </c>
+      <c r="C1609" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="D1609" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1609" t="inlineStr"/>
+      <c r="F1609" t="inlineStr"/>
+      <c r="G1609" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1609" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1609" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1609" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1609" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1609" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1610">
+      <c r="A1610" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1610" t="inlineStr">
+        <is>
+          <t>Panetolikos vs PAOK</t>
+        </is>
+      </c>
+      <c r="C1610" t="inlineStr">
+        <is>
+          <t>PAOK</t>
+        </is>
+      </c>
+      <c r="D1610" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1610" t="inlineStr"/>
+      <c r="F1610" t="inlineStr"/>
+      <c r="G1610" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H1610" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1610" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1610" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1610" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1610" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1611">
+      <c r="A1611" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1611" t="inlineStr">
+        <is>
+          <t>Sport Huancayo vs UTC</t>
+        </is>
+      </c>
+      <c r="C1611" t="inlineStr">
+        <is>
+          <t>Sport Huancayo</t>
+        </is>
+      </c>
+      <c r="D1611" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1611" t="inlineStr"/>
+      <c r="F1611" t="inlineStr"/>
+      <c r="G1611" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1611" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1611" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1611" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1611" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1611" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1612">
+      <c r="A1612" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1612" t="inlineStr">
+        <is>
+          <t>Técnico Universitario vs Delfín</t>
+        </is>
+      </c>
+      <c r="C1612" t="inlineStr">
+        <is>
+          <t>Técnico Universitario</t>
+        </is>
+      </c>
+      <c r="D1612" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1612" t="inlineStr"/>
+      <c r="F1612" t="inlineStr"/>
+      <c r="G1612" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1612" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1612" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1612" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1612" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1612" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1613">
+      <c r="A1613" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1613" t="inlineStr">
+        <is>
+          <t>Marseille vs Paris Saint-Germain</t>
+        </is>
+      </c>
+      <c r="C1613" t="inlineStr">
+        <is>
+          <t>Paris Saint-Germain</t>
+        </is>
+      </c>
+      <c r="D1613" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1613" t="inlineStr"/>
+      <c r="F1613" t="inlineStr"/>
+      <c r="G1613" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1613" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1613" t="n">
+        <v>6</v>
+      </c>
+      <c r="J1613" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1613" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1613" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1614">
+      <c r="A1614" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1614" t="inlineStr">
+        <is>
+          <t>AC Milan vs Lecce</t>
+        </is>
+      </c>
+      <c r="C1614" t="inlineStr">
+        <is>
+          <t>AC Milan</t>
+        </is>
+      </c>
+      <c r="D1614" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1614" t="inlineStr"/>
+      <c r="F1614" t="inlineStr"/>
+      <c r="G1614" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1614" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1614" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1614" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1614" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1614" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1615">
+      <c r="A1615" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1615" t="inlineStr">
+        <is>
+          <t>Corinthians vs Fluminense</t>
+        </is>
+      </c>
+      <c r="C1615" t="inlineStr">
+        <is>
+          <t>Corinthians</t>
+        </is>
+      </c>
+      <c r="D1615" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1615" t="inlineStr"/>
+      <c r="F1615" t="inlineStr"/>
+      <c r="G1615" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H1615" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1615" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1615" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1615" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1615" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1616">
+      <c r="A1616" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1616" t="inlineStr">
+        <is>
+          <t>Goiás vs Avaí</t>
+        </is>
+      </c>
+      <c r="C1616" t="inlineStr">
+        <is>
+          <t>Goiás</t>
+        </is>
+      </c>
+      <c r="D1616" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1616" t="inlineStr"/>
+      <c r="F1616" t="inlineStr"/>
+      <c r="G1616" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1616" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1616" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1616" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1616" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1616" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1617">
+      <c r="A1617" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1617" t="inlineStr">
+        <is>
+          <t>Sportivo San Lorenzo vs Club Olimpia</t>
+        </is>
+      </c>
+      <c r="C1617" t="inlineStr">
+        <is>
+          <t>Club Olimpia</t>
+        </is>
+      </c>
+      <c r="D1617" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1617" t="inlineStr"/>
+      <c r="F1617" t="inlineStr"/>
+      <c r="G1617" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H1617" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1617" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1617" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1617" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1617" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1618">
+      <c r="A1618" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1618" t="inlineStr">
+        <is>
+          <t>Leganés vs Granada</t>
+        </is>
+      </c>
+      <c r="C1618" t="inlineStr">
+        <is>
+          <t>Leganés</t>
+        </is>
+      </c>
+      <c r="D1618" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1618" t="inlineStr"/>
+      <c r="F1618" t="inlineStr"/>
+      <c r="G1618" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1618" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1618" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1618" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1618" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1618" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1619">
+      <c r="A1619" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1619" t="inlineStr">
+        <is>
+          <t>Vitória vs Cruzeiro</t>
+        </is>
+      </c>
+      <c r="C1619" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="D1619" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1619" t="inlineStr"/>
+      <c r="F1619" t="inlineStr"/>
+      <c r="G1619" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H1619" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1619" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1619" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1619" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1619" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1620">
+      <c r="A1620" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1620" t="inlineStr">
+        <is>
+          <t>Platense vs Newell's Old Boys</t>
+        </is>
+      </c>
+      <c r="C1620" t="inlineStr">
+        <is>
+          <t>Platense</t>
+        </is>
+      </c>
+      <c r="D1620" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1620" t="inlineStr"/>
+      <c r="F1620" t="inlineStr"/>
+      <c r="G1620" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1620" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1620" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1620" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1620" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1620" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1621">
+      <c r="A1621" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1621" t="inlineStr">
+        <is>
+          <t>Rosario Central vs Argentinos Juniors</t>
+        </is>
+      </c>
+      <c r="C1621" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="D1621" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1621" t="inlineStr"/>
+      <c r="F1621" t="inlineStr"/>
+      <c r="G1621" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1621" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1621" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1621" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1621" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1621" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1622">
+      <c r="A1622" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1622" t="inlineStr">
+        <is>
+          <t>Deportivo Cuenca vs Mushuc Runa</t>
+        </is>
+      </c>
+      <c r="C1622" t="inlineStr">
+        <is>
+          <t>Deportivo Cuenca</t>
+        </is>
+      </c>
+      <c r="D1622" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1622" t="inlineStr"/>
+      <c r="F1622" t="inlineStr"/>
+      <c r="G1622" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1622" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1622" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1622" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1622" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1622" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1623">
+      <c r="A1623" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1623" t="inlineStr">
+        <is>
+          <t>Indy Eleven vs Oakland Roots</t>
+        </is>
+      </c>
+      <c r="C1623" t="inlineStr">
+        <is>
+          <t>Indy Eleven</t>
+        </is>
+      </c>
+      <c r="D1623" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1623" t="inlineStr"/>
+      <c r="F1623" t="inlineStr"/>
+      <c r="G1623" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1623" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1623" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1623" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1623" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1623" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1624">
+      <c r="A1624" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1624" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga vs Internacional de Bogotá</t>
+        </is>
+      </c>
+      <c r="C1624" t="inlineStr">
+        <is>
+          <t>Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="D1624" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1624" t="inlineStr"/>
+      <c r="F1624" t="inlineStr"/>
+      <c r="G1624" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1624" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1624" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1624" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1624" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1624" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1625">
+      <c r="A1625" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1625" t="inlineStr">
+        <is>
+          <t>Flamengo vs Red Bull Bragantino</t>
+        </is>
+      </c>
+      <c r="C1625" t="inlineStr">
+        <is>
+          <t>Flamengo</t>
+        </is>
+      </c>
+      <c r="D1625" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1625" t="inlineStr"/>
+      <c r="F1625" t="inlineStr"/>
+      <c r="G1625" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1625" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1625" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1625" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1625" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1625" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1626">
+      <c r="A1626" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1626" t="inlineStr">
+        <is>
+          <t>Sportivo Luqueño vs Deportivo Recoleta</t>
+        </is>
+      </c>
+      <c r="C1626" t="inlineStr">
+        <is>
+          <t>Sportivo Luqueño</t>
+        </is>
+      </c>
+      <c r="D1626" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1626" t="inlineStr"/>
+      <c r="F1626" t="inlineStr"/>
+      <c r="G1626" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1626" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1626" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1626" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1626" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1626" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1627">
+      <c r="A1627" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1627" t="inlineStr">
+        <is>
+          <t>Belgrano (Córdoba) vs Estudiantes de Río Cuarto</t>
+        </is>
+      </c>
+      <c r="C1627" t="inlineStr">
+        <is>
+          <t>Belgrano (Córdoba)</t>
+        </is>
+      </c>
+      <c r="D1627" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1627" t="inlineStr"/>
+      <c r="F1627" t="inlineStr"/>
+      <c r="G1627" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1627" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1627" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1627" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1627" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1627" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1628">
+      <c r="A1628" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1628" t="inlineStr">
+        <is>
+          <t>Liverpool vs Racing (Montevideo)</t>
+        </is>
+      </c>
+      <c r="C1628" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="D1628" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1628" t="inlineStr"/>
+      <c r="F1628" t="inlineStr"/>
+      <c r="G1628" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1628" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1628" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1628" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1628" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1628" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1629">
+      <c r="A1629" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1629" t="inlineStr">
+        <is>
+          <t>Inter Miami CF vs San Diego FC</t>
+        </is>
+      </c>
+      <c r="C1629" t="inlineStr">
+        <is>
+          <t>Inter Miami CF</t>
+        </is>
+      </c>
+      <c r="D1629" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1629" t="inlineStr"/>
+      <c r="F1629" t="inlineStr"/>
+      <c r="G1629" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1629" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1629" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1629" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1629" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1629" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1630">
+      <c r="A1630" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1630" t="inlineStr">
+        <is>
+          <t>Tapatío vs Tlaxcala FC</t>
+        </is>
+      </c>
+      <c r="C1630" t="inlineStr">
+        <is>
+          <t>Tapatío</t>
+        </is>
+      </c>
+      <c r="D1630" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1630" t="inlineStr"/>
+      <c r="F1630" t="inlineStr"/>
+      <c r="G1630" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H1630" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1630" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1630" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1630" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1630" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1631">
+      <c r="A1631" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1631" t="inlineStr">
+        <is>
+          <t>Sacramento Republic FC vs San Antonio FC</t>
+        </is>
+      </c>
+      <c r="C1631" t="inlineStr">
+        <is>
+          <t>Sacramento Republic FC</t>
+        </is>
+      </c>
+      <c r="D1631" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1631" t="inlineStr"/>
+      <c r="F1631" t="inlineStr"/>
+      <c r="G1631" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1631" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1631" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1631" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1631" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1631" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1632">
+      <c r="A1632" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1632" t="inlineStr">
+        <is>
+          <t>Spokane Velocity FC vs Athletic Club Boise</t>
+        </is>
+      </c>
+      <c r="C1632" t="inlineStr">
+        <is>
+          <t>Spokane Velocity FC</t>
+        </is>
+      </c>
+      <c r="D1632" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1632" t="inlineStr"/>
+      <c r="F1632" t="inlineStr"/>
+      <c r="G1632" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1632" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1632" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1632" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1632" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1632" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1633">
+      <c r="A1633" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1633" t="inlineStr">
+        <is>
+          <t>Deportes Tolima vs América de Cali</t>
+        </is>
+      </c>
+      <c r="C1633" t="inlineStr">
+        <is>
+          <t>Deportes Tolima</t>
+        </is>
+      </c>
+      <c r="D1633" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1633" t="inlineStr"/>
+      <c r="F1633" t="inlineStr"/>
+      <c r="G1633" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1633" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1633" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1633" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1633" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1633" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1634">
+      <c r="A1634" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1634" t="inlineStr">
+        <is>
+          <t>Toluca vs Santos</t>
+        </is>
+      </c>
+      <c r="C1634" t="inlineStr">
+        <is>
+          <t>Toluca</t>
+        </is>
+      </c>
+      <c r="D1634" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1634" t="inlineStr"/>
+      <c r="F1634" t="inlineStr"/>
+      <c r="G1634" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H1634" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1634" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1634" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1634" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1634" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1635">
+      <c r="A1635" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1635" t="inlineStr">
+        <is>
+          <t>Pachuca vs Tijuana</t>
+        </is>
+      </c>
+      <c r="C1635" t="inlineStr">
+        <is>
+          <t>Pachuca</t>
+        </is>
+      </c>
+      <c r="D1635" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1635" t="inlineStr"/>
+      <c r="F1635" t="inlineStr"/>
+      <c r="G1635" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1635" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1635" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1635" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1635" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1635" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1636">
+      <c r="A1636" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1636" t="inlineStr">
+        <is>
+          <t>Vélez Sarsfield vs Tigre</t>
+        </is>
+      </c>
+      <c r="C1636" t="inlineStr">
+        <is>
+          <t>Vélez Sarsfield</t>
+        </is>
+      </c>
+      <c r="D1636" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1636" t="inlineStr"/>
+      <c r="F1636" t="inlineStr"/>
+      <c r="G1636" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1636" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1636" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1636" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1636" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1636" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1637">
+      <c r="A1637" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1637" t="inlineStr">
+        <is>
+          <t>Llaneros FC vs Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="C1637" t="inlineStr">
+        <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="D1637" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1637" t="inlineStr"/>
+      <c r="F1637" t="inlineStr"/>
+      <c r="G1637" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1637" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1637" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1637" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1637" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1637" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1638">
+      <c r="A1638" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B1638" t="inlineStr">
+        <is>
+          <t>Querétaro vs León</t>
+        </is>
+      </c>
+      <c r="C1638" t="inlineStr">
+        <is>
+          <t>León</t>
+        </is>
+      </c>
+      <c r="D1638" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1638" t="inlineStr"/>
+      <c r="F1638" t="inlineStr"/>
+      <c r="G1638" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1638" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1638" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1638" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1638" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1638" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -72043,7 +76003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -72791,6 +76751,25 @@
       </c>
       <c r="E40" t="n">
         <v>108</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>87</v>
+      </c>
+      <c r="C41" t="n">
+        <v>65</v>
+      </c>
+      <c r="D41" t="n">
+        <v>74.7</v>
+      </c>
+      <c r="E41" t="n">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -72804,7 +76783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E211"/>
+  <dimension ref="A1:E220"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77244,6 +81223,195 @@
         <v>0</v>
       </c>
     </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C212" t="n">
+        <v>14</v>
+      </c>
+      <c r="D212" t="n">
+        <v>1</v>
+      </c>
+      <c r="E212" t="n">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C213" t="n">
+        <v>2</v>
+      </c>
+      <c r="D213" t="n">
+        <v>1</v>
+      </c>
+      <c r="E213" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C214" t="n">
+        <v>10</v>
+      </c>
+      <c r="D214" t="n">
+        <v>3</v>
+      </c>
+      <c r="E214" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>gol_de_cierre</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>4</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0</v>
+      </c>
+      <c r="E215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>5</v>
+      </c>
+      <c r="D216" t="n">
+        <v>0</v>
+      </c>
+      <c r="E216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>6</v>
+      </c>
+      <c r="D217" t="n">
+        <v>2</v>
+      </c>
+      <c r="E217" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C218" t="n">
+        <v>4</v>
+      </c>
+      <c r="D218" t="n">
+        <v>0</v>
+      </c>
+      <c r="E218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>siguen_empatados_55</t>
+        </is>
+      </c>
+      <c r="C219" t="n">
+        <v>1</v>
+      </c>
+      <c r="D219" t="n">
+        <v>0</v>
+      </c>
+      <c r="E219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C220" t="n">
+        <v>6</v>
+      </c>
+      <c r="D220" t="n">
+        <v>0</v>
+      </c>
+      <c r="E220" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1638"/>
+  <dimension ref="A1:L1646"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -71837,8 +71837,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1552" t="inlineStr"/>
-      <c r="F1552" t="inlineStr"/>
       <c r="G1552" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -71885,8 +71883,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1553" t="inlineStr"/>
-      <c r="F1553" t="inlineStr"/>
       <c r="G1553" t="inlineStr">
         <is>
           <t>5-0</t>
@@ -71933,8 +71929,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1554" t="inlineStr"/>
-      <c r="F1554" t="inlineStr"/>
       <c r="G1554" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -71981,8 +71975,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1555" t="inlineStr"/>
-      <c r="F1555" t="inlineStr"/>
       <c r="G1555" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -72029,8 +72021,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1556" t="inlineStr"/>
-      <c r="F1556" t="inlineStr"/>
       <c r="G1556" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -72077,8 +72067,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1557" t="inlineStr"/>
-      <c r="F1557" t="inlineStr"/>
       <c r="G1557" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -72125,8 +72113,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1558" t="inlineStr"/>
-      <c r="F1558" t="inlineStr"/>
       <c r="G1558" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -72173,8 +72159,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1559" t="inlineStr"/>
-      <c r="F1559" t="inlineStr"/>
       <c r="G1559" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -72221,8 +72205,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1560" t="inlineStr"/>
-      <c r="F1560" t="inlineStr"/>
       <c r="G1560" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -72269,8 +72251,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1561" t="inlineStr"/>
-      <c r="F1561" t="inlineStr"/>
       <c r="G1561" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -72317,8 +72297,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1562" t="inlineStr"/>
-      <c r="F1562" t="inlineStr"/>
       <c r="G1562" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -72365,8 +72343,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1563" t="inlineStr"/>
-      <c r="F1563" t="inlineStr"/>
       <c r="G1563" t="inlineStr">
         <is>
           <t>3-4</t>
@@ -72413,8 +72389,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1564" t="inlineStr"/>
-      <c r="F1564" t="inlineStr"/>
       <c r="G1564" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -72461,8 +72435,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1565" t="inlineStr"/>
-      <c r="F1565" t="inlineStr"/>
       <c r="G1565" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -72509,8 +72481,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1566" t="inlineStr"/>
-      <c r="F1566" t="inlineStr"/>
       <c r="G1566" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -72557,8 +72527,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1567" t="inlineStr"/>
-      <c r="F1567" t="inlineStr"/>
       <c r="G1567" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -72605,8 +72573,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1568" t="inlineStr"/>
-      <c r="F1568" t="inlineStr"/>
       <c r="G1568" t="inlineStr">
         <is>
           <t>5-3</t>
@@ -72653,8 +72619,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1569" t="inlineStr"/>
-      <c r="F1569" t="inlineStr"/>
       <c r="G1569" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -72701,8 +72665,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1570" t="inlineStr"/>
-      <c r="F1570" t="inlineStr"/>
       <c r="G1570" t="inlineStr">
         <is>
           <t>1-4</t>
@@ -72749,8 +72711,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1571" t="inlineStr"/>
-      <c r="F1571" t="inlineStr"/>
       <c r="G1571" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -72797,8 +72757,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1572" t="inlineStr"/>
-      <c r="F1572" t="inlineStr"/>
       <c r="G1572" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -72845,8 +72803,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1573" t="inlineStr"/>
-      <c r="F1573" t="inlineStr"/>
       <c r="G1573" t="inlineStr">
         <is>
           <t>0-4</t>
@@ -72893,8 +72849,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1574" t="inlineStr"/>
-      <c r="F1574" t="inlineStr"/>
       <c r="G1574" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -72941,8 +72895,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1575" t="inlineStr"/>
-      <c r="F1575" t="inlineStr"/>
       <c r="G1575" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -72989,8 +72941,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1576" t="inlineStr"/>
-      <c r="F1576" t="inlineStr"/>
       <c r="G1576" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -73037,8 +72987,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1577" t="inlineStr"/>
-      <c r="F1577" t="inlineStr"/>
       <c r="G1577" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -73085,8 +73033,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1578" t="inlineStr"/>
-      <c r="F1578" t="inlineStr"/>
       <c r="G1578" t="inlineStr">
         <is>
           <t>8-0</t>
@@ -73133,8 +73079,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1579" t="inlineStr"/>
-      <c r="F1579" t="inlineStr"/>
       <c r="G1579" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -73181,8 +73125,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1580" t="inlineStr"/>
-      <c r="F1580" t="inlineStr"/>
       <c r="G1580" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -73229,8 +73171,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1581" t="inlineStr"/>
-      <c r="F1581" t="inlineStr"/>
       <c r="G1581" t="inlineStr">
         <is>
           <t>6-1</t>
@@ -73277,8 +73217,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1582" t="inlineStr"/>
-      <c r="F1582" t="inlineStr"/>
       <c r="G1582" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -73325,8 +73263,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1583" t="inlineStr"/>
-      <c r="F1583" t="inlineStr"/>
       <c r="G1583" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -73373,8 +73309,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1584" t="inlineStr"/>
-      <c r="F1584" t="inlineStr"/>
       <c r="G1584" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -73421,8 +73355,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1585" t="inlineStr"/>
-      <c r="F1585" t="inlineStr"/>
       <c r="G1585" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -73469,8 +73401,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1586" t="inlineStr"/>
-      <c r="F1586" t="inlineStr"/>
       <c r="G1586" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -73517,8 +73447,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1587" t="inlineStr"/>
-      <c r="F1587" t="inlineStr"/>
       <c r="G1587" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -73565,8 +73493,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1588" t="inlineStr"/>
-      <c r="F1588" t="inlineStr"/>
       <c r="G1588" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -73613,8 +73539,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1589" t="inlineStr"/>
-      <c r="F1589" t="inlineStr"/>
       <c r="G1589" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -73661,8 +73585,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1590" t="inlineStr"/>
-      <c r="F1590" t="inlineStr"/>
       <c r="G1590" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -73709,8 +73631,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1591" t="inlineStr"/>
-      <c r="F1591" t="inlineStr"/>
       <c r="G1591" t="inlineStr">
         <is>
           <t>5-1</t>
@@ -73757,8 +73677,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1592" t="inlineStr"/>
-      <c r="F1592" t="inlineStr"/>
       <c r="G1592" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -73805,8 +73723,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1593" t="inlineStr"/>
-      <c r="F1593" t="inlineStr"/>
       <c r="G1593" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -73853,8 +73769,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1594" t="inlineStr"/>
-      <c r="F1594" t="inlineStr"/>
       <c r="G1594" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -73901,8 +73815,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1595" t="inlineStr"/>
-      <c r="F1595" t="inlineStr"/>
       <c r="G1595" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -73949,8 +73861,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1596" t="inlineStr"/>
-      <c r="F1596" t="inlineStr"/>
       <c r="G1596" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -73997,8 +73907,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1597" t="inlineStr"/>
-      <c r="F1597" t="inlineStr"/>
       <c r="G1597" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -74045,8 +73953,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1598" t="inlineStr"/>
-      <c r="F1598" t="inlineStr"/>
       <c r="G1598" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -74093,8 +73999,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1599" t="inlineStr"/>
-      <c r="F1599" t="inlineStr"/>
       <c r="G1599" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -74141,8 +74045,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1600" t="inlineStr"/>
-      <c r="F1600" t="inlineStr"/>
       <c r="G1600" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -74189,8 +74091,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1601" t="inlineStr"/>
-      <c r="F1601" t="inlineStr"/>
       <c r="G1601" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -74237,8 +74137,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1602" t="inlineStr"/>
-      <c r="F1602" t="inlineStr"/>
       <c r="G1602" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -74285,8 +74183,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1603" t="inlineStr"/>
-      <c r="F1603" t="inlineStr"/>
       <c r="G1603" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -74333,8 +74229,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1604" t="inlineStr"/>
-      <c r="F1604" t="inlineStr"/>
       <c r="G1604" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -74381,8 +74275,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1605" t="inlineStr"/>
-      <c r="F1605" t="inlineStr"/>
       <c r="G1605" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -74429,8 +74321,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1606" t="inlineStr"/>
-      <c r="F1606" t="inlineStr"/>
       <c r="G1606" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -74477,8 +74367,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1607" t="inlineStr"/>
-      <c r="F1607" t="inlineStr"/>
       <c r="G1607" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -74525,8 +74413,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1608" t="inlineStr"/>
-      <c r="F1608" t="inlineStr"/>
       <c r="G1608" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -74573,8 +74459,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1609" t="inlineStr"/>
-      <c r="F1609" t="inlineStr"/>
       <c r="G1609" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -74621,8 +74505,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1610" t="inlineStr"/>
-      <c r="F1610" t="inlineStr"/>
       <c r="G1610" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -74669,8 +74551,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1611" t="inlineStr"/>
-      <c r="F1611" t="inlineStr"/>
       <c r="G1611" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -74717,8 +74597,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1612" t="inlineStr"/>
-      <c r="F1612" t="inlineStr"/>
       <c r="G1612" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -74765,8 +74643,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1613" t="inlineStr"/>
-      <c r="F1613" t="inlineStr"/>
       <c r="G1613" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -74813,8 +74689,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1614" t="inlineStr"/>
-      <c r="F1614" t="inlineStr"/>
       <c r="G1614" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -74861,8 +74735,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1615" t="inlineStr"/>
-      <c r="F1615" t="inlineStr"/>
       <c r="G1615" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -74909,8 +74781,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1616" t="inlineStr"/>
-      <c r="F1616" t="inlineStr"/>
       <c r="G1616" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -74957,8 +74827,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1617" t="inlineStr"/>
-      <c r="F1617" t="inlineStr"/>
       <c r="G1617" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -75005,8 +74873,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1618" t="inlineStr"/>
-      <c r="F1618" t="inlineStr"/>
       <c r="G1618" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -75053,8 +74919,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1619" t="inlineStr"/>
-      <c r="F1619" t="inlineStr"/>
       <c r="G1619" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -75101,8 +74965,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1620" t="inlineStr"/>
-      <c r="F1620" t="inlineStr"/>
       <c r="G1620" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -75149,8 +75011,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1621" t="inlineStr"/>
-      <c r="F1621" t="inlineStr"/>
       <c r="G1621" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -75197,8 +75057,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1622" t="inlineStr"/>
-      <c r="F1622" t="inlineStr"/>
       <c r="G1622" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -75245,8 +75103,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1623" t="inlineStr"/>
-      <c r="F1623" t="inlineStr"/>
       <c r="G1623" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -75293,8 +75149,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1624" t="inlineStr"/>
-      <c r="F1624" t="inlineStr"/>
       <c r="G1624" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -75341,8 +75195,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1625" t="inlineStr"/>
-      <c r="F1625" t="inlineStr"/>
       <c r="G1625" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -75389,8 +75241,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1626" t="inlineStr"/>
-      <c r="F1626" t="inlineStr"/>
       <c r="G1626" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -75437,8 +75287,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1627" t="inlineStr"/>
-      <c r="F1627" t="inlineStr"/>
       <c r="G1627" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -75485,8 +75333,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1628" t="inlineStr"/>
-      <c r="F1628" t="inlineStr"/>
       <c r="G1628" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -75533,8 +75379,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1629" t="inlineStr"/>
-      <c r="F1629" t="inlineStr"/>
       <c r="G1629" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -75581,8 +75425,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1630" t="inlineStr"/>
-      <c r="F1630" t="inlineStr"/>
       <c r="G1630" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -75629,8 +75471,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1631" t="inlineStr"/>
-      <c r="F1631" t="inlineStr"/>
       <c r="G1631" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -75677,8 +75517,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1632" t="inlineStr"/>
-      <c r="F1632" t="inlineStr"/>
       <c r="G1632" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -75725,8 +75563,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1633" t="inlineStr"/>
-      <c r="F1633" t="inlineStr"/>
       <c r="G1633" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -75773,8 +75609,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1634" t="inlineStr"/>
-      <c r="F1634" t="inlineStr"/>
       <c r="G1634" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -75821,8 +75655,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1635" t="inlineStr"/>
-      <c r="F1635" t="inlineStr"/>
       <c r="G1635" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -75869,8 +75701,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1636" t="inlineStr"/>
-      <c r="F1636" t="inlineStr"/>
       <c r="G1636" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -75917,8 +75747,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1637" t="inlineStr"/>
-      <c r="F1637" t="inlineStr"/>
       <c r="G1637" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -75965,8 +75793,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1638" t="inlineStr"/>
-      <c r="F1638" t="inlineStr"/>
       <c r="G1638" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -75987,6 +75813,390 @@
         <v>0</v>
       </c>
       <c r="L1638" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t>New Caledonia vs Solomon Islands</t>
+        </is>
+      </c>
+      <c r="C1639" t="inlineStr">
+        <is>
+          <t>New Caledonia</t>
+        </is>
+      </c>
+      <c r="D1639" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1639" t="inlineStr"/>
+      <c r="F1639" t="inlineStr"/>
+      <c r="G1639" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1639" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1639" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1639" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1639" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1639" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t>Fiji vs Vanuatu</t>
+        </is>
+      </c>
+      <c r="C1640" t="inlineStr">
+        <is>
+          <t>Fiji</t>
+        </is>
+      </c>
+      <c r="D1640" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1640" t="inlineStr"/>
+      <c r="F1640" t="inlineStr"/>
+      <c r="G1640" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1640" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1640" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1640" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1640" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1640" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t>Tristán Suárez vs Atlanta</t>
+        </is>
+      </c>
+      <c r="C1641" t="inlineStr">
+        <is>
+          <t>Tristán Suárez</t>
+        </is>
+      </c>
+      <c r="D1641" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1641" t="inlineStr"/>
+      <c r="F1641" t="inlineStr"/>
+      <c r="G1641" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1641" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1641" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1641" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1641" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1641" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t>Barracas Central vs Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="C1642" t="inlineStr">
+        <is>
+          <t>Independiente Rivadavia</t>
+        </is>
+      </c>
+      <c r="D1642" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1642" t="inlineStr"/>
+      <c r="F1642" t="inlineStr"/>
+      <c r="G1642" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1642" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1642" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1642" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1642" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1642" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t>Nueva Chicago vs Patronato</t>
+        </is>
+      </c>
+      <c r="C1643" t="inlineStr">
+        <is>
+          <t>Nueva Chicago</t>
+        </is>
+      </c>
+      <c r="D1643" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1643" t="inlineStr"/>
+      <c r="F1643" t="inlineStr"/>
+      <c r="G1643" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1643" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1643" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1643" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1643" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1643" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t>Guabirá vs San Antonio Bulo Bulo</t>
+        </is>
+      </c>
+      <c r="C1644" t="inlineStr">
+        <is>
+          <t>Guabirá</t>
+        </is>
+      </c>
+      <c r="D1644" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1644" t="inlineStr"/>
+      <c r="F1644" t="inlineStr"/>
+      <c r="G1644" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1644" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1644" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1644" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1644" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1644" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t>Lanús vs Estudiantes de La Plata</t>
+        </is>
+      </c>
+      <c r="C1645" t="inlineStr">
+        <is>
+          <t>Lanús</t>
+        </is>
+      </c>
+      <c r="D1645" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1645" t="inlineStr"/>
+      <c r="F1645" t="inlineStr"/>
+      <c r="G1645" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1645" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1645" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1645" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1645" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1645" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t>Cuiabá vs Náutico</t>
+        </is>
+      </c>
+      <c r="C1646" t="inlineStr">
+        <is>
+          <t>Cuiabá</t>
+        </is>
+      </c>
+      <c r="D1646" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1646" t="inlineStr"/>
+      <c r="F1646" t="inlineStr"/>
+      <c r="G1646" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1646" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1646" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1646" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1646" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1646" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -76003,7 +76213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E41"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76770,6 +76980,25 @@
       </c>
       <c r="E41" t="n">
         <v>87</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>8</v>
+      </c>
+      <c r="C42" t="n">
+        <v>6</v>
+      </c>
+      <c r="D42" t="n">
+        <v>75</v>
+      </c>
+      <c r="E42" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -76783,7 +77012,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E220"/>
+  <dimension ref="A1:E222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81412,6 +81641,48 @@
         <v>0</v>
       </c>
     </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C221" t="n">
+        <v>2</v>
+      </c>
+      <c r="D221" t="n">
+        <v>0</v>
+      </c>
+      <c r="E221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C222" t="n">
+        <v>3</v>
+      </c>
+      <c r="D222" t="n">
+        <v>0</v>
+      </c>
+      <c r="E222" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1646"/>
+  <dimension ref="A1:L1687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -75839,8 +75839,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1639" t="inlineStr"/>
-      <c r="F1639" t="inlineStr"/>
       <c r="G1639" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -75887,8 +75885,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1640" t="inlineStr"/>
-      <c r="F1640" t="inlineStr"/>
       <c r="G1640" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -75935,8 +75931,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1641" t="inlineStr"/>
-      <c r="F1641" t="inlineStr"/>
       <c r="G1641" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -75983,8 +75977,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1642" t="inlineStr"/>
-      <c r="F1642" t="inlineStr"/>
       <c r="G1642" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -76031,8 +76023,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1643" t="inlineStr"/>
-      <c r="F1643" t="inlineStr"/>
       <c r="G1643" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -76079,8 +76069,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1644" t="inlineStr"/>
-      <c r="F1644" t="inlineStr"/>
       <c r="G1644" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -76127,8 +76115,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1645" t="inlineStr"/>
-      <c r="F1645" t="inlineStr"/>
       <c r="G1645" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -76175,8 +76161,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1646" t="inlineStr"/>
-      <c r="F1646" t="inlineStr"/>
       <c r="G1646" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -76197,6 +76181,1974 @@
         <v>0</v>
       </c>
       <c r="L1646" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t>Salford City vs Sheffield Wednesday</t>
+        </is>
+      </c>
+      <c r="C1647" t="inlineStr">
+        <is>
+          <t>Sheffield Wednesday</t>
+        </is>
+      </c>
+      <c r="D1647" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1647" t="inlineStr"/>
+      <c r="F1647" t="inlineStr"/>
+      <c r="G1647" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1647" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1647" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1647" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1647" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1647" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t>Accrington Stanley vs Sunderland U21</t>
+        </is>
+      </c>
+      <c r="C1648" t="inlineStr">
+        <is>
+          <t>Accrington Stanley</t>
+        </is>
+      </c>
+      <c r="D1648" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1648" t="inlineStr"/>
+      <c r="F1648" t="inlineStr"/>
+      <c r="G1648" t="inlineStr">
+        <is>
+          <t>3-3</t>
+        </is>
+      </c>
+      <c r="H1648" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1648" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1648" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1648" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1648" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t>Wigan Athletic vs Blackpool</t>
+        </is>
+      </c>
+      <c r="C1649" t="inlineStr">
+        <is>
+          <t>Wigan Athletic</t>
+        </is>
+      </c>
+      <c r="D1649" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1649" t="inlineStr"/>
+      <c r="F1649" t="inlineStr"/>
+      <c r="G1649" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1649" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1649" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1649" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1649" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1649" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t>Crewe Alexandra vs Aston Villa U21</t>
+        </is>
+      </c>
+      <c r="C1650" t="inlineStr">
+        <is>
+          <t>Crewe Alexandra</t>
+        </is>
+      </c>
+      <c r="D1650" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1650" t="inlineStr"/>
+      <c r="F1650" t="inlineStr"/>
+      <c r="G1650" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H1650" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1650" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1650" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1650" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1650" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t>York City vs Rotherham United</t>
+        </is>
+      </c>
+      <c r="C1651" t="inlineStr">
+        <is>
+          <t>York City</t>
+        </is>
+      </c>
+      <c r="D1651" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1651" t="inlineStr"/>
+      <c r="F1651" t="inlineStr"/>
+      <c r="G1651" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1651" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1651" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1651" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1651" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1651" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t>Chesterfield vs Port Vale</t>
+        </is>
+      </c>
+      <c r="C1652" t="inlineStr">
+        <is>
+          <t>Chesterfield</t>
+        </is>
+      </c>
+      <c r="D1652" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1652" t="inlineStr"/>
+      <c r="F1652" t="inlineStr"/>
+      <c r="G1652" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1652" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1652" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1652" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1652" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1652" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t>Tranmere Rovers vs Shrewsbury Town</t>
+        </is>
+      </c>
+      <c r="C1653" t="inlineStr">
+        <is>
+          <t>Tranmere Rovers</t>
+        </is>
+      </c>
+      <c r="D1653" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1653" t="inlineStr"/>
+      <c r="F1653" t="inlineStr"/>
+      <c r="G1653" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1653" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1653" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1653" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1653" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1653" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t>Burton Albion vs Nottingham Forest U21</t>
+        </is>
+      </c>
+      <c r="C1654" t="inlineStr">
+        <is>
+          <t>Burton Albion</t>
+        </is>
+      </c>
+      <c r="D1654" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1654" t="inlineStr"/>
+      <c r="F1654" t="inlineStr"/>
+      <c r="G1654" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1654" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1654" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1654" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1654" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1654" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1655" t="inlineStr">
+        <is>
+          <t>Notts County vs Grimsby Town</t>
+        </is>
+      </c>
+      <c r="C1655" t="inlineStr">
+        <is>
+          <t>Notts County</t>
+        </is>
+      </c>
+      <c r="D1655" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1655" t="inlineStr"/>
+      <c r="F1655" t="inlineStr"/>
+      <c r="G1655" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1655" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1655" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1655" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1655" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1655" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1656" t="inlineStr">
+        <is>
+          <t>Barnsley vs Leeds United U21</t>
+        </is>
+      </c>
+      <c r="C1656" t="inlineStr">
+        <is>
+          <t>Barnsley</t>
+        </is>
+      </c>
+      <c r="D1656" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1656" t="inlineStr"/>
+      <c r="F1656" t="inlineStr"/>
+      <c r="G1656" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="H1656" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1656" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1656" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1656" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1656" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t>ACV vs Hoogeveen</t>
+        </is>
+      </c>
+      <c r="C1657" t="inlineStr">
+        <is>
+          <t>ACV</t>
+        </is>
+      </c>
+      <c r="D1657" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1657" t="inlineStr"/>
+      <c r="F1657" t="inlineStr"/>
+      <c r="G1657" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1657" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1657" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1657" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1657" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1657" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t>Eemdijk vs RBC Roosendaal</t>
+        </is>
+      </c>
+      <c r="C1658" t="inlineStr">
+        <is>
+          <t>RBC Roosendaal</t>
+        </is>
+      </c>
+      <c r="D1658" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1658" t="inlineStr"/>
+      <c r="F1658" t="inlineStr"/>
+      <c r="G1658" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1658" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1658" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1658" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1658" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1658" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1659" t="inlineStr">
+        <is>
+          <t>EVV Echt vs RKSV Halsteren</t>
+        </is>
+      </c>
+      <c r="C1659" t="inlineStr">
+        <is>
+          <t>EVV Echt</t>
+        </is>
+      </c>
+      <c r="D1659" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1659" t="inlineStr"/>
+      <c r="F1659" t="inlineStr"/>
+      <c r="G1659" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1659" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1659" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1659" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1659" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1659" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1660" t="inlineStr">
+        <is>
+          <t>GVVV vs DVS '33 Ermelo</t>
+        </is>
+      </c>
+      <c r="C1660" t="inlineStr">
+        <is>
+          <t>GVVV</t>
+        </is>
+      </c>
+      <c r="D1660" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1660" t="inlineStr"/>
+      <c r="F1660" t="inlineStr"/>
+      <c r="G1660" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H1660" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1660" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1660" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1660" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1660" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1661" t="inlineStr">
+        <is>
+          <t>HHC Hardenberg vs BVV Barendrecht</t>
+        </is>
+      </c>
+      <c r="C1661" t="inlineStr">
+        <is>
+          <t>HHC Hardenberg</t>
+        </is>
+      </c>
+      <c r="D1661" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1661" t="inlineStr"/>
+      <c r="F1661" t="inlineStr"/>
+      <c r="G1661" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1661" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1661" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1661" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1661" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1661" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1662" t="inlineStr">
+        <is>
+          <t>Koninklijke HFC vs DOVO</t>
+        </is>
+      </c>
+      <c r="C1662" t="inlineStr">
+        <is>
+          <t>Koninklijke HFC</t>
+        </is>
+      </c>
+      <c r="D1662" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1662" t="inlineStr"/>
+      <c r="F1662" t="inlineStr"/>
+      <c r="G1662" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1662" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1662" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1662" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1662" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1662" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1663">
+      <c r="A1663" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1663" t="inlineStr">
+        <is>
+          <t>FC Rijnvogels vs VVSB</t>
+        </is>
+      </c>
+      <c r="C1663" t="inlineStr">
+        <is>
+          <t>FC Rijnvogels</t>
+        </is>
+      </c>
+      <c r="D1663" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1663" t="inlineStr"/>
+      <c r="F1663" t="inlineStr"/>
+      <c r="G1663" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1663" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1663" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1663" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1663" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1663" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1664">
+      <c r="A1664" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1664" t="inlineStr">
+        <is>
+          <t>RKAV Volendam vs Spakenburg</t>
+        </is>
+      </c>
+      <c r="C1664" t="inlineStr">
+        <is>
+          <t>Spakenburg</t>
+        </is>
+      </c>
+      <c r="D1664" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1664" t="inlineStr"/>
+      <c r="F1664" t="inlineStr"/>
+      <c r="G1664" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1664" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1664" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1664" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1664" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1664" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1665">
+      <c r="A1665" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1665" t="inlineStr">
+        <is>
+          <t>Sportlust '46 vs Excelsior Maassluis</t>
+        </is>
+      </c>
+      <c r="C1665" t="inlineStr">
+        <is>
+          <t>Excelsior Maassluis</t>
+        </is>
+      </c>
+      <c r="D1665" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1665" t="inlineStr"/>
+      <c r="F1665" t="inlineStr"/>
+      <c r="G1665" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1665" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1665" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1665" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1665" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1665" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1666">
+      <c r="A1666" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1666" t="inlineStr">
+        <is>
+          <t>Bradford City vs Newcastle United U21</t>
+        </is>
+      </c>
+      <c r="C1666" t="inlineStr">
+        <is>
+          <t>Bradford City</t>
+        </is>
+      </c>
+      <c r="D1666" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1666" t="inlineStr"/>
+      <c r="F1666" t="inlineStr"/>
+      <c r="G1666" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1666" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1666" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1666" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1666" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1666" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1667">
+      <c r="A1667" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1667" t="inlineStr">
+        <is>
+          <t>Clachnacuddin vs Ross County</t>
+        </is>
+      </c>
+      <c r="C1667" t="inlineStr">
+        <is>
+          <t>Ross County</t>
+        </is>
+      </c>
+      <c r="D1667" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1667" t="inlineStr"/>
+      <c r="F1667" t="inlineStr"/>
+      <c r="G1667" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="H1667" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1667" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1667" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1667" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1667" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1668">
+      <c r="A1668" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1668" t="inlineStr">
+        <is>
+          <t>East Kilbride vs Celtic B</t>
+        </is>
+      </c>
+      <c r="C1668" t="inlineStr">
+        <is>
+          <t>East Kilbride</t>
+        </is>
+      </c>
+      <c r="D1668" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1668" t="inlineStr"/>
+      <c r="F1668" t="inlineStr"/>
+      <c r="G1668" t="inlineStr">
+        <is>
+          <t>3-3</t>
+        </is>
+      </c>
+      <c r="H1668" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1668" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1668" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1668" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1668" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1669">
+      <c r="A1669" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1669" t="inlineStr">
+        <is>
+          <t>Edinburgh City vs Dundee United B</t>
+        </is>
+      </c>
+      <c r="C1669" t="inlineStr">
+        <is>
+          <t>Edinburgh City</t>
+        </is>
+      </c>
+      <c r="D1669" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1669" t="inlineStr"/>
+      <c r="F1669" t="inlineStr"/>
+      <c r="G1669" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1669" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1669" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1669" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1669" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1669" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1670">
+      <c r="A1670" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1670" t="inlineStr">
+        <is>
+          <t>Elgin City vs Dundee B</t>
+        </is>
+      </c>
+      <c r="C1670" t="inlineStr">
+        <is>
+          <t>Elgin City</t>
+        </is>
+      </c>
+      <c r="D1670" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1670" t="inlineStr"/>
+      <c r="F1670" t="inlineStr"/>
+      <c r="G1670" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1670" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1670" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1670" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1670" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1670" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1671">
+      <c r="A1671" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1671" t="inlineStr">
+        <is>
+          <t>Forfar Athletic vs Peterhead</t>
+        </is>
+      </c>
+      <c r="C1671" t="inlineStr">
+        <is>
+          <t>Peterhead</t>
+        </is>
+      </c>
+      <c r="D1671" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1671" t="inlineStr"/>
+      <c r="F1671" t="inlineStr"/>
+      <c r="G1671" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1671" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1671" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1671" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1671" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1671" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1672">
+      <c r="A1672" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1672" t="inlineStr">
+        <is>
+          <t>Formartine United vs Montrose</t>
+        </is>
+      </c>
+      <c r="C1672" t="inlineStr">
+        <is>
+          <t>Montrose</t>
+        </is>
+      </c>
+      <c r="D1672" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1672" t="inlineStr"/>
+      <c r="F1672" t="inlineStr"/>
+      <c r="G1672" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1672" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1672" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1672" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1672" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1672" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1673">
+      <c r="A1673" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1673" t="inlineStr">
+        <is>
+          <t>Fraserburgh vs Cove Rangers</t>
+        </is>
+      </c>
+      <c r="C1673" t="inlineStr">
+        <is>
+          <t>Cove Rangers</t>
+        </is>
+      </c>
+      <c r="D1673" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1673" t="inlineStr"/>
+      <c r="F1673" t="inlineStr"/>
+      <c r="G1673" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="H1673" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1673" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1673" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1673" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1673" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1674">
+      <c r="A1674" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1674" t="inlineStr">
+        <is>
+          <t>Gala Fairydean vs Spartans FC</t>
+        </is>
+      </c>
+      <c r="C1674" t="inlineStr">
+        <is>
+          <t>Spartans FC</t>
+        </is>
+      </c>
+      <c r="D1674" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1674" t="inlineStr"/>
+      <c r="F1674" t="inlineStr"/>
+      <c r="G1674" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1674" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1674" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1674" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1674" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1674" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1675">
+      <c r="A1675" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1675" t="inlineStr">
+        <is>
+          <t>Dagenham &amp; Redbridge vs Waltham Abbey</t>
+        </is>
+      </c>
+      <c r="C1675" t="inlineStr">
+        <is>
+          <t>Dagenham &amp; Redbridge</t>
+        </is>
+      </c>
+      <c r="D1675" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1675" t="inlineStr"/>
+      <c r="F1675" t="inlineStr"/>
+      <c r="G1675" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1675" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1675" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1675" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1675" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1675" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1676">
+      <c r="A1676" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1676" t="inlineStr">
+        <is>
+          <t>Gainsborough Trinity vs Leamington</t>
+        </is>
+      </c>
+      <c r="C1676" t="inlineStr">
+        <is>
+          <t>Gainsborough Trinity</t>
+        </is>
+      </c>
+      <c r="D1676" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1676" t="inlineStr"/>
+      <c r="F1676" t="inlineStr"/>
+      <c r="G1676" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1676" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1676" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1676" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1676" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1676" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1677">
+      <c r="A1677" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1677" t="inlineStr">
+        <is>
+          <t>Truro City vs Merthyr Town</t>
+        </is>
+      </c>
+      <c r="C1677" t="inlineStr">
+        <is>
+          <t>Truro City</t>
+        </is>
+      </c>
+      <c r="D1677" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1677" t="inlineStr"/>
+      <c r="F1677" t="inlineStr"/>
+      <c r="G1677" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1677" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1677" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1677" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1677" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1677" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1678">
+      <c r="A1678" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1678" t="inlineStr">
+        <is>
+          <t>Worksop Town vs AFC Telford United</t>
+        </is>
+      </c>
+      <c r="C1678" t="inlineStr">
+        <is>
+          <t>Worksop Town</t>
+        </is>
+      </c>
+      <c r="D1678" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1678" t="inlineStr"/>
+      <c r="F1678" t="inlineStr"/>
+      <c r="G1678" t="inlineStr">
+        <is>
+          <t>5-2</t>
+        </is>
+      </c>
+      <c r="H1678" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1678" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1678" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1678" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1678" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1679">
+      <c r="A1679" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1679" t="inlineStr">
+        <is>
+          <t>Alloa Athletic vs Hibernian B</t>
+        </is>
+      </c>
+      <c r="C1679" t="inlineStr">
+        <is>
+          <t>Alloa Athletic</t>
+        </is>
+      </c>
+      <c r="D1679" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1679" t="inlineStr"/>
+      <c r="F1679" t="inlineStr"/>
+      <c r="G1679" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H1679" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1679" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1679" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1679" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1679" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1680" t="inlineStr">
+        <is>
+          <t>Berwick Rangers vs Stranraer</t>
+        </is>
+      </c>
+      <c r="C1680" t="inlineStr">
+        <is>
+          <t>Stranraer</t>
+        </is>
+      </c>
+      <c r="D1680" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1680" t="inlineStr"/>
+      <c r="F1680" t="inlineStr"/>
+      <c r="G1680" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1680" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1680" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1680" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1680" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1680" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1681">
+      <c r="A1681" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1681" t="inlineStr">
+        <is>
+          <t>Dumbarton vs Kilmarnock B</t>
+        </is>
+      </c>
+      <c r="C1681" t="inlineStr">
+        <is>
+          <t>Dumbarton</t>
+        </is>
+      </c>
+      <c r="D1681" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1681" t="inlineStr"/>
+      <c r="F1681" t="inlineStr"/>
+      <c r="G1681" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1681" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1681" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1681" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1681" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1681" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1682">
+      <c r="A1682" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1682" t="inlineStr">
+        <is>
+          <t>Puerto Montt vs Ñublense</t>
+        </is>
+      </c>
+      <c r="C1682" t="inlineStr">
+        <is>
+          <t>Ñublense</t>
+        </is>
+      </c>
+      <c r="D1682" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1682" t="inlineStr"/>
+      <c r="F1682" t="inlineStr"/>
+      <c r="G1682" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1682" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1682" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1682" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1682" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1682" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1683">
+      <c r="A1683" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1683" t="inlineStr">
+        <is>
+          <t>Independiente Medellín vs Jaguares de Córdoba</t>
+        </is>
+      </c>
+      <c r="C1683" t="inlineStr">
+        <is>
+          <t>Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="D1683" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1683" t="inlineStr"/>
+      <c r="F1683" t="inlineStr"/>
+      <c r="G1683" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1683" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1683" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1683" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1683" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1683" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1684">
+      <c r="A1684" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1684" t="inlineStr">
+        <is>
+          <t>Nacional Potosí vs Real Potosí</t>
+        </is>
+      </c>
+      <c r="C1684" t="inlineStr">
+        <is>
+          <t>Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="D1684" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1684" t="inlineStr"/>
+      <c r="F1684" t="inlineStr"/>
+      <c r="G1684" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1684" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1684" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1684" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1684" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1684" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1685" t="inlineStr">
+        <is>
+          <t>Audax Italiano vs Colo Colo</t>
+        </is>
+      </c>
+      <c r="C1685" t="inlineStr">
+        <is>
+          <t>Colo Colo</t>
+        </is>
+      </c>
+      <c r="D1685" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1685" t="inlineStr"/>
+      <c r="F1685" t="inlineStr"/>
+      <c r="G1685" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1685" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1685" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1685" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1685" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1685" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1686">
+      <c r="A1686" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1686" t="inlineStr">
+        <is>
+          <t>Cobreloa vs Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="C1686" t="inlineStr">
+        <is>
+          <t>Coquimbo Unido</t>
+        </is>
+      </c>
+      <c r="D1686" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1686" t="inlineStr"/>
+      <c r="F1686" t="inlineStr"/>
+      <c r="G1686" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1686" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1686" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1686" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1686" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1686" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1687">
+      <c r="A1687" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B1687" t="inlineStr">
+        <is>
+          <t>Independiente Santa Fe vs Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="C1687" t="inlineStr">
+        <is>
+          <t>Independiente Santa Fe</t>
+        </is>
+      </c>
+      <c r="D1687" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1687" t="inlineStr"/>
+      <c r="F1687" t="inlineStr"/>
+      <c r="G1687" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1687" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1687" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1687" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1687" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1687" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -76213,7 +78165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76999,6 +78951,25 @@
       </c>
       <c r="E42" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>41</v>
+      </c>
+      <c r="C43" t="n">
+        <v>28</v>
+      </c>
+      <c r="D43" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="E43" t="n">
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -77012,7 +78983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E222"/>
+  <dimension ref="A1:E230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81683,6 +83654,174 @@
         <v>0</v>
       </c>
     </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C223" t="n">
+        <v>9</v>
+      </c>
+      <c r="D223" t="n">
+        <v>0</v>
+      </c>
+      <c r="E223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C224" t="n">
+        <v>1</v>
+      </c>
+      <c r="D224" t="n">
+        <v>1</v>
+      </c>
+      <c r="E224" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>siguen_empatados_70</t>
+        </is>
+      </c>
+      <c r="C225" t="n">
+        <v>2</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0</v>
+      </c>
+      <c r="E225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>gol_de_cierre</t>
+        </is>
+      </c>
+      <c r="C226" t="n">
+        <v>1</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0</v>
+      </c>
+      <c r="E226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C227" t="n">
+        <v>7</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0</v>
+      </c>
+      <c r="E227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C228" t="n">
+        <v>1</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0</v>
+      </c>
+      <c r="E228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>siguen_empatados_55</t>
+        </is>
+      </c>
+      <c r="C229" t="n">
+        <v>1</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0</v>
+      </c>
+      <c r="E229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C230" t="n">
+        <v>1</v>
+      </c>
+      <c r="D230" t="n">
+        <v>1</v>
+      </c>
+      <c r="E230" t="n">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1687"/>
+  <dimension ref="A1:L1705"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -76207,8 +76207,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1647" t="inlineStr"/>
-      <c r="F1647" t="inlineStr"/>
       <c r="G1647" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -76255,8 +76253,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1648" t="inlineStr"/>
-      <c r="F1648" t="inlineStr"/>
       <c r="G1648" t="inlineStr">
         <is>
           <t>3-3</t>
@@ -76303,8 +76299,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1649" t="inlineStr"/>
-      <c r="F1649" t="inlineStr"/>
       <c r="G1649" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -76351,8 +76345,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1650" t="inlineStr"/>
-      <c r="F1650" t="inlineStr"/>
       <c r="G1650" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -76399,8 +76391,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1651" t="inlineStr"/>
-      <c r="F1651" t="inlineStr"/>
       <c r="G1651" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -76447,8 +76437,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1652" t="inlineStr"/>
-      <c r="F1652" t="inlineStr"/>
       <c r="G1652" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -76495,8 +76483,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1653" t="inlineStr"/>
-      <c r="F1653" t="inlineStr"/>
       <c r="G1653" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -76543,8 +76529,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1654" t="inlineStr"/>
-      <c r="F1654" t="inlineStr"/>
       <c r="G1654" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -76591,8 +76575,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1655" t="inlineStr"/>
-      <c r="F1655" t="inlineStr"/>
       <c r="G1655" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -76639,8 +76621,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1656" t="inlineStr"/>
-      <c r="F1656" t="inlineStr"/>
       <c r="G1656" t="inlineStr">
         <is>
           <t>3-4</t>
@@ -76687,8 +76667,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1657" t="inlineStr"/>
-      <c r="F1657" t="inlineStr"/>
       <c r="G1657" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -76735,8 +76713,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1658" t="inlineStr"/>
-      <c r="F1658" t="inlineStr"/>
       <c r="G1658" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -76783,8 +76759,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1659" t="inlineStr"/>
-      <c r="F1659" t="inlineStr"/>
       <c r="G1659" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -76831,8 +76805,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1660" t="inlineStr"/>
-      <c r="F1660" t="inlineStr"/>
       <c r="G1660" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -76879,8 +76851,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1661" t="inlineStr"/>
-      <c r="F1661" t="inlineStr"/>
       <c r="G1661" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -76927,8 +76897,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1662" t="inlineStr"/>
-      <c r="F1662" t="inlineStr"/>
       <c r="G1662" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -76975,8 +76943,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1663" t="inlineStr"/>
-      <c r="F1663" t="inlineStr"/>
       <c r="G1663" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -77023,8 +76989,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1664" t="inlineStr"/>
-      <c r="F1664" t="inlineStr"/>
       <c r="G1664" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -77071,8 +77035,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1665" t="inlineStr"/>
-      <c r="F1665" t="inlineStr"/>
       <c r="G1665" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -77119,8 +77081,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1666" t="inlineStr"/>
-      <c r="F1666" t="inlineStr"/>
       <c r="G1666" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -77167,8 +77127,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1667" t="inlineStr"/>
-      <c r="F1667" t="inlineStr"/>
       <c r="G1667" t="inlineStr">
         <is>
           <t>1-5</t>
@@ -77215,8 +77173,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1668" t="inlineStr"/>
-      <c r="F1668" t="inlineStr"/>
       <c r="G1668" t="inlineStr">
         <is>
           <t>3-3</t>
@@ -77263,8 +77219,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1669" t="inlineStr"/>
-      <c r="F1669" t="inlineStr"/>
       <c r="G1669" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -77311,8 +77265,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1670" t="inlineStr"/>
-      <c r="F1670" t="inlineStr"/>
       <c r="G1670" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -77359,8 +77311,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1671" t="inlineStr"/>
-      <c r="F1671" t="inlineStr"/>
       <c r="G1671" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -77407,8 +77357,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1672" t="inlineStr"/>
-      <c r="F1672" t="inlineStr"/>
       <c r="G1672" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -77455,8 +77403,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1673" t="inlineStr"/>
-      <c r="F1673" t="inlineStr"/>
       <c r="G1673" t="inlineStr">
         <is>
           <t>0-5</t>
@@ -77503,8 +77449,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1674" t="inlineStr"/>
-      <c r="F1674" t="inlineStr"/>
       <c r="G1674" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -77551,8 +77495,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1675" t="inlineStr"/>
-      <c r="F1675" t="inlineStr"/>
       <c r="G1675" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -77599,8 +77541,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1676" t="inlineStr"/>
-      <c r="F1676" t="inlineStr"/>
       <c r="G1676" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -77647,8 +77587,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1677" t="inlineStr"/>
-      <c r="F1677" t="inlineStr"/>
       <c r="G1677" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -77695,8 +77633,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1678" t="inlineStr"/>
-      <c r="F1678" t="inlineStr"/>
       <c r="G1678" t="inlineStr">
         <is>
           <t>5-2</t>
@@ -77743,8 +77679,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1679" t="inlineStr"/>
-      <c r="F1679" t="inlineStr"/>
       <c r="G1679" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -77791,8 +77725,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1680" t="inlineStr"/>
-      <c r="F1680" t="inlineStr"/>
       <c r="G1680" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -77839,8 +77771,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1681" t="inlineStr"/>
-      <c r="F1681" t="inlineStr"/>
       <c r="G1681" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -77887,8 +77817,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1682" t="inlineStr"/>
-      <c r="F1682" t="inlineStr"/>
       <c r="G1682" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -77935,8 +77863,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1683" t="inlineStr"/>
-      <c r="F1683" t="inlineStr"/>
       <c r="G1683" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -77983,8 +77909,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1684" t="inlineStr"/>
-      <c r="F1684" t="inlineStr"/>
       <c r="G1684" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -78031,8 +77955,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1685" t="inlineStr"/>
-      <c r="F1685" t="inlineStr"/>
       <c r="G1685" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -78079,8 +78001,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1686" t="inlineStr"/>
-      <c r="F1686" t="inlineStr"/>
       <c r="G1686" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -78127,8 +78047,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1687" t="inlineStr"/>
-      <c r="F1687" t="inlineStr"/>
       <c r="G1687" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -78149,6 +78067,870 @@
         <v>0</v>
       </c>
       <c r="L1687" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1688">
+      <c r="A1688" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1688" t="inlineStr">
+        <is>
+          <t>Iraq vs Oman</t>
+        </is>
+      </c>
+      <c r="C1688" t="inlineStr">
+        <is>
+          <t>Iraq</t>
+        </is>
+      </c>
+      <c r="D1688" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1688" t="inlineStr"/>
+      <c r="F1688" t="inlineStr"/>
+      <c r="G1688" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1688" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1688" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1688" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1688" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1688" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1689">
+      <c r="A1689" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1689" t="inlineStr">
+        <is>
+          <t>Birmingham Legion FC vs Brooklyn FC</t>
+        </is>
+      </c>
+      <c r="C1689" t="inlineStr">
+        <is>
+          <t>Birmingham Legion FC</t>
+        </is>
+      </c>
+      <c r="D1689" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1689" t="inlineStr"/>
+      <c r="F1689" t="inlineStr"/>
+      <c r="G1689" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H1689" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1689" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1689" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1689" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1689" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1690">
+      <c r="A1690" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1690" t="inlineStr">
+        <is>
+          <t>Azerbaijan vs Tajikistan</t>
+        </is>
+      </c>
+      <c r="C1690" t="inlineStr">
+        <is>
+          <t>Azerbaijan</t>
+        </is>
+      </c>
+      <c r="D1690" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1690" t="inlineStr"/>
+      <c r="F1690" t="inlineStr"/>
+      <c r="G1690" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1690" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1690" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1690" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1690" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1690" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1691">
+      <c r="A1691" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1691" t="inlineStr">
+        <is>
+          <t>Gibraltar vs Sao Tome and Principe</t>
+        </is>
+      </c>
+      <c r="C1691" t="inlineStr">
+        <is>
+          <t>Gibraltar</t>
+        </is>
+      </c>
+      <c r="D1691" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1691" t="inlineStr"/>
+      <c r="F1691" t="inlineStr"/>
+      <c r="G1691" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1691" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1691" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1691" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1691" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1691" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1692">
+      <c r="A1692" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1692" t="inlineStr">
+        <is>
+          <t>IJsselmeervogels vs Gemert</t>
+        </is>
+      </c>
+      <c r="C1692" t="inlineStr">
+        <is>
+          <t>IJsselmeervogels</t>
+        </is>
+      </c>
+      <c r="D1692" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1692" t="inlineStr"/>
+      <c r="F1692" t="inlineStr"/>
+      <c r="G1692" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H1692" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1692" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1692" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1692" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1692" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1693">
+      <c r="A1693" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1693" t="inlineStr">
+        <is>
+          <t>Zwaluwen '30 vs Purmersteijn</t>
+        </is>
+      </c>
+      <c r="C1693" t="inlineStr">
+        <is>
+          <t>Zwaluwen '30</t>
+        </is>
+      </c>
+      <c r="D1693" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1693" t="inlineStr"/>
+      <c r="F1693" t="inlineStr"/>
+      <c r="G1693" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1693" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1693" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1693" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1693" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1693" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1694">
+      <c r="A1694" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1694" t="inlineStr">
+        <is>
+          <t>Saudi Arabia vs Kuwait</t>
+        </is>
+      </c>
+      <c r="C1694" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D1694" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1694" t="inlineStr"/>
+      <c r="F1694" t="inlineStr"/>
+      <c r="G1694" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1694" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1694" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1694" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1694" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1694" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1695">
+      <c r="A1695" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1695" t="inlineStr">
+        <is>
+          <t>Hamilton Academical vs Cowdenbeath</t>
+        </is>
+      </c>
+      <c r="C1695" t="inlineStr">
+        <is>
+          <t>Hamilton Academical</t>
+        </is>
+      </c>
+      <c r="D1695" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1695" t="inlineStr"/>
+      <c r="F1695" t="inlineStr"/>
+      <c r="G1695" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1695" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1695" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1695" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1695" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1695" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1696">
+      <c r="A1696" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1696" t="inlineStr">
+        <is>
+          <t>Turks and Caicos Islands vs Montserrat</t>
+        </is>
+      </c>
+      <c r="C1696" t="inlineStr">
+        <is>
+          <t>Montserrat</t>
+        </is>
+      </c>
+      <c r="D1696" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1696" t="inlineStr"/>
+      <c r="F1696" t="inlineStr"/>
+      <c r="G1696" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1696" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1696" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1696" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1696" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1696" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1697">
+      <c r="A1697" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1697" t="inlineStr">
+        <is>
+          <t>ADT vs Cienciano del Cusco</t>
+        </is>
+      </c>
+      <c r="C1697" t="inlineStr">
+        <is>
+          <t>Cienciano del Cusco</t>
+        </is>
+      </c>
+      <c r="D1697" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1697" t="inlineStr"/>
+      <c r="F1697" t="inlineStr"/>
+      <c r="G1697" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1697" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1697" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1697" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1697" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1697" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1698">
+      <c r="A1698" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1698" t="inlineStr">
+        <is>
+          <t>Bahamas vs St. Martin</t>
+        </is>
+      </c>
+      <c r="C1698" t="inlineStr">
+        <is>
+          <t>St. Martin</t>
+        </is>
+      </c>
+      <c r="D1698" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1698" t="inlineStr"/>
+      <c r="F1698" t="inlineStr"/>
+      <c r="G1698" t="inlineStr">
+        <is>
+          <t>0-8</t>
+        </is>
+      </c>
+      <c r="H1698" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1698" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1698" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1698" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1698" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1699">
+      <c r="A1699" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1699" t="inlineStr">
+        <is>
+          <t>Curicó Unido vs Deportes Concepcion</t>
+        </is>
+      </c>
+      <c r="C1699" t="inlineStr">
+        <is>
+          <t>Deportes Concepcion</t>
+        </is>
+      </c>
+      <c r="D1699" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1699" t="inlineStr"/>
+      <c r="F1699" t="inlineStr"/>
+      <c r="G1699" t="inlineStr">
+        <is>
+          <t>0-4</t>
+        </is>
+      </c>
+      <c r="H1699" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1699" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1699" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1699" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1700">
+      <c r="A1700" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1700" t="inlineStr">
+        <is>
+          <t>Aruba vs Antigua and Barbuda</t>
+        </is>
+      </c>
+      <c r="C1700" t="inlineStr">
+        <is>
+          <t>Antigua and Barbuda</t>
+        </is>
+      </c>
+      <c r="D1700" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1700" t="inlineStr"/>
+      <c r="F1700" t="inlineStr"/>
+      <c r="G1700" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1700" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1700" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1700" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1700" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1700" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1701">
+      <c r="A1701" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1701" t="inlineStr">
+        <is>
+          <t>América de Cali vs Águilas Doradas</t>
+        </is>
+      </c>
+      <c r="C1701" t="inlineStr">
+        <is>
+          <t>América de Cali</t>
+        </is>
+      </c>
+      <c r="D1701" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1701" t="inlineStr"/>
+      <c r="F1701" t="inlineStr"/>
+      <c r="G1701" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1701" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1701" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1701" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1701" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1701" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1702">
+      <c r="A1702" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1702" t="inlineStr">
+        <is>
+          <t>Luis Ángel Firpo vs Cacahuatique</t>
+        </is>
+      </c>
+      <c r="C1702" t="inlineStr">
+        <is>
+          <t>Luis Ángel Firpo</t>
+        </is>
+      </c>
+      <c r="D1702" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1702" t="inlineStr"/>
+      <c r="F1702" t="inlineStr"/>
+      <c r="G1702" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1702" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1702" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1703">
+      <c r="A1703" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1703" t="inlineStr">
+        <is>
+          <t>Alianza FC vs Fuerte San Francisco</t>
+        </is>
+      </c>
+      <c r="C1703" t="inlineStr">
+        <is>
+          <t>Alianza FC</t>
+        </is>
+      </c>
+      <c r="D1703" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1703" t="inlineStr"/>
+      <c r="F1703" t="inlineStr"/>
+      <c r="G1703" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1703" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1703" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1703" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1703" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1703" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1704" t="inlineStr">
+        <is>
+          <t>Seattle Sounders FC vs Real Salt Lake</t>
+        </is>
+      </c>
+      <c r="C1704" t="inlineStr">
+        <is>
+          <t>Seattle Sounders FC</t>
+        </is>
+      </c>
+      <c r="D1704" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1704" t="inlineStr"/>
+      <c r="F1704" t="inlineStr"/>
+      <c r="G1704" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1704" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1704" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1704" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1704" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1704" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1705">
+      <c r="A1705" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B1705" t="inlineStr">
+        <is>
+          <t>Xelajú MC vs Antigua GFC</t>
+        </is>
+      </c>
+      <c r="C1705" t="inlineStr">
+        <is>
+          <t>Xelajú MC</t>
+        </is>
+      </c>
+      <c r="D1705" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1705" t="inlineStr"/>
+      <c r="F1705" t="inlineStr"/>
+      <c r="G1705" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H1705" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1705" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1705" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1705" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1705" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -78165,7 +78947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78970,6 +79752,25 @@
       </c>
       <c r="E43" t="n">
         <v>41</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>18</v>
+      </c>
+      <c r="C44" t="n">
+        <v>11</v>
+      </c>
+      <c r="D44" t="n">
+        <v>61.1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -78983,7 +79784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E230"/>
+  <dimension ref="A1:E235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83822,6 +84623,111 @@
         <v>100</v>
       </c>
     </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C231" t="n">
+        <v>1</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0</v>
+      </c>
+      <c r="E231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C232" t="n">
+        <v>4</v>
+      </c>
+      <c r="D232" t="n">
+        <v>2</v>
+      </c>
+      <c r="E232" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C233" t="n">
+        <v>1</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0</v>
+      </c>
+      <c r="E233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C234" t="n">
+        <v>1</v>
+      </c>
+      <c r="D234" t="n">
+        <v>0</v>
+      </c>
+      <c r="E234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C235" t="n">
+        <v>1</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0</v>
+      </c>
+      <c r="E235" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1705"/>
+  <dimension ref="A1:L1739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78093,8 +78093,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1688" t="inlineStr"/>
-      <c r="F1688" t="inlineStr"/>
       <c r="G1688" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -78141,8 +78139,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1689" t="inlineStr"/>
-      <c r="F1689" t="inlineStr"/>
       <c r="G1689" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -78189,8 +78185,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1690" t="inlineStr"/>
-      <c r="F1690" t="inlineStr"/>
       <c r="G1690" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -78237,8 +78231,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1691" t="inlineStr"/>
-      <c r="F1691" t="inlineStr"/>
       <c r="G1691" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -78285,8 +78277,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1692" t="inlineStr"/>
-      <c r="F1692" t="inlineStr"/>
       <c r="G1692" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -78333,8 +78323,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1693" t="inlineStr"/>
-      <c r="F1693" t="inlineStr"/>
       <c r="G1693" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -78381,8 +78369,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1694" t="inlineStr"/>
-      <c r="F1694" t="inlineStr"/>
       <c r="G1694" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -78429,8 +78415,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1695" t="inlineStr"/>
-      <c r="F1695" t="inlineStr"/>
       <c r="G1695" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -78477,8 +78461,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1696" t="inlineStr"/>
-      <c r="F1696" t="inlineStr"/>
       <c r="G1696" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -78525,8 +78507,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1697" t="inlineStr"/>
-      <c r="F1697" t="inlineStr"/>
       <c r="G1697" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -78573,8 +78553,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1698" t="inlineStr"/>
-      <c r="F1698" t="inlineStr"/>
       <c r="G1698" t="inlineStr">
         <is>
           <t>0-8</t>
@@ -78621,8 +78599,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1699" t="inlineStr"/>
-      <c r="F1699" t="inlineStr"/>
       <c r="G1699" t="inlineStr">
         <is>
           <t>0-4</t>
@@ -78669,8 +78645,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1700" t="inlineStr"/>
-      <c r="F1700" t="inlineStr"/>
       <c r="G1700" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -78717,8 +78691,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1701" t="inlineStr"/>
-      <c r="F1701" t="inlineStr"/>
       <c r="G1701" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -78765,8 +78737,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1702" t="inlineStr"/>
-      <c r="F1702" t="inlineStr"/>
       <c r="G1702" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -78813,8 +78783,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1703" t="inlineStr"/>
-      <c r="F1703" t="inlineStr"/>
       <c r="G1703" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -78861,8 +78829,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1704" t="inlineStr"/>
-      <c r="F1704" t="inlineStr"/>
       <c r="G1704" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -78909,8 +78875,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1705" t="inlineStr"/>
-      <c r="F1705" t="inlineStr"/>
       <c r="G1705" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -78931,6 +78895,1638 @@
         <v>0</v>
       </c>
       <c r="L1705" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1706">
+      <c r="A1706" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1706" t="inlineStr">
+        <is>
+          <t>Solomon Islands vs Vanuatu</t>
+        </is>
+      </c>
+      <c r="C1706" t="inlineStr">
+        <is>
+          <t>Solomon Islands</t>
+        </is>
+      </c>
+      <c r="D1706" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1706" t="inlineStr"/>
+      <c r="F1706" t="inlineStr"/>
+      <c r="G1706" t="inlineStr">
+        <is>
+          <t>3-3</t>
+        </is>
+      </c>
+      <c r="H1706" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1706" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1706" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1706" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1706" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1707">
+      <c r="A1707" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1707" t="inlineStr">
+        <is>
+          <t>Papua New Guinea vs New Caledonia</t>
+        </is>
+      </c>
+      <c r="C1707" t="inlineStr">
+        <is>
+          <t>Papua New Guinea</t>
+        </is>
+      </c>
+      <c r="D1707" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1707" t="inlineStr"/>
+      <c r="F1707" t="inlineStr"/>
+      <c r="G1707" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1707" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1707" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1707" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1707" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1707" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1708">
+      <c r="A1708" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1708" t="inlineStr">
+        <is>
+          <t>Palestine vs New Zealand</t>
+        </is>
+      </c>
+      <c r="C1708" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="D1708" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1708" t="inlineStr"/>
+      <c r="F1708" t="inlineStr"/>
+      <c r="G1708" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1708" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1708" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1708" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1708" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1708" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1709">
+      <c r="A1709" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1709" t="inlineStr">
+        <is>
+          <t>Japan vs Uruguay</t>
+        </is>
+      </c>
+      <c r="C1709" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D1709" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1709" t="inlineStr"/>
+      <c r="F1709" t="inlineStr"/>
+      <c r="G1709" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1709" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1709" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1709" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1709" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1709" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1710">
+      <c r="A1710" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1710" t="inlineStr">
+        <is>
+          <t>South Korea vs Ecuador</t>
+        </is>
+      </c>
+      <c r="C1710" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="D1710" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1710" t="inlineStr"/>
+      <c r="F1710" t="inlineStr"/>
+      <c r="G1710" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1710" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1710" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1710" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1710" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1710" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1711">
+      <c r="A1711" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1711" t="inlineStr">
+        <is>
+          <t>China vs Maldives</t>
+        </is>
+      </c>
+      <c r="C1711" t="inlineStr">
+        <is>
+          <t>China</t>
+        </is>
+      </c>
+      <c r="D1711" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1711" t="inlineStr"/>
+      <c r="F1711" t="inlineStr"/>
+      <c r="G1711" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1711" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1711" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1711" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1711" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1711" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1712">
+      <c r="A1712" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1712" t="inlineStr">
+        <is>
+          <t>Namibia vs Congo</t>
+        </is>
+      </c>
+      <c r="C1712" t="inlineStr">
+        <is>
+          <t>Namibia</t>
+        </is>
+      </c>
+      <c r="D1712" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1712" t="inlineStr"/>
+      <c r="F1712" t="inlineStr"/>
+      <c r="G1712" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1712" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1712" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1712" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1712" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1712" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1713">
+      <c r="A1713" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1713" t="inlineStr">
+        <is>
+          <t>United Arab Emirates vs Yemen</t>
+        </is>
+      </c>
+      <c r="C1713" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="D1713" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1713" t="inlineStr"/>
+      <c r="F1713" t="inlineStr"/>
+      <c r="G1713" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H1713" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1713" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1713" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1713" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1713" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1714">
+      <c r="A1714" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1714" t="inlineStr">
+        <is>
+          <t>Andorra vs Malta</t>
+        </is>
+      </c>
+      <c r="C1714" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="D1714" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1714" t="inlineStr"/>
+      <c r="F1714" t="inlineStr"/>
+      <c r="G1714" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1714" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1714" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1714" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1714" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1714" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1715">
+      <c r="A1715" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1715" t="inlineStr">
+        <is>
+          <t>Congo DR vs Equatorial Guinea</t>
+        </is>
+      </c>
+      <c r="C1715" t="inlineStr">
+        <is>
+          <t>Congo DR</t>
+        </is>
+      </c>
+      <c r="D1715" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1715" t="inlineStr"/>
+      <c r="F1715" t="inlineStr"/>
+      <c r="G1715" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1715" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1715" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1715" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1715" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1715" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1716">
+      <c r="A1716" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1716" t="inlineStr">
+        <is>
+          <t>Libya vs Botswana</t>
+        </is>
+      </c>
+      <c r="C1716" t="inlineStr">
+        <is>
+          <t>Libya</t>
+        </is>
+      </c>
+      <c r="D1716" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1716" t="inlineStr"/>
+      <c r="F1716" t="inlineStr"/>
+      <c r="G1716" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1716" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1716" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1716" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1716" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1716" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1717">
+      <c r="A1717" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1717" t="inlineStr">
+        <is>
+          <t>Mauritania vs Central African Republic</t>
+        </is>
+      </c>
+      <c r="C1717" t="inlineStr">
+        <is>
+          <t>Mauritania</t>
+        </is>
+      </c>
+      <c r="D1717" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1717" t="inlineStr"/>
+      <c r="F1717" t="inlineStr"/>
+      <c r="G1717" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1717" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1717" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1717" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1717" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1717" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1718">
+      <c r="A1718" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1718" t="inlineStr">
+        <is>
+          <t>Belgium U21 vs Belarus U21</t>
+        </is>
+      </c>
+      <c r="C1718" t="inlineStr">
+        <is>
+          <t>Belgium U21</t>
+        </is>
+      </c>
+      <c r="D1718" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1718" t="inlineStr"/>
+      <c r="F1718" t="inlineStr"/>
+      <c r="G1718" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1718" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1718" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1718" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1718" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1718" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1719">
+      <c r="A1719" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1719" t="inlineStr">
+        <is>
+          <t>Qatar vs Bahrain</t>
+        </is>
+      </c>
+      <c r="C1719" t="inlineStr">
+        <is>
+          <t>Qatar</t>
+        </is>
+      </c>
+      <c r="D1719" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1719" t="inlineStr"/>
+      <c r="F1719" t="inlineStr"/>
+      <c r="G1719" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1719" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1719" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1719" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1719" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1719" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1720">
+      <c r="A1720" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1720" t="inlineStr">
+        <is>
+          <t>San Marino U21 vs Kosovo U21</t>
+        </is>
+      </c>
+      <c r="C1720" t="inlineStr">
+        <is>
+          <t>Kosovo U21</t>
+        </is>
+      </c>
+      <c r="D1720" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1720" t="inlineStr"/>
+      <c r="F1720" t="inlineStr"/>
+      <c r="G1720" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H1720" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1720" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1720" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1720" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1720" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1721">
+      <c r="A1721" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1721" t="inlineStr">
+        <is>
+          <t>Austria vs Israel</t>
+        </is>
+      </c>
+      <c r="C1721" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="D1721" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1721" t="inlineStr"/>
+      <c r="F1721" t="inlineStr"/>
+      <c r="G1721" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1721" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1721" t="n">
+        <v>6</v>
+      </c>
+      <c r="J1721" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1721" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1721" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1722">
+      <c r="A1722" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1722" t="inlineStr">
+        <is>
+          <t>Netherlands vs Germany</t>
+        </is>
+      </c>
+      <c r="C1722" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D1722" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1722" t="inlineStr"/>
+      <c r="F1722" t="inlineStr"/>
+      <c r="G1722" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1722" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1722" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1722" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1722" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1722" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1723">
+      <c r="A1723" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1723" t="inlineStr">
+        <is>
+          <t>Portugal vs Wales</t>
+        </is>
+      </c>
+      <c r="C1723" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D1723" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1723" t="inlineStr"/>
+      <c r="F1723" t="inlineStr"/>
+      <c r="G1723" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1723" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1723" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1723" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1723" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1723" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1724">
+      <c r="A1724" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1724" t="inlineStr">
+        <is>
+          <t>Norway vs Denmark</t>
+        </is>
+      </c>
+      <c r="C1724" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="D1724" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1724" t="inlineStr"/>
+      <c r="F1724" t="inlineStr"/>
+      <c r="G1724" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1724" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1724" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1724" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1724" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1724" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1725">
+      <c r="A1725" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1725" t="inlineStr">
+        <is>
+          <t>Kosovo vs Republic of Ireland</t>
+        </is>
+      </c>
+      <c r="C1725" t="inlineStr">
+        <is>
+          <t>Kosovo</t>
+        </is>
+      </c>
+      <c r="D1725" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1725" t="inlineStr"/>
+      <c r="F1725" t="inlineStr"/>
+      <c r="G1725" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1725" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1725" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1725" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1725" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1725" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1726">
+      <c r="A1726" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1726" t="inlineStr">
+        <is>
+          <t>Liechtenstein vs Lithuania</t>
+        </is>
+      </c>
+      <c r="C1726" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="D1726" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1726" t="inlineStr"/>
+      <c r="F1726" t="inlineStr"/>
+      <c r="G1726" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1726" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1726" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1726" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1726" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1726" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1727" t="inlineStr">
+        <is>
+          <t>Tunisia vs Uganda</t>
+        </is>
+      </c>
+      <c r="C1727" t="inlineStr">
+        <is>
+          <t>Tunisia</t>
+        </is>
+      </c>
+      <c r="D1727" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1727" t="inlineStr"/>
+      <c r="F1727" t="inlineStr"/>
+      <c r="G1727" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1727" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1727" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1727" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1727" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1727" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1728" t="inlineStr">
+        <is>
+          <t>Sierra Leone vs Zimbabwe</t>
+        </is>
+      </c>
+      <c r="C1728" t="inlineStr">
+        <is>
+          <t>Sierra Leone</t>
+        </is>
+      </c>
+      <c r="D1728" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1728" t="inlineStr"/>
+      <c r="F1728" t="inlineStr"/>
+      <c r="G1728" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H1728" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1728" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1728" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1728" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1728" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1729" t="inlineStr">
+        <is>
+          <t>Cameroon vs Comoros</t>
+        </is>
+      </c>
+      <c r="C1729" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="D1729" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1729" t="inlineStr"/>
+      <c r="F1729" t="inlineStr"/>
+      <c r="G1729" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1729" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1729" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1729" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1729" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1729" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1730" t="inlineStr">
+        <is>
+          <t>Ivory Coast vs Ghana</t>
+        </is>
+      </c>
+      <c r="C1730" t="inlineStr">
+        <is>
+          <t>Ivory Coast</t>
+        </is>
+      </c>
+      <c r="D1730" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1730" t="inlineStr"/>
+      <c r="F1730" t="inlineStr"/>
+      <c r="G1730" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1730" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1730" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1730" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1730" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1730" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1731" t="inlineStr">
+        <is>
+          <t>Puerto Rico vs Guyana</t>
+        </is>
+      </c>
+      <c r="C1731" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="D1731" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1731" t="inlineStr"/>
+      <c r="F1731" t="inlineStr"/>
+      <c r="G1731" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1731" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1731" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1731" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1731" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1731" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1732" t="inlineStr">
+        <is>
+          <t>O'Higgins vs Deportes Santa Cruz</t>
+        </is>
+      </c>
+      <c r="C1732" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="D1732" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1732" t="inlineStr"/>
+      <c r="F1732" t="inlineStr"/>
+      <c r="G1732" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1732" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1732" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1732" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1732" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1732" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1733" t="inlineStr">
+        <is>
+          <t>Dominican Republic vs Nicaragua</t>
+        </is>
+      </c>
+      <c r="C1733" t="inlineStr">
+        <is>
+          <t>Dominican Republic</t>
+        </is>
+      </c>
+      <c r="D1733" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1733" t="inlineStr"/>
+      <c r="F1733" t="inlineStr"/>
+      <c r="G1733" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1733" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1733" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1733" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1733" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1733" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1734" t="inlineStr">
+        <is>
+          <t>Cayman Islands vs Dominica</t>
+        </is>
+      </c>
+      <c r="C1734" t="inlineStr">
+        <is>
+          <t>Dominica</t>
+        </is>
+      </c>
+      <c r="D1734" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1734" t="inlineStr"/>
+      <c r="F1734" t="inlineStr"/>
+      <c r="G1734" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1734" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1734" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1734" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1734" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1734" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1735" t="inlineStr">
+        <is>
+          <t>Haiti vs Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="C1735" t="inlineStr">
+        <is>
+          <t>Haiti</t>
+        </is>
+      </c>
+      <c r="D1735" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1735" t="inlineStr"/>
+      <c r="F1735" t="inlineStr"/>
+      <c r="G1735" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1735" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1735" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1735" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1735" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1735" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1736" t="inlineStr">
+        <is>
+          <t>Atlético Nacional vs Millonarios</t>
+        </is>
+      </c>
+      <c r="C1736" t="inlineStr">
+        <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="D1736" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1736" t="inlineStr"/>
+      <c r="F1736" t="inlineStr"/>
+      <c r="G1736" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1736" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1736" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1736" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1736" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1736" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1737" t="inlineStr">
+        <is>
+          <t>Mineros de Zacatecas vs Piratas</t>
+        </is>
+      </c>
+      <c r="C1737" t="inlineStr">
+        <is>
+          <t>Piratas</t>
+        </is>
+      </c>
+      <c r="D1737" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1737" t="inlineStr"/>
+      <c r="F1737" t="inlineStr"/>
+      <c r="G1737" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1737" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1737" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1737" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1737" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1737" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1738" t="inlineStr">
+        <is>
+          <t>Municipal vs Suchitepequez</t>
+        </is>
+      </c>
+      <c r="C1738" t="inlineStr">
+        <is>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="D1738" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1738" t="inlineStr"/>
+      <c r="F1738" t="inlineStr"/>
+      <c r="G1738" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1738" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1738" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1738" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1738" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1738" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B1739" t="inlineStr">
+        <is>
+          <t>Costa Rica vs Curaçao</t>
+        </is>
+      </c>
+      <c r="C1739" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+      <c r="D1739" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1739" t="inlineStr"/>
+      <c r="F1739" t="inlineStr"/>
+      <c r="G1739" t="inlineStr">
+        <is>
+          <t>3-4</t>
+        </is>
+      </c>
+      <c r="H1739" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1739" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1739" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1739" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1739" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -78947,7 +80543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E44"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79771,6 +81367,25 @@
       </c>
       <c r="E44" t="n">
         <v>18</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>34</v>
+      </c>
+      <c r="C45" t="n">
+        <v>28</v>
+      </c>
+      <c r="D45" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="E45" t="n">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -79784,7 +81399,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E235"/>
+  <dimension ref="A1:E244"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84728,6 +86343,195 @@
         <v>0</v>
       </c>
     </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C236" t="n">
+        <v>4</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0</v>
+      </c>
+      <c r="E236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C237" t="n">
+        <v>2</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0</v>
+      </c>
+      <c r="E237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>siguen_empatados_55</t>
+        </is>
+      </c>
+      <c r="C238" t="n">
+        <v>1</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0</v>
+      </c>
+      <c r="E238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>siguen_empatados_70</t>
+        </is>
+      </c>
+      <c r="C239" t="n">
+        <v>2</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0</v>
+      </c>
+      <c r="E239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C240" t="n">
+        <v>2</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0</v>
+      </c>
+      <c r="E240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C241" t="n">
+        <v>11</v>
+      </c>
+      <c r="D241" t="n">
+        <v>2</v>
+      </c>
+      <c r="E241" t="n">
+        <v>18.2</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C242" t="n">
+        <v>2</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0</v>
+      </c>
+      <c r="E242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C243" t="n">
+        <v>5</v>
+      </c>
+      <c r="D243" t="n">
+        <v>1</v>
+      </c>
+      <c r="E243" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C244" t="n">
+        <v>2</v>
+      </c>
+      <c r="D244" t="n">
+        <v>0</v>
+      </c>
+      <c r="E244" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1739"/>
+  <dimension ref="A1:L1800"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78921,8 +78921,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1706" t="inlineStr"/>
-      <c r="F1706" t="inlineStr"/>
       <c r="G1706" t="inlineStr">
         <is>
           <t>3-3</t>
@@ -78969,8 +78967,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1707" t="inlineStr"/>
-      <c r="F1707" t="inlineStr"/>
       <c r="G1707" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -79017,8 +79013,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1708" t="inlineStr"/>
-      <c r="F1708" t="inlineStr"/>
       <c r="G1708" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -79065,8 +79059,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1709" t="inlineStr"/>
-      <c r="F1709" t="inlineStr"/>
       <c r="G1709" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -79113,8 +79105,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1710" t="inlineStr"/>
-      <c r="F1710" t="inlineStr"/>
       <c r="G1710" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -79161,8 +79151,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1711" t="inlineStr"/>
-      <c r="F1711" t="inlineStr"/>
       <c r="G1711" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -79209,8 +79197,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1712" t="inlineStr"/>
-      <c r="F1712" t="inlineStr"/>
       <c r="G1712" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -79257,8 +79243,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1713" t="inlineStr"/>
-      <c r="F1713" t="inlineStr"/>
       <c r="G1713" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -79305,8 +79289,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1714" t="inlineStr"/>
-      <c r="F1714" t="inlineStr"/>
       <c r="G1714" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -79353,8 +79335,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1715" t="inlineStr"/>
-      <c r="F1715" t="inlineStr"/>
       <c r="G1715" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -79401,8 +79381,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1716" t="inlineStr"/>
-      <c r="F1716" t="inlineStr"/>
       <c r="G1716" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -79449,8 +79427,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1717" t="inlineStr"/>
-      <c r="F1717" t="inlineStr"/>
       <c r="G1717" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -79497,8 +79473,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1718" t="inlineStr"/>
-      <c r="F1718" t="inlineStr"/>
       <c r="G1718" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -79545,8 +79519,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1719" t="inlineStr"/>
-      <c r="F1719" t="inlineStr"/>
       <c r="G1719" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -79593,8 +79565,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1720" t="inlineStr"/>
-      <c r="F1720" t="inlineStr"/>
       <c r="G1720" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -79641,8 +79611,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1721" t="inlineStr"/>
-      <c r="F1721" t="inlineStr"/>
       <c r="G1721" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -79689,8 +79657,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1722" t="inlineStr"/>
-      <c r="F1722" t="inlineStr"/>
       <c r="G1722" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -79737,8 +79703,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1723" t="inlineStr"/>
-      <c r="F1723" t="inlineStr"/>
       <c r="G1723" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -79785,8 +79749,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1724" t="inlineStr"/>
-      <c r="F1724" t="inlineStr"/>
       <c r="G1724" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -79833,8 +79795,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1725" t="inlineStr"/>
-      <c r="F1725" t="inlineStr"/>
       <c r="G1725" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -79881,8 +79841,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1726" t="inlineStr"/>
-      <c r="F1726" t="inlineStr"/>
       <c r="G1726" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -79929,8 +79887,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1727" t="inlineStr"/>
-      <c r="F1727" t="inlineStr"/>
       <c r="G1727" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -79977,8 +79933,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1728" t="inlineStr"/>
-      <c r="F1728" t="inlineStr"/>
       <c r="G1728" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -80025,8 +79979,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1729" t="inlineStr"/>
-      <c r="F1729" t="inlineStr"/>
       <c r="G1729" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -80073,8 +80025,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1730" t="inlineStr"/>
-      <c r="F1730" t="inlineStr"/>
       <c r="G1730" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -80121,8 +80071,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1731" t="inlineStr"/>
-      <c r="F1731" t="inlineStr"/>
       <c r="G1731" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -80169,8 +80117,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1732" t="inlineStr"/>
-      <c r="F1732" t="inlineStr"/>
       <c r="G1732" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -80217,8 +80163,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1733" t="inlineStr"/>
-      <c r="F1733" t="inlineStr"/>
       <c r="G1733" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -80265,8 +80209,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1734" t="inlineStr"/>
-      <c r="F1734" t="inlineStr"/>
       <c r="G1734" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -80313,8 +80255,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1735" t="inlineStr"/>
-      <c r="F1735" t="inlineStr"/>
       <c r="G1735" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -80361,8 +80301,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1736" t="inlineStr"/>
-      <c r="F1736" t="inlineStr"/>
       <c r="G1736" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -80409,8 +80347,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1737" t="inlineStr"/>
-      <c r="F1737" t="inlineStr"/>
       <c r="G1737" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -80457,8 +80393,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1738" t="inlineStr"/>
-      <c r="F1738" t="inlineStr"/>
       <c r="G1738" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -80505,8 +80439,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1739" t="inlineStr"/>
-      <c r="F1739" t="inlineStr"/>
       <c r="G1739" t="inlineStr">
         <is>
           <t>3-4</t>
@@ -80527,6 +80459,2934 @@
         <v>0</v>
       </c>
       <c r="L1739" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1740" t="inlineStr">
+        <is>
+          <t>Australia vs Brazil</t>
+        </is>
+      </c>
+      <c r="C1740" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="D1740" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1740" t="inlineStr"/>
+      <c r="F1740" t="inlineStr"/>
+      <c r="G1740" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1740" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1740" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1740" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1740" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1740" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1741" t="inlineStr">
+        <is>
+          <t>Sudan vs Ethiopia</t>
+        </is>
+      </c>
+      <c r="C1741" t="inlineStr">
+        <is>
+          <t>Sudan</t>
+        </is>
+      </c>
+      <c r="D1741" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1741" t="inlineStr"/>
+      <c r="F1741" t="inlineStr"/>
+      <c r="G1741" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1741" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1741" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1741" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1741" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1741" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1742" t="inlineStr">
+        <is>
+          <t>India vs Panama</t>
+        </is>
+      </c>
+      <c r="C1742" t="inlineStr">
+        <is>
+          <t>Panama</t>
+        </is>
+      </c>
+      <c r="D1742" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1742" t="inlineStr"/>
+      <c r="F1742" t="inlineStr"/>
+      <c r="G1742" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1742" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1742" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1742" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1742" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1742" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1743" t="inlineStr">
+        <is>
+          <t>VfB Stuttgart vs 1. FC Heidenheim 1846</t>
+        </is>
+      </c>
+      <c r="C1743" t="inlineStr">
+        <is>
+          <t>VfB Stuttgart</t>
+        </is>
+      </c>
+      <c r="D1743" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1743" t="inlineStr"/>
+      <c r="F1743" t="inlineStr"/>
+      <c r="G1743" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1743" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1743" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1743" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1743" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1743" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1744" t="inlineStr">
+        <is>
+          <t>Niger vs Lesotho</t>
+        </is>
+      </c>
+      <c r="C1744" t="inlineStr">
+        <is>
+          <t>Niger</t>
+        </is>
+      </c>
+      <c r="D1744" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1744" t="inlineStr"/>
+      <c r="F1744" t="inlineStr"/>
+      <c r="G1744" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1744" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1744" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1744" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1744" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1744" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1745" t="inlineStr">
+        <is>
+          <t>Iceland U21 vs France U21</t>
+        </is>
+      </c>
+      <c r="C1745" t="inlineStr">
+        <is>
+          <t>France U21</t>
+        </is>
+      </c>
+      <c r="D1745" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1745" t="inlineStr"/>
+      <c r="F1745" t="inlineStr"/>
+      <c r="G1745" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1745" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1745" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1745" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1745" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1745" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1746" t="inlineStr">
+        <is>
+          <t>Finland U21 vs Spain U21</t>
+        </is>
+      </c>
+      <c r="C1746" t="inlineStr">
+        <is>
+          <t>Spain U21</t>
+        </is>
+      </c>
+      <c r="D1746" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1746" t="inlineStr"/>
+      <c r="F1746" t="inlineStr"/>
+      <c r="G1746" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1746" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1746" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1746" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1746" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1746" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1747" t="inlineStr">
+        <is>
+          <t>Bulgaria U21 vs Portugal U21</t>
+        </is>
+      </c>
+      <c r="C1747" t="inlineStr">
+        <is>
+          <t>Portugal U21</t>
+        </is>
+      </c>
+      <c r="D1747" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1747" t="inlineStr"/>
+      <c r="F1747" t="inlineStr"/>
+      <c r="G1747" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1747" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1747" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1747" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1747" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1747" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1748" t="inlineStr">
+        <is>
+          <t>Georgia vs Northern Ireland</t>
+        </is>
+      </c>
+      <c r="C1748" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="D1748" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1748" t="inlineStr"/>
+      <c r="F1748" t="inlineStr"/>
+      <c r="G1748" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1748" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1748" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1748" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1748" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1748" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1749" t="inlineStr">
+        <is>
+          <t>Armenia vs Latvia</t>
+        </is>
+      </c>
+      <c r="C1749" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="D1749" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1749" t="inlineStr"/>
+      <c r="F1749" t="inlineStr"/>
+      <c r="G1749" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1749" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1749" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1749" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1749" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1749" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1750" t="inlineStr">
+        <is>
+          <t>Gambia vs Somalia</t>
+        </is>
+      </c>
+      <c r="C1750" t="inlineStr">
+        <is>
+          <t>Gambia</t>
+        </is>
+      </c>
+      <c r="D1750" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1750" t="inlineStr"/>
+      <c r="F1750" t="inlineStr"/>
+      <c r="G1750" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1750" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1750" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1750" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1750" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1750" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1751" t="inlineStr">
+        <is>
+          <t>Malawi vs South Sudan</t>
+        </is>
+      </c>
+      <c r="C1751" t="inlineStr">
+        <is>
+          <t>Malawi</t>
+        </is>
+      </c>
+      <c r="D1751" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1751" t="inlineStr"/>
+      <c r="F1751" t="inlineStr"/>
+      <c r="G1751" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1751" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1751" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1751" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1751" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1751" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1752" t="inlineStr">
+        <is>
+          <t>Nigeria vs Madagascar</t>
+        </is>
+      </c>
+      <c r="C1752" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="D1752" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1752" t="inlineStr"/>
+      <c r="F1752" t="inlineStr"/>
+      <c r="G1752" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1752" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1752" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1752" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1752" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1752" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1753" t="inlineStr">
+        <is>
+          <t>Rwanda vs Liberia</t>
+        </is>
+      </c>
+      <c r="C1753" t="inlineStr">
+        <is>
+          <t>Rwanda</t>
+        </is>
+      </c>
+      <c r="D1753" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1753" t="inlineStr"/>
+      <c r="F1753" t="inlineStr"/>
+      <c r="G1753" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1753" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1753" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1753" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1753" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1753" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1754" t="inlineStr">
+        <is>
+          <t>Estonia U21 vs Faroe Islands U21</t>
+        </is>
+      </c>
+      <c r="C1754" t="inlineStr">
+        <is>
+          <t>Estonia U21</t>
+        </is>
+      </c>
+      <c r="D1754" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1754" t="inlineStr"/>
+      <c r="F1754" t="inlineStr"/>
+      <c r="G1754" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1754" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1754" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1754" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1754" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1754" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1755" t="inlineStr">
+        <is>
+          <t>Cyprus U21 vs Romania U21</t>
+        </is>
+      </c>
+      <c r="C1755" t="inlineStr">
+        <is>
+          <t>Romania U21</t>
+        </is>
+      </c>
+      <c r="D1755" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1755" t="inlineStr"/>
+      <c r="F1755" t="inlineStr"/>
+      <c r="G1755" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H1755" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1755" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1755" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1755" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1755" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1756" t="inlineStr">
+        <is>
+          <t>Slovakia U21 vs Republic of Ireland U21</t>
+        </is>
+      </c>
+      <c r="C1756" t="inlineStr">
+        <is>
+          <t>Slovakia U21</t>
+        </is>
+      </c>
+      <c r="D1756" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1756" t="inlineStr"/>
+      <c r="F1756" t="inlineStr"/>
+      <c r="G1756" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1756" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1756" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1756" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1756" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1756" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1757" t="inlineStr">
+        <is>
+          <t>Netherlands U21 vs Norway U21</t>
+        </is>
+      </c>
+      <c r="C1757" t="inlineStr">
+        <is>
+          <t>Netherlands U21</t>
+        </is>
+      </c>
+      <c r="D1757" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1757" t="inlineStr"/>
+      <c r="F1757" t="inlineStr"/>
+      <c r="G1757" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1757" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1757" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1757" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1757" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1757" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1758" t="inlineStr">
+        <is>
+          <t>Switzerland U21 vs Luxembourg U21</t>
+        </is>
+      </c>
+      <c r="C1758" t="inlineStr">
+        <is>
+          <t>Switzerland U21</t>
+        </is>
+      </c>
+      <c r="D1758" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1758" t="inlineStr"/>
+      <c r="F1758" t="inlineStr"/>
+      <c r="G1758" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="H1758" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1758" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1758" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1758" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1758" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1759" t="inlineStr">
+        <is>
+          <t>Girona vs Albacete</t>
+        </is>
+      </c>
+      <c r="C1759" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="D1759" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1759" t="inlineStr"/>
+      <c r="F1759" t="inlineStr"/>
+      <c r="G1759" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1759" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1759" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1759" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1759" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1759" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1760" t="inlineStr">
+        <is>
+          <t>England U21 vs Kazakhstan U21</t>
+        </is>
+      </c>
+      <c r="C1760" t="inlineStr">
+        <is>
+          <t>England U21</t>
+        </is>
+      </c>
+      <c r="D1760" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1760" t="inlineStr"/>
+      <c r="F1760" t="inlineStr"/>
+      <c r="G1760" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="H1760" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1760" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1760" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1760" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1760" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1761" t="inlineStr">
+        <is>
+          <t>Arbroath vs Queen's Park</t>
+        </is>
+      </c>
+      <c r="C1761" t="inlineStr">
+        <is>
+          <t>Arbroath</t>
+        </is>
+      </c>
+      <c r="D1761" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1761" t="inlineStr"/>
+      <c r="F1761" t="inlineStr"/>
+      <c r="G1761" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1761" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1761" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1761" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1761" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1761" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1762">
+      <c r="A1762" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1762" t="inlineStr">
+        <is>
+          <t>Ayr United vs Stenhousemuir</t>
+        </is>
+      </c>
+      <c r="C1762" t="inlineStr">
+        <is>
+          <t>Ayr United</t>
+        </is>
+      </c>
+      <c r="D1762" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1762" t="inlineStr"/>
+      <c r="F1762" t="inlineStr"/>
+      <c r="G1762" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1762" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1762" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1762" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1762" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1762" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1763">
+      <c r="A1763" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1763" t="inlineStr">
+        <is>
+          <t>Inverness Caledonian Thistle vs Greenock Morton</t>
+        </is>
+      </c>
+      <c r="C1763" t="inlineStr">
+        <is>
+          <t>Inverness Caledonian Thistle</t>
+        </is>
+      </c>
+      <c r="D1763" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1763" t="inlineStr"/>
+      <c r="F1763" t="inlineStr"/>
+      <c r="G1763" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1763" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1763" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1763" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1763" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1763" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1764">
+      <c r="A1764" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1764" t="inlineStr">
+        <is>
+          <t>Raith Rovers vs Livingston</t>
+        </is>
+      </c>
+      <c r="C1764" t="inlineStr">
+        <is>
+          <t>Raith Rovers</t>
+        </is>
+      </c>
+      <c r="D1764" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1764" t="inlineStr"/>
+      <c r="F1764" t="inlineStr"/>
+      <c r="G1764" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1764" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1764" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1764" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1764" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1764" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1765" t="inlineStr">
+        <is>
+          <t>Türkiye vs France</t>
+        </is>
+      </c>
+      <c r="C1765" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D1765" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1765" t="inlineStr"/>
+      <c r="F1765" t="inlineStr"/>
+      <c r="G1765" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1765" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1765" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1765" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1765" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1765" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1766" t="inlineStr">
+        <is>
+          <t>Italy vs Belgium</t>
+        </is>
+      </c>
+      <c r="C1766" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="D1766" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1766" t="inlineStr"/>
+      <c r="F1766" t="inlineStr"/>
+      <c r="G1766" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1766" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1766" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1766" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1766" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1766" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1767" t="inlineStr">
+        <is>
+          <t>Hungary vs Ukraine</t>
+        </is>
+      </c>
+      <c r="C1767" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="D1767" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1767" t="inlineStr"/>
+      <c r="F1767" t="inlineStr"/>
+      <c r="G1767" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1767" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1767" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1767" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1767" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1767" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1768">
+      <c r="A1768" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1768" t="inlineStr">
+        <is>
+          <t>Poland vs Bosnia-Herzegovina</t>
+        </is>
+      </c>
+      <c r="C1768" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+      <c r="D1768" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1768" t="inlineStr"/>
+      <c r="F1768" t="inlineStr"/>
+      <c r="G1768" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1768" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1768" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1768" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1768" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1768" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1769">
+      <c r="A1769" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1769" t="inlineStr">
+        <is>
+          <t>Sweden vs Romania</t>
+        </is>
+      </c>
+      <c r="C1769" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="D1769" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1769" t="inlineStr"/>
+      <c r="F1769" t="inlineStr"/>
+      <c r="G1769" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1769" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1769" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1769" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1769" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1769" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1770">
+      <c r="A1770" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1770" t="inlineStr">
+        <is>
+          <t>Montenegro vs Cyprus</t>
+        </is>
+      </c>
+      <c r="C1770" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="D1770" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1770" t="inlineStr"/>
+      <c r="F1770" t="inlineStr"/>
+      <c r="G1770" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1770" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1770" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1770" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1770" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1770" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1771">
+      <c r="A1771" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1771" t="inlineStr">
+        <is>
+          <t>Spartans FC vs Dundee B</t>
+        </is>
+      </c>
+      <c r="C1771" t="inlineStr">
+        <is>
+          <t>Spartans FC</t>
+        </is>
+      </c>
+      <c r="D1771" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1771" t="inlineStr"/>
+      <c r="F1771" t="inlineStr"/>
+      <c r="G1771" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1771" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1771" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1771" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1771" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1771" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1772" t="inlineStr">
+        <is>
+          <t>FC Dordrecht vs Almere City</t>
+        </is>
+      </c>
+      <c r="C1772" t="inlineStr">
+        <is>
+          <t>Almere City</t>
+        </is>
+      </c>
+      <c r="D1772" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1772" t="inlineStr"/>
+      <c r="F1772" t="inlineStr"/>
+      <c r="G1772" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1772" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1772" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1772" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1772" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1772" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1773" t="inlineStr">
+        <is>
+          <t>Algeria vs Zambia</t>
+        </is>
+      </c>
+      <c r="C1773" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="D1773" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1773" t="inlineStr"/>
+      <c r="F1773" t="inlineStr"/>
+      <c r="G1773" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1773" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1773" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1773" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1773" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1773" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1774">
+      <c r="A1774" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1774" t="inlineStr">
+        <is>
+          <t>Burkina Faso vs Benin</t>
+        </is>
+      </c>
+      <c r="C1774" t="inlineStr">
+        <is>
+          <t>Burkina Faso</t>
+        </is>
+      </c>
+      <c r="D1774" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1774" t="inlineStr"/>
+      <c r="F1774" t="inlineStr"/>
+      <c r="G1774" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1774" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1774" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1774" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1774" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1774" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1775" t="inlineStr">
+        <is>
+          <t>Egypt vs Angola</t>
+        </is>
+      </c>
+      <c r="C1775" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D1775" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1775" t="inlineStr"/>
+      <c r="F1775" t="inlineStr"/>
+      <c r="G1775" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1775" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1775" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1775" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1775" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1775" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1776" t="inlineStr">
+        <is>
+          <t>Morocco vs Gabon</t>
+        </is>
+      </c>
+      <c r="C1776" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="D1776" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1776" t="inlineStr"/>
+      <c r="F1776" t="inlineStr"/>
+      <c r="G1776" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1776" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1776" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1776" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1776" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1776" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1777" t="inlineStr">
+        <is>
+          <t>Bermuda vs Guadeloupe</t>
+        </is>
+      </c>
+      <c r="C1777" t="inlineStr">
+        <is>
+          <t>Guadeloupe</t>
+        </is>
+      </c>
+      <c r="D1777" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1777" t="inlineStr"/>
+      <c r="F1777" t="inlineStr"/>
+      <c r="G1777" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1777" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1777" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1777" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1777" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1777" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1778" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo vs Real Potosí</t>
+        </is>
+      </c>
+      <c r="C1778" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
+      <c r="D1778" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1778" t="inlineStr"/>
+      <c r="F1778" t="inlineStr"/>
+      <c r="G1778" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1778" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1778" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1778" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1778" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1778" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1779" t="inlineStr">
+        <is>
+          <t>Mali vs Cape Verde</t>
+        </is>
+      </c>
+      <c r="C1779" t="inlineStr">
+        <is>
+          <t>Mali</t>
+        </is>
+      </c>
+      <c r="D1779" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1779" t="inlineStr"/>
+      <c r="F1779" t="inlineStr"/>
+      <c r="G1779" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1779" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1779" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1779" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1779" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1779" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1780" t="inlineStr">
+        <is>
+          <t>Sportivo Luqueño vs Guaraní</t>
+        </is>
+      </c>
+      <c r="C1780" t="inlineStr">
+        <is>
+          <t>Guaraní</t>
+        </is>
+      </c>
+      <c r="D1780" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1780" t="inlineStr"/>
+      <c r="F1780" t="inlineStr"/>
+      <c r="G1780" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1780" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1780" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1780" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1780" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1780" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1781" t="inlineStr">
+        <is>
+          <t>Grenada vs Cuba</t>
+        </is>
+      </c>
+      <c r="C1781" t="inlineStr">
+        <is>
+          <t>Cuba</t>
+        </is>
+      </c>
+      <c r="D1781" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1781" t="inlineStr"/>
+      <c r="F1781" t="inlineStr"/>
+      <c r="G1781" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H1781" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1781" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1781" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1781" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1781" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1782" t="inlineStr">
+        <is>
+          <t>ABB vs Aurora</t>
+        </is>
+      </c>
+      <c r="C1782" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="D1782" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1782" t="inlineStr"/>
+      <c r="F1782" t="inlineStr"/>
+      <c r="G1782" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1782" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1782" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1782" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1782" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1782" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1783" t="inlineStr">
+        <is>
+          <t>Ituzaingó vs Defensores Unidos</t>
+        </is>
+      </c>
+      <c r="C1783" t="inlineStr">
+        <is>
+          <t>Defensores Unidos</t>
+        </is>
+      </c>
+      <c r="D1783" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1783" t="inlineStr"/>
+      <c r="F1783" t="inlineStr"/>
+      <c r="G1783" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1783" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1783" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1783" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1783" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1783" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1784">
+      <c r="A1784" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1784" t="inlineStr">
+        <is>
+          <t>Nacional Asunción vs Sportivo Ameliano</t>
+        </is>
+      </c>
+      <c r="C1784" t="inlineStr">
+        <is>
+          <t>Nacional Asunción</t>
+        </is>
+      </c>
+      <c r="D1784" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1784" t="inlineStr"/>
+      <c r="F1784" t="inlineStr"/>
+      <c r="G1784" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1784" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1784" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1784" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1784" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1784" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1785">
+      <c r="A1785" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1785" t="inlineStr">
+        <is>
+          <t>Novorizontino vs São Bernardo</t>
+        </is>
+      </c>
+      <c r="C1785" t="inlineStr">
+        <is>
+          <t>Novorizontino</t>
+        </is>
+      </c>
+      <c r="D1785" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1785" t="inlineStr"/>
+      <c r="F1785" t="inlineStr"/>
+      <c r="G1785" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1785" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1785" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1785" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1785" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1785" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1786">
+      <c r="A1786" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1786" t="inlineStr">
+        <is>
+          <t>Excursionistas vs Real Pilar</t>
+        </is>
+      </c>
+      <c r="C1786" t="inlineStr">
+        <is>
+          <t>Excursionistas</t>
+        </is>
+      </c>
+      <c r="D1786" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1786" t="inlineStr"/>
+      <c r="F1786" t="inlineStr"/>
+      <c r="G1786" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1786" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1786" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1786" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1786" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1786" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1787">
+      <c r="A1787" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1787" t="inlineStr">
+        <is>
+          <t>Colo Colo vs Audax Italiano</t>
+        </is>
+      </c>
+      <c r="C1787" t="inlineStr">
+        <is>
+          <t>Colo Colo</t>
+        </is>
+      </c>
+      <c r="D1787" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1787" t="inlineStr"/>
+      <c r="F1787" t="inlineStr"/>
+      <c r="G1787" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1787" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1787" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1787" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1787" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1787" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1788">
+      <c r="A1788" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1788" t="inlineStr">
+        <is>
+          <t>Unión Magdalena vs Independiente Santa Fe</t>
+        </is>
+      </c>
+      <c r="C1788" t="inlineStr">
+        <is>
+          <t>Independiente Santa Fe</t>
+        </is>
+      </c>
+      <c r="D1788" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1788" t="inlineStr"/>
+      <c r="F1788" t="inlineStr"/>
+      <c r="G1788" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1788" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1788" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1788" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1788" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1788" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1789">
+      <c r="A1789" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1789" t="inlineStr">
+        <is>
+          <t>Hartford Athletic vs Louisville City FC</t>
+        </is>
+      </c>
+      <c r="C1789" t="inlineStr">
+        <is>
+          <t>Louisville City FC</t>
+        </is>
+      </c>
+      <c r="D1789" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1789" t="inlineStr"/>
+      <c r="F1789" t="inlineStr"/>
+      <c r="G1789" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1789" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1789" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1789" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1789" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1789" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1790">
+      <c r="A1790" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1790" t="inlineStr">
+        <is>
+          <t>Vila Nova vs Londrina</t>
+        </is>
+      </c>
+      <c r="C1790" t="inlineStr">
+        <is>
+          <t>Vila Nova</t>
+        </is>
+      </c>
+      <c r="D1790" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1790" t="inlineStr"/>
+      <c r="F1790" t="inlineStr"/>
+      <c r="G1790" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1790" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1790" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1790" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1790" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1790" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1791">
+      <c r="A1791" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1791" t="inlineStr">
+        <is>
+          <t>Sporting JAX vs Loudoun United FC</t>
+        </is>
+      </c>
+      <c r="C1791" t="inlineStr">
+        <is>
+          <t>Loudoun United FC</t>
+        </is>
+      </c>
+      <c r="D1791" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1791" t="inlineStr"/>
+      <c r="F1791" t="inlineStr"/>
+      <c r="G1791" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="H1791" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1791" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1791" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1791" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1791" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1792">
+      <c r="A1792" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1792" t="inlineStr">
+        <is>
+          <t>Nacional Potosí vs Always Ready</t>
+        </is>
+      </c>
+      <c r="C1792" t="inlineStr">
+        <is>
+          <t>Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="D1792" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1792" t="inlineStr"/>
+      <c r="F1792" t="inlineStr"/>
+      <c r="G1792" t="inlineStr">
+        <is>
+          <t>9-0</t>
+        </is>
+      </c>
+      <c r="H1792" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1792" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1792" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1792" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1792" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1793">
+      <c r="A1793" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1793" t="inlineStr">
+        <is>
+          <t>Barbados vs St. Lucia</t>
+        </is>
+      </c>
+      <c r="C1793" t="inlineStr">
+        <is>
+          <t>St. Lucia</t>
+        </is>
+      </c>
+      <c r="D1793" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1793" t="inlineStr"/>
+      <c r="F1793" t="inlineStr"/>
+      <c r="G1793" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1793" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1793" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1793" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1793" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1793" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1794">
+      <c r="A1794" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1794" t="inlineStr">
+        <is>
+          <t>Jamaica vs Guatemala</t>
+        </is>
+      </c>
+      <c r="C1794" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="D1794" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1794" t="inlineStr"/>
+      <c r="F1794" t="inlineStr"/>
+      <c r="G1794" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1794" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1794" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1794" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1794" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1794" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1795">
+      <c r="A1795" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1795" t="inlineStr">
+        <is>
+          <t>Atlante vs Monterrey</t>
+        </is>
+      </c>
+      <c r="C1795" t="inlineStr">
+        <is>
+          <t>Monterrey</t>
+        </is>
+      </c>
+      <c r="D1795" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1795" t="inlineStr"/>
+      <c r="F1795" t="inlineStr"/>
+      <c r="G1795" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="H1795" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1795" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1795" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1795" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1795" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1796">
+      <c r="A1796" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1796" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive FC vs FC Tulsa</t>
+        </is>
+      </c>
+      <c r="C1796" t="inlineStr">
+        <is>
+          <t>El Paso Locomotive FC</t>
+        </is>
+      </c>
+      <c r="D1796" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1796" t="inlineStr"/>
+      <c r="F1796" t="inlineStr"/>
+      <c r="G1796" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1796" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1796" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1796" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1796" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1796" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1797">
+      <c r="A1797" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1797" t="inlineStr">
+        <is>
+          <t>Honduras vs Suriname</t>
+        </is>
+      </c>
+      <c r="C1797" t="inlineStr">
+        <is>
+          <t>Honduras</t>
+        </is>
+      </c>
+      <c r="D1797" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1797" t="inlineStr"/>
+      <c r="F1797" t="inlineStr"/>
+      <c r="G1797" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H1797" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1797" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1797" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1797" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1797" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1798">
+      <c r="A1798" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1798" t="inlineStr">
+        <is>
+          <t>Once Caldas vs Atlético Bucaramanga</t>
+        </is>
+      </c>
+      <c r="C1798" t="inlineStr">
+        <is>
+          <t>Once Caldas</t>
+        </is>
+      </c>
+      <c r="D1798" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1798" t="inlineStr"/>
+      <c r="F1798" t="inlineStr"/>
+      <c r="G1798" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H1798" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1798" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1798" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1798" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1798" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1799">
+      <c r="A1799" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1799" t="inlineStr">
+        <is>
+          <t>Tijuana vs Atlas</t>
+        </is>
+      </c>
+      <c r="C1799" t="inlineStr">
+        <is>
+          <t>Tijuana</t>
+        </is>
+      </c>
+      <c r="D1799" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1799" t="inlineStr"/>
+      <c r="F1799" t="inlineStr"/>
+      <c r="G1799" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H1799" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1799" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1799" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1799" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1799" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1800">
+      <c r="A1800" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B1800" t="inlineStr">
+        <is>
+          <t>El Salvador vs Martinique</t>
+        </is>
+      </c>
+      <c r="C1800" t="inlineStr">
+        <is>
+          <t>El Salvador</t>
+        </is>
+      </c>
+      <c r="D1800" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1800" t="inlineStr"/>
+      <c r="F1800" t="inlineStr"/>
+      <c r="G1800" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1800" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1800" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1800" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1800" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1800" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -80543,7 +83403,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E45"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81386,6 +84246,25 @@
       </c>
       <c r="E45" t="n">
         <v>34</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>61</v>
+      </c>
+      <c r="C46" t="n">
+        <v>39</v>
+      </c>
+      <c r="D46" t="n">
+        <v>63.9</v>
+      </c>
+      <c r="E46" t="n">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -81399,7 +84278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E244"/>
+  <dimension ref="A1:E254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86532,6 +89411,216 @@
         <v>0</v>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C245" t="n">
+        <v>5</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0</v>
+      </c>
+      <c r="E245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C246" t="n">
+        <v>9</v>
+      </c>
+      <c r="D246" t="n">
+        <v>3</v>
+      </c>
+      <c r="E246" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C247" t="n">
+        <v>10</v>
+      </c>
+      <c r="D247" t="n">
+        <v>1</v>
+      </c>
+      <c r="E247" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C248" t="n">
+        <v>6</v>
+      </c>
+      <c r="D248" t="n">
+        <v>0</v>
+      </c>
+      <c r="E248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C249" t="n">
+        <v>6</v>
+      </c>
+      <c r="D249" t="n">
+        <v>1</v>
+      </c>
+      <c r="E249" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C250" t="n">
+        <v>6</v>
+      </c>
+      <c r="D250" t="n">
+        <v>1</v>
+      </c>
+      <c r="E250" t="n">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>siguen_empatados_55</t>
+        </is>
+      </c>
+      <c r="C251" t="n">
+        <v>3</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0</v>
+      </c>
+      <c r="E251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C252" t="n">
+        <v>3</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0</v>
+      </c>
+      <c r="E252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>gol_de_cierre</t>
+        </is>
+      </c>
+      <c r="C253" t="n">
+        <v>2</v>
+      </c>
+      <c r="D253" t="n">
+        <v>1</v>
+      </c>
+      <c r="E253" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>siguen_empatados_70</t>
+        </is>
+      </c>
+      <c r="C254" t="n">
+        <v>2</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0</v>
+      </c>
+      <c r="E254" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1800"/>
+  <dimension ref="A1:L1859"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80485,8 +80485,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1740" t="inlineStr"/>
-      <c r="F1740" t="inlineStr"/>
       <c r="G1740" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -80533,8 +80531,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1741" t="inlineStr"/>
-      <c r="F1741" t="inlineStr"/>
       <c r="G1741" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -80581,8 +80577,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1742" t="inlineStr"/>
-      <c r="F1742" t="inlineStr"/>
       <c r="G1742" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -80629,8 +80623,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1743" t="inlineStr"/>
-      <c r="F1743" t="inlineStr"/>
       <c r="G1743" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -80677,8 +80669,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1744" t="inlineStr"/>
-      <c r="F1744" t="inlineStr"/>
       <c r="G1744" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -80725,8 +80715,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1745" t="inlineStr"/>
-      <c r="F1745" t="inlineStr"/>
       <c r="G1745" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -80773,8 +80761,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1746" t="inlineStr"/>
-      <c r="F1746" t="inlineStr"/>
       <c r="G1746" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -80821,8 +80807,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1747" t="inlineStr"/>
-      <c r="F1747" t="inlineStr"/>
       <c r="G1747" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -80869,8 +80853,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1748" t="inlineStr"/>
-      <c r="F1748" t="inlineStr"/>
       <c r="G1748" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -80917,8 +80899,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1749" t="inlineStr"/>
-      <c r="F1749" t="inlineStr"/>
       <c r="G1749" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -80965,8 +80945,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1750" t="inlineStr"/>
-      <c r="F1750" t="inlineStr"/>
       <c r="G1750" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -81013,8 +80991,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1751" t="inlineStr"/>
-      <c r="F1751" t="inlineStr"/>
       <c r="G1751" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -81061,8 +81037,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1752" t="inlineStr"/>
-      <c r="F1752" t="inlineStr"/>
       <c r="G1752" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -81109,8 +81083,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1753" t="inlineStr"/>
-      <c r="F1753" t="inlineStr"/>
       <c r="G1753" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -81157,8 +81129,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1754" t="inlineStr"/>
-      <c r="F1754" t="inlineStr"/>
       <c r="G1754" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -81205,8 +81175,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1755" t="inlineStr"/>
-      <c r="F1755" t="inlineStr"/>
       <c r="G1755" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -81253,8 +81221,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1756" t="inlineStr"/>
-      <c r="F1756" t="inlineStr"/>
       <c r="G1756" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -81301,8 +81267,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1757" t="inlineStr"/>
-      <c r="F1757" t="inlineStr"/>
       <c r="G1757" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -81349,8 +81313,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1758" t="inlineStr"/>
-      <c r="F1758" t="inlineStr"/>
       <c r="G1758" t="inlineStr">
         <is>
           <t>5-0</t>
@@ -81397,8 +81359,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1759" t="inlineStr"/>
-      <c r="F1759" t="inlineStr"/>
       <c r="G1759" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -81445,8 +81405,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1760" t="inlineStr"/>
-      <c r="F1760" t="inlineStr"/>
       <c r="G1760" t="inlineStr">
         <is>
           <t>4-2</t>
@@ -81493,8 +81451,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1761" t="inlineStr"/>
-      <c r="F1761" t="inlineStr"/>
       <c r="G1761" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -81541,8 +81497,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1762" t="inlineStr"/>
-      <c r="F1762" t="inlineStr"/>
       <c r="G1762" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -81589,8 +81543,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1763" t="inlineStr"/>
-      <c r="F1763" t="inlineStr"/>
       <c r="G1763" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -81637,8 +81589,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1764" t="inlineStr"/>
-      <c r="F1764" t="inlineStr"/>
       <c r="G1764" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -81685,8 +81635,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1765" t="inlineStr"/>
-      <c r="F1765" t="inlineStr"/>
       <c r="G1765" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -81733,8 +81681,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1766" t="inlineStr"/>
-      <c r="F1766" t="inlineStr"/>
       <c r="G1766" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -81781,8 +81727,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1767" t="inlineStr"/>
-      <c r="F1767" t="inlineStr"/>
       <c r="G1767" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -81829,8 +81773,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1768" t="inlineStr"/>
-      <c r="F1768" t="inlineStr"/>
       <c r="G1768" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -81877,8 +81819,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1769" t="inlineStr"/>
-      <c r="F1769" t="inlineStr"/>
       <c r="G1769" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -81925,8 +81865,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1770" t="inlineStr"/>
-      <c r="F1770" t="inlineStr"/>
       <c r="G1770" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -81973,8 +81911,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1771" t="inlineStr"/>
-      <c r="F1771" t="inlineStr"/>
       <c r="G1771" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -82021,8 +81957,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1772" t="inlineStr"/>
-      <c r="F1772" t="inlineStr"/>
       <c r="G1772" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -82069,8 +82003,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1773" t="inlineStr"/>
-      <c r="F1773" t="inlineStr"/>
       <c r="G1773" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -82117,8 +82049,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1774" t="inlineStr"/>
-      <c r="F1774" t="inlineStr"/>
       <c r="G1774" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -82165,8 +82095,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1775" t="inlineStr"/>
-      <c r="F1775" t="inlineStr"/>
       <c r="G1775" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -82213,8 +82141,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1776" t="inlineStr"/>
-      <c r="F1776" t="inlineStr"/>
       <c r="G1776" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -82261,8 +82187,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1777" t="inlineStr"/>
-      <c r="F1777" t="inlineStr"/>
       <c r="G1777" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -82309,8 +82233,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1778" t="inlineStr"/>
-      <c r="F1778" t="inlineStr"/>
       <c r="G1778" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -82357,8 +82279,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1779" t="inlineStr"/>
-      <c r="F1779" t="inlineStr"/>
       <c r="G1779" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -82405,8 +82325,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1780" t="inlineStr"/>
-      <c r="F1780" t="inlineStr"/>
       <c r="G1780" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -82453,8 +82371,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1781" t="inlineStr"/>
-      <c r="F1781" t="inlineStr"/>
       <c r="G1781" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -82501,8 +82417,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1782" t="inlineStr"/>
-      <c r="F1782" t="inlineStr"/>
       <c r="G1782" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -82549,8 +82463,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1783" t="inlineStr"/>
-      <c r="F1783" t="inlineStr"/>
       <c r="G1783" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -82597,8 +82509,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1784" t="inlineStr"/>
-      <c r="F1784" t="inlineStr"/>
       <c r="G1784" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -82645,8 +82555,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1785" t="inlineStr"/>
-      <c r="F1785" t="inlineStr"/>
       <c r="G1785" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -82693,8 +82601,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1786" t="inlineStr"/>
-      <c r="F1786" t="inlineStr"/>
       <c r="G1786" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -82741,8 +82647,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1787" t="inlineStr"/>
-      <c r="F1787" t="inlineStr"/>
       <c r="G1787" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -82789,8 +82693,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1788" t="inlineStr"/>
-      <c r="F1788" t="inlineStr"/>
       <c r="G1788" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -82837,8 +82739,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1789" t="inlineStr"/>
-      <c r="F1789" t="inlineStr"/>
       <c r="G1789" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -82885,8 +82785,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1790" t="inlineStr"/>
-      <c r="F1790" t="inlineStr"/>
       <c r="G1790" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -82933,8 +82831,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1791" t="inlineStr"/>
-      <c r="F1791" t="inlineStr"/>
       <c r="G1791" t="inlineStr">
         <is>
           <t>1-4</t>
@@ -82981,8 +82877,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1792" t="inlineStr"/>
-      <c r="F1792" t="inlineStr"/>
       <c r="G1792" t="inlineStr">
         <is>
           <t>9-0</t>
@@ -83029,8 +82923,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1793" t="inlineStr"/>
-      <c r="F1793" t="inlineStr"/>
       <c r="G1793" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -83077,8 +82969,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1794" t="inlineStr"/>
-      <c r="F1794" t="inlineStr"/>
       <c r="G1794" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -83125,8 +83015,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1795" t="inlineStr"/>
-      <c r="F1795" t="inlineStr"/>
       <c r="G1795" t="inlineStr">
         <is>
           <t>4-2</t>
@@ -83173,8 +83061,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1796" t="inlineStr"/>
-      <c r="F1796" t="inlineStr"/>
       <c r="G1796" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -83221,8 +83107,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1797" t="inlineStr"/>
-      <c r="F1797" t="inlineStr"/>
       <c r="G1797" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -83269,8 +83153,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1798" t="inlineStr"/>
-      <c r="F1798" t="inlineStr"/>
       <c r="G1798" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -83317,8 +83199,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1799" t="inlineStr"/>
-      <c r="F1799" t="inlineStr"/>
       <c r="G1799" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -83365,8 +83245,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1800" t="inlineStr"/>
-      <c r="F1800" t="inlineStr"/>
       <c r="G1800" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -83387,6 +83265,2838 @@
         <v>0</v>
       </c>
       <c r="L1800" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1801">
+      <c r="A1801" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1801" t="inlineStr">
+        <is>
+          <t>Ceuta vs Real Sociedad II</t>
+        </is>
+      </c>
+      <c r="C1801" t="inlineStr">
+        <is>
+          <t>Ceuta</t>
+        </is>
+      </c>
+      <c r="D1801" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1801" t="inlineStr"/>
+      <c r="F1801" t="inlineStr"/>
+      <c r="G1801" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1801" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1801" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1801" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1801" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1801" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1802">
+      <c r="A1802" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1802" t="inlineStr">
+        <is>
+          <t>Slovenia vs Scotland</t>
+        </is>
+      </c>
+      <c r="C1802" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="D1802" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1802" t="inlineStr"/>
+      <c r="F1802" t="inlineStr"/>
+      <c r="G1802" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1802" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1802" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1802" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1802" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1802" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1803">
+      <c r="A1803" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1803" t="inlineStr">
+        <is>
+          <t>Kenya vs Eritrea</t>
+        </is>
+      </c>
+      <c r="C1803" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="D1803" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1803" t="inlineStr"/>
+      <c r="F1803" t="inlineStr"/>
+      <c r="G1803" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1803" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1803" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1803" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1803" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1803" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1804">
+      <c r="A1804" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1804" t="inlineStr">
+        <is>
+          <t>South Africa vs Guinea</t>
+        </is>
+      </c>
+      <c r="C1804" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="D1804" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1804" t="inlineStr"/>
+      <c r="F1804" t="inlineStr"/>
+      <c r="G1804" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1804" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1804" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1804" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1804" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1804" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1805">
+      <c r="A1805" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1805" t="inlineStr">
+        <is>
+          <t>Progreso vs Racing (Montevideo)</t>
+        </is>
+      </c>
+      <c r="C1805" t="inlineStr">
+        <is>
+          <t>Racing (Montevideo)</t>
+        </is>
+      </c>
+      <c r="D1805" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1805" t="inlineStr"/>
+      <c r="F1805" t="inlineStr"/>
+      <c r="G1805" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1805" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1805" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1805" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1805" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1805" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1806">
+      <c r="A1806" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1806" t="inlineStr">
+        <is>
+          <t>Pogon Szczecin vs Udinese</t>
+        </is>
+      </c>
+      <c r="C1806" t="inlineStr">
+        <is>
+          <t>Udinese</t>
+        </is>
+      </c>
+      <c r="D1806" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1806" t="inlineStr"/>
+      <c r="F1806" t="inlineStr"/>
+      <c r="G1806" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1806" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1806" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1806" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1806" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1806" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1807">
+      <c r="A1807" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1807" t="inlineStr">
+        <is>
+          <t>San Marino vs Finland</t>
+        </is>
+      </c>
+      <c r="C1807" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="D1807" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1807" t="inlineStr"/>
+      <c r="F1807" t="inlineStr"/>
+      <c r="G1807" t="inlineStr">
+        <is>
+          <t>0-7</t>
+        </is>
+      </c>
+      <c r="H1807" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1807" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1807" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1807" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1807" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1808">
+      <c r="A1808" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1808" t="inlineStr">
+        <is>
+          <t>Faroe Islands vs Kazakhstan</t>
+        </is>
+      </c>
+      <c r="C1808" t="inlineStr">
+        <is>
+          <t>Faroe Islands</t>
+        </is>
+      </c>
+      <c r="D1808" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1808" t="inlineStr"/>
+      <c r="F1808" t="inlineStr"/>
+      <c r="G1808" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1808" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1808" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1808" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1808" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1808" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1809">
+      <c r="A1809" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1809" t="inlineStr">
+        <is>
+          <t>Iceland vs Estonia</t>
+        </is>
+      </c>
+      <c r="C1809" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="D1809" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1809" t="inlineStr"/>
+      <c r="F1809" t="inlineStr"/>
+      <c r="G1809" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1809" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1809" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1809" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1809" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1809" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1810">
+      <c r="A1810" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1810" t="inlineStr">
+        <is>
+          <t>Bulgaria vs Luxembourg</t>
+        </is>
+      </c>
+      <c r="C1810" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="D1810" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1810" t="inlineStr"/>
+      <c r="F1810" t="inlineStr"/>
+      <c r="G1810" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1810" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1810" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1810" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1810" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1810" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1811">
+      <c r="A1811" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1811" t="inlineStr">
+        <is>
+          <t>Tenerife vs Cádiz</t>
+        </is>
+      </c>
+      <c r="C1811" t="inlineStr">
+        <is>
+          <t>Tenerife</t>
+        </is>
+      </c>
+      <c r="D1811" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1811" t="inlineStr"/>
+      <c r="F1811" t="inlineStr"/>
+      <c r="G1811" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1811" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1811" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1811" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1811" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1811" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1812">
+      <c r="A1812" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1812" t="inlineStr">
+        <is>
+          <t>Cerro Largo vs Nacional</t>
+        </is>
+      </c>
+      <c r="C1812" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="D1812" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1812" t="inlineStr"/>
+      <c r="F1812" t="inlineStr"/>
+      <c r="G1812" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1812" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1812" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1812" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1812" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1812" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1813">
+      <c r="A1813" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1813" t="inlineStr">
+        <is>
+          <t>Charlotte Independence vs Fort Wayne</t>
+        </is>
+      </c>
+      <c r="C1813" t="inlineStr">
+        <is>
+          <t>Charlotte Independence</t>
+        </is>
+      </c>
+      <c r="D1813" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1813" t="inlineStr"/>
+      <c r="F1813" t="inlineStr"/>
+      <c r="G1813" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1813" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1813" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1813" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1813" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1813" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1814">
+      <c r="A1814" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1814" t="inlineStr">
+        <is>
+          <t>England vs Spain</t>
+        </is>
+      </c>
+      <c r="C1814" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D1814" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1814" t="inlineStr"/>
+      <c r="F1814" t="inlineStr"/>
+      <c r="G1814" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H1814" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1814" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1814" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1814" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1814" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1815">
+      <c r="A1815" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1815" t="inlineStr">
+        <is>
+          <t>Czechia vs Croatia</t>
+        </is>
+      </c>
+      <c r="C1815" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="D1815" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1815" t="inlineStr"/>
+      <c r="F1815" t="inlineStr"/>
+      <c r="G1815" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1815" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1815" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1815" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1815" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1815" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1816">
+      <c r="A1816" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1816" t="inlineStr">
+        <is>
+          <t>Albania vs Belarus</t>
+        </is>
+      </c>
+      <c r="C1816" t="inlineStr">
+        <is>
+          <t>Albania</t>
+        </is>
+      </c>
+      <c r="D1816" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1816" t="inlineStr"/>
+      <c r="F1816" t="inlineStr"/>
+      <c r="G1816" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1816" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1816" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1816" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1816" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1816" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1817">
+      <c r="A1817" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1817" t="inlineStr">
+        <is>
+          <t>Slovakia vs Moldova</t>
+        </is>
+      </c>
+      <c r="C1817" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="D1817" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1817" t="inlineStr"/>
+      <c r="F1817" t="inlineStr"/>
+      <c r="G1817" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1817" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1817" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1817" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1817" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1817" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1818">
+      <c r="A1818" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1818" t="inlineStr">
+        <is>
+          <t>Montserrat vs British Virgin Islands</t>
+        </is>
+      </c>
+      <c r="C1818" t="inlineStr">
+        <is>
+          <t>Montserrat</t>
+        </is>
+      </c>
+      <c r="D1818" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1818" t="inlineStr"/>
+      <c r="F1818" t="inlineStr"/>
+      <c r="G1818" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1818" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1818" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1818" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1818" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1818" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1819">
+      <c r="A1819" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1819" t="inlineStr">
+        <is>
+          <t>Náutico vs Sport</t>
+        </is>
+      </c>
+      <c r="C1819" t="inlineStr">
+        <is>
+          <t>Náutico</t>
+        </is>
+      </c>
+      <c r="D1819" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1819" t="inlineStr"/>
+      <c r="F1819" t="inlineStr"/>
+      <c r="G1819" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1819" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1819" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1819" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1819" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1819" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1820">
+      <c r="A1820" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1820" t="inlineStr">
+        <is>
+          <t>Operário PR vs Ceará</t>
+        </is>
+      </c>
+      <c r="C1820" t="inlineStr">
+        <is>
+          <t>Operário PR</t>
+        </is>
+      </c>
+      <c r="D1820" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1820" t="inlineStr"/>
+      <c r="F1820" t="inlineStr"/>
+      <c r="G1820" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1820" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1820" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1820" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1820" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1820" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1821">
+      <c r="A1821" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1821" t="inlineStr">
+        <is>
+          <t>St. Martin vs US Virgin Islands</t>
+        </is>
+      </c>
+      <c r="C1821" t="inlineStr">
+        <is>
+          <t>St. Martin</t>
+        </is>
+      </c>
+      <c r="D1821" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1821" t="inlineStr"/>
+      <c r="F1821" t="inlineStr"/>
+      <c r="G1821" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1821" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1821" t="n">
+        <v>7</v>
+      </c>
+      <c r="J1821" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1821" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1821" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1822">
+      <c r="A1822" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1822" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira vs Internacional de Bogotá</t>
+        </is>
+      </c>
+      <c r="C1822" t="inlineStr">
+        <is>
+          <t>Internacional de Bogotá</t>
+        </is>
+      </c>
+      <c r="D1822" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1822" t="inlineStr"/>
+      <c r="F1822" t="inlineStr"/>
+      <c r="G1822" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1822" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1822" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1822" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1822" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1822" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1823">
+      <c r="A1823" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1823" t="inlineStr">
+        <is>
+          <t>Portland Hearts of Pine vs Sarasota Paradise</t>
+        </is>
+      </c>
+      <c r="C1823" t="inlineStr">
+        <is>
+          <t>Portland Hearts of Pine</t>
+        </is>
+      </c>
+      <c r="D1823" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1823" t="inlineStr"/>
+      <c r="F1823" t="inlineStr"/>
+      <c r="G1823" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="H1823" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1823" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1823" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1823" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1823" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1824">
+      <c r="A1824" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1824" t="inlineStr">
+        <is>
+          <t>St. Vincent and the Grenadines vs French Guiana</t>
+        </is>
+      </c>
+      <c r="C1824" t="inlineStr">
+        <is>
+          <t>French Guiana</t>
+        </is>
+      </c>
+      <c r="D1824" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1824" t="inlineStr"/>
+      <c r="F1824" t="inlineStr"/>
+      <c r="G1824" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1824" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1824" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1824" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1824" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1824" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1825">
+      <c r="A1825" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1825" t="inlineStr">
+        <is>
+          <t>Peñarol vs Boston River</t>
+        </is>
+      </c>
+      <c r="C1825" t="inlineStr">
+        <is>
+          <t>Peñarol</t>
+        </is>
+      </c>
+      <c r="D1825" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1825" t="inlineStr"/>
+      <c r="F1825" t="inlineStr"/>
+      <c r="G1825" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1825" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1825" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1825" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1825" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1825" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1826">
+      <c r="A1826" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1826" t="inlineStr">
+        <is>
+          <t>Sportivo Trinidense vs Cerro Porteño</t>
+        </is>
+      </c>
+      <c r="C1826" t="inlineStr">
+        <is>
+          <t>Cerro Porteño</t>
+        </is>
+      </c>
+      <c r="D1826" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1826" t="inlineStr"/>
+      <c r="F1826" t="inlineStr"/>
+      <c r="G1826" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1826" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1826" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1826" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1826" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1826" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1827">
+      <c r="A1827" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1827" t="inlineStr">
+        <is>
+          <t>Tlaxcala FC vs Cancún FC</t>
+        </is>
+      </c>
+      <c r="C1827" t="inlineStr">
+        <is>
+          <t>Tlaxcala FC</t>
+        </is>
+      </c>
+      <c r="D1827" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1827" t="inlineStr"/>
+      <c r="F1827" t="inlineStr"/>
+      <c r="G1827" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H1827" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1827" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1827" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1827" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1827" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1828">
+      <c r="A1828" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1828" t="inlineStr">
+        <is>
+          <t>Forward Madison FC vs Spokane Velocity FC</t>
+        </is>
+      </c>
+      <c r="C1828" t="inlineStr">
+        <is>
+          <t>Forward Madison FC</t>
+        </is>
+      </c>
+      <c r="D1828" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1828" t="inlineStr"/>
+      <c r="F1828" t="inlineStr"/>
+      <c r="G1828" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1828" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1828" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1828" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1828" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1828" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1829">
+      <c r="A1829" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1829" t="inlineStr">
+        <is>
+          <t>Cruz Azul vs Toluca</t>
+        </is>
+      </c>
+      <c r="C1829" t="inlineStr">
+        <is>
+          <t>Toluca</t>
+        </is>
+      </c>
+      <c r="D1829" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1829" t="inlineStr"/>
+      <c r="F1829" t="inlineStr"/>
+      <c r="G1829" t="inlineStr">
+        <is>
+          <t>3-3</t>
+        </is>
+      </c>
+      <c r="H1829" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1829" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1829" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1829" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1829" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1830">
+      <c r="A1830" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1830" t="inlineStr">
+        <is>
+          <t>Charleston Battery vs Rhode Island FC</t>
+        </is>
+      </c>
+      <c r="C1830" t="inlineStr">
+        <is>
+          <t>Charleston Battery</t>
+        </is>
+      </c>
+      <c r="D1830" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1830" t="inlineStr"/>
+      <c r="F1830" t="inlineStr"/>
+      <c r="G1830" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1830" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1830" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1830" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1830" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1830" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1831">
+      <c r="A1831" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1831" t="inlineStr">
+        <is>
+          <t>Detroit City FC vs Colorado Springs Switchbacks FC</t>
+        </is>
+      </c>
+      <c r="C1831" t="inlineStr">
+        <is>
+          <t>Detroit City FC</t>
+        </is>
+      </c>
+      <c r="D1831" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1831" t="inlineStr"/>
+      <c r="F1831" t="inlineStr"/>
+      <c r="G1831" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1831" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1831" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1831" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1831" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1831" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1832">
+      <c r="A1832" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1832" t="inlineStr">
+        <is>
+          <t>Indy Eleven vs Miami FC</t>
+        </is>
+      </c>
+      <c r="C1832" t="inlineStr">
+        <is>
+          <t>Indy Eleven</t>
+        </is>
+      </c>
+      <c r="D1832" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1832" t="inlineStr"/>
+      <c r="F1832" t="inlineStr"/>
+      <c r="G1832" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1832" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1832" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1832" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1832" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1832" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1833">
+      <c r="A1833" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1833" t="inlineStr">
+        <is>
+          <t>FC Naples vs Chattanooga Red Wolves</t>
+        </is>
+      </c>
+      <c r="C1833" t="inlineStr">
+        <is>
+          <t>FC Naples</t>
+        </is>
+      </c>
+      <c r="D1833" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1833" t="inlineStr"/>
+      <c r="F1833" t="inlineStr"/>
+      <c r="G1833" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1833" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1833" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1833" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1833" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1833" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1834">
+      <c r="A1834" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1834" t="inlineStr">
+        <is>
+          <t>Greenville Triumph vs Union Omaha</t>
+        </is>
+      </c>
+      <c r="C1834" t="inlineStr">
+        <is>
+          <t>Union Omaha</t>
+        </is>
+      </c>
+      <c r="D1834" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1834" t="inlineStr"/>
+      <c r="F1834" t="inlineStr"/>
+      <c r="G1834" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H1834" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1834" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1834" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1834" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1834" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1835">
+      <c r="A1835" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1835" t="inlineStr">
+        <is>
+          <t>Antigua and Barbuda vs Anguilla</t>
+        </is>
+      </c>
+      <c r="C1835" t="inlineStr">
+        <is>
+          <t>Antigua and Barbuda</t>
+        </is>
+      </c>
+      <c r="D1835" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1835" t="inlineStr"/>
+      <c r="F1835" t="inlineStr"/>
+      <c r="G1835" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="H1835" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1835" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1835" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1835" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1835" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1836">
+      <c r="A1836" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1836" t="inlineStr">
+        <is>
+          <t>Canada vs Chile</t>
+        </is>
+      </c>
+      <c r="C1836" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D1836" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1836" t="inlineStr"/>
+      <c r="F1836" t="inlineStr"/>
+      <c r="G1836" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1836" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1836" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1836" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1836" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1836" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1837">
+      <c r="A1837" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1837" t="inlineStr">
+        <is>
+          <t>Guadalajara vs Querétaro</t>
+        </is>
+      </c>
+      <c r="C1837" t="inlineStr">
+        <is>
+          <t>Guadalajara</t>
+        </is>
+      </c>
+      <c r="D1837" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1837" t="inlineStr"/>
+      <c r="F1837" t="inlineStr"/>
+      <c r="G1837" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1837" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1837" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1837" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1837" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1837" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1838">
+      <c r="A1838" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1838" t="inlineStr">
+        <is>
+          <t>Cúcuta Deportivo vs Llaneros FC</t>
+        </is>
+      </c>
+      <c r="C1838" t="inlineStr">
+        <is>
+          <t>Cúcuta Deportivo</t>
+        </is>
+      </c>
+      <c r="D1838" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1838" t="inlineStr"/>
+      <c r="F1838" t="inlineStr"/>
+      <c r="G1838" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1838" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1838" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1838" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1838" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1838" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1839">
+      <c r="A1839" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1839" t="inlineStr">
+        <is>
+          <t>Philadelphia Union vs Orlando City SC</t>
+        </is>
+      </c>
+      <c r="C1839" t="inlineStr">
+        <is>
+          <t>Philadelphia Union</t>
+        </is>
+      </c>
+      <c r="D1839" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1839" t="inlineStr"/>
+      <c r="F1839" t="inlineStr"/>
+      <c r="G1839" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="H1839" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1839" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1839" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1839" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1839" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1840">
+      <c r="A1840" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1840" t="inlineStr">
+        <is>
+          <t>Atlanta United FC vs New York City FC</t>
+        </is>
+      </c>
+      <c r="C1840" t="inlineStr">
+        <is>
+          <t>Atlanta United FC</t>
+        </is>
+      </c>
+      <c r="D1840" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1840" t="inlineStr"/>
+      <c r="F1840" t="inlineStr"/>
+      <c r="G1840" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1840" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1840" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1840" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1840" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1840" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1841">
+      <c r="A1841" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1841" t="inlineStr">
+        <is>
+          <t>CF Montréal vs FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="C1841" t="inlineStr">
+        <is>
+          <t>FC Cincinnati</t>
+        </is>
+      </c>
+      <c r="D1841" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1841" t="inlineStr"/>
+      <c r="F1841" t="inlineStr"/>
+      <c r="G1841" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1841" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1841" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1841" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1841" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1841" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1842">
+      <c r="A1842" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1842" t="inlineStr">
+        <is>
+          <t>Charlotte FC vs Chicago Fire FC</t>
+        </is>
+      </c>
+      <c r="C1842" t="inlineStr">
+        <is>
+          <t>Charlotte FC</t>
+        </is>
+      </c>
+      <c r="D1842" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1842" t="inlineStr"/>
+      <c r="F1842" t="inlineStr"/>
+      <c r="G1842" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1842" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1842" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1842" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1842" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1842" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1843">
+      <c r="A1843" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1843" t="inlineStr">
+        <is>
+          <t>FC Dallas vs LAFC</t>
+        </is>
+      </c>
+      <c r="C1843" t="inlineStr">
+        <is>
+          <t>FC Dallas</t>
+        </is>
+      </c>
+      <c r="D1843" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1843" t="inlineStr"/>
+      <c r="F1843" t="inlineStr"/>
+      <c r="G1843" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1843" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1843" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1843" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1843" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1843" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1844">
+      <c r="A1844" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1844" t="inlineStr">
+        <is>
+          <t>Seattle Sounders FC vs Minnesota United FC</t>
+        </is>
+      </c>
+      <c r="C1844" t="inlineStr">
+        <is>
+          <t>Seattle Sounders FC</t>
+        </is>
+      </c>
+      <c r="D1844" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1844" t="inlineStr"/>
+      <c r="F1844" t="inlineStr"/>
+      <c r="G1844" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1844" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1844" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1844" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1844" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1844" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1845">
+      <c r="A1845" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1845" t="inlineStr">
+        <is>
+          <t>Nashville SC vs Toronto FC</t>
+        </is>
+      </c>
+      <c r="C1845" t="inlineStr">
+        <is>
+          <t>Nashville SC</t>
+        </is>
+      </c>
+      <c r="D1845" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1845" t="inlineStr"/>
+      <c r="F1845" t="inlineStr"/>
+      <c r="G1845" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1845" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1845" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1845" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1845" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1845" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1846">
+      <c r="A1846" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1846" t="inlineStr">
+        <is>
+          <t>Houston Dynamo FC vs Sporting Kansas City</t>
+        </is>
+      </c>
+      <c r="C1846" t="inlineStr">
+        <is>
+          <t>Houston Dynamo FC</t>
+        </is>
+      </c>
+      <c r="D1846" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1846" t="inlineStr"/>
+      <c r="F1846" t="inlineStr"/>
+      <c r="G1846" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1846" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1846" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1846" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1846" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1846" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1847">
+      <c r="A1847" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1847" t="inlineStr">
+        <is>
+          <t>San Antonio FC vs Tampa Bay Rowdies</t>
+        </is>
+      </c>
+      <c r="C1847" t="inlineStr">
+        <is>
+          <t>Tampa Bay Rowdies</t>
+        </is>
+      </c>
+      <c r="D1847" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1847" t="inlineStr"/>
+      <c r="F1847" t="inlineStr"/>
+      <c r="G1847" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1847" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1847" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1847" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1847" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1847" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1848">
+      <c r="A1848" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1848" t="inlineStr">
+        <is>
+          <t>Corpus Christi FC vs Athletic Club Boise</t>
+        </is>
+      </c>
+      <c r="C1848" t="inlineStr">
+        <is>
+          <t>Athletic Club Boise</t>
+        </is>
+      </c>
+      <c r="D1848" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1848" t="inlineStr"/>
+      <c r="F1848" t="inlineStr"/>
+      <c r="G1848" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1848" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1848" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1848" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1848" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1848" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1849">
+      <c r="A1849" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1849" t="inlineStr">
+        <is>
+          <t>New Mexico United vs Sacramento Republic FC</t>
+        </is>
+      </c>
+      <c r="C1849" t="inlineStr">
+        <is>
+          <t>Sacramento Republic FC</t>
+        </is>
+      </c>
+      <c r="D1849" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1849" t="inlineStr"/>
+      <c r="F1849" t="inlineStr"/>
+      <c r="G1849" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H1849" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1849" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1849" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1849" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1849" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1850">
+      <c r="A1850" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1850" t="inlineStr">
+        <is>
+          <t>Atlético Junior vs Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="C1850" t="inlineStr">
+        <is>
+          <t>Atlético Junior</t>
+        </is>
+      </c>
+      <c r="D1850" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1850" t="inlineStr"/>
+      <c r="F1850" t="inlineStr"/>
+      <c r="G1850" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1850" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1850" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1850" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1850" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1850" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1851">
+      <c r="A1851" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1851" t="inlineStr">
+        <is>
+          <t>Monterey Bay vs Lexington</t>
+        </is>
+      </c>
+      <c r="C1851" t="inlineStr">
+        <is>
+          <t>Lexington</t>
+        </is>
+      </c>
+      <c r="D1851" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1851" t="inlineStr"/>
+      <c r="F1851" t="inlineStr"/>
+      <c r="G1851" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H1851" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1851" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1851" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1851" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1851" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1852">
+      <c r="A1852" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1852" t="inlineStr">
+        <is>
+          <t>Oakland Roots vs Phoenix Rising FC</t>
+        </is>
+      </c>
+      <c r="C1852" t="inlineStr">
+        <is>
+          <t>Oakland Roots</t>
+        </is>
+      </c>
+      <c r="D1852" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1852" t="inlineStr"/>
+      <c r="F1852" t="inlineStr"/>
+      <c r="G1852" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1852" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1852" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1852" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1852" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1852" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1853">
+      <c r="A1853" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1853" t="inlineStr">
+        <is>
+          <t>Orange County SC vs Pittsburgh Riverhounds</t>
+        </is>
+      </c>
+      <c r="C1853" t="inlineStr">
+        <is>
+          <t>Pittsburgh Riverhounds</t>
+        </is>
+      </c>
+      <c r="D1853" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1853" t="inlineStr"/>
+      <c r="F1853" t="inlineStr"/>
+      <c r="G1853" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1853" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1853" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1853" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1853" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1853" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1854">
+      <c r="A1854" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1854" t="inlineStr">
+        <is>
+          <t>Sint Maarten vs Belize</t>
+        </is>
+      </c>
+      <c r="C1854" t="inlineStr">
+        <is>
+          <t>Belize</t>
+        </is>
+      </c>
+      <c r="D1854" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1854" t="inlineStr"/>
+      <c r="F1854" t="inlineStr"/>
+      <c r="G1854" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1854" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1854" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1854" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1854" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1854" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1855">
+      <c r="A1855" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1855" t="inlineStr">
+        <is>
+          <t>LA Galaxy vs Colorado Rapids</t>
+        </is>
+      </c>
+      <c r="C1855" t="inlineStr">
+        <is>
+          <t>LA Galaxy</t>
+        </is>
+      </c>
+      <c r="D1855" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1855" t="inlineStr"/>
+      <c r="F1855" t="inlineStr"/>
+      <c r="G1855" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1855" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1855" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1855" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1855" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1855" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1856">
+      <c r="A1856" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1856" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps vs D.C. United</t>
+        </is>
+      </c>
+      <c r="C1856" t="inlineStr">
+        <is>
+          <t>Vancouver Whitecaps</t>
+        </is>
+      </c>
+      <c r="D1856" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1856" t="inlineStr"/>
+      <c r="F1856" t="inlineStr"/>
+      <c r="G1856" t="inlineStr">
+        <is>
+          <t>3-3</t>
+        </is>
+      </c>
+      <c r="H1856" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1856" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1856" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1856" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1856" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1857" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes vs Portland Timbers</t>
+        </is>
+      </c>
+      <c r="C1857" t="inlineStr">
+        <is>
+          <t>San Jose Earthquakes</t>
+        </is>
+      </c>
+      <c r="D1857" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1857" t="inlineStr"/>
+      <c r="F1857" t="inlineStr"/>
+      <c r="G1857" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1857" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1857" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1857" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1857" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1857" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1858">
+      <c r="A1858" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1858" t="inlineStr">
+        <is>
+          <t>Santos vs Pachuca</t>
+        </is>
+      </c>
+      <c r="C1858" t="inlineStr">
+        <is>
+          <t>Pachuca</t>
+        </is>
+      </c>
+      <c r="D1858" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1858" t="inlineStr"/>
+      <c r="F1858" t="inlineStr"/>
+      <c r="G1858" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1858" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1858" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1858" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1858" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1858" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1859">
+      <c r="A1859" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B1859" t="inlineStr">
+        <is>
+          <t>Tigres UANL vs Puebla</t>
+        </is>
+      </c>
+      <c r="C1859" t="inlineStr">
+        <is>
+          <t>Tigres UANL</t>
+        </is>
+      </c>
+      <c r="D1859" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1859" t="inlineStr"/>
+      <c r="F1859" t="inlineStr"/>
+      <c r="G1859" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1859" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1859" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1859" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1859" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1859" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -83403,7 +86113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84265,6 +86975,25 @@
       </c>
       <c r="E46" t="n">
         <v>61</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>59</v>
+      </c>
+      <c r="C47" t="n">
+        <v>41</v>
+      </c>
+      <c r="D47" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="E47" t="n">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -84278,7 +87007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E254"/>
+  <dimension ref="A1:E262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89621,6 +92350,174 @@
         <v>0</v>
       </c>
     </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C255" t="n">
+        <v>7</v>
+      </c>
+      <c r="D255" t="n">
+        <v>1</v>
+      </c>
+      <c r="E255" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C256" t="n">
+        <v>8</v>
+      </c>
+      <c r="D256" t="n">
+        <v>0</v>
+      </c>
+      <c r="E256" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C257" t="n">
+        <v>3</v>
+      </c>
+      <c r="D257" t="n">
+        <v>0</v>
+      </c>
+      <c r="E257" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C258" t="n">
+        <v>4</v>
+      </c>
+      <c r="D258" t="n">
+        <v>0</v>
+      </c>
+      <c r="E258" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C259" t="n">
+        <v>6</v>
+      </c>
+      <c r="D259" t="n">
+        <v>3</v>
+      </c>
+      <c r="E259" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C260" t="n">
+        <v>2</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0</v>
+      </c>
+      <c r="E260" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>siguen_empatados_55</t>
+        </is>
+      </c>
+      <c r="C261" t="n">
+        <v>1</v>
+      </c>
+      <c r="D261" t="n">
+        <v>0</v>
+      </c>
+      <c r="E261" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C262" t="n">
+        <v>9</v>
+      </c>
+      <c r="D262" t="n">
+        <v>0</v>
+      </c>
+      <c r="E262" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1859"/>
+  <dimension ref="A1:L1911"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83291,8 +83291,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1801" t="inlineStr"/>
-      <c r="F1801" t="inlineStr"/>
       <c r="G1801" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -83339,8 +83337,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1802" t="inlineStr"/>
-      <c r="F1802" t="inlineStr"/>
       <c r="G1802" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -83387,8 +83383,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1803" t="inlineStr"/>
-      <c r="F1803" t="inlineStr"/>
       <c r="G1803" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -83435,8 +83429,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1804" t="inlineStr"/>
-      <c r="F1804" t="inlineStr"/>
       <c r="G1804" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -83483,8 +83475,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1805" t="inlineStr"/>
-      <c r="F1805" t="inlineStr"/>
       <c r="G1805" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -83531,8 +83521,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1806" t="inlineStr"/>
-      <c r="F1806" t="inlineStr"/>
       <c r="G1806" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -83579,8 +83567,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1807" t="inlineStr"/>
-      <c r="F1807" t="inlineStr"/>
       <c r="G1807" t="inlineStr">
         <is>
           <t>0-7</t>
@@ -83627,8 +83613,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1808" t="inlineStr"/>
-      <c r="F1808" t="inlineStr"/>
       <c r="G1808" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -83675,8 +83659,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1809" t="inlineStr"/>
-      <c r="F1809" t="inlineStr"/>
       <c r="G1809" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -83723,8 +83705,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1810" t="inlineStr"/>
-      <c r="F1810" t="inlineStr"/>
       <c r="G1810" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -83771,8 +83751,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1811" t="inlineStr"/>
-      <c r="F1811" t="inlineStr"/>
       <c r="G1811" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -83819,8 +83797,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1812" t="inlineStr"/>
-      <c r="F1812" t="inlineStr"/>
       <c r="G1812" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -83867,8 +83843,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1813" t="inlineStr"/>
-      <c r="F1813" t="inlineStr"/>
       <c r="G1813" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -83915,8 +83889,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1814" t="inlineStr"/>
-      <c r="F1814" t="inlineStr"/>
       <c r="G1814" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -83963,8 +83935,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1815" t="inlineStr"/>
-      <c r="F1815" t="inlineStr"/>
       <c r="G1815" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -84011,8 +83981,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1816" t="inlineStr"/>
-      <c r="F1816" t="inlineStr"/>
       <c r="G1816" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -84059,8 +84027,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1817" t="inlineStr"/>
-      <c r="F1817" t="inlineStr"/>
       <c r="G1817" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -84107,8 +84073,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1818" t="inlineStr"/>
-      <c r="F1818" t="inlineStr"/>
       <c r="G1818" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -84155,8 +84119,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1819" t="inlineStr"/>
-      <c r="F1819" t="inlineStr"/>
       <c r="G1819" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -84203,8 +84165,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1820" t="inlineStr"/>
-      <c r="F1820" t="inlineStr"/>
       <c r="G1820" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -84251,8 +84211,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1821" t="inlineStr"/>
-      <c r="F1821" t="inlineStr"/>
       <c r="G1821" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -84299,8 +84257,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1822" t="inlineStr"/>
-      <c r="F1822" t="inlineStr"/>
       <c r="G1822" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -84347,8 +84303,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1823" t="inlineStr"/>
-      <c r="F1823" t="inlineStr"/>
       <c r="G1823" t="inlineStr">
         <is>
           <t>1-4</t>
@@ -84395,8 +84349,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1824" t="inlineStr"/>
-      <c r="F1824" t="inlineStr"/>
       <c r="G1824" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -84443,8 +84395,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1825" t="inlineStr"/>
-      <c r="F1825" t="inlineStr"/>
       <c r="G1825" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -84491,8 +84441,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1826" t="inlineStr"/>
-      <c r="F1826" t="inlineStr"/>
       <c r="G1826" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -84539,8 +84487,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1827" t="inlineStr"/>
-      <c r="F1827" t="inlineStr"/>
       <c r="G1827" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -84587,8 +84533,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1828" t="inlineStr"/>
-      <c r="F1828" t="inlineStr"/>
       <c r="G1828" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -84635,8 +84579,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1829" t="inlineStr"/>
-      <c r="F1829" t="inlineStr"/>
       <c r="G1829" t="inlineStr">
         <is>
           <t>3-3</t>
@@ -84683,8 +84625,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1830" t="inlineStr"/>
-      <c r="F1830" t="inlineStr"/>
       <c r="G1830" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -84731,8 +84671,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1831" t="inlineStr"/>
-      <c r="F1831" t="inlineStr"/>
       <c r="G1831" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -84779,8 +84717,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1832" t="inlineStr"/>
-      <c r="F1832" t="inlineStr"/>
       <c r="G1832" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -84827,8 +84763,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1833" t="inlineStr"/>
-      <c r="F1833" t="inlineStr"/>
       <c r="G1833" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -84875,8 +84809,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1834" t="inlineStr"/>
-      <c r="F1834" t="inlineStr"/>
       <c r="G1834" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -84923,8 +84855,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1835" t="inlineStr"/>
-      <c r="F1835" t="inlineStr"/>
       <c r="G1835" t="inlineStr">
         <is>
           <t>5-0</t>
@@ -84971,8 +84901,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1836" t="inlineStr"/>
-      <c r="F1836" t="inlineStr"/>
       <c r="G1836" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -85019,8 +84947,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1837" t="inlineStr"/>
-      <c r="F1837" t="inlineStr"/>
       <c r="G1837" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -85067,8 +84993,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1838" t="inlineStr"/>
-      <c r="F1838" t="inlineStr"/>
       <c r="G1838" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -85115,8 +85039,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1839" t="inlineStr"/>
-      <c r="F1839" t="inlineStr"/>
       <c r="G1839" t="inlineStr">
         <is>
           <t>4-2</t>
@@ -85163,8 +85085,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1840" t="inlineStr"/>
-      <c r="F1840" t="inlineStr"/>
       <c r="G1840" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -85211,8 +85131,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1841" t="inlineStr"/>
-      <c r="F1841" t="inlineStr"/>
       <c r="G1841" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -85259,8 +85177,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1842" t="inlineStr"/>
-      <c r="F1842" t="inlineStr"/>
       <c r="G1842" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -85307,8 +85223,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1843" t="inlineStr"/>
-      <c r="F1843" t="inlineStr"/>
       <c r="G1843" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -85355,8 +85269,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1844" t="inlineStr"/>
-      <c r="F1844" t="inlineStr"/>
       <c r="G1844" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -85403,8 +85315,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1845" t="inlineStr"/>
-      <c r="F1845" t="inlineStr"/>
       <c r="G1845" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -85451,8 +85361,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1846" t="inlineStr"/>
-      <c r="F1846" t="inlineStr"/>
       <c r="G1846" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -85499,8 +85407,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1847" t="inlineStr"/>
-      <c r="F1847" t="inlineStr"/>
       <c r="G1847" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -85547,8 +85453,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1848" t="inlineStr"/>
-      <c r="F1848" t="inlineStr"/>
       <c r="G1848" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -85595,8 +85499,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1849" t="inlineStr"/>
-      <c r="F1849" t="inlineStr"/>
       <c r="G1849" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -85643,8 +85545,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1850" t="inlineStr"/>
-      <c r="F1850" t="inlineStr"/>
       <c r="G1850" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -85691,8 +85591,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1851" t="inlineStr"/>
-      <c r="F1851" t="inlineStr"/>
       <c r="G1851" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -85739,8 +85637,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1852" t="inlineStr"/>
-      <c r="F1852" t="inlineStr"/>
       <c r="G1852" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -85787,8 +85683,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1853" t="inlineStr"/>
-      <c r="F1853" t="inlineStr"/>
       <c r="G1853" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -85835,8 +85729,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1854" t="inlineStr"/>
-      <c r="F1854" t="inlineStr"/>
       <c r="G1854" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -85883,8 +85775,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1855" t="inlineStr"/>
-      <c r="F1855" t="inlineStr"/>
       <c r="G1855" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -85931,8 +85821,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1856" t="inlineStr"/>
-      <c r="F1856" t="inlineStr"/>
       <c r="G1856" t="inlineStr">
         <is>
           <t>3-3</t>
@@ -85979,8 +85867,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1857" t="inlineStr"/>
-      <c r="F1857" t="inlineStr"/>
       <c r="G1857" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -86027,8 +85913,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1858" t="inlineStr"/>
-      <c r="F1858" t="inlineStr"/>
       <c r="G1858" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -86075,8 +85959,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1859" t="inlineStr"/>
-      <c r="F1859" t="inlineStr"/>
       <c r="G1859" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -86097,6 +85979,2502 @@
         <v>0</v>
       </c>
       <c r="L1859" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1860">
+      <c r="A1860" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1860" t="inlineStr">
+        <is>
+          <t>Vanuatu vs New Caledonia</t>
+        </is>
+      </c>
+      <c r="C1860" t="inlineStr">
+        <is>
+          <t>New Caledonia</t>
+        </is>
+      </c>
+      <c r="D1860" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1860" t="inlineStr"/>
+      <c r="F1860" t="inlineStr"/>
+      <c r="G1860" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H1860" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1860" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1860" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1860" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1860" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1861">
+      <c r="A1861" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1861" t="inlineStr">
+        <is>
+          <t>Fiji vs Papua New Guinea</t>
+        </is>
+      </c>
+      <c r="C1861" t="inlineStr">
+        <is>
+          <t>Fiji</t>
+        </is>
+      </c>
+      <c r="D1861" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1861" t="inlineStr"/>
+      <c r="F1861" t="inlineStr"/>
+      <c r="G1861" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1861" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1861" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1861" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1861" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1861" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1862">
+      <c r="A1862" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1862" t="inlineStr">
+        <is>
+          <t>China vs New Zealand</t>
+        </is>
+      </c>
+      <c r="C1862" t="inlineStr">
+        <is>
+          <t>New Zealand</t>
+        </is>
+      </c>
+      <c r="D1862" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1862" t="inlineStr"/>
+      <c r="F1862" t="inlineStr"/>
+      <c r="G1862" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H1862" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1862" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1862" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1862" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1862" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1863">
+      <c r="A1863" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1863" t="inlineStr">
+        <is>
+          <t>Real Valladolid vs Córdoba</t>
+        </is>
+      </c>
+      <c r="C1863" t="inlineStr">
+        <is>
+          <t>Real Valladolid</t>
+        </is>
+      </c>
+      <c r="D1863" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1863" t="inlineStr"/>
+      <c r="F1863" t="inlineStr"/>
+      <c r="G1863" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1863" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1863" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1863" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1863" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1863" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1864">
+      <c r="A1864" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1864" t="inlineStr">
+        <is>
+          <t>Shanghai Shenhua vs Zenit St Petersburg</t>
+        </is>
+      </c>
+      <c r="C1864" t="inlineStr">
+        <is>
+          <t>Zenit St Petersburg</t>
+        </is>
+      </c>
+      <c r="D1864" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1864" t="inlineStr"/>
+      <c r="F1864" t="inlineStr"/>
+      <c r="G1864" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1864" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1864" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1864" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1864" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1864" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1865">
+      <c r="A1865" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1865" t="inlineStr">
+        <is>
+          <t>De Graafschap vs FC Den Bosch</t>
+        </is>
+      </c>
+      <c r="C1865" t="inlineStr">
+        <is>
+          <t>De Graafschap</t>
+        </is>
+      </c>
+      <c r="D1865" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1865" t="inlineStr"/>
+      <c r="F1865" t="inlineStr"/>
+      <c r="G1865" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1865" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1865" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1865" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1865" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1865" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1866">
+      <c r="A1866" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1866" t="inlineStr">
+        <is>
+          <t>Lithuania vs Azerbaijan</t>
+        </is>
+      </c>
+      <c r="C1866" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="D1866" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1866" t="inlineStr"/>
+      <c r="F1866" t="inlineStr"/>
+      <c r="G1866" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1866" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1866" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1866" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1866" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1866" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1867">
+      <c r="A1867" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1867" t="inlineStr">
+        <is>
+          <t>Central Español Fútbol Club vs Liverpool</t>
+        </is>
+      </c>
+      <c r="C1867" t="inlineStr">
+        <is>
+          <t>Liverpool</t>
+        </is>
+      </c>
+      <c r="D1867" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1867" t="inlineStr"/>
+      <c r="F1867" t="inlineStr"/>
+      <c r="G1867" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1867" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1867" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1867" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1867" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1867" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1868">
+      <c r="A1868" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1868" t="inlineStr">
+        <is>
+          <t>Criciúma vs Avaí</t>
+        </is>
+      </c>
+      <c r="C1868" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="D1868" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1868" t="inlineStr"/>
+      <c r="F1868" t="inlineStr"/>
+      <c r="G1868" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1868" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1868" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1868" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1868" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1868" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1869">
+      <c r="A1869" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1869" t="inlineStr">
+        <is>
+          <t>Camacha vs Florgrade</t>
+        </is>
+      </c>
+      <c r="C1869" t="inlineStr">
+        <is>
+          <t>Camacha</t>
+        </is>
+      </c>
+      <c r="D1869" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1869" t="inlineStr"/>
+      <c r="F1869" t="inlineStr"/>
+      <c r="G1869" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1869" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1869" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1869" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1869" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1869" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1870">
+      <c r="A1870" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1870" t="inlineStr">
+        <is>
+          <t>Mallorca vs Almería</t>
+        </is>
+      </c>
+      <c r="C1870" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="D1870" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1870" t="inlineStr"/>
+      <c r="F1870" t="inlineStr"/>
+      <c r="G1870" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1870" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1870" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1870" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1870" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1870" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1871">
+      <c r="A1871" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1871" t="inlineStr">
+        <is>
+          <t>Antofagasta vs Deportes Iquique</t>
+        </is>
+      </c>
+      <c r="C1871" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="D1871" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1871" t="inlineStr"/>
+      <c r="F1871" t="inlineStr"/>
+      <c r="G1871" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H1871" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1871" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1871" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1871" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1871" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1872">
+      <c r="A1872" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1872" t="inlineStr">
+        <is>
+          <t>Serbia vs Netherlands</t>
+        </is>
+      </c>
+      <c r="C1872" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D1872" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1872" t="inlineStr"/>
+      <c r="F1872" t="inlineStr"/>
+      <c r="G1872" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1872" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1872" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1872" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1872" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1872" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1873">
+      <c r="A1873" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1873" t="inlineStr">
+        <is>
+          <t>Denmark vs Wales</t>
+        </is>
+      </c>
+      <c r="C1873" t="inlineStr">
+        <is>
+          <t>Denmark</t>
+        </is>
+      </c>
+      <c r="D1873" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1873" t="inlineStr"/>
+      <c r="F1873" t="inlineStr"/>
+      <c r="G1873" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1873" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1873" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1873" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1873" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1873" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1874">
+      <c r="A1874" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1874" t="inlineStr">
+        <is>
+          <t>Austria vs Kosovo</t>
+        </is>
+      </c>
+      <c r="C1874" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="D1874" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1874" t="inlineStr"/>
+      <c r="F1874" t="inlineStr"/>
+      <c r="G1874" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1874" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1874" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1874" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1874" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1874" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1875">
+      <c r="A1875" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1875" t="inlineStr">
+        <is>
+          <t>Gibraltar vs Andorra</t>
+        </is>
+      </c>
+      <c r="C1875" t="inlineStr">
+        <is>
+          <t>Andorra</t>
+        </is>
+      </c>
+      <c r="D1875" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1875" t="inlineStr"/>
+      <c r="F1875" t="inlineStr"/>
+      <c r="G1875" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1875" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1875" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1875" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1875" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1875" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1876">
+      <c r="A1876" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1876" t="inlineStr">
+        <is>
+          <t>Burgos vs Eldense</t>
+        </is>
+      </c>
+      <c r="C1876" t="inlineStr">
+        <is>
+          <t>Burgos</t>
+        </is>
+      </c>
+      <c r="D1876" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1876" t="inlineStr"/>
+      <c r="F1876" t="inlineStr"/>
+      <c r="G1876" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1876" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1876" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1876" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1876" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1876" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1877">
+      <c r="A1877" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1877" t="inlineStr">
+        <is>
+          <t>Eibar vs Las Palmas</t>
+        </is>
+      </c>
+      <c r="C1877" t="inlineStr">
+        <is>
+          <t>Eibar</t>
+        </is>
+      </c>
+      <c r="D1877" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1877" t="inlineStr"/>
+      <c r="F1877" t="inlineStr"/>
+      <c r="G1877" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1877" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1877" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1877" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1877" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1877" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1878">
+      <c r="A1878" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1878" t="inlineStr">
+        <is>
+          <t>Malta vs Liechtenstein</t>
+        </is>
+      </c>
+      <c r="C1878" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="D1878" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1878" t="inlineStr"/>
+      <c r="F1878" t="inlineStr"/>
+      <c r="G1878" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1878" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1878" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1878" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1878" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1878" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1879">
+      <c r="A1879" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1879" t="inlineStr">
+        <is>
+          <t>Jordan vs Syria</t>
+        </is>
+      </c>
+      <c r="C1879" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="D1879" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1879" t="inlineStr"/>
+      <c r="F1879" t="inlineStr"/>
+      <c r="G1879" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1879" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1879" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1879" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1879" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1879" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1880">
+      <c r="A1880" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1880" t="inlineStr">
+        <is>
+          <t>Pumas UNAM vs Atlético de San Luis</t>
+        </is>
+      </c>
+      <c r="C1880" t="inlineStr">
+        <is>
+          <t>Pumas UNAM</t>
+        </is>
+      </c>
+      <c r="D1880" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1880" t="inlineStr"/>
+      <c r="F1880" t="inlineStr"/>
+      <c r="G1880" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H1880" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1880" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1880" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1880" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1880" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1881">
+      <c r="A1881" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1881" t="inlineStr">
+        <is>
+          <t>Juventud vs Cerro</t>
+        </is>
+      </c>
+      <c r="C1881" t="inlineStr">
+        <is>
+          <t>Juventud</t>
+        </is>
+      </c>
+      <c r="D1881" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1881" t="inlineStr"/>
+      <c r="F1881" t="inlineStr"/>
+      <c r="G1881" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1881" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1881" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1881" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1881" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1881" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1882">
+      <c r="A1882" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1882" t="inlineStr">
+        <is>
+          <t>Argentino de Quilmes vs Comunicaciones</t>
+        </is>
+      </c>
+      <c r="C1882" t="inlineStr">
+        <is>
+          <t>Comunicaciones</t>
+        </is>
+      </c>
+      <c r="D1882" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1882" t="inlineStr"/>
+      <c r="F1882" t="inlineStr"/>
+      <c r="G1882" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1882" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1882" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1882" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1882" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1882" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1883">
+      <c r="A1883" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1883" t="inlineStr">
+        <is>
+          <t>Villa Dálmine vs UAI Urquiza</t>
+        </is>
+      </c>
+      <c r="C1883" t="inlineStr">
+        <is>
+          <t>Villa Dálmine</t>
+        </is>
+      </c>
+      <c r="D1883" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1883" t="inlineStr"/>
+      <c r="F1883" t="inlineStr"/>
+      <c r="G1883" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1883" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1883" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1883" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1883" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1883" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1884">
+      <c r="A1884" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1884" t="inlineStr">
+        <is>
+          <t>Deportes Concepcion vs Curicó Unido</t>
+        </is>
+      </c>
+      <c r="C1884" t="inlineStr">
+        <is>
+          <t>Deportes Concepcion</t>
+        </is>
+      </c>
+      <c r="D1884" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1884" t="inlineStr"/>
+      <c r="F1884" t="inlineStr"/>
+      <c r="G1884" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1884" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1884" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1884" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1884" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1884" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1885">
+      <c r="A1885" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1885" t="inlineStr">
+        <is>
+          <t>Almagro vs Nueva Chicago</t>
+        </is>
+      </c>
+      <c r="C1885" t="inlineStr">
+        <is>
+          <t>Almagro</t>
+        </is>
+      </c>
+      <c r="D1885" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1885" t="inlineStr"/>
+      <c r="F1885" t="inlineStr"/>
+      <c r="G1885" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1885" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1885" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1885" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1885" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1885" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1886">
+      <c r="A1886" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1886" t="inlineStr">
+        <is>
+          <t>Atlanta vs Agropecuario</t>
+        </is>
+      </c>
+      <c r="C1886" t="inlineStr">
+        <is>
+          <t>Atlanta</t>
+        </is>
+      </c>
+      <c r="D1886" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1886" t="inlineStr"/>
+      <c r="F1886" t="inlineStr"/>
+      <c r="G1886" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1886" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1886" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1886" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1886" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1886" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1887">
+      <c r="A1887" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1887" t="inlineStr">
+        <is>
+          <t>Germany vs Greece</t>
+        </is>
+      </c>
+      <c r="C1887" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D1887" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1887" t="inlineStr"/>
+      <c r="F1887" t="inlineStr"/>
+      <c r="G1887" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1887" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1887" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1887" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1887" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1887" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1888">
+      <c r="A1888" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1888" t="inlineStr">
+        <is>
+          <t>Israel vs Republic of Ireland</t>
+        </is>
+      </c>
+      <c r="C1888" t="inlineStr">
+        <is>
+          <t>Republic of Ireland</t>
+        </is>
+      </c>
+      <c r="D1888" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1888" t="inlineStr"/>
+      <c r="F1888" t="inlineStr"/>
+      <c r="G1888" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H1888" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1888" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1888" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1888" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1888" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1889">
+      <c r="A1889" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1889" t="inlineStr">
+        <is>
+          <t>Mitre (Santiago del Estero) vs San Telmo</t>
+        </is>
+      </c>
+      <c r="C1889" t="inlineStr">
+        <is>
+          <t>Mitre (Santiago del Estero)</t>
+        </is>
+      </c>
+      <c r="D1889" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1889" t="inlineStr"/>
+      <c r="F1889" t="inlineStr"/>
+      <c r="G1889" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1889" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1889" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1889" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1889" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1889" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1890">
+      <c r="A1890" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1890" t="inlineStr">
+        <is>
+          <t>CRB vs Cuiabá</t>
+        </is>
+      </c>
+      <c r="C1890" t="inlineStr">
+        <is>
+          <t>CRB</t>
+        </is>
+      </c>
+      <c r="D1890" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1890" t="inlineStr"/>
+      <c r="F1890" t="inlineStr"/>
+      <c r="G1890" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1890" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1890" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1890" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1890" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1890" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1891">
+      <c r="A1891" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1891" t="inlineStr">
+        <is>
+          <t>Cobán Imperial vs Aurora FC</t>
+        </is>
+      </c>
+      <c r="C1891" t="inlineStr">
+        <is>
+          <t>Cobán Imperial</t>
+        </is>
+      </c>
+      <c r="D1891" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1891" t="inlineStr"/>
+      <c r="F1891" t="inlineStr"/>
+      <c r="G1891" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H1891" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1891" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1891" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1891" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1891" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1892">
+      <c r="A1892" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1892" t="inlineStr">
+        <is>
+          <t>Real Oviedo vs Sporting Gijón</t>
+        </is>
+      </c>
+      <c r="C1892" t="inlineStr">
+        <is>
+          <t>Real Oviedo</t>
+        </is>
+      </c>
+      <c r="D1892" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1892" t="inlineStr"/>
+      <c r="F1892" t="inlineStr"/>
+      <c r="G1892" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1892" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1892" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1892" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1892" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1892" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1893">
+      <c r="A1893" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1893" t="inlineStr">
+        <is>
+          <t>Guyana vs Cayman Islands</t>
+        </is>
+      </c>
+      <c r="C1893" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="D1893" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1893" t="inlineStr"/>
+      <c r="F1893" t="inlineStr"/>
+      <c r="G1893" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1893" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1893" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1893" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1893" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1893" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1894">
+      <c r="A1894" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1894" t="inlineStr">
+        <is>
+          <t>Deportivo Maipú vs Temperley</t>
+        </is>
+      </c>
+      <c r="C1894" t="inlineStr">
+        <is>
+          <t>Deportivo Maipú</t>
+        </is>
+      </c>
+      <c r="D1894" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1894" t="inlineStr"/>
+      <c r="F1894" t="inlineStr"/>
+      <c r="G1894" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1894" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1894" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1894" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1894" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1894" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1895">
+      <c r="A1895" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1895" t="inlineStr">
+        <is>
+          <t>Midland vs Tristán Suárez</t>
+        </is>
+      </c>
+      <c r="C1895" t="inlineStr">
+        <is>
+          <t>Midland</t>
+        </is>
+      </c>
+      <c r="D1895" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1895" t="inlineStr"/>
+      <c r="F1895" t="inlineStr"/>
+      <c r="G1895" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1895" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1895" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1895" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1895" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1895" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1896">
+      <c r="A1896" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1896" t="inlineStr">
+        <is>
+          <t>Racing Club vs Boca Juniors</t>
+        </is>
+      </c>
+      <c r="C1896" t="inlineStr">
+        <is>
+          <t>Boca Juniors</t>
+        </is>
+      </c>
+      <c r="D1896" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1896" t="inlineStr"/>
+      <c r="F1896" t="inlineStr"/>
+      <c r="G1896" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H1896" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1896" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1896" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1896" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1896" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1897">
+      <c r="A1897" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1897" t="inlineStr">
+        <is>
+          <t>Bolivia vs Paraguay</t>
+        </is>
+      </c>
+      <c r="C1897" t="inlineStr">
+        <is>
+          <t>Paraguay</t>
+        </is>
+      </c>
+      <c r="D1897" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1897" t="inlineStr"/>
+      <c r="F1897" t="inlineStr"/>
+      <c r="G1897" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1897" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1897" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1897" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1897" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1897" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1898">
+      <c r="A1898" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1898" t="inlineStr">
+        <is>
+          <t>Defensor Sporting vs Danubio</t>
+        </is>
+      </c>
+      <c r="C1898" t="inlineStr">
+        <is>
+          <t>Defensor Sporting</t>
+        </is>
+      </c>
+      <c r="D1898" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1898" t="inlineStr"/>
+      <c r="F1898" t="inlineStr"/>
+      <c r="G1898" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1898" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1898" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1898" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1898" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1898" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1899">
+      <c r="A1899" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1899" t="inlineStr">
+        <is>
+          <t>Gimnasia y Tiro (Salta) vs Atletico Rafaela</t>
+        </is>
+      </c>
+      <c r="C1899" t="inlineStr">
+        <is>
+          <t>Gimnasia y Tiro (Salta)</t>
+        </is>
+      </c>
+      <c r="D1899" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1899" t="inlineStr"/>
+      <c r="F1899" t="inlineStr"/>
+      <c r="G1899" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1899" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1899" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1899" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1899" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1899" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1900">
+      <c r="A1900" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1900" t="inlineStr">
+        <is>
+          <t>Jaguares de Córdoba vs Alianza FC</t>
+        </is>
+      </c>
+      <c r="C1900" t="inlineStr">
+        <is>
+          <t>Jaguares de Córdoba</t>
+        </is>
+      </c>
+      <c r="D1900" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1900" t="inlineStr"/>
+      <c r="F1900" t="inlineStr"/>
+      <c r="G1900" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1900" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1900" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1900" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1900" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1900" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1901">
+      <c r="A1901" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1901" t="inlineStr">
+        <is>
+          <t>Deportivo Mixco vs Antigua GFC</t>
+        </is>
+      </c>
+      <c r="C1901" t="inlineStr">
+        <is>
+          <t>Deportivo Mixco</t>
+        </is>
+      </c>
+      <c r="D1901" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1901" t="inlineStr"/>
+      <c r="F1901" t="inlineStr"/>
+      <c r="G1901" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1901" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1901" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1901" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1901" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1901" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1902">
+      <c r="A1902" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1902" t="inlineStr">
+        <is>
+          <t>Bolívar vs Blooming</t>
+        </is>
+      </c>
+      <c r="C1902" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="D1902" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1902" t="inlineStr"/>
+      <c r="F1902" t="inlineStr"/>
+      <c r="G1902" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1902" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1902" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1902" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1902" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1902" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1903">
+      <c r="A1903" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1903" t="inlineStr">
+        <is>
+          <t>Fortaleza vs Athletic</t>
+        </is>
+      </c>
+      <c r="C1903" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="D1903" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1903" t="inlineStr"/>
+      <c r="F1903" t="inlineStr"/>
+      <c r="G1903" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1903" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1903" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1903" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1903" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1903" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1904">
+      <c r="A1904" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1904" t="inlineStr">
+        <is>
+          <t>Columbus Crew vs Inter Miami CF</t>
+        </is>
+      </c>
+      <c r="C1904" t="inlineStr">
+        <is>
+          <t>Inter Miami CF</t>
+        </is>
+      </c>
+      <c r="D1904" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1904" t="inlineStr"/>
+      <c r="F1904" t="inlineStr"/>
+      <c r="G1904" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1904" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1904" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1904" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1904" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1904" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1905">
+      <c r="A1905" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1905" t="inlineStr">
+        <is>
+          <t>One Knoxville vs Westchester SC</t>
+        </is>
+      </c>
+      <c r="C1905" t="inlineStr">
+        <is>
+          <t>One Knoxville</t>
+        </is>
+      </c>
+      <c r="D1905" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1905" t="inlineStr"/>
+      <c r="F1905" t="inlineStr"/>
+      <c r="G1905" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1905" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1905" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1905" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1905" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1905" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1906">
+      <c r="A1906" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1906" t="inlineStr">
+        <is>
+          <t>Deportes Santa Cruz vs O'Higgins</t>
+        </is>
+      </c>
+      <c r="C1906" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="D1906" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1906" t="inlineStr"/>
+      <c r="F1906" t="inlineStr"/>
+      <c r="G1906" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H1906" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1906" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1906" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1906" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1906" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1907">
+      <c r="A1907" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1907" t="inlineStr">
+        <is>
+          <t>Haiti vs Costa Rica</t>
+        </is>
+      </c>
+      <c r="C1907" t="inlineStr">
+        <is>
+          <t>Costa Rica</t>
+        </is>
+      </c>
+      <c r="D1907" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1907" t="inlineStr"/>
+      <c r="F1907" t="inlineStr"/>
+      <c r="G1907" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1907" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1907" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1907" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1907" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1907" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1908">
+      <c r="A1908" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1908" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Real Oruro</t>
+        </is>
+      </c>
+      <c r="C1908" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="D1908" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1908" t="inlineStr"/>
+      <c r="F1908" t="inlineStr"/>
+      <c r="G1908" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1908" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1908" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1908" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1908" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1908" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1909">
+      <c r="A1909" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1909" t="inlineStr">
+        <is>
+          <t>León vs FC Juarez</t>
+        </is>
+      </c>
+      <c r="C1909" t="inlineStr">
+        <is>
+          <t>León</t>
+        </is>
+      </c>
+      <c r="D1909" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1909" t="inlineStr"/>
+      <c r="F1909" t="inlineStr"/>
+      <c r="G1909" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1909" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1909" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1909" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1909" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1909" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1910">
+      <c r="A1910" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1910" t="inlineStr">
+        <is>
+          <t>Deportivo Cali vs Águilas Doradas</t>
+        </is>
+      </c>
+      <c r="C1910" t="inlineStr">
+        <is>
+          <t>Deportivo Cali</t>
+        </is>
+      </c>
+      <c r="D1910" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1910" t="inlineStr"/>
+      <c r="F1910" t="inlineStr"/>
+      <c r="G1910" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1910" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1910" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1910" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1910" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1910" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1911">
+      <c r="A1911" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B1911" t="inlineStr">
+        <is>
+          <t>Necaxa vs América</t>
+        </is>
+      </c>
+      <c r="C1911" t="inlineStr">
+        <is>
+          <t>América</t>
+        </is>
+      </c>
+      <c r="D1911" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1911" t="inlineStr"/>
+      <c r="F1911" t="inlineStr"/>
+      <c r="G1911" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="H1911" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1911" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1911" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1911" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1911" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -86113,7 +88491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86994,6 +89372,25 @@
       </c>
       <c r="E47" t="n">
         <v>59</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>52</v>
+      </c>
+      <c r="C48" t="n">
+        <v>37</v>
+      </c>
+      <c r="D48" t="n">
+        <v>71.2</v>
+      </c>
+      <c r="E48" t="n">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -87007,7 +89404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E262"/>
+  <dimension ref="A1:E271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92518,6 +94915,195 @@
         <v>0</v>
       </c>
     </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C263" t="n">
+        <v>5</v>
+      </c>
+      <c r="D263" t="n">
+        <v>2</v>
+      </c>
+      <c r="E263" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C264" t="n">
+        <v>7</v>
+      </c>
+      <c r="D264" t="n">
+        <v>1</v>
+      </c>
+      <c r="E264" t="n">
+        <v>14.3</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C265" t="n">
+        <v>2</v>
+      </c>
+      <c r="D265" t="n">
+        <v>0</v>
+      </c>
+      <c r="E265" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>siguen_empatados_55</t>
+        </is>
+      </c>
+      <c r="C266" t="n">
+        <v>1</v>
+      </c>
+      <c r="D266" t="n">
+        <v>0</v>
+      </c>
+      <c r="E266" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C267" t="n">
+        <v>6</v>
+      </c>
+      <c r="D267" t="n">
+        <v>0</v>
+      </c>
+      <c r="E267" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C268" t="n">
+        <v>4</v>
+      </c>
+      <c r="D268" t="n">
+        <v>0</v>
+      </c>
+      <c r="E268" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C269" t="n">
+        <v>4</v>
+      </c>
+      <c r="D269" t="n">
+        <v>0</v>
+      </c>
+      <c r="E269" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C270" t="n">
+        <v>2</v>
+      </c>
+      <c r="D270" t="n">
+        <v>0</v>
+      </c>
+      <c r="E270" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>gol_de_cierre</t>
+        </is>
+      </c>
+      <c r="C271" t="n">
+        <v>1</v>
+      </c>
+      <c r="D271" t="n">
+        <v>0</v>
+      </c>
+      <c r="E271" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1911"/>
+  <dimension ref="A1:L1935"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86005,8 +86005,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1860" t="inlineStr"/>
-      <c r="F1860" t="inlineStr"/>
       <c r="G1860" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -86053,8 +86051,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1861" t="inlineStr"/>
-      <c r="F1861" t="inlineStr"/>
       <c r="G1861" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -86101,8 +86097,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1862" t="inlineStr"/>
-      <c r="F1862" t="inlineStr"/>
       <c r="G1862" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -86149,8 +86143,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1863" t="inlineStr"/>
-      <c r="F1863" t="inlineStr"/>
       <c r="G1863" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -86197,8 +86189,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1864" t="inlineStr"/>
-      <c r="F1864" t="inlineStr"/>
       <c r="G1864" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -86245,8 +86235,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1865" t="inlineStr"/>
-      <c r="F1865" t="inlineStr"/>
       <c r="G1865" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -86293,8 +86281,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1866" t="inlineStr"/>
-      <c r="F1866" t="inlineStr"/>
       <c r="G1866" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -86341,8 +86327,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1867" t="inlineStr"/>
-      <c r="F1867" t="inlineStr"/>
       <c r="G1867" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -86389,8 +86373,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1868" t="inlineStr"/>
-      <c r="F1868" t="inlineStr"/>
       <c r="G1868" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -86437,8 +86419,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1869" t="inlineStr"/>
-      <c r="F1869" t="inlineStr"/>
       <c r="G1869" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -86485,8 +86465,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1870" t="inlineStr"/>
-      <c r="F1870" t="inlineStr"/>
       <c r="G1870" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -86533,8 +86511,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1871" t="inlineStr"/>
-      <c r="F1871" t="inlineStr"/>
       <c r="G1871" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -86581,8 +86557,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1872" t="inlineStr"/>
-      <c r="F1872" t="inlineStr"/>
       <c r="G1872" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -86629,8 +86603,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1873" t="inlineStr"/>
-      <c r="F1873" t="inlineStr"/>
       <c r="G1873" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -86677,8 +86649,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1874" t="inlineStr"/>
-      <c r="F1874" t="inlineStr"/>
       <c r="G1874" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -86725,8 +86695,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1875" t="inlineStr"/>
-      <c r="F1875" t="inlineStr"/>
       <c r="G1875" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -86773,8 +86741,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1876" t="inlineStr"/>
-      <c r="F1876" t="inlineStr"/>
       <c r="G1876" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -86821,8 +86787,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1877" t="inlineStr"/>
-      <c r="F1877" t="inlineStr"/>
       <c r="G1877" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -86869,8 +86833,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1878" t="inlineStr"/>
-      <c r="F1878" t="inlineStr"/>
       <c r="G1878" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -86917,8 +86879,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1879" t="inlineStr"/>
-      <c r="F1879" t="inlineStr"/>
       <c r="G1879" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -86965,8 +86925,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1880" t="inlineStr"/>
-      <c r="F1880" t="inlineStr"/>
       <c r="G1880" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -87013,8 +86971,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1881" t="inlineStr"/>
-      <c r="F1881" t="inlineStr"/>
       <c r="G1881" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -87061,8 +87017,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1882" t="inlineStr"/>
-      <c r="F1882" t="inlineStr"/>
       <c r="G1882" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -87109,8 +87063,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1883" t="inlineStr"/>
-      <c r="F1883" t="inlineStr"/>
       <c r="G1883" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -87157,8 +87109,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1884" t="inlineStr"/>
-      <c r="F1884" t="inlineStr"/>
       <c r="G1884" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -87205,8 +87155,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1885" t="inlineStr"/>
-      <c r="F1885" t="inlineStr"/>
       <c r="G1885" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -87253,8 +87201,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1886" t="inlineStr"/>
-      <c r="F1886" t="inlineStr"/>
       <c r="G1886" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -87301,8 +87247,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1887" t="inlineStr"/>
-      <c r="F1887" t="inlineStr"/>
       <c r="G1887" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -87349,8 +87293,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1888" t="inlineStr"/>
-      <c r="F1888" t="inlineStr"/>
       <c r="G1888" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -87397,8 +87339,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1889" t="inlineStr"/>
-      <c r="F1889" t="inlineStr"/>
       <c r="G1889" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -87445,8 +87385,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1890" t="inlineStr"/>
-      <c r="F1890" t="inlineStr"/>
       <c r="G1890" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -87493,8 +87431,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1891" t="inlineStr"/>
-      <c r="F1891" t="inlineStr"/>
       <c r="G1891" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -87541,8 +87477,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1892" t="inlineStr"/>
-      <c r="F1892" t="inlineStr"/>
       <c r="G1892" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -87589,8 +87523,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1893" t="inlineStr"/>
-      <c r="F1893" t="inlineStr"/>
       <c r="G1893" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -87637,8 +87569,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1894" t="inlineStr"/>
-      <c r="F1894" t="inlineStr"/>
       <c r="G1894" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -87685,8 +87615,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1895" t="inlineStr"/>
-      <c r="F1895" t="inlineStr"/>
       <c r="G1895" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -87733,8 +87661,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1896" t="inlineStr"/>
-      <c r="F1896" t="inlineStr"/>
       <c r="G1896" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -87781,8 +87707,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1897" t="inlineStr"/>
-      <c r="F1897" t="inlineStr"/>
       <c r="G1897" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -87829,8 +87753,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1898" t="inlineStr"/>
-      <c r="F1898" t="inlineStr"/>
       <c r="G1898" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -87877,8 +87799,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1899" t="inlineStr"/>
-      <c r="F1899" t="inlineStr"/>
       <c r="G1899" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -87925,8 +87845,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1900" t="inlineStr"/>
-      <c r="F1900" t="inlineStr"/>
       <c r="G1900" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -87973,8 +87891,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1901" t="inlineStr"/>
-      <c r="F1901" t="inlineStr"/>
       <c r="G1901" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -88021,8 +87937,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1902" t="inlineStr"/>
-      <c r="F1902" t="inlineStr"/>
       <c r="G1902" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -88069,8 +87983,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1903" t="inlineStr"/>
-      <c r="F1903" t="inlineStr"/>
       <c r="G1903" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -88117,8 +88029,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1904" t="inlineStr"/>
-      <c r="F1904" t="inlineStr"/>
       <c r="G1904" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -88165,8 +88075,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1905" t="inlineStr"/>
-      <c r="F1905" t="inlineStr"/>
       <c r="G1905" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -88213,8 +88121,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1906" t="inlineStr"/>
-      <c r="F1906" t="inlineStr"/>
       <c r="G1906" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -88261,8 +88167,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1907" t="inlineStr"/>
-      <c r="F1907" t="inlineStr"/>
       <c r="G1907" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -88309,8 +88213,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1908" t="inlineStr"/>
-      <c r="F1908" t="inlineStr"/>
       <c r="G1908" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -88357,8 +88259,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1909" t="inlineStr"/>
-      <c r="F1909" t="inlineStr"/>
       <c r="G1909" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -88405,8 +88305,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1910" t="inlineStr"/>
-      <c r="F1910" t="inlineStr"/>
       <c r="G1910" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -88453,8 +88351,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1911" t="inlineStr"/>
-      <c r="F1911" t="inlineStr"/>
       <c r="G1911" t="inlineStr">
         <is>
           <t>2-4</t>
@@ -88475,6 +88371,1158 @@
         <v>0</v>
       </c>
       <c r="L1911" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1912">
+      <c r="A1912" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1912" t="inlineStr">
+        <is>
+          <t>Japan vs Venezuela</t>
+        </is>
+      </c>
+      <c r="C1912" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D1912" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1912" t="inlineStr"/>
+      <c r="F1912" t="inlineStr"/>
+      <c r="G1912" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1912" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1912" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1912" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1912" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1912" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1913" t="inlineStr">
+        <is>
+          <t>South Korea vs Uruguay</t>
+        </is>
+      </c>
+      <c r="C1913" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="D1913" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1913" t="inlineStr"/>
+      <c r="F1913" t="inlineStr"/>
+      <c r="G1913" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="H1913" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1913" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1913" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1913" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1913" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1914">
+      <c r="A1914" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1914" t="inlineStr">
+        <is>
+          <t>Tajikistan vs Palestine</t>
+        </is>
+      </c>
+      <c r="C1914" t="inlineStr">
+        <is>
+          <t>Palestine</t>
+        </is>
+      </c>
+      <c r="D1914" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1914" t="inlineStr"/>
+      <c r="F1914" t="inlineStr"/>
+      <c r="G1914" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="H1914" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1914" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1914" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1914" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1914" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1915" t="inlineStr">
+        <is>
+          <t>Armenia vs Montenegro</t>
+        </is>
+      </c>
+      <c r="C1915" t="inlineStr">
+        <is>
+          <t>Montenegro</t>
+        </is>
+      </c>
+      <c r="D1915" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1915" t="inlineStr"/>
+      <c r="F1915" t="inlineStr"/>
+      <c r="G1915" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H1915" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1915" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1915" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1915" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1915" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1916">
+      <c r="A1916" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1916" t="inlineStr">
+        <is>
+          <t>Zimbabwe vs Congo DR</t>
+        </is>
+      </c>
+      <c r="C1916" t="inlineStr">
+        <is>
+          <t>Congo DR</t>
+        </is>
+      </c>
+      <c r="D1916" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1916" t="inlineStr"/>
+      <c r="F1916" t="inlineStr"/>
+      <c r="G1916" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1916" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1916" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1916" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1916" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1916" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1917">
+      <c r="A1917" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1917" t="inlineStr">
+        <is>
+          <t>Equatorial Guinea vs Sierra Leone</t>
+        </is>
+      </c>
+      <c r="C1917" t="inlineStr">
+        <is>
+          <t>Equatorial Guinea</t>
+        </is>
+      </c>
+      <c r="D1917" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1917" t="inlineStr"/>
+      <c r="F1917" t="inlineStr"/>
+      <c r="G1917" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1917" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1917" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1917" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1917" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1917" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1918">
+      <c r="A1918" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1918" t="inlineStr">
+        <is>
+          <t>Central African Republic vs Burkina Faso</t>
+        </is>
+      </c>
+      <c r="C1918" t="inlineStr">
+        <is>
+          <t>Burkina Faso</t>
+        </is>
+      </c>
+      <c r="D1918" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1918" t="inlineStr"/>
+      <c r="F1918" t="inlineStr"/>
+      <c r="G1918" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1918" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1918" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1918" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1918" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1918" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1919">
+      <c r="A1919" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1919" t="inlineStr">
+        <is>
+          <t>Denmark U21 vs Belarus U21</t>
+        </is>
+      </c>
+      <c r="C1919" t="inlineStr">
+        <is>
+          <t>Denmark U21</t>
+        </is>
+      </c>
+      <c r="D1919" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1919" t="inlineStr"/>
+      <c r="F1919" t="inlineStr"/>
+      <c r="G1919" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1919" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1919" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1919" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1919" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1919" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1920">
+      <c r="A1920" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1920" t="inlineStr">
+        <is>
+          <t>Flandria vs Dock Sud</t>
+        </is>
+      </c>
+      <c r="C1920" t="inlineStr">
+        <is>
+          <t>Flandria</t>
+        </is>
+      </c>
+      <c r="D1920" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1920" t="inlineStr"/>
+      <c r="F1920" t="inlineStr"/>
+      <c r="G1920" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1920" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1920" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1920" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1920" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1920" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1921">
+      <c r="A1921" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1921" t="inlineStr">
+        <is>
+          <t>Leganés vs Castellón</t>
+        </is>
+      </c>
+      <c r="C1921" t="inlineStr">
+        <is>
+          <t>Castellón</t>
+        </is>
+      </c>
+      <c r="D1921" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1921" t="inlineStr"/>
+      <c r="F1921" t="inlineStr"/>
+      <c r="G1921" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1921" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1921" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1921" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1921" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1921" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1922">
+      <c r="A1922" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1922" t="inlineStr">
+        <is>
+          <t>Belgium vs France</t>
+        </is>
+      </c>
+      <c r="C1922" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D1922" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1922" t="inlineStr"/>
+      <c r="F1922" t="inlineStr"/>
+      <c r="G1922" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1922" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1922" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1922" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1922" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1922" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1923">
+      <c r="A1923" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1923" t="inlineStr">
+        <is>
+          <t>Sweden vs Poland</t>
+        </is>
+      </c>
+      <c r="C1923" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="D1923" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1923" t="inlineStr"/>
+      <c r="F1923" t="inlineStr"/>
+      <c r="G1923" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1923" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1923" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1923" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1923" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1923" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1924">
+      <c r="A1924" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1924" t="inlineStr">
+        <is>
+          <t>Romania vs Bosnia-Herzegovina</t>
+        </is>
+      </c>
+      <c r="C1924" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+      <c r="D1924" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1924" t="inlineStr"/>
+      <c r="F1924" t="inlineStr"/>
+      <c r="G1924" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="H1924" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1924" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1924" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1924" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1924" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1925">
+      <c r="A1925" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1925" t="inlineStr">
+        <is>
+          <t>Guadeloupe vs Barbados</t>
+        </is>
+      </c>
+      <c r="C1925" t="inlineStr">
+        <is>
+          <t>Guadeloupe</t>
+        </is>
+      </c>
+      <c r="D1925" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1925" t="inlineStr"/>
+      <c r="F1925" t="inlineStr"/>
+      <c r="G1925" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1925" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1925" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1925" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1925" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1925" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1926">
+      <c r="A1926" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1926" t="inlineStr">
+        <is>
+          <t>Sportivo San Lorenzo vs Deportivo Recoleta</t>
+        </is>
+      </c>
+      <c r="C1926" t="inlineStr">
+        <is>
+          <t>Deportivo Recoleta</t>
+        </is>
+      </c>
+      <c r="D1926" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1926" t="inlineStr"/>
+      <c r="F1926" t="inlineStr"/>
+      <c r="G1926" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1926" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1926" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1926" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1926" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1926" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1927">
+      <c r="A1927" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1927" t="inlineStr">
+        <is>
+          <t>Cuba vs Bonaire</t>
+        </is>
+      </c>
+      <c r="C1927" t="inlineStr">
+        <is>
+          <t>Cuba</t>
+        </is>
+      </c>
+      <c r="D1927" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1927" t="inlineStr"/>
+      <c r="F1927" t="inlineStr"/>
+      <c r="G1927" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1927" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1927" t="n">
+        <v>3</v>
+      </c>
+      <c r="J1927" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1927" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1927" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1928">
+      <c r="A1928" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1928" t="inlineStr">
+        <is>
+          <t>Suriname vs Martinique</t>
+        </is>
+      </c>
+      <c r="C1928" t="inlineStr">
+        <is>
+          <t>Suriname</t>
+        </is>
+      </c>
+      <c r="D1928" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1928" t="inlineStr"/>
+      <c r="F1928" t="inlineStr"/>
+      <c r="G1928" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1928" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1928" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1928" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1928" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1928" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1929">
+      <c r="A1929" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1929" t="inlineStr">
+        <is>
+          <t>Libertad vs Club Olimpia</t>
+        </is>
+      </c>
+      <c r="C1929" t="inlineStr">
+        <is>
+          <t>Club Olimpia</t>
+        </is>
+      </c>
+      <c r="D1929" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1929" t="inlineStr"/>
+      <c r="F1929" t="inlineStr"/>
+      <c r="G1929" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1929" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1929" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1929" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1929" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1929" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1930">
+      <c r="A1930" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1930" t="inlineStr">
+        <is>
+          <t>América Mineiro vs Juventude</t>
+        </is>
+      </c>
+      <c r="C1930" t="inlineStr">
+        <is>
+          <t>Juventude</t>
+        </is>
+      </c>
+      <c r="D1930" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1930" t="inlineStr"/>
+      <c r="F1930" t="inlineStr"/>
+      <c r="G1930" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1930" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1930" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1930" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1930" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1930" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1931">
+      <c r="A1931" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1931" t="inlineStr">
+        <is>
+          <t>Montevideo Wanderers vs Albion FC</t>
+        </is>
+      </c>
+      <c r="C1931" t="inlineStr">
+        <is>
+          <t>Montevideo Wanderers</t>
+        </is>
+      </c>
+      <c r="D1931" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1931" t="inlineStr"/>
+      <c r="F1931" t="inlineStr"/>
+      <c r="G1931" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1931" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1931" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1931" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1931" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1931" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1932">
+      <c r="A1932" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1932" t="inlineStr">
+        <is>
+          <t>Jamaica vs Honduras</t>
+        </is>
+      </c>
+      <c r="C1932" t="inlineStr">
+        <is>
+          <t>Jamaica</t>
+        </is>
+      </c>
+      <c r="D1932" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1932" t="inlineStr"/>
+      <c r="F1932" t="inlineStr"/>
+      <c r="G1932" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1932" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1932" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1932" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1932" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1932" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1933">
+      <c r="A1933" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1933" t="inlineStr">
+        <is>
+          <t>St. Kitts and Nevis vs Grenada</t>
+        </is>
+      </c>
+      <c r="C1933" t="inlineStr">
+        <is>
+          <t>Grenada</t>
+        </is>
+      </c>
+      <c r="D1933" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1933" t="inlineStr"/>
+      <c r="F1933" t="inlineStr"/>
+      <c r="G1933" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1933" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1933" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1933" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1933" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1933" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1934">
+      <c r="A1934" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1934" t="inlineStr">
+        <is>
+          <t>St. Lucia vs Bermuda</t>
+        </is>
+      </c>
+      <c r="C1934" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="D1934" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1934" t="inlineStr"/>
+      <c r="F1934" t="inlineStr"/>
+      <c r="G1934" t="inlineStr">
+        <is>
+          <t>5-2</t>
+        </is>
+      </c>
+      <c r="H1934" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1934" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1934" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1934" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1934" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1935">
+      <c r="A1935" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B1935" t="inlineStr">
+        <is>
+          <t>Guatemala vs El Salvador</t>
+        </is>
+      </c>
+      <c r="C1935" t="inlineStr">
+        <is>
+          <t>Guatemala</t>
+        </is>
+      </c>
+      <c r="D1935" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1935" t="inlineStr"/>
+      <c r="F1935" t="inlineStr"/>
+      <c r="G1935" t="inlineStr">
+        <is>
+          <t>6-0</t>
+        </is>
+      </c>
+      <c r="H1935" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1935" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1935" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1935" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1935" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -88491,7 +89539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89391,6 +90439,25 @@
       </c>
       <c r="E48" t="n">
         <v>52</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>24</v>
+      </c>
+      <c r="C49" t="n">
+        <v>18</v>
+      </c>
+      <c r="D49" t="n">
+        <v>75</v>
+      </c>
+      <c r="E49" t="n">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -89404,7 +90471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E271"/>
+  <dimension ref="A1:E277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95104,6 +96171,132 @@
         <v>0</v>
       </c>
     </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C272" t="n">
+        <v>3</v>
+      </c>
+      <c r="D272" t="n">
+        <v>0</v>
+      </c>
+      <c r="E272" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C273" t="n">
+        <v>1</v>
+      </c>
+      <c r="D273" t="n">
+        <v>0</v>
+      </c>
+      <c r="E273" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C274" t="n">
+        <v>3</v>
+      </c>
+      <c r="D274" t="n">
+        <v>1</v>
+      </c>
+      <c r="E274" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C275" t="n">
+        <v>2</v>
+      </c>
+      <c r="D275" t="n">
+        <v>0</v>
+      </c>
+      <c r="E275" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C276" t="n">
+        <v>1</v>
+      </c>
+      <c r="D276" t="n">
+        <v>0</v>
+      </c>
+      <c r="E276" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C277" t="n">
+        <v>3</v>
+      </c>
+      <c r="D277" t="n">
+        <v>1</v>
+      </c>
+      <c r="E277" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1935"/>
+  <dimension ref="A1:L1985"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88397,8 +88397,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1912" t="inlineStr"/>
-      <c r="F1912" t="inlineStr"/>
       <c r="G1912" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -88445,8 +88443,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1913" t="inlineStr"/>
-      <c r="F1913" t="inlineStr"/>
       <c r="G1913" t="inlineStr">
         <is>
           <t>1-4</t>
@@ -88493,8 +88489,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1914" t="inlineStr"/>
-      <c r="F1914" t="inlineStr"/>
       <c r="G1914" t="inlineStr">
         <is>
           <t>2-4</t>
@@ -88541,8 +88535,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1915" t="inlineStr"/>
-      <c r="F1915" t="inlineStr"/>
       <c r="G1915" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -88589,8 +88581,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1916" t="inlineStr"/>
-      <c r="F1916" t="inlineStr"/>
       <c r="G1916" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -88637,8 +88627,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1917" t="inlineStr"/>
-      <c r="F1917" t="inlineStr"/>
       <c r="G1917" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -88685,8 +88673,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1918" t="inlineStr"/>
-      <c r="F1918" t="inlineStr"/>
       <c r="G1918" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -88733,8 +88719,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1919" t="inlineStr"/>
-      <c r="F1919" t="inlineStr"/>
       <c r="G1919" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -88781,8 +88765,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1920" t="inlineStr"/>
-      <c r="F1920" t="inlineStr"/>
       <c r="G1920" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -88829,8 +88811,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1921" t="inlineStr"/>
-      <c r="F1921" t="inlineStr"/>
       <c r="G1921" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -88877,8 +88857,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1922" t="inlineStr"/>
-      <c r="F1922" t="inlineStr"/>
       <c r="G1922" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -88925,8 +88903,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1923" t="inlineStr"/>
-      <c r="F1923" t="inlineStr"/>
       <c r="G1923" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -88973,8 +88949,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1924" t="inlineStr"/>
-      <c r="F1924" t="inlineStr"/>
       <c r="G1924" t="inlineStr">
         <is>
           <t>2-4</t>
@@ -89021,8 +88995,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1925" t="inlineStr"/>
-      <c r="F1925" t="inlineStr"/>
       <c r="G1925" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -89069,8 +89041,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1926" t="inlineStr"/>
-      <c r="F1926" t="inlineStr"/>
       <c r="G1926" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -89117,8 +89087,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1927" t="inlineStr"/>
-      <c r="F1927" t="inlineStr"/>
       <c r="G1927" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -89165,8 +89133,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1928" t="inlineStr"/>
-      <c r="F1928" t="inlineStr"/>
       <c r="G1928" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -89213,8 +89179,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1929" t="inlineStr"/>
-      <c r="F1929" t="inlineStr"/>
       <c r="G1929" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -89261,8 +89225,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1930" t="inlineStr"/>
-      <c r="F1930" t="inlineStr"/>
       <c r="G1930" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -89309,8 +89271,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1931" t="inlineStr"/>
-      <c r="F1931" t="inlineStr"/>
       <c r="G1931" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -89357,8 +89317,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1932" t="inlineStr"/>
-      <c r="F1932" t="inlineStr"/>
       <c r="G1932" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -89405,8 +89363,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1933" t="inlineStr"/>
-      <c r="F1933" t="inlineStr"/>
       <c r="G1933" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -89453,8 +89409,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1934" t="inlineStr"/>
-      <c r="F1934" t="inlineStr"/>
       <c r="G1934" t="inlineStr">
         <is>
           <t>5-2</t>
@@ -89501,8 +89455,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1935" t="inlineStr"/>
-      <c r="F1935" t="inlineStr"/>
       <c r="G1935" t="inlineStr">
         <is>
           <t>6-0</t>
@@ -89523,6 +89475,2406 @@
         <v>0</v>
       </c>
       <c r="L1935" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1936" t="inlineStr">
+        <is>
+          <t>Australia vs Brazil</t>
+        </is>
+      </c>
+      <c r="C1936" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="D1936" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1936" t="inlineStr"/>
+      <c r="F1936" t="inlineStr"/>
+      <c r="G1936" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="H1936" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1936" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1936" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1936" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1936" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1937">
+      <c r="A1937" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1937" t="inlineStr">
+        <is>
+          <t>Comoros vs Namibia</t>
+        </is>
+      </c>
+      <c r="C1937" t="inlineStr">
+        <is>
+          <t>Comoros</t>
+        </is>
+      </c>
+      <c r="D1937" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1937" t="inlineStr"/>
+      <c r="F1937" t="inlineStr"/>
+      <c r="G1937" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1937" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1937" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1937" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1937" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1937" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1938">
+      <c r="A1938" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1938" t="inlineStr">
+        <is>
+          <t>Ethiopia vs Senegal</t>
+        </is>
+      </c>
+      <c r="C1938" t="inlineStr">
+        <is>
+          <t>Senegal</t>
+        </is>
+      </c>
+      <c r="D1938" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1938" t="inlineStr"/>
+      <c r="F1938" t="inlineStr"/>
+      <c r="G1938" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1938" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1938" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1938" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1938" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1938" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1939">
+      <c r="A1939" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1939" t="inlineStr">
+        <is>
+          <t>Lesotho vs Morocco</t>
+        </is>
+      </c>
+      <c r="C1939" t="inlineStr">
+        <is>
+          <t>Morocco</t>
+        </is>
+      </c>
+      <c r="D1939" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1939" t="inlineStr"/>
+      <c r="F1939" t="inlineStr"/>
+      <c r="G1939" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1939" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1939" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1939" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1939" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1939" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1940">
+      <c r="A1940" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1940" t="inlineStr">
+        <is>
+          <t>South Sudan vs Egypt</t>
+        </is>
+      </c>
+      <c r="C1940" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="D1940" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1940" t="inlineStr"/>
+      <c r="F1940" t="inlineStr"/>
+      <c r="G1940" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="H1940" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1940" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1940" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1940" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1940" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1941">
+      <c r="A1941" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1941" t="inlineStr">
+        <is>
+          <t>Burundi vs Algeria</t>
+        </is>
+      </c>
+      <c r="C1941" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="D1941" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1941" t="inlineStr"/>
+      <c r="F1941" t="inlineStr"/>
+      <c r="G1941" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1941" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1941" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1941" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1941" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1941" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1942">
+      <c r="A1942" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1942" t="inlineStr">
+        <is>
+          <t>Jagiellonia Bialystok vs FK Suduva</t>
+        </is>
+      </c>
+      <c r="C1942" t="inlineStr">
+        <is>
+          <t>Jagiellonia Bialystok</t>
+        </is>
+      </c>
+      <c r="D1942" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1942" t="inlineStr"/>
+      <c r="F1942" t="inlineStr"/>
+      <c r="G1942" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="H1942" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1942" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1942" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1942" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1942" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1943">
+      <c r="A1943" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1943" t="inlineStr">
+        <is>
+          <t>Slovenia U21 vs Israel U21</t>
+        </is>
+      </c>
+      <c r="C1943" t="inlineStr">
+        <is>
+          <t>Slovenia U21</t>
+        </is>
+      </c>
+      <c r="D1943" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1943" t="inlineStr"/>
+      <c r="F1943" t="inlineStr"/>
+      <c r="G1943" t="inlineStr">
+        <is>
+          <t>2-3</t>
+        </is>
+      </c>
+      <c r="H1943" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1943" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1943" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1943" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1943" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1944">
+      <c r="A1944" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1944" t="inlineStr">
+        <is>
+          <t>Iceland U21 vs Switzerland U21</t>
+        </is>
+      </c>
+      <c r="C1944" t="inlineStr">
+        <is>
+          <t>Switzerland U21</t>
+        </is>
+      </c>
+      <c r="D1944" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1944" t="inlineStr"/>
+      <c r="F1944" t="inlineStr"/>
+      <c r="G1944" t="inlineStr">
+        <is>
+          <t>5-1</t>
+        </is>
+      </c>
+      <c r="H1944" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1944" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1944" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1944" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1944" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1945">
+      <c r="A1945" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1945" t="inlineStr">
+        <is>
+          <t>Finland vs Belarus</t>
+        </is>
+      </c>
+      <c r="C1945" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="D1945" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1945" t="inlineStr"/>
+      <c r="F1945" t="inlineStr"/>
+      <c r="G1945" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1945" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1945" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1945" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1945" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1945" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1946">
+      <c r="A1946" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1946" t="inlineStr">
+        <is>
+          <t>Cape Verde vs Rwanda</t>
+        </is>
+      </c>
+      <c r="C1946" t="inlineStr">
+        <is>
+          <t>Cape Verde</t>
+        </is>
+      </c>
+      <c r="D1946" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1946" t="inlineStr"/>
+      <c r="F1946" t="inlineStr"/>
+      <c r="G1946" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1946" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1946" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1946" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1946" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1946" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1947">
+      <c r="A1947" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1947" t="inlineStr">
+        <is>
+          <t>Ghana vs Gambia</t>
+        </is>
+      </c>
+      <c r="C1947" t="inlineStr">
+        <is>
+          <t>Ghana</t>
+        </is>
+      </c>
+      <c r="D1947" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1947" t="inlineStr"/>
+      <c r="F1947" t="inlineStr"/>
+      <c r="G1947" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="H1947" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1947" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1947" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1947" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1947" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1948">
+      <c r="A1948" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1948" t="inlineStr">
+        <is>
+          <t>Guinea-Bissau vs Nigeria</t>
+        </is>
+      </c>
+      <c r="C1948" t="inlineStr">
+        <is>
+          <t>Nigeria</t>
+        </is>
+      </c>
+      <c r="D1948" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1948" t="inlineStr"/>
+      <c r="F1948" t="inlineStr"/>
+      <c r="G1948" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1948" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1948" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1948" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1948" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1948" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1949">
+      <c r="A1949" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1949" t="inlineStr">
+        <is>
+          <t>Russia vs Iran</t>
+        </is>
+      </c>
+      <c r="C1949" t="inlineStr">
+        <is>
+          <t>Russia</t>
+        </is>
+      </c>
+      <c r="D1949" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1949" t="inlineStr"/>
+      <c r="F1949" t="inlineStr"/>
+      <c r="G1949" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1949" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1949" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1949" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1949" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1949" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1950">
+      <c r="A1950" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1950" t="inlineStr">
+        <is>
+          <t>Estonia U21 vs France U21</t>
+        </is>
+      </c>
+      <c r="C1950" t="inlineStr">
+        <is>
+          <t>France U21</t>
+        </is>
+      </c>
+      <c r="D1950" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1950" t="inlineStr"/>
+      <c r="F1950" t="inlineStr"/>
+      <c r="G1950" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1950" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1950" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1950" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1950" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1950" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1951">
+      <c r="A1951" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1951" t="inlineStr">
+        <is>
+          <t>Norway U21 vs Bosnia-Herzegovina U21</t>
+        </is>
+      </c>
+      <c r="C1951" t="inlineStr">
+        <is>
+          <t>Norway U21</t>
+        </is>
+      </c>
+      <c r="D1951" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1951" t="inlineStr"/>
+      <c r="F1951" t="inlineStr"/>
+      <c r="G1951" t="inlineStr">
+        <is>
+          <t>6-1</t>
+        </is>
+      </c>
+      <c r="H1951" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1951" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1951" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1951" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1951" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1952">
+      <c r="A1952" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1952" t="inlineStr">
+        <is>
+          <t>Saudi Arabia vs Iraq</t>
+        </is>
+      </c>
+      <c r="C1952" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="D1952" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1952" t="inlineStr"/>
+      <c r="F1952" t="inlineStr"/>
+      <c r="G1952" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1952" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1952" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1952" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1952" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1952" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1953">
+      <c r="A1953" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1953" t="inlineStr">
+        <is>
+          <t>Oman vs Kuwait</t>
+        </is>
+      </c>
+      <c r="C1953" t="inlineStr">
+        <is>
+          <t>Oman</t>
+        </is>
+      </c>
+      <c r="D1953" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1953" t="inlineStr"/>
+      <c r="F1953" t="inlineStr"/>
+      <c r="G1953" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1953" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1953" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1953" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1953" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1953" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1954">
+      <c r="A1954" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1954" t="inlineStr">
+        <is>
+          <t>Boreham Wood vs Kidderminster Harriers</t>
+        </is>
+      </c>
+      <c r="C1954" t="inlineStr">
+        <is>
+          <t>Boreham Wood</t>
+        </is>
+      </c>
+      <c r="D1954" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1954" t="inlineStr"/>
+      <c r="F1954" t="inlineStr"/>
+      <c r="G1954" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1954" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1954" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1954" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1954" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1954" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1955">
+      <c r="A1955" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1955" t="inlineStr">
+        <is>
+          <t>Belgium U21 vs Wales U21</t>
+        </is>
+      </c>
+      <c r="C1955" t="inlineStr">
+        <is>
+          <t>Belgium U21</t>
+        </is>
+      </c>
+      <c r="D1955" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1955" t="inlineStr"/>
+      <c r="F1955" t="inlineStr"/>
+      <c r="G1955" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H1955" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1955" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1955" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1955" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1955" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1956">
+      <c r="A1956" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1956" t="inlineStr">
+        <is>
+          <t>Republic of Ireland U21 vs Kazakhstan U21</t>
+        </is>
+      </c>
+      <c r="C1956" t="inlineStr">
+        <is>
+          <t>Republic of Ireland U21</t>
+        </is>
+      </c>
+      <c r="D1956" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1956" t="inlineStr"/>
+      <c r="F1956" t="inlineStr"/>
+      <c r="G1956" t="inlineStr">
+        <is>
+          <t>4-3</t>
+        </is>
+      </c>
+      <c r="H1956" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1956" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1956" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1956" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1956" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1957">
+      <c r="A1957" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1957" t="inlineStr">
+        <is>
+          <t>Spain vs Croatia</t>
+        </is>
+      </c>
+      <c r="C1957" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D1957" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1957" t="inlineStr"/>
+      <c r="F1957" t="inlineStr"/>
+      <c r="G1957" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H1957" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1957" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1957" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1957" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1957" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1958">
+      <c r="A1958" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1958" t="inlineStr">
+        <is>
+          <t>Czechia vs England</t>
+        </is>
+      </c>
+      <c r="C1958" t="inlineStr">
+        <is>
+          <t>England</t>
+        </is>
+      </c>
+      <c r="D1958" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1958" t="inlineStr"/>
+      <c r="F1958" t="inlineStr"/>
+      <c r="G1958" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1958" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1958" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1958" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1958" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1958" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1959">
+      <c r="A1959" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1959" t="inlineStr">
+        <is>
+          <t>San Marino vs Albania</t>
+        </is>
+      </c>
+      <c r="C1959" t="inlineStr">
+        <is>
+          <t>Albania</t>
+        </is>
+      </c>
+      <c r="D1959" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1959" t="inlineStr"/>
+      <c r="F1959" t="inlineStr"/>
+      <c r="G1959" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H1959" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1959" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1959" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1959" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1959" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1960" t="inlineStr">
+        <is>
+          <t>Slovakia vs Kazakhstan</t>
+        </is>
+      </c>
+      <c r="C1960" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="D1960" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1960" t="inlineStr"/>
+      <c r="F1960" t="inlineStr"/>
+      <c r="G1960" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1960" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1960" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1960" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1960" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1960" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1961">
+      <c r="A1961" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1961" t="inlineStr">
+        <is>
+          <t>Bulgaria vs Estonia</t>
+        </is>
+      </c>
+      <c r="C1961" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="D1961" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1961" t="inlineStr"/>
+      <c r="F1961" t="inlineStr"/>
+      <c r="G1961" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H1961" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1961" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1961" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1961" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1961" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1962">
+      <c r="A1962" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1962" t="inlineStr">
+        <is>
+          <t>Luxembourg vs Iceland</t>
+        </is>
+      </c>
+      <c r="C1962" t="inlineStr">
+        <is>
+          <t>Iceland</t>
+        </is>
+      </c>
+      <c r="D1962" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1962" t="inlineStr"/>
+      <c r="F1962" t="inlineStr"/>
+      <c r="G1962" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H1962" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1962" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1962" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1962" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1962" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1963">
+      <c r="A1963" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1963" t="inlineStr">
+        <is>
+          <t>Scotland vs Switzerland</t>
+        </is>
+      </c>
+      <c r="C1963" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="D1963" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1963" t="inlineStr"/>
+      <c r="F1963" t="inlineStr"/>
+      <c r="G1963" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H1963" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1963" t="n">
+        <v>4</v>
+      </c>
+      <c r="J1963" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1963" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1963" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1964">
+      <c r="A1964" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1964" t="inlineStr">
+        <is>
+          <t>Slovenia vs North Macedonia</t>
+        </is>
+      </c>
+      <c r="C1964" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="D1964" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1964" t="inlineStr"/>
+      <c r="F1964" t="inlineStr"/>
+      <c r="G1964" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1964" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1964" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1964" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1964" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1964" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1965">
+      <c r="A1965" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1965" t="inlineStr">
+        <is>
+          <t>Barrow vs Scunthorpe United</t>
+        </is>
+      </c>
+      <c r="C1965" t="inlineStr">
+        <is>
+          <t>Barrow</t>
+        </is>
+      </c>
+      <c r="D1965" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1965" t="inlineStr"/>
+      <c r="F1965" t="inlineStr"/>
+      <c r="G1965" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1965" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1965" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1965" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1965" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1965" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1966">
+      <c r="A1966" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1966" t="inlineStr">
+        <is>
+          <t>FC Halifax Town vs Boston United</t>
+        </is>
+      </c>
+      <c r="C1966" t="inlineStr">
+        <is>
+          <t>FC Halifax Town</t>
+        </is>
+      </c>
+      <c r="D1966" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1966" t="inlineStr"/>
+      <c r="F1966" t="inlineStr"/>
+      <c r="G1966" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1966" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1966" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1966" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1966" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1966" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1967">
+      <c r="A1967" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1967" t="inlineStr">
+        <is>
+          <t>Forest Green Rovers vs Wealdstone</t>
+        </is>
+      </c>
+      <c r="C1967" t="inlineStr">
+        <is>
+          <t>Forest Green Rovers</t>
+        </is>
+      </c>
+      <c r="D1967" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1967" t="inlineStr"/>
+      <c r="F1967" t="inlineStr"/>
+      <c r="G1967" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1967" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1967" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1967" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1967" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1967" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1968">
+      <c r="A1968" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1968" t="inlineStr">
+        <is>
+          <t>Gateshead vs Altrincham</t>
+        </is>
+      </c>
+      <c r="C1968" t="inlineStr">
+        <is>
+          <t>Altrincham</t>
+        </is>
+      </c>
+      <c r="D1968" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1968" t="inlineStr"/>
+      <c r="F1968" t="inlineStr"/>
+      <c r="G1968" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1968" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1968" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1968" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1968" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1968" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1969">
+      <c r="A1969" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1969" t="inlineStr">
+        <is>
+          <t>Hartlepool United vs Harrogate Town</t>
+        </is>
+      </c>
+      <c r="C1969" t="inlineStr">
+        <is>
+          <t>Harrogate Town</t>
+        </is>
+      </c>
+      <c r="D1969" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1969" t="inlineStr"/>
+      <c r="F1969" t="inlineStr"/>
+      <c r="G1969" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1969" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1969" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1969" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1969" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1969" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1970">
+      <c r="A1970" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1970" t="inlineStr">
+        <is>
+          <t>AFC Hornchurch vs Aldershot Town</t>
+        </is>
+      </c>
+      <c r="C1970" t="inlineStr">
+        <is>
+          <t>AFC Hornchurch</t>
+        </is>
+      </c>
+      <c r="D1970" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1970" t="inlineStr"/>
+      <c r="F1970" t="inlineStr"/>
+      <c r="G1970" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1970" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1970" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1970" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1970" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1970" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1971">
+      <c r="A1971" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1971" t="inlineStr">
+        <is>
+          <t>Woking vs Solihull Moors</t>
+        </is>
+      </c>
+      <c r="C1971" t="inlineStr">
+        <is>
+          <t>Woking</t>
+        </is>
+      </c>
+      <c r="D1971" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1971" t="inlineStr"/>
+      <c r="F1971" t="inlineStr"/>
+      <c r="G1971" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="H1971" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1971" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1971" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1971" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1971" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1972" t="inlineStr">
+        <is>
+          <t>Yeovil Town vs Worthing</t>
+        </is>
+      </c>
+      <c r="C1972" t="inlineStr">
+        <is>
+          <t>Yeovil Town</t>
+        </is>
+      </c>
+      <c r="D1972" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1972" t="inlineStr"/>
+      <c r="F1972" t="inlineStr"/>
+      <c r="G1972" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1972" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1972" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1972" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1972" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1972" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1973">
+      <c r="A1973" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1973" t="inlineStr">
+        <is>
+          <t>Forfar Athletic vs Formartine United</t>
+        </is>
+      </c>
+      <c r="C1973" t="inlineStr">
+        <is>
+          <t>Forfar Athletic</t>
+        </is>
+      </c>
+      <c r="D1973" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1973" t="inlineStr"/>
+      <c r="F1973" t="inlineStr"/>
+      <c r="G1973" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1973" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1973" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1973" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1973" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1973" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1974">
+      <c r="A1974" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1974" t="inlineStr">
+        <is>
+          <t>AFC Fylde vs Carlisle United</t>
+        </is>
+      </c>
+      <c r="C1974" t="inlineStr">
+        <is>
+          <t>AFC Fylde</t>
+        </is>
+      </c>
+      <c r="D1974" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1974" t="inlineStr"/>
+      <c r="F1974" t="inlineStr"/>
+      <c r="G1974" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1974" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1974" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1974" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1974" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1974" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1975">
+      <c r="A1975" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1975" t="inlineStr">
+        <is>
+          <t>Congo vs Cameroon</t>
+        </is>
+      </c>
+      <c r="C1975" t="inlineStr">
+        <is>
+          <t>Cameroon</t>
+        </is>
+      </c>
+      <c r="D1975" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1975" t="inlineStr"/>
+      <c r="F1975" t="inlineStr"/>
+      <c r="G1975" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1975" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1975" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1975" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1975" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1975" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1976">
+      <c r="A1976" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1976" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto vs Guabirá</t>
+        </is>
+      </c>
+      <c r="C1976" t="inlineStr">
+        <is>
+          <t>Universitario de Vinto</t>
+        </is>
+      </c>
+      <c r="D1976" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1976" t="inlineStr"/>
+      <c r="F1976" t="inlineStr"/>
+      <c r="G1976" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1976" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1976" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1976" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1976" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1976" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1977">
+      <c r="A1977" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1977" t="inlineStr">
+        <is>
+          <t>Gabon vs Niger</t>
+        </is>
+      </c>
+      <c r="C1977" t="inlineStr">
+        <is>
+          <t>Gabon</t>
+        </is>
+      </c>
+      <c r="D1977" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1977" t="inlineStr"/>
+      <c r="F1977" t="inlineStr"/>
+      <c r="G1977" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1977" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1977" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1977" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1977" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1977" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1978">
+      <c r="A1978" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1978" t="inlineStr">
+        <is>
+          <t>Deportivo Pereira vs Independiente Santa Fe</t>
+        </is>
+      </c>
+      <c r="C1978" t="inlineStr">
+        <is>
+          <t>Independiente Santa Fe</t>
+        </is>
+      </c>
+      <c r="D1978" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1978" t="inlineStr"/>
+      <c r="F1978" t="inlineStr"/>
+      <c r="G1978" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="H1978" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1978" t="n">
+        <v>2</v>
+      </c>
+      <c r="J1978" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1978" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1978" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1979">
+      <c r="A1979" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1979" t="inlineStr">
+        <is>
+          <t>Puerto Montt vs Colo Colo</t>
+        </is>
+      </c>
+      <c r="C1979" t="inlineStr">
+        <is>
+          <t>Colo Colo</t>
+        </is>
+      </c>
+      <c r="D1979" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1979" t="inlineStr"/>
+      <c r="F1979" t="inlineStr"/>
+      <c r="G1979" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1979" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1979" t="n">
+        <v>5</v>
+      </c>
+      <c r="J1979" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1979" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1979" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1980">
+      <c r="A1980" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1980" t="inlineStr">
+        <is>
+          <t>Atletico Balboa vs Cacahuatique</t>
+        </is>
+      </c>
+      <c r="C1980" t="inlineStr">
+        <is>
+          <t>Atletico Balboa</t>
+        </is>
+      </c>
+      <c r="D1980" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1980" t="inlineStr"/>
+      <c r="F1980" t="inlineStr"/>
+      <c r="G1980" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1980" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1980" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1980" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1980" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1980" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1981">
+      <c r="A1981" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1981" t="inlineStr">
+        <is>
+          <t>Real Potosí vs ABB</t>
+        </is>
+      </c>
+      <c r="C1981" t="inlineStr">
+        <is>
+          <t>Real Potosí</t>
+        </is>
+      </c>
+      <c r="D1981" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1981" t="inlineStr"/>
+      <c r="F1981" t="inlineStr"/>
+      <c r="G1981" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H1981" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1981" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1981" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1981" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1981" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1982">
+      <c r="A1982" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1982" t="inlineStr">
+        <is>
+          <t>Botafogo-SP vs Ponte Preta</t>
+        </is>
+      </c>
+      <c r="C1982" t="inlineStr">
+        <is>
+          <t>Botafogo-SP</t>
+        </is>
+      </c>
+      <c r="D1982" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1982" t="inlineStr"/>
+      <c r="F1982" t="inlineStr"/>
+      <c r="G1982" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H1982" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1982" t="n">
+        <v>1</v>
+      </c>
+      <c r="J1982" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1982" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1982" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1983">
+      <c r="A1983" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1983" t="inlineStr">
+        <is>
+          <t>Aurora vs San Antonio Bulo Bulo</t>
+        </is>
+      </c>
+      <c r="C1983" t="inlineStr">
+        <is>
+          <t>Aurora</t>
+        </is>
+      </c>
+      <c r="D1983" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1983" t="inlineStr"/>
+      <c r="F1983" t="inlineStr"/>
+      <c r="G1983" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1983" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1983" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1983" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1983" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1983" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1984">
+      <c r="A1984" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1984" t="inlineStr">
+        <is>
+          <t>San Antonio FC vs SV Darmstadt 98</t>
+        </is>
+      </c>
+      <c r="C1984" t="inlineStr">
+        <is>
+          <t>SV Darmstadt 98</t>
+        </is>
+      </c>
+      <c r="D1984" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1984" t="inlineStr"/>
+      <c r="F1984" t="inlineStr"/>
+      <c r="G1984" t="inlineStr">
+        <is>
+          <t>0-7</t>
+        </is>
+      </c>
+      <c r="H1984" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1984" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1984" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1984" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1984" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1985">
+      <c r="A1985" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B1985" t="inlineStr">
+        <is>
+          <t>Independiente Medellín vs Millonarios</t>
+        </is>
+      </c>
+      <c r="C1985" t="inlineStr">
+        <is>
+          <t>Independiente Medellín</t>
+        </is>
+      </c>
+      <c r="D1985" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1985" t="inlineStr"/>
+      <c r="F1985" t="inlineStr"/>
+      <c r="G1985" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H1985" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1985" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1985" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1985" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1985" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -89539,7 +91891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -90458,6 +92810,25 @@
       </c>
       <c r="E49" t="n">
         <v>24</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>50</v>
+      </c>
+      <c r="C50" t="n">
+        <v>38</v>
+      </c>
+      <c r="D50" t="n">
+        <v>76</v>
+      </c>
+      <c r="E50" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -90471,7 +92842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E277"/>
+  <dimension ref="A1:E285"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -96297,6 +98668,174 @@
         <v>33.3</v>
       </c>
     </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C278" t="n">
+        <v>4</v>
+      </c>
+      <c r="D278" t="n">
+        <v>0</v>
+      </c>
+      <c r="E278" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>siguen_empatados_70</t>
+        </is>
+      </c>
+      <c r="C279" t="n">
+        <v>3</v>
+      </c>
+      <c r="D279" t="n">
+        <v>0</v>
+      </c>
+      <c r="E279" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>gol_de_cierre</t>
+        </is>
+      </c>
+      <c r="C280" t="n">
+        <v>1</v>
+      </c>
+      <c r="D280" t="n">
+        <v>0</v>
+      </c>
+      <c r="E280" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C281" t="n">
+        <v>3</v>
+      </c>
+      <c r="D281" t="n">
+        <v>1</v>
+      </c>
+      <c r="E281" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>cuidado_rival_presiona</t>
+        </is>
+      </c>
+      <c r="C282" t="n">
+        <v>3</v>
+      </c>
+      <c r="D282" t="n">
+        <v>0</v>
+      </c>
+      <c r="E282" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>posible_empate</t>
+        </is>
+      </c>
+      <c r="C283" t="n">
+        <v>1</v>
+      </c>
+      <c r="D283" t="n">
+        <v>1</v>
+      </c>
+      <c r="E283" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C284" t="n">
+        <v>5</v>
+      </c>
+      <c r="D284" t="n">
+        <v>0</v>
+      </c>
+      <c r="E284" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C285" t="n">
+        <v>2</v>
+      </c>
+      <c r="D285" t="n">
+        <v>0</v>
+      </c>
+      <c r="E285" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1985"/>
+  <dimension ref="A1:L2016"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -89501,8 +89501,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1936" t="inlineStr"/>
-      <c r="F1936" t="inlineStr"/>
       <c r="G1936" t="inlineStr">
         <is>
           <t>2-4</t>
@@ -89549,8 +89547,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1937" t="inlineStr"/>
-      <c r="F1937" t="inlineStr"/>
       <c r="G1937" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -89597,8 +89593,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1938" t="inlineStr"/>
-      <c r="F1938" t="inlineStr"/>
       <c r="G1938" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -89645,8 +89639,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1939" t="inlineStr"/>
-      <c r="F1939" t="inlineStr"/>
       <c r="G1939" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -89693,8 +89685,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1940" t="inlineStr"/>
-      <c r="F1940" t="inlineStr"/>
       <c r="G1940" t="inlineStr">
         <is>
           <t>0-5</t>
@@ -89741,8 +89731,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1941" t="inlineStr"/>
-      <c r="F1941" t="inlineStr"/>
       <c r="G1941" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -89789,8 +89777,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1942" t="inlineStr"/>
-      <c r="F1942" t="inlineStr"/>
       <c r="G1942" t="inlineStr">
         <is>
           <t>5-0</t>
@@ -89837,8 +89823,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1943" t="inlineStr"/>
-      <c r="F1943" t="inlineStr"/>
       <c r="G1943" t="inlineStr">
         <is>
           <t>2-3</t>
@@ -89885,8 +89869,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1944" t="inlineStr"/>
-      <c r="F1944" t="inlineStr"/>
       <c r="G1944" t="inlineStr">
         <is>
           <t>5-1</t>
@@ -89933,8 +89915,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1945" t="inlineStr"/>
-      <c r="F1945" t="inlineStr"/>
       <c r="G1945" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -89981,8 +89961,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1946" t="inlineStr"/>
-      <c r="F1946" t="inlineStr"/>
       <c r="G1946" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -90029,8 +90007,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1947" t="inlineStr"/>
-      <c r="F1947" t="inlineStr"/>
       <c r="G1947" t="inlineStr">
         <is>
           <t>2-4</t>
@@ -90077,8 +90053,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1948" t="inlineStr"/>
-      <c r="F1948" t="inlineStr"/>
       <c r="G1948" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -90125,8 +90099,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1949" t="inlineStr"/>
-      <c r="F1949" t="inlineStr"/>
       <c r="G1949" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -90173,8 +90145,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1950" t="inlineStr"/>
-      <c r="F1950" t="inlineStr"/>
       <c r="G1950" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -90221,8 +90191,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1951" t="inlineStr"/>
-      <c r="F1951" t="inlineStr"/>
       <c r="G1951" t="inlineStr">
         <is>
           <t>6-1</t>
@@ -90269,8 +90237,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1952" t="inlineStr"/>
-      <c r="F1952" t="inlineStr"/>
       <c r="G1952" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -90317,8 +90283,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1953" t="inlineStr"/>
-      <c r="F1953" t="inlineStr"/>
       <c r="G1953" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -90365,8 +90329,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1954" t="inlineStr"/>
-      <c r="F1954" t="inlineStr"/>
       <c r="G1954" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -90413,8 +90375,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1955" t="inlineStr"/>
-      <c r="F1955" t="inlineStr"/>
       <c r="G1955" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -90461,8 +90421,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1956" t="inlineStr"/>
-      <c r="F1956" t="inlineStr"/>
       <c r="G1956" t="inlineStr">
         <is>
           <t>4-3</t>
@@ -90509,8 +90467,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1957" t="inlineStr"/>
-      <c r="F1957" t="inlineStr"/>
       <c r="G1957" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -90557,8 +90513,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1958" t="inlineStr"/>
-      <c r="F1958" t="inlineStr"/>
       <c r="G1958" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -90605,8 +90559,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1959" t="inlineStr"/>
-      <c r="F1959" t="inlineStr"/>
       <c r="G1959" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -90653,8 +90605,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1960" t="inlineStr"/>
-      <c r="F1960" t="inlineStr"/>
       <c r="G1960" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -90701,8 +90651,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1961" t="inlineStr"/>
-      <c r="F1961" t="inlineStr"/>
       <c r="G1961" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -90749,8 +90697,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1962" t="inlineStr"/>
-      <c r="F1962" t="inlineStr"/>
       <c r="G1962" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -90797,8 +90743,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1963" t="inlineStr"/>
-      <c r="F1963" t="inlineStr"/>
       <c r="G1963" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -90845,8 +90789,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1964" t="inlineStr"/>
-      <c r="F1964" t="inlineStr"/>
       <c r="G1964" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -90893,8 +90835,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1965" t="inlineStr"/>
-      <c r="F1965" t="inlineStr"/>
       <c r="G1965" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -90941,8 +90881,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1966" t="inlineStr"/>
-      <c r="F1966" t="inlineStr"/>
       <c r="G1966" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -90989,8 +90927,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1967" t="inlineStr"/>
-      <c r="F1967" t="inlineStr"/>
       <c r="G1967" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -91037,8 +90973,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1968" t="inlineStr"/>
-      <c r="F1968" t="inlineStr"/>
       <c r="G1968" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -91085,8 +91019,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1969" t="inlineStr"/>
-      <c r="F1969" t="inlineStr"/>
       <c r="G1969" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -91133,8 +91065,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1970" t="inlineStr"/>
-      <c r="F1970" t="inlineStr"/>
       <c r="G1970" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -91181,8 +91111,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1971" t="inlineStr"/>
-      <c r="F1971" t="inlineStr"/>
       <c r="G1971" t="inlineStr">
         <is>
           <t>2-4</t>
@@ -91229,8 +91157,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1972" t="inlineStr"/>
-      <c r="F1972" t="inlineStr"/>
       <c r="G1972" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -91277,8 +91203,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1973" t="inlineStr"/>
-      <c r="F1973" t="inlineStr"/>
       <c r="G1973" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -91325,8 +91249,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1974" t="inlineStr"/>
-      <c r="F1974" t="inlineStr"/>
       <c r="G1974" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -91373,8 +91295,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1975" t="inlineStr"/>
-      <c r="F1975" t="inlineStr"/>
       <c r="G1975" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -91421,8 +91341,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1976" t="inlineStr"/>
-      <c r="F1976" t="inlineStr"/>
       <c r="G1976" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -91469,8 +91387,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1977" t="inlineStr"/>
-      <c r="F1977" t="inlineStr"/>
       <c r="G1977" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -91517,8 +91433,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1978" t="inlineStr"/>
-      <c r="F1978" t="inlineStr"/>
       <c r="G1978" t="inlineStr">
         <is>
           <t>1-2</t>
@@ -91565,8 +91479,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1979" t="inlineStr"/>
-      <c r="F1979" t="inlineStr"/>
       <c r="G1979" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -91613,8 +91525,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1980" t="inlineStr"/>
-      <c r="F1980" t="inlineStr"/>
       <c r="G1980" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -91661,8 +91571,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1981" t="inlineStr"/>
-      <c r="F1981" t="inlineStr"/>
       <c r="G1981" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -91709,8 +91617,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1982" t="inlineStr"/>
-      <c r="F1982" t="inlineStr"/>
       <c r="G1982" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -91757,8 +91663,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1983" t="inlineStr"/>
-      <c r="F1983" t="inlineStr"/>
       <c r="G1983" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -91805,8 +91709,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1984" t="inlineStr"/>
-      <c r="F1984" t="inlineStr"/>
       <c r="G1984" t="inlineStr">
         <is>
           <t>0-7</t>
@@ -91853,8 +91755,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1985" t="inlineStr"/>
-      <c r="F1985" t="inlineStr"/>
       <c r="G1985" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -91875,6 +91775,1494 @@
         <v>0</v>
       </c>
       <c r="L1985" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1986">
+      <c r="A1986" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1986" t="inlineStr">
+        <is>
+          <t>Papua New Guinea vs Solomon Islands</t>
+        </is>
+      </c>
+      <c r="C1986" t="inlineStr">
+        <is>
+          <t>Solomon Islands</t>
+        </is>
+      </c>
+      <c r="D1986" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1986" t="inlineStr"/>
+      <c r="F1986" t="inlineStr"/>
+      <c r="G1986" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1986" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1986" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1986" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1986" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1986" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1987">
+      <c r="A1987" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1987" t="inlineStr">
+        <is>
+          <t>Fiji vs New Caledonia</t>
+        </is>
+      </c>
+      <c r="C1987" t="inlineStr">
+        <is>
+          <t>Fiji</t>
+        </is>
+      </c>
+      <c r="D1987" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1987" t="inlineStr"/>
+      <c r="F1987" t="inlineStr"/>
+      <c r="G1987" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1987" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1987" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1987" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1987" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1987" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1988">
+      <c r="A1988" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1988" t="inlineStr">
+        <is>
+          <t>Seychelles vs Sri Lanka</t>
+        </is>
+      </c>
+      <c r="C1988" t="inlineStr">
+        <is>
+          <t>Sri Lanka</t>
+        </is>
+      </c>
+      <c r="D1988" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1988" t="inlineStr"/>
+      <c r="F1988" t="inlineStr"/>
+      <c r="G1988" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1988" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1988" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1988" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1988" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1988" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1989">
+      <c r="A1989" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1989" t="inlineStr">
+        <is>
+          <t>Eritrea vs South Africa</t>
+        </is>
+      </c>
+      <c r="C1989" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="D1989" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1989" t="inlineStr"/>
+      <c r="F1989" t="inlineStr"/>
+      <c r="G1989" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="H1989" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1989" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1989" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1989" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1989" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1990">
+      <c r="A1990" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1990" t="inlineStr">
+        <is>
+          <t>Lithuania vs Andorra</t>
+        </is>
+      </c>
+      <c r="C1990" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="D1990" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1990" t="inlineStr"/>
+      <c r="F1990" t="inlineStr"/>
+      <c r="G1990" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1990" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1990" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1990" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1990" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1990" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1991">
+      <c r="A1991" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1991" t="inlineStr">
+        <is>
+          <t>SC Kalsdorf vs Grazer AK</t>
+        </is>
+      </c>
+      <c r="C1991" t="inlineStr">
+        <is>
+          <t>Grazer AK</t>
+        </is>
+      </c>
+      <c r="D1991" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1991" t="inlineStr"/>
+      <c r="F1991" t="inlineStr"/>
+      <c r="G1991" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="H1991" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1991" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1991" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1991" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1991" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1992">
+      <c r="A1992" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1992" t="inlineStr">
+        <is>
+          <t>Faroe Islands U21 vs Luxembourg U21</t>
+        </is>
+      </c>
+      <c r="C1992" t="inlineStr">
+        <is>
+          <t>Faroe Islands U21</t>
+        </is>
+      </c>
+      <c r="D1992" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1992" t="inlineStr"/>
+      <c r="F1992" t="inlineStr"/>
+      <c r="G1992" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H1992" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1992" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1992" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1992" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1992" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1993">
+      <c r="A1993" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1993" t="inlineStr">
+        <is>
+          <t>Romania U21 vs Finland U21</t>
+        </is>
+      </c>
+      <c r="C1993" t="inlineStr">
+        <is>
+          <t>Romania U21</t>
+        </is>
+      </c>
+      <c r="D1993" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1993" t="inlineStr"/>
+      <c r="F1993" t="inlineStr"/>
+      <c r="G1993" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H1993" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1993" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1993" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1993" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1993" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1994">
+      <c r="A1994" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1994" t="inlineStr">
+        <is>
+          <t>Poland U21 vs Sweden U21</t>
+        </is>
+      </c>
+      <c r="C1994" t="inlineStr">
+        <is>
+          <t>Poland U21</t>
+        </is>
+      </c>
+      <c r="D1994" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1994" t="inlineStr"/>
+      <c r="F1994" t="inlineStr"/>
+      <c r="G1994" t="inlineStr">
+        <is>
+          <t>3-0</t>
+        </is>
+      </c>
+      <c r="H1994" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1994" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1994" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1994" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1994" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1995">
+      <c r="A1995" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1995" t="inlineStr">
+        <is>
+          <t>Malta U21 vs Germany U21</t>
+        </is>
+      </c>
+      <c r="C1995" t="inlineStr">
+        <is>
+          <t>Germany U21</t>
+        </is>
+      </c>
+      <c r="D1995" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E1995" t="inlineStr"/>
+      <c r="F1995" t="inlineStr"/>
+      <c r="G1995" t="inlineStr">
+        <is>
+          <t>1-4</t>
+        </is>
+      </c>
+      <c r="H1995" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1995" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1995" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1995" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1995" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1996">
+      <c r="A1996" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1996" t="inlineStr">
+        <is>
+          <t>Kosovo U21 vs Cyprus U21</t>
+        </is>
+      </c>
+      <c r="C1996" t="inlineStr">
+        <is>
+          <t>Kosovo U21</t>
+        </is>
+      </c>
+      <c r="D1996" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1996" t="inlineStr"/>
+      <c r="F1996" t="inlineStr"/>
+      <c r="G1996" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H1996" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1996" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1996" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1996" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1996" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1997">
+      <c r="A1997" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1997" t="inlineStr">
+        <is>
+          <t>United Arab Emirates vs Qatar</t>
+        </is>
+      </c>
+      <c r="C1997" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="D1997" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1997" t="inlineStr"/>
+      <c r="F1997" t="inlineStr"/>
+      <c r="G1997" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H1997" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1997" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1997" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1997" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1997" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1998">
+      <c r="A1998" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1998" t="inlineStr">
+        <is>
+          <t>Bahrain vs Yemen</t>
+        </is>
+      </c>
+      <c r="C1998" t="inlineStr">
+        <is>
+          <t>Bahrain</t>
+        </is>
+      </c>
+      <c r="D1998" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1998" t="inlineStr"/>
+      <c r="F1998" t="inlineStr"/>
+      <c r="G1998" t="inlineStr">
+        <is>
+          <t>2-5</t>
+        </is>
+      </c>
+      <c r="H1998" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I1998" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1998" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1998" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1998" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="1999">
+      <c r="A1999" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B1999" t="inlineStr">
+        <is>
+          <t>Scotland U21 vs Azerbaijan U21</t>
+        </is>
+      </c>
+      <c r="C1999" t="inlineStr">
+        <is>
+          <t>Scotland U21</t>
+        </is>
+      </c>
+      <c r="D1999" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E1999" t="inlineStr"/>
+      <c r="F1999" t="inlineStr"/>
+      <c r="G1999" t="inlineStr">
+        <is>
+          <t>5-2</t>
+        </is>
+      </c>
+      <c r="H1999" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I1999" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1999" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1999" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1999" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2000">
+      <c r="A2000" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2000" t="inlineStr">
+        <is>
+          <t>Eastleigh vs Southend United</t>
+        </is>
+      </c>
+      <c r="C2000" t="inlineStr">
+        <is>
+          <t>Southend United</t>
+        </is>
+      </c>
+      <c r="D2000" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E2000" t="inlineStr"/>
+      <c r="F2000" t="inlineStr"/>
+      <c r="G2000" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H2000" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2000" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2000" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2000" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2000" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2001">
+      <c r="A2001" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2001" t="inlineStr">
+        <is>
+          <t>Tamworth vs Sutton United</t>
+        </is>
+      </c>
+      <c r="C2001" t="inlineStr">
+        <is>
+          <t>Tamworth</t>
+        </is>
+      </c>
+      <c r="D2001" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E2001" t="inlineStr"/>
+      <c r="F2001" t="inlineStr"/>
+      <c r="G2001" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H2001" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2001" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2001" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2001" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2001" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2002">
+      <c r="A2002" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2002" t="inlineStr">
+        <is>
+          <t>Portugal U21 vs Gibraltar U21</t>
+        </is>
+      </c>
+      <c r="C2002" t="inlineStr">
+        <is>
+          <t>Portugal U21</t>
+        </is>
+      </c>
+      <c r="D2002" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E2002" t="inlineStr"/>
+      <c r="F2002" t="inlineStr"/>
+      <c r="G2002" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H2002" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2002" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2002" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2002" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2002" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2003">
+      <c r="A2003" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2003" t="inlineStr">
+        <is>
+          <t>Cienciano del Cusco vs Los Chankas</t>
+        </is>
+      </c>
+      <c r="C2003" t="inlineStr">
+        <is>
+          <t>Cienciano del Cusco</t>
+        </is>
+      </c>
+      <c r="D2003" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E2003" t="inlineStr"/>
+      <c r="F2003" t="inlineStr"/>
+      <c r="G2003" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H2003" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I2003" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2003" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2003" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2003" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2004">
+      <c r="A2004" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2004" t="inlineStr">
+        <is>
+          <t>Águila vs Internacional Santa Tecla</t>
+        </is>
+      </c>
+      <c r="C2004" t="inlineStr">
+        <is>
+          <t>Águila</t>
+        </is>
+      </c>
+      <c r="D2004" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E2004" t="inlineStr"/>
+      <c r="F2004" t="inlineStr"/>
+      <c r="G2004" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H2004" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2004" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2004" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2004" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2004" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2005">
+      <c r="A2005" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2005" t="inlineStr">
+        <is>
+          <t>Real Tomayapo vs Nacional Potosí</t>
+        </is>
+      </c>
+      <c r="C2005" t="inlineStr">
+        <is>
+          <t>Real Tomayapo</t>
+        </is>
+      </c>
+      <c r="D2005" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E2005" t="inlineStr"/>
+      <c r="F2005" t="inlineStr"/>
+      <c r="G2005" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H2005" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2005" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2005" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2005" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2005" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2006">
+      <c r="A2006" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2006" t="inlineStr">
+        <is>
+          <t>Brooklyn FC vs Detroit City FC</t>
+        </is>
+      </c>
+      <c r="C2006" t="inlineStr">
+        <is>
+          <t>Detroit City FC</t>
+        </is>
+      </c>
+      <c r="D2006" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E2006" t="inlineStr"/>
+      <c r="F2006" t="inlineStr"/>
+      <c r="G2006" t="inlineStr">
+        <is>
+          <t>1-3</t>
+        </is>
+      </c>
+      <c r="H2006" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2006" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2006" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2006" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2006" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2007">
+      <c r="A2007" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2007" t="inlineStr">
+        <is>
+          <t>Miami FC vs Sporting JAX</t>
+        </is>
+      </c>
+      <c r="C2007" t="inlineStr">
+        <is>
+          <t>Miami FC</t>
+        </is>
+      </c>
+      <c r="D2007" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E2007" t="inlineStr"/>
+      <c r="F2007" t="inlineStr"/>
+      <c r="G2007" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="H2007" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2007" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2007" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2007" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2007" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2008">
+      <c r="A2008" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2008" t="inlineStr">
+        <is>
+          <t>Rhode Island FC vs Indy Eleven</t>
+        </is>
+      </c>
+      <c r="C2008" t="inlineStr">
+        <is>
+          <t>Rhode Island FC</t>
+        </is>
+      </c>
+      <c r="D2008" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E2008" t="inlineStr"/>
+      <c r="F2008" t="inlineStr"/>
+      <c r="G2008" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H2008" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2008" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2008" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2008" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2008" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2009">
+      <c r="A2009" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2009" t="inlineStr">
+        <is>
+          <t>D.C. United vs SC Paderborn 07</t>
+        </is>
+      </c>
+      <c r="C2009" t="inlineStr">
+        <is>
+          <t>SC Paderborn 07</t>
+        </is>
+      </c>
+      <c r="D2009" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E2009" t="inlineStr"/>
+      <c r="F2009" t="inlineStr"/>
+      <c r="G2009" t="inlineStr">
+        <is>
+          <t>0-1</t>
+        </is>
+      </c>
+      <c r="H2009" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2009" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2009" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2009" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2009" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2010">
+      <c r="A2010" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2010" t="inlineStr">
+        <is>
+          <t>Alianza FC vs C.D. Platense</t>
+        </is>
+      </c>
+      <c r="C2010" t="inlineStr">
+        <is>
+          <t>Alianza FC</t>
+        </is>
+      </c>
+      <c r="D2010" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E2010" t="inlineStr"/>
+      <c r="F2010" t="inlineStr"/>
+      <c r="G2010" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H2010" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2010" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2010" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2010" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2010" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2011">
+      <c r="A2011" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2011" t="inlineStr">
+        <is>
+          <t>FC Tulsa vs New Mexico United</t>
+        </is>
+      </c>
+      <c r="C2011" t="inlineStr">
+        <is>
+          <t>FC Tulsa</t>
+        </is>
+      </c>
+      <c r="D2011" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E2011" t="inlineStr"/>
+      <c r="F2011" t="inlineStr"/>
+      <c r="G2011" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H2011" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2011" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2011" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2011" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2011" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2012">
+      <c r="A2012" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2012" t="inlineStr">
+        <is>
+          <t>Argentina vs Bolivia</t>
+        </is>
+      </c>
+      <c r="C2012" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="D2012" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E2012" t="inlineStr"/>
+      <c r="F2012" t="inlineStr"/>
+      <c r="G2012" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="H2012" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2012" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2012" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2012" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2012" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2013">
+      <c r="A2013" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2013" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero vs The Strongest</t>
+        </is>
+      </c>
+      <c r="C2013" t="inlineStr">
+        <is>
+          <t>Oriente Petrolero</t>
+        </is>
+      </c>
+      <c r="D2013" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E2013" t="inlineStr"/>
+      <c r="F2013" t="inlineStr"/>
+      <c r="G2013" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H2013" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2013" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2013" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2013" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2013" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2014">
+      <c r="A2014" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2014" t="inlineStr">
+        <is>
+          <t>Atlético Nacional vs Atlético Junior</t>
+        </is>
+      </c>
+      <c r="C2014" t="inlineStr">
+        <is>
+          <t>Atlético Nacional</t>
+        </is>
+      </c>
+      <c r="D2014" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E2014" t="inlineStr"/>
+      <c r="F2014" t="inlineStr"/>
+      <c r="G2014" t="inlineStr">
+        <is>
+          <t>3-1</t>
+        </is>
+      </c>
+      <c r="H2014" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2014" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2014" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2014" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2014" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2015">
+      <c r="A2015" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2015" t="inlineStr">
+        <is>
+          <t>CD FAS vs Isidro Metapán</t>
+        </is>
+      </c>
+      <c r="C2015" t="inlineStr">
+        <is>
+          <t>CD FAS</t>
+        </is>
+      </c>
+      <c r="D2015" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E2015" t="inlineStr"/>
+      <c r="F2015" t="inlineStr"/>
+      <c r="G2015" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H2015" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2015" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2015" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2015" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2015" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2016">
+      <c r="A2016" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B2016" t="inlineStr">
+        <is>
+          <t>Sacramento Republic FC vs Las Vegas Lights FC</t>
+        </is>
+      </c>
+      <c r="C2016" t="inlineStr">
+        <is>
+          <t>Sacramento Republic FC</t>
+        </is>
+      </c>
+      <c r="D2016" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E2016" t="inlineStr"/>
+      <c r="F2016" t="inlineStr"/>
+      <c r="G2016" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="H2016" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2016" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2016" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2016" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2016" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -91891,7 +93279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -92829,6 +94217,25 @@
       </c>
       <c r="E50" t="n">
         <v>50</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>31</v>
+      </c>
+      <c r="C51" t="n">
+        <v>26</v>
+      </c>
+      <c r="D51" t="n">
+        <v>83.90000000000001</v>
+      </c>
+      <c r="E51" t="n">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -92842,7 +94249,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E285"/>
+  <dimension ref="A1:E290"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -98836,6 +100243,111 @@
         <v>0</v>
       </c>
     </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C286" t="n">
+        <v>3</v>
+      </c>
+      <c r="D286" t="n">
+        <v>0</v>
+      </c>
+      <c r="E286" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C287" t="n">
+        <v>3</v>
+      </c>
+      <c r="D287" t="n">
+        <v>1</v>
+      </c>
+      <c r="E287" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>siguen_empatados_70</t>
+        </is>
+      </c>
+      <c r="C288" t="n">
+        <v>1</v>
+      </c>
+      <c r="D288" t="n">
+        <v>0</v>
+      </c>
+      <c r="E288" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C289" t="n">
+        <v>3</v>
+      </c>
+      <c r="D289" t="n">
+        <v>0</v>
+      </c>
+      <c r="E289" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C290" t="n">
+        <v>3</v>
+      </c>
+      <c r="D290" t="n">
+        <v>1</v>
+      </c>
+      <c r="E290" t="n">
+        <v>33.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L2016"/>
+  <dimension ref="A1:L2034"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -91801,8 +91801,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1986" t="inlineStr"/>
-      <c r="F1986" t="inlineStr"/>
       <c r="G1986" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -91849,8 +91847,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1987" t="inlineStr"/>
-      <c r="F1987" t="inlineStr"/>
       <c r="G1987" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -91897,8 +91893,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1988" t="inlineStr"/>
-      <c r="F1988" t="inlineStr"/>
       <c r="G1988" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -91945,8 +91939,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1989" t="inlineStr"/>
-      <c r="F1989" t="inlineStr"/>
       <c r="G1989" t="inlineStr">
         <is>
           <t>0-5</t>
@@ -91993,8 +91985,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1990" t="inlineStr"/>
-      <c r="F1990" t="inlineStr"/>
       <c r="G1990" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -92041,8 +92031,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1991" t="inlineStr"/>
-      <c r="F1991" t="inlineStr"/>
       <c r="G1991" t="inlineStr">
         <is>
           <t>1-5</t>
@@ -92089,8 +92077,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1992" t="inlineStr"/>
-      <c r="F1992" t="inlineStr"/>
       <c r="G1992" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -92137,8 +92123,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1993" t="inlineStr"/>
-      <c r="F1993" t="inlineStr"/>
       <c r="G1993" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -92185,8 +92169,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1994" t="inlineStr"/>
-      <c r="F1994" t="inlineStr"/>
       <c r="G1994" t="inlineStr">
         <is>
           <t>3-0</t>
@@ -92233,8 +92215,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E1995" t="inlineStr"/>
-      <c r="F1995" t="inlineStr"/>
       <c r="G1995" t="inlineStr">
         <is>
           <t>1-4</t>
@@ -92281,8 +92261,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1996" t="inlineStr"/>
-      <c r="F1996" t="inlineStr"/>
       <c r="G1996" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -92329,8 +92307,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1997" t="inlineStr"/>
-      <c r="F1997" t="inlineStr"/>
       <c r="G1997" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -92377,8 +92353,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1998" t="inlineStr"/>
-      <c r="F1998" t="inlineStr"/>
       <c r="G1998" t="inlineStr">
         <is>
           <t>2-5</t>
@@ -92425,8 +92399,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E1999" t="inlineStr"/>
-      <c r="F1999" t="inlineStr"/>
       <c r="G1999" t="inlineStr">
         <is>
           <t>5-2</t>
@@ -92473,8 +92445,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E2000" t="inlineStr"/>
-      <c r="F2000" t="inlineStr"/>
       <c r="G2000" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -92521,8 +92491,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E2001" t="inlineStr"/>
-      <c r="F2001" t="inlineStr"/>
       <c r="G2001" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -92569,8 +92537,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E2002" t="inlineStr"/>
-      <c r="F2002" t="inlineStr"/>
       <c r="G2002" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -92617,8 +92583,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E2003" t="inlineStr"/>
-      <c r="F2003" t="inlineStr"/>
       <c r="G2003" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -92665,8 +92629,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E2004" t="inlineStr"/>
-      <c r="F2004" t="inlineStr"/>
       <c r="G2004" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -92713,8 +92675,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E2005" t="inlineStr"/>
-      <c r="F2005" t="inlineStr"/>
       <c r="G2005" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -92761,8 +92721,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E2006" t="inlineStr"/>
-      <c r="F2006" t="inlineStr"/>
       <c r="G2006" t="inlineStr">
         <is>
           <t>1-3</t>
@@ -92809,8 +92767,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E2007" t="inlineStr"/>
-      <c r="F2007" t="inlineStr"/>
       <c r="G2007" t="inlineStr">
         <is>
           <t>4-1</t>
@@ -92857,8 +92813,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E2008" t="inlineStr"/>
-      <c r="F2008" t="inlineStr"/>
       <c r="G2008" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -92905,8 +92859,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E2009" t="inlineStr"/>
-      <c r="F2009" t="inlineStr"/>
       <c r="G2009" t="inlineStr">
         <is>
           <t>0-1</t>
@@ -92953,8 +92905,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E2010" t="inlineStr"/>
-      <c r="F2010" t="inlineStr"/>
       <c r="G2010" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -93001,8 +92951,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E2011" t="inlineStr"/>
-      <c r="F2011" t="inlineStr"/>
       <c r="G2011" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -93049,8 +92997,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E2012" t="inlineStr"/>
-      <c r="F2012" t="inlineStr"/>
       <c r="G2012" t="inlineStr">
         <is>
           <t>4-0</t>
@@ -93097,8 +93043,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E2013" t="inlineStr"/>
-      <c r="F2013" t="inlineStr"/>
       <c r="G2013" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -93145,8 +93089,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E2014" t="inlineStr"/>
-      <c r="F2014" t="inlineStr"/>
       <c r="G2014" t="inlineStr">
         <is>
           <t>3-1</t>
@@ -93193,8 +93135,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E2015" t="inlineStr"/>
-      <c r="F2015" t="inlineStr"/>
       <c r="G2015" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -93241,8 +93181,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E2016" t="inlineStr"/>
-      <c r="F2016" t="inlineStr"/>
       <c r="G2016" t="inlineStr">
         <is>
           <t>3-2</t>
@@ -93263,6 +93201,870 @@
         <v>0</v>
       </c>
       <c r="L2016" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2017">
+      <c r="A2017" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2017" t="inlineStr">
+        <is>
+          <t>SSV Jahn Regensburg vs WSG Swarovski Tirol</t>
+        </is>
+      </c>
+      <c r="C2017" t="inlineStr">
+        <is>
+          <t>SSV Jahn Regensburg</t>
+        </is>
+      </c>
+      <c r="D2017" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E2017" t="inlineStr"/>
+      <c r="F2017" t="inlineStr"/>
+      <c r="G2017" t="inlineStr">
+        <is>
+          <t>0-6</t>
+        </is>
+      </c>
+      <c r="H2017" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2017" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2017" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2018">
+      <c r="A2018" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2018" t="inlineStr">
+        <is>
+          <t>Greece U21 vs Latvia U21</t>
+        </is>
+      </c>
+      <c r="C2018" t="inlineStr">
+        <is>
+          <t>Greece U21</t>
+        </is>
+      </c>
+      <c r="D2018" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E2018" t="inlineStr"/>
+      <c r="F2018" t="inlineStr"/>
+      <c r="G2018" t="inlineStr">
+        <is>
+          <t>4-2</t>
+        </is>
+      </c>
+      <c r="H2018" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2018" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2018" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2019">
+      <c r="A2019" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2019" t="inlineStr">
+        <is>
+          <t>VfB Stuttgart vs SpVgg Greuther Fürth</t>
+        </is>
+      </c>
+      <c r="C2019" t="inlineStr">
+        <is>
+          <t>VfB Stuttgart</t>
+        </is>
+      </c>
+      <c r="D2019" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E2019" t="inlineStr"/>
+      <c r="F2019" t="inlineStr"/>
+      <c r="G2019" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="H2019" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2019" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2019" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2020">
+      <c r="A2020" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2020" t="inlineStr">
+        <is>
+          <t>Azerbaijan vs Liechtenstein</t>
+        </is>
+      </c>
+      <c r="C2020" t="inlineStr">
+        <is>
+          <t>Azerbaijan</t>
+        </is>
+      </c>
+      <c r="D2020" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E2020" t="inlineStr"/>
+      <c r="F2020" t="inlineStr"/>
+      <c r="G2020" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H2020" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2020" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2020" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2021">
+      <c r="A2021" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2021" t="inlineStr">
+        <is>
+          <t>Guinea vs Kenya</t>
+        </is>
+      </c>
+      <c r="C2021" t="inlineStr">
+        <is>
+          <t>Guinea</t>
+        </is>
+      </c>
+      <c r="D2021" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E2021" t="inlineStr"/>
+      <c r="F2021" t="inlineStr"/>
+      <c r="G2021" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H2021" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2021" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2021" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2022">
+      <c r="A2022" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2022" t="inlineStr">
+        <is>
+          <t>North Macedonia U21 vs Montenegro U21</t>
+        </is>
+      </c>
+      <c r="C2022" t="inlineStr">
+        <is>
+          <t>North Macedonia U21</t>
+        </is>
+      </c>
+      <c r="D2022" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E2022" t="inlineStr"/>
+      <c r="F2022" t="inlineStr"/>
+      <c r="G2022" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H2022" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2022" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2022" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2023">
+      <c r="A2023" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2023" t="inlineStr">
+        <is>
+          <t>Germany vs Serbia</t>
+        </is>
+      </c>
+      <c r="C2023" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D2023" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E2023" t="inlineStr"/>
+      <c r="F2023" t="inlineStr"/>
+      <c r="G2023" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H2023" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2023" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2023" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2024">
+      <c r="A2024" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2024" t="inlineStr">
+        <is>
+          <t>Greece vs Netherlands</t>
+        </is>
+      </c>
+      <c r="C2024" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D2024" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E2024" t="inlineStr"/>
+      <c r="F2024" t="inlineStr"/>
+      <c r="G2024" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H2024" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2024" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2024" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2024" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2024" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2025">
+      <c r="A2025" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2025" t="inlineStr">
+        <is>
+          <t>Denmark vs Portugal</t>
+        </is>
+      </c>
+      <c r="C2025" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="D2025" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E2025" t="inlineStr"/>
+      <c r="F2025" t="inlineStr"/>
+      <c r="G2025" t="inlineStr">
+        <is>
+          <t>2-4</t>
+        </is>
+      </c>
+      <c r="H2025" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2025" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2025" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2025" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2025" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2026">
+      <c r="A2026" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2026" t="inlineStr">
+        <is>
+          <t>Wales vs Norway</t>
+        </is>
+      </c>
+      <c r="C2026" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="D2026" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E2026" t="inlineStr"/>
+      <c r="F2026" t="inlineStr"/>
+      <c r="G2026" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="H2026" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I2026" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2026" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2026" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2026" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2027">
+      <c r="A2027" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2027" t="inlineStr">
+        <is>
+          <t>Republic of Ireland vs Austria</t>
+        </is>
+      </c>
+      <c r="C2027" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="D2027" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E2027" t="inlineStr"/>
+      <c r="F2027" t="inlineStr"/>
+      <c r="G2027" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="H2027" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2027" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2027" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2027" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2027" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2028" t="inlineStr">
+        <is>
+          <t>Israel vs Kosovo</t>
+        </is>
+      </c>
+      <c r="C2028" t="inlineStr">
+        <is>
+          <t>Kosovo</t>
+        </is>
+      </c>
+      <c r="D2028" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E2028" t="inlineStr"/>
+      <c r="F2028" t="inlineStr"/>
+      <c r="G2028" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="H2028" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2028" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2028" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2028" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2028" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2029" t="inlineStr">
+        <is>
+          <t>Malta vs Gibraltar</t>
+        </is>
+      </c>
+      <c r="C2029" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="D2029" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E2029" t="inlineStr"/>
+      <c r="F2029" t="inlineStr"/>
+      <c r="G2029" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="H2029" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I2029" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2029" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2029" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2029" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2030">
+      <c r="A2030" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2030" t="inlineStr">
+        <is>
+          <t>British Virgin Islands vs Montserrat</t>
+        </is>
+      </c>
+      <c r="C2030" t="inlineStr">
+        <is>
+          <t>Montserrat</t>
+        </is>
+      </c>
+      <c r="D2030" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E2030" t="inlineStr"/>
+      <c r="F2030" t="inlineStr"/>
+      <c r="G2030" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="H2030" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2030" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2030" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2030" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2030" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2031">
+      <c r="A2031" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2031" t="inlineStr">
+        <is>
+          <t>US Virgin Islands vs St. Martin</t>
+        </is>
+      </c>
+      <c r="C2031" t="inlineStr">
+        <is>
+          <t>St. Martin</t>
+        </is>
+      </c>
+      <c r="D2031" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E2031" t="inlineStr"/>
+      <c r="F2031" t="inlineStr"/>
+      <c r="G2031" t="inlineStr">
+        <is>
+          <t>0-5</t>
+        </is>
+      </c>
+      <c r="H2031" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2031" t="n">
+        <v>3</v>
+      </c>
+      <c r="J2031" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2031" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2031" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2032">
+      <c r="A2032" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2032" t="inlineStr">
+        <is>
+          <t>Dominica vs Guyana</t>
+        </is>
+      </c>
+      <c r="C2032" t="inlineStr">
+        <is>
+          <t>Guyana</t>
+        </is>
+      </c>
+      <c r="D2032" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E2032" t="inlineStr"/>
+      <c r="F2032" t="inlineStr"/>
+      <c r="G2032" t="inlineStr">
+        <is>
+          <t>1-5</t>
+        </is>
+      </c>
+      <c r="H2032" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2032" t="n">
+        <v>1</v>
+      </c>
+      <c r="J2032" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2032" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2032" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2033">
+      <c r="A2033" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2033" t="inlineStr">
+        <is>
+          <t>Fuerte San Francisco vs Luis Ángel Firpo</t>
+        </is>
+      </c>
+      <c r="C2033" t="inlineStr">
+        <is>
+          <t>Luis Ángel Firpo</t>
+        </is>
+      </c>
+      <c r="D2033" t="inlineStr">
+        <is>
+          <t>Visitante</t>
+        </is>
+      </c>
+      <c r="E2033" t="inlineStr"/>
+      <c r="F2033" t="inlineStr"/>
+      <c r="G2033" t="inlineStr">
+        <is>
+          <t>0-3</t>
+        </is>
+      </c>
+      <c r="H2033" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2033" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2033" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2033" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2033" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="2034">
+      <c r="A2034" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B2034" t="inlineStr">
+        <is>
+          <t>Curaçao vs Trinidad and Tobago</t>
+        </is>
+      </c>
+      <c r="C2034" t="inlineStr">
+        <is>
+          <t>Curaçao</t>
+        </is>
+      </c>
+      <c r="D2034" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+      <c r="E2034" t="inlineStr"/>
+      <c r="F2034" t="inlineStr"/>
+      <c r="G2034" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="H2034" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="I2034" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2034" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2034" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2034" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -93279,7 +94081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -94236,6 +95038,25 @@
       </c>
       <c r="E51" t="n">
         <v>31</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>18</v>
+      </c>
+      <c r="C52" t="n">
+        <v>14</v>
+      </c>
+      <c r="D52" t="n">
+        <v>77.8</v>
+      </c>
+      <c r="E52" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -94249,7 +95070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E290"/>
+  <dimension ref="A1:E295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -100348,6 +101169,111 @@
         <v>33.3</v>
       </c>
     </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>tarjeta_roja</t>
+        </is>
+      </c>
+      <c r="C291" t="n">
+        <v>2</v>
+      </c>
+      <c r="D291" t="n">
+        <v>0</v>
+      </c>
+      <c r="E291" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>penal</t>
+        </is>
+      </c>
+      <c r="C292" t="n">
+        <v>2</v>
+      </c>
+      <c r="D292" t="n">
+        <v>0</v>
+      </c>
+      <c r="E292" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>posible_victoria_favorito</t>
+        </is>
+      </c>
+      <c r="C293" t="n">
+        <v>2</v>
+      </c>
+      <c r="D293" t="n">
+        <v>1</v>
+      </c>
+      <c r="E293" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>ampliacion_marcador</t>
+        </is>
+      </c>
+      <c r="C294" t="n">
+        <v>3</v>
+      </c>
+      <c r="D294" t="n">
+        <v>0</v>
+      </c>
+      <c r="E294" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>siguen_empatados_22</t>
+        </is>
+      </c>
+      <c r="C295" t="n">
+        <v>1</v>
+      </c>
+      <c r="D295" t="n">
+        <v>0</v>
+      </c>
+      <c r="E295" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -93227,8 +93227,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E2017" t="inlineStr"/>
-      <c r="F2017" t="inlineStr"/>
       <c r="G2017" t="inlineStr">
         <is>
           <t>0-6</t>
@@ -93275,8 +93273,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E2018" t="inlineStr"/>
-      <c r="F2018" t="inlineStr"/>
       <c r="G2018" t="inlineStr">
         <is>
           <t>4-2</t>
@@ -93323,8 +93319,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E2019" t="inlineStr"/>
-      <c r="F2019" t="inlineStr"/>
       <c r="G2019" t="inlineStr">
         <is>
           <t>5-0</t>
@@ -93371,8 +93365,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E2020" t="inlineStr"/>
-      <c r="F2020" t="inlineStr"/>
       <c r="G2020" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -93419,8 +93411,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E2021" t="inlineStr"/>
-      <c r="F2021" t="inlineStr"/>
       <c r="G2021" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -93467,8 +93457,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E2022" t="inlineStr"/>
-      <c r="F2022" t="inlineStr"/>
       <c r="G2022" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -93515,8 +93503,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E2023" t="inlineStr"/>
-      <c r="F2023" t="inlineStr"/>
       <c r="G2023" t="inlineStr">
         <is>
           <t>2-0</t>
@@ -93563,8 +93549,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E2024" t="inlineStr"/>
-      <c r="F2024" t="inlineStr"/>
       <c r="G2024" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -93611,8 +93595,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E2025" t="inlineStr"/>
-      <c r="F2025" t="inlineStr"/>
       <c r="G2025" t="inlineStr">
         <is>
           <t>2-4</t>
@@ -93659,8 +93641,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E2026" t="inlineStr"/>
-      <c r="F2026" t="inlineStr"/>
       <c r="G2026" t="inlineStr">
         <is>
           <t>2-1</t>
@@ -93707,8 +93687,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E2027" t="inlineStr"/>
-      <c r="F2027" t="inlineStr"/>
       <c r="G2027" t="inlineStr">
         <is>
           <t>2-2</t>
@@ -93755,8 +93733,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E2028" t="inlineStr"/>
-      <c r="F2028" t="inlineStr"/>
       <c r="G2028" t="inlineStr">
         <is>
           <t>0-0</t>
@@ -93803,8 +93779,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E2029" t="inlineStr"/>
-      <c r="F2029" t="inlineStr"/>
       <c r="G2029" t="inlineStr">
         <is>
           <t>1-1</t>
@@ -93851,8 +93825,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E2030" t="inlineStr"/>
-      <c r="F2030" t="inlineStr"/>
       <c r="G2030" t="inlineStr">
         <is>
           <t>0-2</t>
@@ -93899,8 +93871,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E2031" t="inlineStr"/>
-      <c r="F2031" t="inlineStr"/>
       <c r="G2031" t="inlineStr">
         <is>
           <t>0-5</t>
@@ -93947,8 +93917,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E2032" t="inlineStr"/>
-      <c r="F2032" t="inlineStr"/>
       <c r="G2032" t="inlineStr">
         <is>
           <t>1-5</t>
@@ -93995,8 +93963,6 @@
           <t>Visitante</t>
         </is>
       </c>
-      <c r="E2033" t="inlineStr"/>
-      <c r="F2033" t="inlineStr"/>
       <c r="G2033" t="inlineStr">
         <is>
           <t>0-3</t>
@@ -94043,8 +94009,6 @@
           <t>Local</t>
         </is>
       </c>
-      <c r="E2034" t="inlineStr"/>
-      <c r="F2034" t="inlineStr"/>
       <c r="G2034" t="inlineStr">
         <is>
           <t>1-0</t>
@@ -94081,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95057,6 +95021,22 @@
       </c>
       <c r="E52" t="n">
         <v>18</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95036,6 +95036,22 @@
         <v>0</v>
       </c>
       <c r="E53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95052,6 +95052,22 @@
         <v>0</v>
       </c>
       <c r="E54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0</v>
+      </c>
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95069,6 +95069,22 @@
       </c>
       <c r="E55" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95085,6 +95085,22 @@
       </c>
       <c r="E56" t="n">
         <v>39</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95100,6 +95100,22 @@
         <v>0</v>
       </c>
       <c r="E57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95116,6 +95116,22 @@
         <v>0</v>
       </c>
       <c r="E58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95132,6 +95132,22 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E60"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95148,6 +95148,22 @@
         <v>0</v>
       </c>
       <c r="E60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95165,6 +95165,22 @@
       </c>
       <c r="E61" t="n">
         <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95181,6 +95181,22 @@
       </c>
       <c r="E62" t="n">
         <v>39</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0</v>
+      </c>
+      <c r="C63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95196,6 +95196,22 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95212,6 +95212,22 @@
         <v>0</v>
       </c>
       <c r="E64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95228,6 +95228,22 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E66"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95244,6 +95244,22 @@
         <v>0</v>
       </c>
       <c r="E66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:E68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95260,6 +95260,22 @@
         <v>0</v>
       </c>
       <c r="E67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0</v>
+      </c>
+      <c r="C68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95276,6 +95276,22 @@
         <v>0</v>
       </c>
       <c r="E68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E69"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95292,6 +95292,22 @@
         <v>0</v>
       </c>
       <c r="E69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E70"/>
+  <dimension ref="A1:E71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95308,6 +95308,22 @@
         <v>0</v>
       </c>
       <c r="E70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E71"/>
+  <dimension ref="A1:E72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95324,6 +95324,22 @@
         <v>0</v>
       </c>
       <c r="E71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E72"/>
+  <dimension ref="A1:E73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95340,6 +95340,22 @@
         <v>0</v>
       </c>
       <c r="E72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95356,6 +95356,22 @@
         <v>0</v>
       </c>
       <c r="E73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95372,6 +95372,22 @@
         <v>0</v>
       </c>
       <c r="E74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E75"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95388,6 +95388,22 @@
         <v>0</v>
       </c>
       <c r="E75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0</v>
+      </c>
+      <c r="C76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95404,6 +95404,22 @@
         <v>0</v>
       </c>
       <c r="E76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E77"/>
+  <dimension ref="A1:E78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95420,6 +95420,22 @@
         <v>0</v>
       </c>
       <c r="E77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
         <v>0</v>
       </c>
     </row>

--- a/data/estadisticas.xlsx
+++ b/data/estadisticas.xlsx
@@ -94045,7 +94045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E78"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95436,6 +95436,22 @@
         <v>0</v>
       </c>
       <c r="E78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
         <v>0</v>
       </c>
     </row>
